--- a/tornament_standard.xlsx
+++ b/tornament_standard.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ayumu/Desktop/Python/classmach/tornament/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ayumu/Desktop/programming/Python/classmach/tournament/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{250CEEB5-03A2-D541-A3C3-0F0685720DAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A92443D-A36B-924C-8B2D-8780B47359B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="17420" firstSheet="3" activeTab="13" xr2:uid="{ACC25020-1812-3D45-8CD3-466514F5749C}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17420" firstSheet="3" activeTab="18" xr2:uid="{ACC25020-1812-3D45-8CD3-466514F5749C}"/>
   </bookViews>
   <sheets>
     <sheet name="仕様書" sheetId="7" r:id="rId1"/>
@@ -31,7 +31,8 @@
     <sheet name="22" sheetId="1" r:id="rId16"/>
     <sheet name="23" sheetId="3" r:id="rId17"/>
     <sheet name="24" sheetId="2" r:id="rId18"/>
-    <sheet name="timetable" sheetId="14" r:id="rId19"/>
+    <sheet name="25" sheetId="23" r:id="rId19"/>
+    <sheet name="timetable" sheetId="14" r:id="rId20"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -54,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="65">
   <si>
     <t>①</t>
     <phoneticPr fontId="1"/>
@@ -451,6 +452,13 @@
     <t>1S</t>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>⑬</t>
+    <rPh sb="0" eb="1">
+      <t>⑩サンマル</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
@@ -459,7 +467,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="h:mm;@"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="20">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -610,6 +618,15 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -619,7 +636,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="26">
+  <borders count="28">
     <border>
       <left/>
       <right/>
@@ -902,13 +919,37 @@
         <color rgb="FF000000"/>
       </diagonal>
     </border>
+    <border>
+      <left style="thick">
+        <color auto="1"/>
+      </left>
+      <right style="thick">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color auto="1"/>
+      </left>
+      <right style="thick">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thick">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -975,6 +1016,18 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -987,16 +1040,28 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1005,22 +1070,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1029,16 +1079,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1053,13 +1094,13 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1086,13 +1127,13 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1107,6 +1148,12 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1116,13 +1163,40 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1528,10 +1602,10 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="30" customHeight="1"/>
   <sheetData>
     <row r="1" spans="1:12" ht="30" customHeight="1" thickBot="1">
-      <c r="A1" s="33"/>
+      <c r="A1" s="25"/>
       <c r="B1" s="10"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
       <c r="E1" s="32"/>
       <c r="F1" s="44" t="s">
         <v>14</v>
@@ -1541,246 +1615,246 @@
       <c r="I1" s="32"/>
       <c r="J1" s="32"/>
       <c r="K1" s="7"/>
-      <c r="L1" s="30"/>
+      <c r="L1" s="38"/>
     </row>
     <row r="2" spans="1:12" ht="30" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A2" s="33"/>
-      <c r="B2" s="36" t="s">
+      <c r="A2" s="25"/>
+      <c r="B2" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="31"/>
-      <c r="D2" s="30"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="38"/>
       <c r="E2" s="32"/>
       <c r="F2" s="44"/>
       <c r="G2" s="44"/>
       <c r="H2" s="32"/>
       <c r="I2" s="32"/>
-      <c r="J2" s="40"/>
-      <c r="K2" s="38" t="s">
+      <c r="J2" s="33"/>
+      <c r="K2" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="L2" s="30"/>
+      <c r="L2" s="38"/>
     </row>
     <row r="3" spans="1:12" ht="30" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A3" s="33"/>
-      <c r="B3" s="37"/>
-      <c r="C3" s="36" t="s">
+      <c r="A3" s="25"/>
+      <c r="B3" s="36"/>
+      <c r="C3" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="30"/>
+      <c r="D3" s="38"/>
       <c r="E3" s="32"/>
       <c r="F3" s="44"/>
       <c r="G3" s="44"/>
       <c r="H3" s="32"/>
       <c r="I3" s="32"/>
-      <c r="J3" s="38" t="s">
+      <c r="J3" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="K3" s="39"/>
-      <c r="L3" s="33"/>
+      <c r="K3" s="42"/>
+      <c r="L3" s="25"/>
     </row>
     <row r="4" spans="1:12" ht="30" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A4" s="33"/>
-      <c r="B4" s="43"/>
-      <c r="C4" s="42"/>
-      <c r="D4" s="31"/>
+      <c r="A4" s="25"/>
+      <c r="B4" s="40"/>
+      <c r="C4" s="35"/>
+      <c r="D4" s="39"/>
       <c r="E4" s="32"/>
       <c r="F4" s="44"/>
       <c r="G4" s="44"/>
       <c r="H4" s="32"/>
-      <c r="I4" s="40"/>
-      <c r="J4" s="41"/>
-      <c r="K4" s="35"/>
-      <c r="L4" s="33"/>
+      <c r="I4" s="33"/>
+      <c r="J4" s="43"/>
+      <c r="K4" s="31"/>
+      <c r="L4" s="25"/>
     </row>
     <row r="5" spans="1:12" ht="30" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A5" s="33"/>
-      <c r="B5" s="31"/>
-      <c r="C5" s="42"/>
-      <c r="D5" s="36" t="s">
+      <c r="A5" s="25"/>
+      <c r="B5" s="39"/>
+      <c r="C5" s="35"/>
+      <c r="D5" s="34" t="s">
         <v>1</v>
       </c>
       <c r="E5" s="32"/>
-      <c r="F5" s="29" t="s">
+      <c r="F5" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="G5" s="29"/>
+      <c r="G5" s="22"/>
       <c r="H5" s="32"/>
-      <c r="I5" s="38" t="s">
+      <c r="I5" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="J5" s="41"/>
-      <c r="K5" s="40"/>
-      <c r="L5" s="30"/>
+      <c r="J5" s="43"/>
+      <c r="K5" s="33"/>
+      <c r="L5" s="38"/>
     </row>
     <row r="6" spans="1:12" ht="30" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A6" s="33"/>
-      <c r="B6" s="36" t="s">
+      <c r="A6" s="25"/>
+      <c r="B6" s="34" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="37"/>
-      <c r="D6" s="42"/>
+      <c r="C6" s="36"/>
+      <c r="D6" s="35"/>
       <c r="E6" s="32"/>
-      <c r="F6" s="29"/>
-      <c r="G6" s="29"/>
+      <c r="F6" s="22"/>
+      <c r="G6" s="22"/>
       <c r="H6" s="32"/>
-      <c r="I6" s="41"/>
-      <c r="J6" s="39"/>
-      <c r="K6" s="38" t="s">
+      <c r="I6" s="43"/>
+      <c r="J6" s="42"/>
+      <c r="K6" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="L6" s="30"/>
+      <c r="L6" s="38"/>
     </row>
     <row r="7" spans="1:12" ht="30" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A7" s="33"/>
-      <c r="B7" s="37"/>
-      <c r="C7" s="35"/>
-      <c r="D7" s="42"/>
+      <c r="A7" s="25"/>
+      <c r="B7" s="36"/>
+      <c r="C7" s="31"/>
+      <c r="D7" s="35"/>
       <c r="E7" s="32"/>
-      <c r="F7" s="42"/>
-      <c r="G7" s="41"/>
+      <c r="F7" s="35"/>
+      <c r="G7" s="43"/>
       <c r="H7" s="32"/>
-      <c r="I7" s="41"/>
-      <c r="J7" s="35"/>
-      <c r="K7" s="39"/>
-      <c r="L7" s="30"/>
+      <c r="I7" s="43"/>
+      <c r="J7" s="31"/>
+      <c r="K7" s="42"/>
+      <c r="L7" s="38"/>
     </row>
     <row r="8" spans="1:12" ht="30" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A8" s="33"/>
-      <c r="B8" s="43"/>
+      <c r="A8" s="25"/>
+      <c r="B8" s="40"/>
       <c r="C8" s="32"/>
-      <c r="D8" s="42"/>
+      <c r="D8" s="35"/>
       <c r="E8" s="32"/>
-      <c r="F8" s="37"/>
-      <c r="G8" s="39"/>
+      <c r="F8" s="36"/>
+      <c r="G8" s="42"/>
       <c r="H8" s="32"/>
-      <c r="I8" s="41"/>
+      <c r="I8" s="43"/>
       <c r="J8" s="32"/>
-      <c r="K8" s="35"/>
-      <c r="L8" s="30"/>
+      <c r="K8" s="31"/>
+      <c r="L8" s="38"/>
     </row>
     <row r="9" spans="1:12" ht="30" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A9" s="33"/>
-      <c r="B9" s="31"/>
+      <c r="A9" s="25"/>
+      <c r="B9" s="39"/>
       <c r="C9" s="32"/>
-      <c r="D9" s="42"/>
-      <c r="E9" s="35"/>
-      <c r="F9" s="35" t="s">
+      <c r="D9" s="35"/>
+      <c r="E9" s="31"/>
+      <c r="F9" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="G9" s="35"/>
-      <c r="H9" s="35"/>
-      <c r="I9" s="41"/>
+      <c r="G9" s="31"/>
+      <c r="H9" s="31"/>
+      <c r="I9" s="43"/>
       <c r="J9" s="32"/>
-      <c r="K9" s="40"/>
-      <c r="L9" s="30"/>
+      <c r="K9" s="33"/>
+      <c r="L9" s="38"/>
     </row>
     <row r="10" spans="1:12" ht="30" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A10" s="33"/>
-      <c r="B10" s="36" t="s">
+      <c r="A10" s="25"/>
+      <c r="B10" s="34" t="s">
         <v>6</v>
       </c>
       <c r="C10" s="32"/>
-      <c r="D10" s="42"/>
+      <c r="D10" s="35"/>
       <c r="E10" s="32"/>
       <c r="F10" s="32"/>
       <c r="G10" s="32"/>
       <c r="H10" s="32"/>
-      <c r="I10" s="41"/>
-      <c r="J10" s="40"/>
-      <c r="K10" s="38" t="s">
+      <c r="I10" s="43"/>
+      <c r="J10" s="33"/>
+      <c r="K10" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="L10" s="30"/>
+      <c r="L10" s="38"/>
     </row>
     <row r="11" spans="1:12" ht="30" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A11" s="33"/>
-      <c r="B11" s="37"/>
-      <c r="C11" s="36"/>
-      <c r="D11" s="42"/>
+      <c r="A11" s="25"/>
+      <c r="B11" s="36"/>
+      <c r="C11" s="34"/>
+      <c r="D11" s="35"/>
       <c r="E11" s="32"/>
-      <c r="F11" s="30"/>
-      <c r="G11" s="30"/>
+      <c r="F11" s="38"/>
+      <c r="G11" s="38"/>
       <c r="H11" s="32"/>
-      <c r="I11" s="41"/>
-      <c r="J11" s="38" t="s">
+      <c r="I11" s="43"/>
+      <c r="J11" s="41" t="s">
         <v>13</v>
       </c>
-      <c r="K11" s="39"/>
-      <c r="L11" s="30"/>
+      <c r="K11" s="42"/>
+      <c r="L11" s="38"/>
     </row>
     <row r="12" spans="1:12" ht="30" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A12" s="33"/>
-      <c r="B12" s="43"/>
-      <c r="C12" s="42"/>
-      <c r="D12" s="37"/>
+      <c r="A12" s="25"/>
+      <c r="B12" s="40"/>
+      <c r="C12" s="35"/>
+      <c r="D12" s="36"/>
       <c r="E12" s="32"/>
-      <c r="F12" s="30"/>
-      <c r="G12" s="30"/>
+      <c r="F12" s="38"/>
+      <c r="G12" s="38"/>
       <c r="H12" s="32"/>
-      <c r="I12" s="39"/>
-      <c r="J12" s="41"/>
-      <c r="K12" s="35"/>
-      <c r="L12" s="30"/>
+      <c r="I12" s="42"/>
+      <c r="J12" s="43"/>
+      <c r="K12" s="31"/>
+      <c r="L12" s="38"/>
     </row>
     <row r="13" spans="1:12" ht="30" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A13" s="33"/>
-      <c r="B13" s="31"/>
-      <c r="C13" s="42"/>
+      <c r="A13" s="25"/>
+      <c r="B13" s="39"/>
+      <c r="C13" s="35"/>
       <c r="D13" s="32"/>
       <c r="E13" s="32"/>
-      <c r="F13" s="30"/>
-      <c r="G13" s="30"/>
+      <c r="F13" s="38"/>
+      <c r="G13" s="38"/>
       <c r="H13" s="32"/>
-      <c r="I13" s="35"/>
-      <c r="J13" s="41"/>
-      <c r="K13" s="40"/>
-      <c r="L13" s="30"/>
+      <c r="I13" s="31"/>
+      <c r="J13" s="43"/>
+      <c r="K13" s="33"/>
+      <c r="L13" s="38"/>
     </row>
     <row r="14" spans="1:12" ht="30" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A14" s="33"/>
-      <c r="B14" s="36" t="s">
+      <c r="A14" s="25"/>
+      <c r="B14" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="37"/>
+      <c r="C14" s="36"/>
       <c r="D14" s="32"/>
       <c r="E14" s="32"/>
-      <c r="F14" s="30"/>
-      <c r="G14" s="30"/>
+      <c r="F14" s="38"/>
+      <c r="G14" s="38"/>
       <c r="H14" s="32"/>
       <c r="I14" s="32"/>
-      <c r="J14" s="39"/>
-      <c r="K14" s="38" t="s">
+      <c r="J14" s="42"/>
+      <c r="K14" s="41" t="s">
         <v>8</v>
       </c>
-      <c r="L14" s="30"/>
+      <c r="L14" s="38"/>
     </row>
     <row r="15" spans="1:12" ht="30" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A15" s="33"/>
-      <c r="B15" s="37"/>
+      <c r="A15" s="25"/>
+      <c r="B15" s="36"/>
       <c r="C15" s="32"/>
       <c r="D15" s="32"/>
       <c r="E15" s="32"/>
-      <c r="F15" s="30"/>
-      <c r="G15" s="30"/>
+      <c r="F15" s="38"/>
+      <c r="G15" s="38"/>
       <c r="H15" s="32"/>
       <c r="I15" s="32"/>
-      <c r="J15" s="35"/>
-      <c r="K15" s="39"/>
-      <c r="L15" s="30"/>
+      <c r="J15" s="31"/>
+      <c r="K15" s="42"/>
+      <c r="L15" s="38"/>
     </row>
     <row r="16" spans="1:12" ht="30" customHeight="1" thickTop="1">
-      <c r="A16" s="33"/>
+      <c r="A16" s="25"/>
       <c r="C16" s="32"/>
       <c r="D16" s="32"/>
       <c r="E16" s="32"/>
-      <c r="F16" s="30"/>
-      <c r="G16" s="30"/>
+      <c r="F16" s="38"/>
+      <c r="G16" s="38"/>
       <c r="H16" s="32"/>
       <c r="I16" s="32"/>
       <c r="J16" s="32"/>
       <c r="K16" s="2"/>
-      <c r="L16" s="30"/>
+      <c r="L16" s="38"/>
     </row>
     <row r="18" spans="1:12" ht="30" customHeight="1">
       <c r="A18" s="4"/>
@@ -1848,6 +1922,47 @@
     </row>
   </sheetData>
   <mergeCells count="56">
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="D5:D12"/>
+    <mergeCell ref="D13:D16"/>
+    <mergeCell ref="E1:E8"/>
+    <mergeCell ref="E9:E16"/>
+    <mergeCell ref="C3:C6"/>
+    <mergeCell ref="C7:C10"/>
+    <mergeCell ref="C11:C14"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D4"/>
+    <mergeCell ref="F11:G16"/>
+    <mergeCell ref="H1:H8"/>
+    <mergeCell ref="H9:H16"/>
+    <mergeCell ref="I1:I4"/>
+    <mergeCell ref="I5:I12"/>
+    <mergeCell ref="I13:I16"/>
+    <mergeCell ref="F1:G4"/>
+    <mergeCell ref="F5:G6"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="G7:G8"/>
+    <mergeCell ref="F9:G10"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="J3:J6"/>
+    <mergeCell ref="J7:J10"/>
+    <mergeCell ref="J11:J14"/>
+    <mergeCell ref="J15:J16"/>
     <mergeCell ref="K12:K13"/>
     <mergeCell ref="K14:K15"/>
     <mergeCell ref="L1:L2"/>
@@ -1863,47 +1978,6 @@
     <mergeCell ref="K6:K7"/>
     <mergeCell ref="K8:K9"/>
     <mergeCell ref="K10:K11"/>
-    <mergeCell ref="J1:J2"/>
-    <mergeCell ref="J3:J6"/>
-    <mergeCell ref="J7:J10"/>
-    <mergeCell ref="J11:J14"/>
-    <mergeCell ref="J15:J16"/>
-    <mergeCell ref="F11:G16"/>
-    <mergeCell ref="H1:H8"/>
-    <mergeCell ref="H9:H16"/>
-    <mergeCell ref="I1:I4"/>
-    <mergeCell ref="I5:I12"/>
-    <mergeCell ref="I13:I16"/>
-    <mergeCell ref="F1:G4"/>
-    <mergeCell ref="F5:G6"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="G7:G8"/>
-    <mergeCell ref="F9:G10"/>
-    <mergeCell ref="C15:C16"/>
-    <mergeCell ref="D5:D12"/>
-    <mergeCell ref="D13:D16"/>
-    <mergeCell ref="E1:E8"/>
-    <mergeCell ref="E9:E16"/>
-    <mergeCell ref="C3:C6"/>
-    <mergeCell ref="C7:C10"/>
-    <mergeCell ref="C11:C14"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D4"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="A3:A4"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1917,7 +1991,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="26" customHeight="1"/>
   <sheetData>
     <row r="1" spans="1:12" ht="26" customHeight="1" thickBot="1">
-      <c r="A1" s="33"/>
+      <c r="A1" s="25"/>
       <c r="C1" s="32"/>
       <c r="D1" s="32"/>
       <c r="E1" s="32"/>
@@ -1932,8 +2006,8 @@
       <c r="L1" s="4"/>
     </row>
     <row r="2" spans="1:12" ht="26" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A2" s="33"/>
-      <c r="B2" s="36" t="s">
+      <c r="A2" s="25"/>
+      <c r="B2" s="34" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="32"/>
@@ -1944,13 +2018,13 @@
       <c r="H2" s="32"/>
       <c r="I2" s="32"/>
       <c r="J2" s="32"/>
-      <c r="K2" s="40"/>
-      <c r="L2" s="30"/>
+      <c r="K2" s="33"/>
+      <c r="L2" s="38"/>
     </row>
     <row r="3" spans="1:12" ht="26" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A3" s="33"/>
-      <c r="B3" s="49"/>
-      <c r="C3" s="36" t="s">
+      <c r="A3" s="25"/>
+      <c r="B3" s="48"/>
+      <c r="C3" s="34" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="32"/>
@@ -1959,244 +2033,244 @@
       <c r="G3" s="44"/>
       <c r="H3" s="32"/>
       <c r="I3" s="32"/>
-      <c r="J3" s="40"/>
-      <c r="K3" s="38" t="s">
+      <c r="J3" s="33"/>
+      <c r="K3" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="L3" s="30"/>
+      <c r="L3" s="38"/>
     </row>
     <row r="4" spans="1:12" ht="26" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A4" s="33"/>
-      <c r="B4" s="30"/>
-      <c r="C4" s="42"/>
+      <c r="A4" s="25"/>
+      <c r="B4" s="38"/>
+      <c r="C4" s="35"/>
       <c r="D4" s="32"/>
-      <c r="E4" s="40"/>
+      <c r="E4" s="33"/>
       <c r="F4" s="44"/>
       <c r="G4" s="44"/>
       <c r="H4" s="32"/>
       <c r="I4" s="32"/>
-      <c r="J4" s="38" t="s">
+      <c r="J4" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="K4" s="39"/>
-      <c r="L4" s="30"/>
+      <c r="K4" s="42"/>
+      <c r="L4" s="38"/>
     </row>
     <row r="5" spans="1:12" ht="26" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A5" s="33"/>
-      <c r="B5" s="48"/>
-      <c r="C5" s="42"/>
-      <c r="D5" s="35"/>
-      <c r="E5" s="36" t="s">
+      <c r="A5" s="25"/>
+      <c r="B5" s="50"/>
+      <c r="C5" s="35"/>
+      <c r="D5" s="31"/>
+      <c r="E5" s="34" t="s">
         <v>2</v>
       </c>
       <c r="F5" s="44"/>
       <c r="G5" s="44"/>
       <c r="H5" s="32"/>
-      <c r="I5" s="40"/>
-      <c r="J5" s="41"/>
-      <c r="K5" s="35"/>
-      <c r="L5" s="30"/>
+      <c r="I5" s="33"/>
+      <c r="J5" s="43"/>
+      <c r="K5" s="31"/>
+      <c r="L5" s="38"/>
     </row>
     <row r="6" spans="1:12" ht="26" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A6" s="33"/>
-      <c r="B6" s="36" t="s">
+      <c r="A6" s="25"/>
+      <c r="B6" s="34" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="37"/>
+      <c r="C6" s="36"/>
       <c r="D6" s="32"/>
-      <c r="E6" s="42"/>
+      <c r="E6" s="35"/>
       <c r="F6" s="44"/>
       <c r="G6" s="44"/>
       <c r="H6" s="32"/>
-      <c r="I6" s="38" t="s">
+      <c r="I6" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="J6" s="41"/>
-      <c r="K6" s="40"/>
-      <c r="L6" s="30"/>
+      <c r="J6" s="43"/>
+      <c r="K6" s="33"/>
+      <c r="L6" s="38"/>
     </row>
     <row r="7" spans="1:12" ht="26" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A7" s="33"/>
-      <c r="B7" s="49"/>
-      <c r="C7" s="35"/>
+      <c r="A7" s="25"/>
+      <c r="B7" s="48"/>
+      <c r="C7" s="31"/>
       <c r="D7" s="32"/>
-      <c r="E7" s="42"/>
-      <c r="F7" s="29" t="s">
+      <c r="E7" s="35"/>
+      <c r="F7" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="G7" s="29"/>
+      <c r="G7" s="22"/>
       <c r="H7" s="32"/>
-      <c r="I7" s="41"/>
-      <c r="J7" s="39"/>
-      <c r="K7" s="38" t="s">
+      <c r="I7" s="43"/>
+      <c r="J7" s="42"/>
+      <c r="K7" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="L7" s="30"/>
+      <c r="L7" s="38"/>
     </row>
     <row r="8" spans="1:12" ht="26" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A8" s="33"/>
-      <c r="B8" s="30"/>
+      <c r="A8" s="25"/>
+      <c r="B8" s="38"/>
       <c r="C8" s="32"/>
       <c r="D8" s="32"/>
-      <c r="E8" s="42"/>
-      <c r="F8" s="29"/>
-      <c r="G8" s="29"/>
+      <c r="E8" s="35"/>
+      <c r="F8" s="22"/>
+      <c r="G8" s="22"/>
       <c r="H8" s="32"/>
-      <c r="I8" s="41"/>
-      <c r="J8" s="35"/>
-      <c r="K8" s="39"/>
-      <c r="L8" s="30"/>
+      <c r="I8" s="43"/>
+      <c r="J8" s="31"/>
+      <c r="K8" s="42"/>
+      <c r="L8" s="38"/>
     </row>
     <row r="9" spans="1:12" ht="26" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A9" s="33"/>
-      <c r="B9" s="48"/>
+      <c r="A9" s="25"/>
+      <c r="B9" s="50"/>
       <c r="C9" s="32"/>
       <c r="D9" s="32"/>
-      <c r="E9" s="42"/>
-      <c r="F9" s="42"/>
-      <c r="G9" s="41"/>
+      <c r="E9" s="35"/>
+      <c r="F9" s="35"/>
+      <c r="G9" s="43"/>
       <c r="H9" s="32"/>
-      <c r="I9" s="41"/>
+      <c r="I9" s="43"/>
       <c r="J9" s="32"/>
-      <c r="K9" s="35"/>
-      <c r="L9" s="30"/>
+      <c r="K9" s="31"/>
+      <c r="L9" s="38"/>
     </row>
     <row r="10" spans="1:12" ht="26" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A10" s="33"/>
-      <c r="B10" s="36" t="s">
+      <c r="A10" s="25"/>
+      <c r="B10" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="40"/>
+      <c r="C10" s="33"/>
       <c r="D10" s="32"/>
-      <c r="E10" s="42"/>
-      <c r="F10" s="37"/>
-      <c r="G10" s="39"/>
+      <c r="E10" s="35"/>
+      <c r="F10" s="36"/>
+      <c r="G10" s="42"/>
       <c r="H10" s="32"/>
-      <c r="I10" s="41"/>
+      <c r="I10" s="43"/>
       <c r="J10" s="32"/>
-      <c r="K10" s="40"/>
-      <c r="L10" s="30"/>
+      <c r="K10" s="33"/>
+      <c r="L10" s="38"/>
     </row>
     <row r="11" spans="1:12" ht="26" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A11" s="33"/>
-      <c r="B11" s="49"/>
-      <c r="C11" s="50"/>
-      <c r="D11" s="36" t="s">
+      <c r="A11" s="25"/>
+      <c r="B11" s="48"/>
+      <c r="C11" s="49"/>
+      <c r="D11" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="E11" s="42"/>
-      <c r="F11" s="35" t="s">
+      <c r="E11" s="35"/>
+      <c r="F11" s="31" t="s">
         <v>10</v>
       </c>
-      <c r="G11" s="35"/>
-      <c r="H11" s="35"/>
-      <c r="I11" s="41"/>
-      <c r="J11" s="40"/>
-      <c r="K11" s="38" t="s">
+      <c r="G11" s="31"/>
+      <c r="H11" s="31"/>
+      <c r="I11" s="43"/>
+      <c r="J11" s="33"/>
+      <c r="K11" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="L11" s="30"/>
+      <c r="L11" s="38"/>
     </row>
     <row r="12" spans="1:12" ht="26" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A12" s="33"/>
-      <c r="B12" s="30"/>
-      <c r="C12" s="50"/>
-      <c r="D12" s="42"/>
-      <c r="E12" s="42"/>
+      <c r="A12" s="25"/>
+      <c r="B12" s="38"/>
+      <c r="C12" s="49"/>
+      <c r="D12" s="35"/>
+      <c r="E12" s="35"/>
       <c r="F12" s="32"/>
       <c r="G12" s="32"/>
       <c r="H12" s="32"/>
-      <c r="I12" s="41"/>
-      <c r="J12" s="38" t="s">
+      <c r="I12" s="43"/>
+      <c r="J12" s="41" t="s">
         <v>13</v>
       </c>
-      <c r="K12" s="39"/>
-      <c r="L12" s="30"/>
+      <c r="K12" s="42"/>
+      <c r="L12" s="38"/>
     </row>
     <row r="13" spans="1:12" ht="26" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A13" s="33"/>
-      <c r="B13" s="48"/>
-      <c r="C13" s="50"/>
-      <c r="D13" s="42"/>
-      <c r="E13" s="37"/>
-      <c r="F13" s="30"/>
-      <c r="G13" s="30"/>
+      <c r="A13" s="25"/>
+      <c r="B13" s="50"/>
+      <c r="C13" s="49"/>
+      <c r="D13" s="35"/>
+      <c r="E13" s="36"/>
+      <c r="F13" s="38"/>
+      <c r="G13" s="38"/>
       <c r="H13" s="32"/>
-      <c r="I13" s="39"/>
-      <c r="J13" s="41"/>
-      <c r="K13" s="35"/>
-      <c r="L13" s="30"/>
+      <c r="I13" s="42"/>
+      <c r="J13" s="43"/>
+      <c r="K13" s="31"/>
+      <c r="L13" s="38"/>
     </row>
     <row r="14" spans="1:12" ht="26" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A14" s="33"/>
-      <c r="B14" s="36" t="s">
+      <c r="A14" s="25"/>
+      <c r="B14" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="50"/>
-      <c r="D14" s="42"/>
-      <c r="E14" s="35"/>
-      <c r="F14" s="30"/>
-      <c r="G14" s="30"/>
+      <c r="C14" s="49"/>
+      <c r="D14" s="35"/>
+      <c r="E14" s="31"/>
+      <c r="F14" s="38"/>
+      <c r="G14" s="38"/>
       <c r="H14" s="32"/>
       <c r="I14" s="32"/>
-      <c r="J14" s="41"/>
-      <c r="K14" s="40"/>
-      <c r="L14" s="30"/>
+      <c r="J14" s="43"/>
+      <c r="K14" s="33"/>
+      <c r="L14" s="38"/>
     </row>
     <row r="15" spans="1:12" ht="26" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A15" s="33"/>
-      <c r="B15" s="49"/>
-      <c r="C15" s="36" t="s">
+      <c r="A15" s="25"/>
+      <c r="B15" s="48"/>
+      <c r="C15" s="34" t="s">
         <v>62</v>
       </c>
-      <c r="D15" s="37"/>
+      <c r="D15" s="36"/>
       <c r="E15" s="32"/>
-      <c r="F15" s="30"/>
-      <c r="G15" s="30"/>
+      <c r="F15" s="38"/>
+      <c r="G15" s="38"/>
       <c r="H15" s="32"/>
       <c r="I15" s="32"/>
-      <c r="J15" s="39"/>
-      <c r="K15" s="38" t="s">
+      <c r="J15" s="42"/>
+      <c r="K15" s="41" t="s">
         <v>8</v>
       </c>
-      <c r="L15" s="30"/>
+      <c r="L15" s="38"/>
     </row>
     <row r="16" spans="1:12" ht="26" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A16" s="33"/>
-      <c r="B16" s="43"/>
-      <c r="C16" s="42"/>
-      <c r="D16" s="35"/>
+      <c r="A16" s="25"/>
+      <c r="B16" s="40"/>
+      <c r="C16" s="35"/>
+      <c r="D16" s="31"/>
       <c r="E16" s="32"/>
-      <c r="F16" s="30"/>
-      <c r="G16" s="30"/>
+      <c r="F16" s="38"/>
+      <c r="G16" s="38"/>
       <c r="H16" s="32"/>
       <c r="I16" s="32"/>
-      <c r="J16" s="35"/>
-      <c r="K16" s="39"/>
-      <c r="L16" s="30"/>
+      <c r="J16" s="31"/>
+      <c r="K16" s="42"/>
+      <c r="L16" s="38"/>
     </row>
     <row r="17" spans="1:12" ht="26" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A17" s="33"/>
-      <c r="B17" s="31"/>
-      <c r="C17" s="37"/>
+      <c r="A17" s="25"/>
+      <c r="B17" s="39"/>
+      <c r="C17" s="36"/>
       <c r="D17" s="32"/>
       <c r="E17" s="32"/>
-      <c r="F17" s="30"/>
-      <c r="G17" s="30"/>
+      <c r="F17" s="38"/>
+      <c r="G17" s="38"/>
       <c r="H17" s="32"/>
       <c r="I17" s="32"/>
       <c r="J17" s="32"/>
-      <c r="K17" s="35"/>
-      <c r="L17" s="30"/>
+      <c r="K17" s="31"/>
+      <c r="L17" s="38"/>
     </row>
     <row r="18" spans="1:12" ht="26" customHeight="1" thickTop="1">
-      <c r="A18" s="33"/>
+      <c r="A18" s="25"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
       <c r="D18" s="32"/>
       <c r="E18" s="32"/>
-      <c r="F18" s="30"/>
-      <c r="G18" s="30"/>
+      <c r="F18" s="38"/>
+      <c r="G18" s="38"/>
       <c r="H18" s="32"/>
       <c r="I18" s="32"/>
       <c r="J18" s="32"/>
@@ -2258,25 +2332,33 @@
     </row>
   </sheetData>
   <mergeCells count="62">
-    <mergeCell ref="E1:E4"/>
-    <mergeCell ref="E14:E18"/>
-    <mergeCell ref="D16:D18"/>
-    <mergeCell ref="H1:H10"/>
-    <mergeCell ref="H11:H18"/>
-    <mergeCell ref="F1:G6"/>
-    <mergeCell ref="F7:G8"/>
-    <mergeCell ref="F9:F10"/>
-    <mergeCell ref="G9:G10"/>
-    <mergeCell ref="F11:G12"/>
-    <mergeCell ref="F13:G18"/>
-    <mergeCell ref="J4:J7"/>
-    <mergeCell ref="J8:J11"/>
-    <mergeCell ref="J12:J15"/>
-    <mergeCell ref="J16:J18"/>
-    <mergeCell ref="I1:I5"/>
-    <mergeCell ref="I6:I13"/>
-    <mergeCell ref="I14:I18"/>
-    <mergeCell ref="J1:J3"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="C7:C10"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="C3:C6"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D11:D15"/>
+    <mergeCell ref="D5:D10"/>
+    <mergeCell ref="E5:E13"/>
+    <mergeCell ref="D1:D4"/>
+    <mergeCell ref="C15:C17"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="C11:C14"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="B16:B17"/>
     <mergeCell ref="K15:K16"/>
     <mergeCell ref="K17:K18"/>
     <mergeCell ref="L2:L3"/>
@@ -2293,33 +2375,25 @@
     <mergeCell ref="L14:L15"/>
     <mergeCell ref="L16:L17"/>
     <mergeCell ref="K3:K4"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C15:C17"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="C11:C14"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="K1:K2"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="C7:C10"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="C3:C6"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D11:D15"/>
-    <mergeCell ref="D5:D10"/>
-    <mergeCell ref="E5:E13"/>
-    <mergeCell ref="D1:D4"/>
+    <mergeCell ref="J4:J7"/>
+    <mergeCell ref="J8:J11"/>
+    <mergeCell ref="J12:J15"/>
+    <mergeCell ref="J16:J18"/>
+    <mergeCell ref="I1:I5"/>
+    <mergeCell ref="I6:I13"/>
+    <mergeCell ref="I14:I18"/>
+    <mergeCell ref="J1:J3"/>
+    <mergeCell ref="E1:E4"/>
+    <mergeCell ref="E14:E18"/>
+    <mergeCell ref="D16:D18"/>
+    <mergeCell ref="H1:H10"/>
+    <mergeCell ref="H11:H18"/>
+    <mergeCell ref="F1:G6"/>
+    <mergeCell ref="F7:G8"/>
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="G9:G10"/>
+    <mergeCell ref="F11:G12"/>
+    <mergeCell ref="F13:G18"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2333,293 +2407,293 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="26" customHeight="1"/>
   <sheetData>
     <row r="1" spans="1:12" ht="26" customHeight="1" thickBot="1">
-      <c r="A1" s="33"/>
+      <c r="A1" s="25"/>
       <c r="C1" s="32"/>
       <c r="D1" s="32"/>
       <c r="E1" s="32"/>
-      <c r="F1" s="25" t="s">
+      <c r="F1" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="G1" s="25"/>
+      <c r="G1" s="29"/>
       <c r="H1" s="32"/>
       <c r="I1" s="32"/>
       <c r="J1" s="32"/>
       <c r="K1" s="7"/>
-      <c r="L1" s="33"/>
+      <c r="L1" s="25"/>
     </row>
     <row r="2" spans="1:12" ht="26" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A2" s="33"/>
-      <c r="B2" s="36" t="s">
+      <c r="A2" s="25"/>
+      <c r="B2" s="34" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="32"/>
       <c r="D2" s="32"/>
       <c r="E2" s="32"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
       <c r="H2" s="32"/>
       <c r="I2" s="32"/>
-      <c r="J2" s="40"/>
-      <c r="K2" s="38" t="s">
+      <c r="J2" s="33"/>
+      <c r="K2" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="L2" s="33"/>
+      <c r="L2" s="25"/>
     </row>
     <row r="3" spans="1:12" ht="26" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A3" s="33"/>
-      <c r="B3" s="49"/>
-      <c r="C3" s="36" t="s">
+      <c r="A3" s="25"/>
+      <c r="B3" s="48"/>
+      <c r="C3" s="34" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="32"/>
       <c r="E3" s="32"/>
-      <c r="F3" s="25"/>
-      <c r="G3" s="25"/>
+      <c r="F3" s="29"/>
+      <c r="G3" s="29"/>
       <c r="H3" s="32"/>
       <c r="I3" s="32"/>
-      <c r="J3" s="38" t="s">
+      <c r="J3" s="41" t="s">
         <v>13</v>
       </c>
-      <c r="K3" s="39"/>
-      <c r="L3" s="33"/>
+      <c r="K3" s="42"/>
+      <c r="L3" s="25"/>
     </row>
     <row r="4" spans="1:12" ht="26" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A4" s="33"/>
-      <c r="B4" s="30"/>
-      <c r="C4" s="42"/>
+      <c r="A4" s="25"/>
+      <c r="B4" s="38"/>
+      <c r="C4" s="35"/>
       <c r="D4" s="32"/>
-      <c r="E4" s="40"/>
-      <c r="F4" s="25"/>
-      <c r="G4" s="25"/>
-      <c r="H4" s="40"/>
-      <c r="I4" s="40"/>
-      <c r="J4" s="41"/>
-      <c r="K4" s="35"/>
-      <c r="L4" s="33"/>
+      <c r="E4" s="33"/>
+      <c r="F4" s="29"/>
+      <c r="G4" s="29"/>
+      <c r="H4" s="33"/>
+      <c r="I4" s="33"/>
+      <c r="J4" s="43"/>
+      <c r="K4" s="31"/>
+      <c r="L4" s="25"/>
     </row>
     <row r="5" spans="1:12" ht="26" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A5" s="33"/>
-      <c r="B5" s="48"/>
-      <c r="C5" s="42"/>
-      <c r="D5" s="35"/>
-      <c r="E5" s="36" t="s">
+      <c r="A5" s="25"/>
+      <c r="B5" s="50"/>
+      <c r="C5" s="35"/>
+      <c r="D5" s="31"/>
+      <c r="E5" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="F5" s="25"/>
-      <c r="G5" s="25"/>
-      <c r="H5" s="38" t="s">
+      <c r="F5" s="29"/>
+      <c r="G5" s="29"/>
+      <c r="H5" s="41" t="s">
         <v>2</v>
       </c>
-      <c r="I5" s="35"/>
-      <c r="J5" s="41"/>
-      <c r="K5" s="40"/>
-      <c r="L5" s="33"/>
+      <c r="I5" s="31"/>
+      <c r="J5" s="43"/>
+      <c r="K5" s="33"/>
+      <c r="L5" s="25"/>
     </row>
     <row r="6" spans="1:12" ht="26" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A6" s="33"/>
-      <c r="B6" s="36" t="s">
+      <c r="A6" s="25"/>
+      <c r="B6" s="34" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="37"/>
+      <c r="C6" s="36"/>
       <c r="D6" s="32"/>
-      <c r="E6" s="42"/>
-      <c r="F6" s="25"/>
-      <c r="G6" s="25"/>
-      <c r="H6" s="41"/>
+      <c r="E6" s="35"/>
+      <c r="F6" s="29"/>
+      <c r="G6" s="29"/>
+      <c r="H6" s="43"/>
       <c r="I6" s="32"/>
-      <c r="J6" s="39"/>
-      <c r="K6" s="38" t="s">
+      <c r="J6" s="42"/>
+      <c r="K6" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="L6" s="33"/>
+      <c r="L6" s="25"/>
     </row>
     <row r="7" spans="1:12" ht="26" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A7" s="33"/>
-      <c r="B7" s="49"/>
-      <c r="C7" s="35"/>
+      <c r="A7" s="25"/>
+      <c r="B7" s="48"/>
+      <c r="C7" s="31"/>
       <c r="D7" s="32"/>
-      <c r="E7" s="42"/>
-      <c r="F7" s="29" t="s">
+      <c r="E7" s="35"/>
+      <c r="F7" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="G7" s="29"/>
-      <c r="H7" s="41"/>
+      <c r="G7" s="22"/>
+      <c r="H7" s="43"/>
       <c r="I7" s="32"/>
       <c r="J7" s="32"/>
-      <c r="K7" s="39"/>
-      <c r="L7" s="33"/>
+      <c r="K7" s="42"/>
+      <c r="L7" s="25"/>
     </row>
     <row r="8" spans="1:12" ht="26" customHeight="1" thickTop="1">
-      <c r="A8" s="33"/>
-      <c r="B8" s="30"/>
+      <c r="A8" s="25"/>
+      <c r="B8" s="38"/>
       <c r="C8" s="32"/>
       <c r="D8" s="32"/>
-      <c r="E8" s="42"/>
-      <c r="F8" s="29"/>
-      <c r="G8" s="29"/>
-      <c r="H8" s="41"/>
+      <c r="E8" s="35"/>
+      <c r="F8" s="22"/>
+      <c r="G8" s="22"/>
+      <c r="H8" s="43"/>
       <c r="I8" s="32"/>
       <c r="J8" s="32"/>
-      <c r="K8" s="35"/>
-      <c r="L8" s="33"/>
+      <c r="K8" s="31"/>
+      <c r="L8" s="25"/>
     </row>
     <row r="9" spans="1:12" ht="26" customHeight="1" thickBot="1">
-      <c r="A9" s="33"/>
-      <c r="B9" s="48"/>
+      <c r="A9" s="25"/>
+      <c r="B9" s="50"/>
       <c r="C9" s="32"/>
       <c r="D9" s="32"/>
-      <c r="E9" s="42"/>
-      <c r="F9" s="42"/>
-      <c r="G9" s="41"/>
-      <c r="H9" s="41"/>
+      <c r="E9" s="35"/>
+      <c r="F9" s="35"/>
+      <c r="G9" s="43"/>
+      <c r="H9" s="43"/>
       <c r="I9" s="32"/>
       <c r="J9" s="32"/>
-      <c r="K9" s="40"/>
-      <c r="L9" s="33"/>
+      <c r="K9" s="33"/>
+      <c r="L9" s="25"/>
     </row>
     <row r="10" spans="1:12" ht="26" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A10" s="33"/>
-      <c r="B10" s="36" t="s">
+      <c r="A10" s="25"/>
+      <c r="B10" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="40"/>
+      <c r="C10" s="33"/>
       <c r="D10" s="32"/>
-      <c r="E10" s="42"/>
-      <c r="F10" s="37"/>
-      <c r="G10" s="39"/>
-      <c r="H10" s="41"/>
-      <c r="I10" s="40"/>
+      <c r="E10" s="35"/>
+      <c r="F10" s="36"/>
+      <c r="G10" s="42"/>
+      <c r="H10" s="43"/>
+      <c r="I10" s="33"/>
       <c r="J10" s="32"/>
-      <c r="K10" s="38" t="s">
+      <c r="K10" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="L10" s="33"/>
+      <c r="L10" s="25"/>
     </row>
     <row r="11" spans="1:12" ht="26" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A11" s="33"/>
-      <c r="B11" s="49"/>
-      <c r="C11" s="50"/>
-      <c r="D11" s="36" t="s">
+      <c r="A11" s="25"/>
+      <c r="B11" s="48"/>
+      <c r="C11" s="49"/>
+      <c r="D11" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="E11" s="42"/>
-      <c r="F11" s="35" t="s">
+      <c r="E11" s="35"/>
+      <c r="F11" s="31" t="s">
         <v>10</v>
       </c>
-      <c r="G11" s="35"/>
-      <c r="H11" s="41"/>
-      <c r="I11" s="38" t="s">
+      <c r="G11" s="31"/>
+      <c r="H11" s="43"/>
+      <c r="I11" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="J11" s="35"/>
-      <c r="K11" s="39"/>
-      <c r="L11" s="33"/>
+      <c r="J11" s="31"/>
+      <c r="K11" s="42"/>
+      <c r="L11" s="25"/>
     </row>
     <row r="12" spans="1:12" ht="26" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A12" s="33"/>
-      <c r="B12" s="30"/>
-      <c r="C12" s="50"/>
-      <c r="D12" s="42"/>
-      <c r="E12" s="42"/>
+      <c r="A12" s="25"/>
+      <c r="B12" s="38"/>
+      <c r="C12" s="49"/>
+      <c r="D12" s="35"/>
+      <c r="E12" s="35"/>
       <c r="F12" s="32"/>
       <c r="G12" s="32"/>
-      <c r="H12" s="41"/>
-      <c r="I12" s="41"/>
+      <c r="H12" s="43"/>
+      <c r="I12" s="43"/>
       <c r="J12" s="32"/>
-      <c r="K12" s="35"/>
-      <c r="L12" s="33"/>
+      <c r="K12" s="31"/>
+      <c r="L12" s="25"/>
     </row>
     <row r="13" spans="1:12" ht="26" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A13" s="33"/>
-      <c r="B13" s="48"/>
-      <c r="C13" s="50"/>
-      <c r="D13" s="42"/>
-      <c r="E13" s="37"/>
-      <c r="F13" s="30"/>
-      <c r="G13" s="30"/>
-      <c r="H13" s="39"/>
-      <c r="I13" s="41"/>
+      <c r="A13" s="25"/>
+      <c r="B13" s="50"/>
+      <c r="C13" s="49"/>
+      <c r="D13" s="35"/>
+      <c r="E13" s="36"/>
+      <c r="F13" s="38"/>
+      <c r="G13" s="38"/>
+      <c r="H13" s="42"/>
+      <c r="I13" s="43"/>
       <c r="J13" s="32"/>
-      <c r="K13" s="40"/>
-      <c r="L13" s="33"/>
+      <c r="K13" s="33"/>
+      <c r="L13" s="25"/>
     </row>
     <row r="14" spans="1:12" ht="26" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A14" s="33"/>
-      <c r="B14" s="36" t="s">
+      <c r="A14" s="25"/>
+      <c r="B14" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="50"/>
-      <c r="D14" s="42"/>
-      <c r="E14" s="35"/>
-      <c r="F14" s="30"/>
-      <c r="G14" s="30"/>
-      <c r="H14" s="35"/>
-      <c r="I14" s="41"/>
-      <c r="J14" s="40"/>
-      <c r="K14" s="38" t="s">
+      <c r="C14" s="49"/>
+      <c r="D14" s="35"/>
+      <c r="E14" s="31"/>
+      <c r="F14" s="38"/>
+      <c r="G14" s="38"/>
+      <c r="H14" s="31"/>
+      <c r="I14" s="43"/>
+      <c r="J14" s="33"/>
+      <c r="K14" s="41" t="s">
         <v>8</v>
       </c>
-      <c r="L14" s="33"/>
+      <c r="L14" s="25"/>
     </row>
     <row r="15" spans="1:12" ht="26" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A15" s="33"/>
-      <c r="B15" s="49"/>
-      <c r="C15" s="36" t="s">
+      <c r="A15" s="25"/>
+      <c r="B15" s="48"/>
+      <c r="C15" s="34" t="s">
         <v>62</v>
       </c>
-      <c r="D15" s="37"/>
+      <c r="D15" s="36"/>
       <c r="E15" s="32"/>
-      <c r="F15" s="30"/>
-      <c r="G15" s="30"/>
+      <c r="F15" s="38"/>
+      <c r="G15" s="38"/>
       <c r="H15" s="32"/>
-      <c r="I15" s="39"/>
-      <c r="J15" s="38" t="s">
+      <c r="I15" s="42"/>
+      <c r="J15" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="K15" s="39"/>
-      <c r="L15" s="33"/>
+      <c r="K15" s="42"/>
+      <c r="L15" s="25"/>
     </row>
     <row r="16" spans="1:12" ht="26" customHeight="1" thickTop="1">
-      <c r="A16" s="33"/>
-      <c r="B16" s="43"/>
-      <c r="C16" s="42"/>
-      <c r="D16" s="35"/>
+      <c r="A16" s="25"/>
+      <c r="B16" s="40"/>
+      <c r="C16" s="35"/>
+      <c r="D16" s="31"/>
       <c r="E16" s="32"/>
-      <c r="F16" s="30"/>
-      <c r="G16" s="30"/>
+      <c r="F16" s="38"/>
+      <c r="G16" s="38"/>
       <c r="H16" s="32"/>
-      <c r="I16" s="35"/>
-      <c r="J16" s="41"/>
-      <c r="K16" s="35"/>
-      <c r="L16" s="33"/>
+      <c r="I16" s="31"/>
+      <c r="J16" s="43"/>
+      <c r="K16" s="31"/>
+      <c r="L16" s="25"/>
     </row>
     <row r="17" spans="1:12" ht="26" customHeight="1" thickBot="1">
-      <c r="A17" s="33"/>
-      <c r="B17" s="31"/>
-      <c r="C17" s="37"/>
+      <c r="A17" s="25"/>
+      <c r="B17" s="39"/>
+      <c r="C17" s="36"/>
       <c r="D17" s="32"/>
       <c r="E17" s="32"/>
-      <c r="F17" s="30"/>
-      <c r="G17" s="30"/>
+      <c r="F17" s="38"/>
+      <c r="G17" s="38"/>
       <c r="H17" s="32"/>
       <c r="I17" s="32"/>
-      <c r="J17" s="39"/>
-      <c r="K17" s="40"/>
-      <c r="L17" s="33"/>
+      <c r="J17" s="42"/>
+      <c r="K17" s="33"/>
+      <c r="L17" s="25"/>
     </row>
     <row r="18" spans="1:12" ht="26" customHeight="1" thickTop="1">
-      <c r="A18" s="33"/>
+      <c r="A18" s="25"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
       <c r="D18" s="32"/>
       <c r="E18" s="32"/>
-      <c r="F18" s="30"/>
-      <c r="G18" s="30"/>
+      <c r="F18" s="38"/>
+      <c r="G18" s="38"/>
       <c r="H18" s="32"/>
       <c r="I18" s="32"/>
       <c r="J18" s="1"/>
       <c r="K18" s="1"/>
-      <c r="L18" s="33"/>
+      <c r="L18" s="25"/>
     </row>
     <row r="19" spans="1:12" ht="26" customHeight="1">
       <c r="A19" s="4"/>
@@ -2676,6 +2750,54 @@
     </row>
   </sheetData>
   <mergeCells count="64">
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="I1:I4"/>
+    <mergeCell ref="L3:L4"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D4"/>
+    <mergeCell ref="K4:K5"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="D5:D10"/>
+    <mergeCell ref="I5:I10"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="C3:C6"/>
+    <mergeCell ref="J3:J6"/>
+    <mergeCell ref="E1:E4"/>
+    <mergeCell ref="F1:G6"/>
+    <mergeCell ref="H1:H4"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="L9:L10"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="K10:K11"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="C11:C14"/>
+    <mergeCell ref="C7:C10"/>
+    <mergeCell ref="J7:J10"/>
+    <mergeCell ref="L7:L8"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="K8:K9"/>
+    <mergeCell ref="L13:L14"/>
+    <mergeCell ref="D11:D15"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="K6:K7"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="K12:K13"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="K14:K15"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="C15:C17"/>
+    <mergeCell ref="J15:J17"/>
+    <mergeCell ref="D16:D18"/>
+    <mergeCell ref="I16:I18"/>
+    <mergeCell ref="J11:J14"/>
+    <mergeCell ref="B12:B13"/>
     <mergeCell ref="L17:L18"/>
     <mergeCell ref="B16:B17"/>
     <mergeCell ref="K16:K17"/>
@@ -2692,54 +2814,6 @@
     <mergeCell ref="H14:H18"/>
     <mergeCell ref="L11:L12"/>
     <mergeCell ref="L5:L6"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="K12:K13"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="K14:K15"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="C15:C17"/>
-    <mergeCell ref="J15:J17"/>
-    <mergeCell ref="D16:D18"/>
-    <mergeCell ref="I16:I18"/>
-    <mergeCell ref="J11:J14"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="L9:L10"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="K10:K11"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="C11:C14"/>
-    <mergeCell ref="C7:C10"/>
-    <mergeCell ref="J7:J10"/>
-    <mergeCell ref="L7:L8"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="K8:K9"/>
-    <mergeCell ref="L13:L14"/>
-    <mergeCell ref="D11:D15"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="K6:K7"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D4"/>
-    <mergeCell ref="K4:K5"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="D5:D10"/>
-    <mergeCell ref="I5:I10"/>
-    <mergeCell ref="J1:J2"/>
-    <mergeCell ref="C3:C6"/>
-    <mergeCell ref="J3:J6"/>
-    <mergeCell ref="E1:E4"/>
-    <mergeCell ref="F1:G6"/>
-    <mergeCell ref="H1:H4"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="L1:L2"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="K2:K3"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="I1:I4"/>
-    <mergeCell ref="L3:L4"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2753,7 +2827,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="24" customHeight="1"/>
   <sheetData>
     <row r="1" spans="1:12" ht="24" customHeight="1" thickBot="1">
-      <c r="A1" s="33"/>
+      <c r="A1" s="25"/>
       <c r="C1" s="32"/>
       <c r="D1" s="32"/>
       <c r="E1" s="32"/>
@@ -2765,11 +2839,11 @@
       <c r="I1" s="32"/>
       <c r="J1" s="32"/>
       <c r="K1" s="7"/>
-      <c r="L1" s="33"/>
+      <c r="L1" s="25"/>
     </row>
     <row r="2" spans="1:12" ht="24" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A2" s="33"/>
-      <c r="B2" s="36" t="s">
+      <c r="A2" s="25"/>
+      <c r="B2" s="34" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="32"/>
@@ -2779,16 +2853,16 @@
       <c r="G2" s="44"/>
       <c r="H2" s="32"/>
       <c r="I2" s="32"/>
-      <c r="J2" s="40"/>
-      <c r="K2" s="38" t="s">
+      <c r="J2" s="33"/>
+      <c r="K2" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="L2" s="33"/>
+      <c r="L2" s="25"/>
     </row>
     <row r="3" spans="1:12" ht="24" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A3" s="33"/>
-      <c r="B3" s="49"/>
-      <c r="C3" s="36" t="s">
+      <c r="A3" s="25"/>
+      <c r="B3" s="48"/>
+      <c r="C3" s="34" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="32"/>
@@ -2797,243 +2871,243 @@
       <c r="G3" s="44"/>
       <c r="H3" s="32"/>
       <c r="I3" s="32"/>
-      <c r="J3" s="38" t="s">
+      <c r="J3" s="41" t="s">
         <v>13</v>
       </c>
-      <c r="K3" s="39"/>
-      <c r="L3" s="33"/>
+      <c r="K3" s="42"/>
+      <c r="L3" s="25"/>
     </row>
     <row r="4" spans="1:12" ht="24" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A4" s="33"/>
-      <c r="B4" s="30"/>
-      <c r="C4" s="42"/>
+      <c r="A4" s="25"/>
+      <c r="B4" s="38"/>
+      <c r="C4" s="35"/>
       <c r="D4" s="32"/>
       <c r="E4" s="32"/>
       <c r="F4" s="44"/>
       <c r="G4" s="44"/>
-      <c r="H4" s="40"/>
-      <c r="I4" s="40"/>
-      <c r="J4" s="41"/>
-      <c r="K4" s="35"/>
-      <c r="L4" s="33"/>
+      <c r="H4" s="33"/>
+      <c r="I4" s="33"/>
+      <c r="J4" s="43"/>
+      <c r="K4" s="31"/>
+      <c r="L4" s="25"/>
     </row>
     <row r="5" spans="1:12" ht="24" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A5" s="33"/>
-      <c r="B5" s="48"/>
-      <c r="C5" s="42"/>
-      <c r="D5" s="36" t="s">
+      <c r="A5" s="25"/>
+      <c r="B5" s="50"/>
+      <c r="C5" s="35"/>
+      <c r="D5" s="34" t="s">
         <v>2</v>
       </c>
       <c r="E5" s="32"/>
       <c r="F5" s="44"/>
       <c r="G5" s="44"/>
-      <c r="H5" s="38" t="s">
+      <c r="H5" s="41" t="s">
         <v>2</v>
       </c>
-      <c r="I5" s="35"/>
-      <c r="J5" s="41"/>
-      <c r="K5" s="40"/>
-      <c r="L5" s="33"/>
+      <c r="I5" s="31"/>
+      <c r="J5" s="43"/>
+      <c r="K5" s="33"/>
+      <c r="L5" s="25"/>
     </row>
     <row r="6" spans="1:12" ht="24" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A6" s="33"/>
-      <c r="B6" s="36" t="s">
+      <c r="A6" s="25"/>
+      <c r="B6" s="34" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="37"/>
-      <c r="D6" s="42"/>
+      <c r="C6" s="36"/>
+      <c r="D6" s="35"/>
       <c r="E6" s="32"/>
       <c r="F6" s="44"/>
       <c r="G6" s="44"/>
-      <c r="H6" s="41"/>
+      <c r="H6" s="43"/>
       <c r="I6" s="32"/>
-      <c r="J6" s="39"/>
-      <c r="K6" s="38" t="s">
+      <c r="J6" s="42"/>
+      <c r="K6" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="L6" s="33"/>
+      <c r="L6" s="25"/>
     </row>
     <row r="7" spans="1:12" ht="24" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A7" s="33"/>
-      <c r="B7" s="49"/>
-      <c r="C7" s="35"/>
-      <c r="D7" s="42"/>
+      <c r="A7" s="25"/>
+      <c r="B7" s="48"/>
+      <c r="C7" s="31"/>
+      <c r="D7" s="35"/>
       <c r="E7" s="32"/>
       <c r="F7" s="44"/>
       <c r="G7" s="44"/>
-      <c r="H7" s="41"/>
+      <c r="H7" s="43"/>
       <c r="I7" s="32"/>
       <c r="J7" s="32"/>
-      <c r="K7" s="39"/>
-      <c r="L7" s="33"/>
+      <c r="K7" s="42"/>
+      <c r="L7" s="25"/>
     </row>
     <row r="8" spans="1:12" ht="24" customHeight="1" thickTop="1">
-      <c r="A8" s="33"/>
-      <c r="B8" s="30"/>
+      <c r="A8" s="25"/>
+      <c r="B8" s="38"/>
       <c r="C8" s="32"/>
-      <c r="D8" s="42"/>
+      <c r="D8" s="35"/>
       <c r="E8" s="51" t="s">
         <v>10</v>
       </c>
-      <c r="F8" s="29" t="s">
+      <c r="F8" s="22" t="s">
         <v>5</v>
       </c>
       <c r="G8" s="54"/>
-      <c r="H8" s="41"/>
+      <c r="H8" s="43"/>
       <c r="I8" s="32"/>
       <c r="J8" s="32"/>
-      <c r="K8" s="35"/>
-      <c r="L8" s="33"/>
+      <c r="K8" s="31"/>
+      <c r="L8" s="25"/>
     </row>
     <row r="9" spans="1:12" ht="24" customHeight="1" thickBot="1">
-      <c r="A9" s="33"/>
-      <c r="B9" s="48"/>
+      <c r="A9" s="25"/>
+      <c r="B9" s="50"/>
       <c r="C9" s="32"/>
-      <c r="D9" s="42"/>
+      <c r="D9" s="35"/>
       <c r="E9" s="52"/>
-      <c r="F9" s="29"/>
+      <c r="F9" s="22"/>
       <c r="G9" s="54"/>
-      <c r="H9" s="41"/>
+      <c r="H9" s="43"/>
       <c r="I9" s="32"/>
       <c r="J9" s="32"/>
-      <c r="K9" s="40"/>
-      <c r="L9" s="33"/>
+      <c r="K9" s="33"/>
+      <c r="L9" s="25"/>
     </row>
     <row r="10" spans="1:12" ht="24" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A10" s="33"/>
-      <c r="B10" s="36" t="s">
+      <c r="A10" s="25"/>
+      <c r="B10" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="40"/>
-      <c r="D10" s="37"/>
+      <c r="C10" s="33"/>
+      <c r="D10" s="36"/>
       <c r="E10" s="52"/>
-      <c r="F10" s="42"/>
-      <c r="G10" s="41"/>
-      <c r="H10" s="41"/>
-      <c r="I10" s="40"/>
+      <c r="F10" s="35"/>
+      <c r="G10" s="43"/>
+      <c r="H10" s="43"/>
+      <c r="I10" s="33"/>
       <c r="J10" s="32"/>
-      <c r="K10" s="38" t="s">
+      <c r="K10" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="L10" s="33"/>
+      <c r="L10" s="25"/>
     </row>
     <row r="11" spans="1:12" ht="24" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A11" s="33"/>
-      <c r="B11" s="49"/>
-      <c r="C11" s="50"/>
+      <c r="A11" s="25"/>
+      <c r="B11" s="48"/>
+      <c r="C11" s="49"/>
       <c r="D11" s="32"/>
       <c r="E11" s="52"/>
-      <c r="F11" s="37"/>
-      <c r="G11" s="39"/>
-      <c r="H11" s="41"/>
-      <c r="I11" s="38" t="s">
+      <c r="F11" s="36"/>
+      <c r="G11" s="42"/>
+      <c r="H11" s="43"/>
+      <c r="I11" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="J11" s="35"/>
-      <c r="K11" s="39"/>
-      <c r="L11" s="33"/>
+      <c r="J11" s="31"/>
+      <c r="K11" s="42"/>
+      <c r="L11" s="25"/>
     </row>
     <row r="12" spans="1:12" ht="24" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A12" s="33"/>
-      <c r="B12" s="30"/>
-      <c r="C12" s="50"/>
+      <c r="A12" s="25"/>
+      <c r="B12" s="38"/>
+      <c r="C12" s="49"/>
       <c r="D12" s="32"/>
       <c r="E12" s="52"/>
       <c r="F12" s="55" t="s">
         <v>4</v>
       </c>
       <c r="G12" s="51"/>
-      <c r="H12" s="41"/>
-      <c r="I12" s="41"/>
+      <c r="H12" s="43"/>
+      <c r="I12" s="43"/>
       <c r="J12" s="32"/>
-      <c r="K12" s="35"/>
-      <c r="L12" s="33"/>
+      <c r="K12" s="31"/>
+      <c r="L12" s="25"/>
     </row>
     <row r="13" spans="1:12" ht="24" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A13" s="33"/>
-      <c r="B13" s="48"/>
-      <c r="C13" s="50"/>
+      <c r="A13" s="25"/>
+      <c r="B13" s="50"/>
+      <c r="C13" s="49"/>
       <c r="D13" s="32"/>
       <c r="E13" s="52"/>
       <c r="F13" s="56"/>
       <c r="G13" s="52"/>
-      <c r="H13" s="39"/>
-      <c r="I13" s="41"/>
+      <c r="H13" s="42"/>
+      <c r="I13" s="43"/>
       <c r="J13" s="32"/>
-      <c r="K13" s="40"/>
-      <c r="L13" s="33"/>
+      <c r="K13" s="33"/>
+      <c r="L13" s="25"/>
     </row>
     <row r="14" spans="1:12" ht="24" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A14" s="33"/>
-      <c r="B14" s="36" t="s">
+      <c r="A14" s="25"/>
+      <c r="B14" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="50"/>
+      <c r="C14" s="49"/>
       <c r="D14" s="32"/>
       <c r="E14" s="52"/>
       <c r="F14" s="32"/>
       <c r="G14" s="32"/>
-      <c r="H14" s="35"/>
-      <c r="I14" s="41"/>
-      <c r="J14" s="40"/>
-      <c r="K14" s="38" t="s">
+      <c r="H14" s="31"/>
+      <c r="I14" s="43"/>
+      <c r="J14" s="33"/>
+      <c r="K14" s="41" t="s">
         <v>8</v>
       </c>
-      <c r="L14" s="33"/>
+      <c r="L14" s="25"/>
     </row>
     <row r="15" spans="1:12" ht="24" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A15" s="33"/>
-      <c r="B15" s="49"/>
-      <c r="C15" s="50"/>
-      <c r="D15" s="36" t="s">
+      <c r="A15" s="25"/>
+      <c r="B15" s="48"/>
+      <c r="C15" s="49"/>
+      <c r="D15" s="34" t="s">
         <v>1</v>
       </c>
       <c r="E15" s="52"/>
       <c r="F15" s="32"/>
       <c r="G15" s="32"/>
       <c r="H15" s="32"/>
-      <c r="I15" s="39"/>
-      <c r="J15" s="38" t="s">
+      <c r="I15" s="42"/>
+      <c r="J15" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="K15" s="39"/>
-      <c r="L15" s="33"/>
+      <c r="K15" s="42"/>
+      <c r="L15" s="25"/>
     </row>
     <row r="16" spans="1:12" ht="24" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A16" s="33"/>
-      <c r="B16" s="30"/>
-      <c r="C16" s="50"/>
-      <c r="D16" s="42"/>
+      <c r="A16" s="25"/>
+      <c r="B16" s="38"/>
+      <c r="C16" s="49"/>
+      <c r="D16" s="35"/>
       <c r="E16" s="53"/>
       <c r="F16" s="32"/>
       <c r="G16" s="32"/>
       <c r="H16" s="32"/>
-      <c r="I16" s="35"/>
-      <c r="J16" s="41"/>
-      <c r="K16" s="35"/>
-      <c r="L16" s="33"/>
+      <c r="I16" s="31"/>
+      <c r="J16" s="43"/>
+      <c r="K16" s="31"/>
+      <c r="L16" s="25"/>
     </row>
     <row r="17" spans="1:12" ht="24" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A17" s="33"/>
-      <c r="B17" s="48"/>
-      <c r="C17" s="50"/>
-      <c r="D17" s="42"/>
-      <c r="E17" s="35"/>
+      <c r="A17" s="25"/>
+      <c r="B17" s="50"/>
+      <c r="C17" s="49"/>
+      <c r="D17" s="35"/>
+      <c r="E17" s="31"/>
       <c r="F17" s="32"/>
       <c r="G17" s="32"/>
       <c r="H17" s="32"/>
       <c r="I17" s="32"/>
-      <c r="J17" s="39"/>
-      <c r="K17" s="40"/>
-      <c r="L17" s="33"/>
+      <c r="J17" s="42"/>
+      <c r="K17" s="33"/>
+      <c r="L17" s="25"/>
     </row>
     <row r="18" spans="1:12" ht="24" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A18" s="33"/>
-      <c r="B18" s="36" t="s">
+      <c r="A18" s="25"/>
+      <c r="B18" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="C18" s="35"/>
-      <c r="D18" s="37"/>
+      <c r="C18" s="31"/>
+      <c r="D18" s="36"/>
       <c r="E18" s="32"/>
       <c r="F18" s="32"/>
       <c r="G18" s="32"/>
@@ -3041,13 +3115,13 @@
       <c r="I18" s="32"/>
       <c r="J18" s="1"/>
       <c r="K18" s="1"/>
-      <c r="L18" s="33"/>
+      <c r="L18" s="25"/>
     </row>
     <row r="19" spans="1:12" ht="24" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A19" s="33"/>
-      <c r="B19" s="49"/>
-      <c r="C19" s="35"/>
-      <c r="D19" s="35"/>
+      <c r="A19" s="25"/>
+      <c r="B19" s="48"/>
+      <c r="C19" s="31"/>
+      <c r="D19" s="31"/>
       <c r="E19" s="32"/>
       <c r="F19" s="32"/>
       <c r="G19" s="32"/>
@@ -3055,10 +3129,10 @@
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
-      <c r="L19" s="33"/>
+      <c r="L19" s="25"/>
     </row>
     <row r="20" spans="1:12" ht="24" customHeight="1" thickTop="1">
-      <c r="A20" s="33"/>
+      <c r="A20" s="25"/>
       <c r="B20" s="3"/>
       <c r="C20" s="32"/>
       <c r="D20" s="32"/>
@@ -3069,7 +3143,7 @@
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
-      <c r="L20" s="33"/>
+      <c r="L20" s="25"/>
     </row>
     <row r="21" spans="1:12" ht="24" customHeight="1">
       <c r="A21" s="4"/>
@@ -3099,16 +3173,49 @@
     </row>
   </sheetData>
   <mergeCells count="69">
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D4"/>
-    <mergeCell ref="E1:E7"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="D5:D10"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="L13:L14"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="K14:K15"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="C15:C18"/>
+    <mergeCell ref="D15:D18"/>
+    <mergeCell ref="L15:L16"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="K16:K17"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="L17:L18"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="L19:L20"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="D19:D20"/>
+    <mergeCell ref="E17:E20"/>
+    <mergeCell ref="I16:I18"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="K10:K11"/>
+    <mergeCell ref="C7:C10"/>
+    <mergeCell ref="J7:J10"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="C11:C14"/>
+    <mergeCell ref="D11:D14"/>
+    <mergeCell ref="K12:K13"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="L7:L8"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="E8:E16"/>
+    <mergeCell ref="F8:G9"/>
+    <mergeCell ref="K8:K9"/>
+    <mergeCell ref="J11:J14"/>
+    <mergeCell ref="L11:L12"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="F12:G13"/>
+    <mergeCell ref="F14:G20"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="L9:L10"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="F10:F11"/>
     <mergeCell ref="I1:I4"/>
     <mergeCell ref="J1:J2"/>
     <mergeCell ref="C3:C6"/>
@@ -3125,49 +3232,16 @@
     <mergeCell ref="H14:H18"/>
     <mergeCell ref="J15:J17"/>
     <mergeCell ref="L1:L2"/>
-    <mergeCell ref="K2:K3"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="L7:L8"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="E8:E16"/>
-    <mergeCell ref="F8:G9"/>
-    <mergeCell ref="K8:K9"/>
-    <mergeCell ref="J11:J14"/>
-    <mergeCell ref="L11:L12"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="F12:G13"/>
-    <mergeCell ref="F14:G20"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="L9:L10"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="C11:C14"/>
-    <mergeCell ref="D11:D14"/>
-    <mergeCell ref="K12:K13"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="E17:E20"/>
-    <mergeCell ref="I16:I18"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="K10:K11"/>
-    <mergeCell ref="C7:C10"/>
-    <mergeCell ref="J7:J10"/>
-    <mergeCell ref="L13:L14"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="K14:K15"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="C15:C18"/>
-    <mergeCell ref="D15:D18"/>
-    <mergeCell ref="L15:L16"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="K16:K17"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="L17:L18"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="A19:A20"/>
-    <mergeCell ref="L19:L20"/>
-    <mergeCell ref="C19:C20"/>
-    <mergeCell ref="D19:D20"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D4"/>
+    <mergeCell ref="E1:E7"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="D5:D10"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="B2:B3"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3181,7 +3255,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="24" customHeight="1"/>
   <sheetData>
     <row r="1" spans="1:12" ht="24" customHeight="1" thickBot="1">
-      <c r="A1" s="33"/>
+      <c r="A1" s="25"/>
       <c r="C1" s="32"/>
       <c r="D1" s="32"/>
       <c r="E1" s="32"/>
@@ -3193,11 +3267,11 @@
       <c r="I1" s="32"/>
       <c r="J1" s="32"/>
       <c r="K1" s="1"/>
-      <c r="L1" s="33"/>
+      <c r="L1" s="25"/>
     </row>
     <row r="2" spans="1:12" ht="24" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A2" s="33"/>
-      <c r="B2" s="36" t="s">
+      <c r="A2" s="25"/>
+      <c r="B2" s="34" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="32"/>
@@ -3208,15 +3282,15 @@
       <c r="H2" s="32"/>
       <c r="I2" s="32"/>
       <c r="J2" s="32"/>
-      <c r="K2" s="38" t="s">
+      <c r="K2" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="L2" s="33"/>
+      <c r="L2" s="25"/>
     </row>
     <row r="3" spans="1:12" ht="24" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A3" s="33"/>
-      <c r="B3" s="49"/>
-      <c r="C3" s="36" t="s">
+      <c r="A3" s="25"/>
+      <c r="B3" s="48"/>
+      <c r="C3" s="34" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="32"/>
@@ -3225,146 +3299,146 @@
       <c r="G3" s="44"/>
       <c r="H3" s="32"/>
       <c r="I3" s="32"/>
-      <c r="J3" s="38" t="s">
+      <c r="J3" s="41" t="s">
         <v>13</v>
       </c>
-      <c r="K3" s="39"/>
-      <c r="L3" s="33"/>
+      <c r="K3" s="42"/>
+      <c r="L3" s="25"/>
     </row>
     <row r="4" spans="1:12" ht="24" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A4" s="33"/>
-      <c r="B4" s="30"/>
-      <c r="C4" s="42"/>
+      <c r="A4" s="25"/>
+      <c r="B4" s="38"/>
+      <c r="C4" s="35"/>
       <c r="D4" s="32"/>
       <c r="E4" s="32"/>
       <c r="F4" s="44"/>
       <c r="G4" s="44"/>
       <c r="H4" s="32"/>
       <c r="I4" s="32"/>
-      <c r="J4" s="41"/>
+      <c r="J4" s="43"/>
       <c r="K4" s="57"/>
-      <c r="L4" s="33"/>
+      <c r="L4" s="25"/>
     </row>
     <row r="5" spans="1:12" ht="24" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A5" s="33"/>
-      <c r="B5" s="48"/>
-      <c r="C5" s="42"/>
-      <c r="D5" s="36" t="s">
+      <c r="A5" s="25"/>
+      <c r="B5" s="50"/>
+      <c r="C5" s="35"/>
+      <c r="D5" s="34" t="s">
         <v>2</v>
       </c>
       <c r="E5" s="32"/>
       <c r="F5" s="44"/>
       <c r="G5" s="44"/>
       <c r="H5" s="32"/>
-      <c r="I5" s="38" t="s">
+      <c r="I5" s="41" t="s">
         <v>2</v>
       </c>
-      <c r="J5" s="41"/>
+      <c r="J5" s="43"/>
       <c r="K5" s="32"/>
-      <c r="L5" s="33"/>
+      <c r="L5" s="25"/>
     </row>
     <row r="6" spans="1:12" ht="24" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A6" s="33"/>
-      <c r="B6" s="36" t="s">
+      <c r="A6" s="25"/>
+      <c r="B6" s="34" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="37"/>
-      <c r="D6" s="42"/>
+      <c r="C6" s="36"/>
+      <c r="D6" s="35"/>
       <c r="E6" s="32"/>
       <c r="F6" s="44"/>
       <c r="G6" s="44"/>
       <c r="H6" s="32"/>
-      <c r="I6" s="41"/>
-      <c r="J6" s="39"/>
-      <c r="K6" s="38" t="s">
+      <c r="I6" s="43"/>
+      <c r="J6" s="42"/>
+      <c r="K6" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="L6" s="33"/>
+      <c r="L6" s="25"/>
     </row>
     <row r="7" spans="1:12" ht="24" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A7" s="33"/>
-      <c r="B7" s="49"/>
-      <c r="C7" s="35"/>
-      <c r="D7" s="42"/>
+      <c r="A7" s="25"/>
+      <c r="B7" s="48"/>
+      <c r="C7" s="31"/>
+      <c r="D7" s="35"/>
       <c r="E7" s="32"/>
       <c r="F7" s="44"/>
       <c r="G7" s="44"/>
       <c r="H7" s="32"/>
-      <c r="I7" s="41"/>
-      <c r="J7" s="35"/>
-      <c r="K7" s="39"/>
-      <c r="L7" s="33"/>
+      <c r="I7" s="43"/>
+      <c r="J7" s="31"/>
+      <c r="K7" s="42"/>
+      <c r="L7" s="25"/>
     </row>
     <row r="8" spans="1:12" ht="24" customHeight="1" thickTop="1">
-      <c r="A8" s="33"/>
-      <c r="B8" s="30"/>
+      <c r="A8" s="25"/>
+      <c r="B8" s="38"/>
       <c r="C8" s="32"/>
-      <c r="D8" s="42"/>
+      <c r="D8" s="35"/>
       <c r="E8" s="51" t="s">
         <v>10</v>
       </c>
-      <c r="F8" s="29" t="s">
+      <c r="F8" s="22" t="s">
         <v>5</v>
       </c>
       <c r="G8" s="54"/>
-      <c r="H8" s="35" t="s">
+      <c r="H8" s="31" t="s">
         <v>10</v>
       </c>
-      <c r="I8" s="41"/>
+      <c r="I8" s="43"/>
       <c r="J8" s="32"/>
       <c r="K8" s="57"/>
-      <c r="L8" s="33"/>
+      <c r="L8" s="25"/>
     </row>
     <row r="9" spans="1:12" ht="24" customHeight="1" thickBot="1">
-      <c r="A9" s="33"/>
-      <c r="B9" s="48"/>
+      <c r="A9" s="25"/>
+      <c r="B9" s="50"/>
       <c r="C9" s="32"/>
-      <c r="D9" s="42"/>
+      <c r="D9" s="35"/>
       <c r="E9" s="52"/>
-      <c r="F9" s="29"/>
+      <c r="F9" s="22"/>
       <c r="G9" s="54"/>
       <c r="H9" s="32"/>
-      <c r="I9" s="41"/>
+      <c r="I9" s="43"/>
       <c r="J9" s="32"/>
       <c r="K9" s="32"/>
-      <c r="L9" s="33"/>
+      <c r="L9" s="25"/>
     </row>
     <row r="10" spans="1:12" ht="24" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A10" s="33"/>
-      <c r="B10" s="36" t="s">
+      <c r="A10" s="25"/>
+      <c r="B10" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="40"/>
-      <c r="D10" s="37"/>
+      <c r="C10" s="33"/>
+      <c r="D10" s="36"/>
       <c r="E10" s="52"/>
-      <c r="F10" s="42"/>
-      <c r="G10" s="41"/>
+      <c r="F10" s="35"/>
+      <c r="G10" s="43"/>
       <c r="H10" s="56"/>
-      <c r="I10" s="39"/>
-      <c r="J10" s="40"/>
-      <c r="K10" s="38" t="s">
+      <c r="I10" s="42"/>
+      <c r="J10" s="33"/>
+      <c r="K10" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="L10" s="33"/>
+      <c r="L10" s="25"/>
     </row>
     <row r="11" spans="1:12" ht="24" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A11" s="33"/>
-      <c r="B11" s="49"/>
-      <c r="C11" s="50"/>
+      <c r="A11" s="25"/>
+      <c r="B11" s="48"/>
+      <c r="C11" s="49"/>
       <c r="D11" s="32"/>
       <c r="E11" s="52"/>
-      <c r="F11" s="37"/>
-      <c r="G11" s="39"/>
+      <c r="F11" s="36"/>
+      <c r="G11" s="42"/>
       <c r="H11" s="56"/>
       <c r="I11" s="32"/>
       <c r="J11" s="32"/>
-      <c r="K11" s="39"/>
-      <c r="L11" s="33"/>
+      <c r="K11" s="42"/>
+      <c r="L11" s="25"/>
     </row>
     <row r="12" spans="1:12" ht="24" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A12" s="33"/>
-      <c r="B12" s="30"/>
-      <c r="C12" s="50"/>
+      <c r="A12" s="25"/>
+      <c r="B12" s="38"/>
+      <c r="C12" s="49"/>
       <c r="D12" s="32"/>
       <c r="E12" s="52"/>
       <c r="F12" s="55" t="s">
@@ -3375,12 +3449,12 @@
       <c r="I12" s="32"/>
       <c r="J12" s="32"/>
       <c r="K12" s="57"/>
-      <c r="L12" s="33"/>
+      <c r="L12" s="25"/>
     </row>
     <row r="13" spans="1:12" ht="24" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A13" s="33"/>
-      <c r="B13" s="48"/>
-      <c r="C13" s="50"/>
+      <c r="A13" s="25"/>
+      <c r="B13" s="50"/>
+      <c r="C13" s="49"/>
       <c r="D13" s="32"/>
       <c r="E13" s="52"/>
       <c r="F13" s="56"/>
@@ -3389,14 +3463,14 @@
       <c r="I13" s="32"/>
       <c r="J13" s="32"/>
       <c r="K13" s="32"/>
-      <c r="L13" s="33"/>
+      <c r="L13" s="25"/>
     </row>
     <row r="14" spans="1:12" ht="24" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A14" s="33"/>
-      <c r="B14" s="36" t="s">
+      <c r="A14" s="25"/>
+      <c r="B14" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="50"/>
+      <c r="C14" s="49"/>
       <c r="D14" s="32"/>
       <c r="E14" s="52"/>
       <c r="F14" s="32"/>
@@ -3404,91 +3478,91 @@
       <c r="H14" s="56"/>
       <c r="I14" s="32"/>
       <c r="J14" s="32"/>
-      <c r="K14" s="38" t="s">
+      <c r="K14" s="41" t="s">
         <v>8</v>
       </c>
-      <c r="L14" s="33"/>
+      <c r="L14" s="25"/>
     </row>
     <row r="15" spans="1:12" ht="24" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A15" s="33"/>
-      <c r="B15" s="49"/>
-      <c r="C15" s="50"/>
-      <c r="D15" s="36" t="s">
+      <c r="A15" s="25"/>
+      <c r="B15" s="48"/>
+      <c r="C15" s="49"/>
+      <c r="D15" s="34" t="s">
         <v>1</v>
       </c>
       <c r="E15" s="52"/>
       <c r="F15" s="32"/>
       <c r="G15" s="32"/>
       <c r="H15" s="56"/>
-      <c r="I15" s="38" t="s">
+      <c r="I15" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="J15" s="35"/>
-      <c r="K15" s="39"/>
-      <c r="L15" s="33"/>
+      <c r="J15" s="31"/>
+      <c r="K15" s="42"/>
+      <c r="L15" s="25"/>
     </row>
     <row r="16" spans="1:12" ht="24" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A16" s="33"/>
-      <c r="B16" s="30"/>
-      <c r="C16" s="50"/>
-      <c r="D16" s="42"/>
+      <c r="A16" s="25"/>
+      <c r="B16" s="38"/>
+      <c r="C16" s="49"/>
+      <c r="D16" s="35"/>
       <c r="E16" s="53"/>
       <c r="F16" s="32"/>
       <c r="G16" s="32"/>
       <c r="H16" s="58"/>
-      <c r="I16" s="41"/>
+      <c r="I16" s="43"/>
       <c r="J16" s="32"/>
       <c r="K16" s="57"/>
-      <c r="L16" s="33"/>
+      <c r="L16" s="25"/>
     </row>
     <row r="17" spans="1:12" ht="24" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A17" s="33"/>
-      <c r="B17" s="48"/>
-      <c r="C17" s="50"/>
-      <c r="D17" s="42"/>
-      <c r="E17" s="35"/>
+      <c r="A17" s="25"/>
+      <c r="B17" s="50"/>
+      <c r="C17" s="49"/>
+      <c r="D17" s="35"/>
+      <c r="E17" s="31"/>
       <c r="F17" s="32"/>
       <c r="G17" s="32"/>
-      <c r="H17" s="35"/>
-      <c r="I17" s="41"/>
+      <c r="H17" s="31"/>
+      <c r="I17" s="43"/>
       <c r="J17" s="32"/>
       <c r="K17" s="32"/>
-      <c r="L17" s="33"/>
+      <c r="L17" s="25"/>
     </row>
     <row r="18" spans="1:12" ht="24" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A18" s="33"/>
-      <c r="B18" s="36" t="s">
+      <c r="A18" s="25"/>
+      <c r="B18" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="C18" s="35"/>
-      <c r="D18" s="37"/>
+      <c r="C18" s="31"/>
+      <c r="D18" s="36"/>
       <c r="E18" s="32"/>
       <c r="F18" s="32"/>
       <c r="G18" s="32"/>
       <c r="H18" s="32"/>
-      <c r="I18" s="39"/>
-      <c r="J18" s="40"/>
-      <c r="K18" s="38" t="s">
+      <c r="I18" s="42"/>
+      <c r="J18" s="33"/>
+      <c r="K18" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="L18" s="33"/>
+      <c r="L18" s="25"/>
     </row>
     <row r="19" spans="1:12" ht="24" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A19" s="33"/>
-      <c r="B19" s="49"/>
-      <c r="C19" s="35"/>
-      <c r="D19" s="35"/>
+      <c r="A19" s="25"/>
+      <c r="B19" s="48"/>
+      <c r="C19" s="31"/>
+      <c r="D19" s="31"/>
       <c r="E19" s="32"/>
       <c r="F19" s="32"/>
       <c r="G19" s="32"/>
       <c r="H19" s="32"/>
-      <c r="I19" s="35"/>
-      <c r="J19" s="35"/>
-      <c r="K19" s="39"/>
-      <c r="L19" s="33"/>
+      <c r="I19" s="31"/>
+      <c r="J19" s="31"/>
+      <c r="K19" s="42"/>
+      <c r="L19" s="25"/>
     </row>
     <row r="20" spans="1:12" ht="24" customHeight="1" thickTop="1">
-      <c r="A20" s="33"/>
+      <c r="A20" s="25"/>
       <c r="B20" s="3"/>
       <c r="C20" s="32"/>
       <c r="D20" s="32"/>
@@ -3499,7 +3573,7 @@
       <c r="I20" s="32"/>
       <c r="J20" s="32"/>
       <c r="K20" s="2"/>
-      <c r="L20" s="33"/>
+      <c r="L20" s="25"/>
     </row>
     <row r="21" spans="1:12" ht="24" customHeight="1">
       <c r="A21" s="4"/>
@@ -3529,19 +3603,49 @@
     </row>
   </sheetData>
   <mergeCells count="72">
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D4"/>
-    <mergeCell ref="E1:E7"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="D5:D10"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="L19:L20"/>
+    <mergeCell ref="L15:L16"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="K16:K17"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="L17:L18"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="K18:K19"/>
+    <mergeCell ref="I19:I20"/>
+    <mergeCell ref="J19:J20"/>
+    <mergeCell ref="D15:D18"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="D19:D20"/>
+    <mergeCell ref="E17:E20"/>
+    <mergeCell ref="H17:H20"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="C11:C14"/>
+    <mergeCell ref="D11:D14"/>
+    <mergeCell ref="I11:I14"/>
+    <mergeCell ref="K12:K13"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="K14:K15"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="C15:C18"/>
+    <mergeCell ref="I15:I18"/>
+    <mergeCell ref="J15:J18"/>
+    <mergeCell ref="H8:H16"/>
+    <mergeCell ref="K8:K9"/>
+    <mergeCell ref="J11:J14"/>
+    <mergeCell ref="L11:L12"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="F12:G13"/>
+    <mergeCell ref="F14:G20"/>
+    <mergeCell ref="L9:L10"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="K10:K11"/>
+    <mergeCell ref="C7:C10"/>
+    <mergeCell ref="J7:J10"/>
+    <mergeCell ref="L13:L14"/>
     <mergeCell ref="I1:I4"/>
     <mergeCell ref="J1:J2"/>
     <mergeCell ref="C3:C6"/>
@@ -3558,49 +3662,19 @@
     <mergeCell ref="L7:L8"/>
     <mergeCell ref="E8:E16"/>
     <mergeCell ref="F8:G9"/>
-    <mergeCell ref="L11:L12"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="F12:G13"/>
-    <mergeCell ref="F14:G20"/>
-    <mergeCell ref="L9:L10"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="K10:K11"/>
-    <mergeCell ref="C7:C10"/>
-    <mergeCell ref="J7:J10"/>
-    <mergeCell ref="L13:L14"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="C11:C14"/>
-    <mergeCell ref="D11:D14"/>
-    <mergeCell ref="I11:I14"/>
-    <mergeCell ref="K12:K13"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="K14:K15"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="C15:C18"/>
-    <mergeCell ref="I15:I18"/>
-    <mergeCell ref="J15:J18"/>
-    <mergeCell ref="H8:H16"/>
-    <mergeCell ref="K8:K9"/>
-    <mergeCell ref="J11:J14"/>
-    <mergeCell ref="A19:A20"/>
-    <mergeCell ref="L19:L20"/>
-    <mergeCell ref="L15:L16"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="K16:K17"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="L17:L18"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="K18:K19"/>
-    <mergeCell ref="I19:I20"/>
-    <mergeCell ref="J19:J20"/>
-    <mergeCell ref="D15:D18"/>
-    <mergeCell ref="C19:C20"/>
-    <mergeCell ref="D19:D20"/>
-    <mergeCell ref="E17:E20"/>
-    <mergeCell ref="H17:H20"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D4"/>
+    <mergeCell ref="E1:E7"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="D5:D10"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="A9:A10"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3614,7 +3688,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="22" customHeight="1"/>
   <sheetData>
     <row r="1" spans="1:12" ht="22" customHeight="1" thickBot="1">
-      <c r="A1" s="33"/>
+      <c r="A1" s="25"/>
       <c r="C1" s="32"/>
       <c r="D1" s="32"/>
       <c r="E1" s="32"/>
@@ -3626,11 +3700,11 @@
       <c r="I1" s="32"/>
       <c r="J1" s="32"/>
       <c r="K1" s="1"/>
-      <c r="L1" s="33"/>
+      <c r="L1" s="25"/>
     </row>
     <row r="2" spans="1:12" ht="22" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A2" s="33"/>
-      <c r="B2" s="36" t="s">
+      <c r="A2" s="25"/>
+      <c r="B2" s="34" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="32"/>
@@ -3641,15 +3715,15 @@
       <c r="H2" s="32"/>
       <c r="I2" s="32"/>
       <c r="J2" s="32"/>
-      <c r="K2" s="38" t="s">
+      <c r="K2" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="L2" s="33"/>
+      <c r="L2" s="25"/>
     </row>
     <row r="3" spans="1:12" ht="22" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A3" s="33"/>
-      <c r="B3" s="49"/>
-      <c r="C3" s="36" t="s">
+      <c r="A3" s="25"/>
+      <c r="B3" s="48"/>
+      <c r="C3" s="34" t="s">
         <v>1</v>
       </c>
       <c r="D3" s="32"/>
@@ -3658,146 +3732,146 @@
       <c r="G3" s="44"/>
       <c r="H3" s="32"/>
       <c r="I3" s="32"/>
-      <c r="J3" s="38" t="s">
+      <c r="J3" s="41" t="s">
         <v>13</v>
       </c>
-      <c r="K3" s="39"/>
-      <c r="L3" s="33"/>
+      <c r="K3" s="42"/>
+      <c r="L3" s="25"/>
     </row>
     <row r="4" spans="1:12" ht="22" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A4" s="33"/>
-      <c r="B4" s="30"/>
-      <c r="C4" s="42"/>
+      <c r="A4" s="25"/>
+      <c r="B4" s="38"/>
+      <c r="C4" s="35"/>
       <c r="D4" s="32"/>
       <c r="E4" s="32"/>
       <c r="F4" s="44"/>
       <c r="G4" s="44"/>
       <c r="H4" s="32"/>
       <c r="I4" s="32"/>
-      <c r="J4" s="41"/>
+      <c r="J4" s="43"/>
       <c r="K4" s="57"/>
-      <c r="L4" s="33"/>
+      <c r="L4" s="25"/>
     </row>
     <row r="5" spans="1:12" ht="22" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A5" s="33"/>
-      <c r="B5" s="48"/>
-      <c r="C5" s="42"/>
-      <c r="D5" s="36" t="s">
+      <c r="A5" s="25"/>
+      <c r="B5" s="50"/>
+      <c r="C5" s="35"/>
+      <c r="D5" s="34" t="s">
         <v>2</v>
       </c>
       <c r="E5" s="32"/>
       <c r="F5" s="44"/>
       <c r="G5" s="44"/>
       <c r="H5" s="32"/>
-      <c r="I5" s="38" t="s">
+      <c r="I5" s="41" t="s">
         <v>2</v>
       </c>
-      <c r="J5" s="41"/>
+      <c r="J5" s="43"/>
       <c r="K5" s="32"/>
-      <c r="L5" s="33"/>
+      <c r="L5" s="25"/>
     </row>
     <row r="6" spans="1:12" ht="22" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A6" s="33"/>
-      <c r="B6" s="36" t="s">
+      <c r="A6" s="25"/>
+      <c r="B6" s="34" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="37"/>
-      <c r="D6" s="42"/>
+      <c r="C6" s="36"/>
+      <c r="D6" s="35"/>
       <c r="E6" s="32"/>
       <c r="F6" s="44"/>
       <c r="G6" s="44"/>
       <c r="H6" s="32"/>
-      <c r="I6" s="41"/>
-      <c r="J6" s="39"/>
-      <c r="K6" s="38" t="s">
+      <c r="I6" s="43"/>
+      <c r="J6" s="42"/>
+      <c r="K6" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="L6" s="33"/>
+      <c r="L6" s="25"/>
     </row>
     <row r="7" spans="1:12" ht="22" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A7" s="33"/>
-      <c r="B7" s="49"/>
-      <c r="C7" s="35"/>
-      <c r="D7" s="42"/>
+      <c r="A7" s="25"/>
+      <c r="B7" s="48"/>
+      <c r="C7" s="31"/>
+      <c r="D7" s="35"/>
       <c r="E7" s="32"/>
       <c r="F7" s="44"/>
       <c r="G7" s="44"/>
       <c r="H7" s="32"/>
-      <c r="I7" s="41"/>
-      <c r="J7" s="35"/>
-      <c r="K7" s="39"/>
-      <c r="L7" s="33"/>
+      <c r="I7" s="43"/>
+      <c r="J7" s="31"/>
+      <c r="K7" s="42"/>
+      <c r="L7" s="25"/>
     </row>
     <row r="8" spans="1:12" ht="22" customHeight="1" thickTop="1">
-      <c r="A8" s="33"/>
-      <c r="B8" s="30"/>
+      <c r="A8" s="25"/>
+      <c r="B8" s="38"/>
       <c r="C8" s="32"/>
-      <c r="D8" s="42"/>
+      <c r="D8" s="35"/>
       <c r="E8" s="51" t="s">
         <v>4</v>
       </c>
-      <c r="F8" s="29" t="s">
+      <c r="F8" s="22" t="s">
         <v>5</v>
       </c>
       <c r="G8" s="54"/>
-      <c r="H8" s="35" t="s">
+      <c r="H8" s="31" t="s">
         <v>10</v>
       </c>
-      <c r="I8" s="41"/>
+      <c r="I8" s="43"/>
       <c r="J8" s="32"/>
       <c r="K8" s="57"/>
-      <c r="L8" s="33"/>
+      <c r="L8" s="25"/>
     </row>
     <row r="9" spans="1:12" ht="22" customHeight="1" thickBot="1">
-      <c r="A9" s="33"/>
-      <c r="B9" s="48"/>
+      <c r="A9" s="25"/>
+      <c r="B9" s="50"/>
       <c r="C9" s="32"/>
-      <c r="D9" s="42"/>
+      <c r="D9" s="35"/>
       <c r="E9" s="52"/>
-      <c r="F9" s="29"/>
+      <c r="F9" s="22"/>
       <c r="G9" s="54"/>
       <c r="H9" s="32"/>
-      <c r="I9" s="41"/>
+      <c r="I9" s="43"/>
       <c r="J9" s="32"/>
       <c r="K9" s="32"/>
-      <c r="L9" s="33"/>
+      <c r="L9" s="25"/>
     </row>
     <row r="10" spans="1:12" ht="22" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A10" s="33"/>
-      <c r="B10" s="36" t="s">
+      <c r="A10" s="25"/>
+      <c r="B10" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="40"/>
-      <c r="D10" s="37"/>
+      <c r="C10" s="33"/>
+      <c r="D10" s="36"/>
       <c r="E10" s="52"/>
       <c r="F10" s="8"/>
-      <c r="G10" s="41"/>
+      <c r="G10" s="43"/>
       <c r="H10" s="56"/>
-      <c r="I10" s="39"/>
-      <c r="J10" s="40"/>
-      <c r="K10" s="38" t="s">
+      <c r="I10" s="42"/>
+      <c r="J10" s="33"/>
+      <c r="K10" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="L10" s="33"/>
+      <c r="L10" s="25"/>
     </row>
     <row r="11" spans="1:12" ht="22" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A11" s="33"/>
-      <c r="B11" s="49"/>
-      <c r="C11" s="50"/>
+      <c r="A11" s="25"/>
+      <c r="B11" s="48"/>
+      <c r="C11" s="49"/>
       <c r="D11" s="32"/>
       <c r="E11" s="52"/>
       <c r="F11" s="9"/>
-      <c r="G11" s="39"/>
+      <c r="G11" s="42"/>
       <c r="H11" s="56"/>
       <c r="I11" s="32"/>
       <c r="J11" s="32"/>
-      <c r="K11" s="39"/>
-      <c r="L11" s="33"/>
+      <c r="K11" s="42"/>
+      <c r="L11" s="25"/>
     </row>
     <row r="12" spans="1:12" ht="22" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A12" s="33"/>
-      <c r="B12" s="30"/>
-      <c r="C12" s="50"/>
+      <c r="A12" s="25"/>
+      <c r="B12" s="38"/>
+      <c r="C12" s="49"/>
       <c r="D12" s="32"/>
       <c r="E12" s="52"/>
       <c r="F12" s="55" t="s">
@@ -3808,12 +3882,12 @@
       <c r="I12" s="32"/>
       <c r="J12" s="32"/>
       <c r="K12" s="57"/>
-      <c r="L12" s="33"/>
+      <c r="L12" s="25"/>
     </row>
     <row r="13" spans="1:12" ht="22" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A13" s="33"/>
-      <c r="B13" s="48"/>
-      <c r="C13" s="50"/>
+      <c r="A13" s="25"/>
+      <c r="B13" s="50"/>
+      <c r="C13" s="49"/>
       <c r="D13" s="32"/>
       <c r="E13" s="52"/>
       <c r="F13" s="56"/>
@@ -3822,14 +3896,14 @@
       <c r="I13" s="32"/>
       <c r="J13" s="32"/>
       <c r="K13" s="32"/>
-      <c r="L13" s="33"/>
+      <c r="L13" s="25"/>
     </row>
     <row r="14" spans="1:12" ht="22" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A14" s="33"/>
-      <c r="B14" s="36" t="s">
+      <c r="A14" s="25"/>
+      <c r="B14" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="50"/>
+      <c r="C14" s="49"/>
       <c r="D14" s="32"/>
       <c r="E14" s="52"/>
       <c r="F14" s="32"/>
@@ -3837,95 +3911,95 @@
       <c r="H14" s="56"/>
       <c r="I14" s="32"/>
       <c r="J14" s="32"/>
-      <c r="K14" s="38" t="s">
+      <c r="K14" s="41" t="s">
         <v>8</v>
       </c>
-      <c r="L14" s="33"/>
+      <c r="L14" s="25"/>
     </row>
     <row r="15" spans="1:12" ht="22" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A15" s="33"/>
-      <c r="B15" s="49"/>
-      <c r="C15" s="50"/>
-      <c r="D15" s="36" t="s">
+      <c r="A15" s="25"/>
+      <c r="B15" s="48"/>
+      <c r="C15" s="49"/>
+      <c r="D15" s="34" t="s">
         <v>9</v>
       </c>
       <c r="E15" s="52"/>
       <c r="F15" s="32"/>
       <c r="G15" s="32"/>
       <c r="H15" s="56"/>
-      <c r="I15" s="38" t="s">
+      <c r="I15" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="J15" s="35"/>
-      <c r="K15" s="39"/>
-      <c r="L15" s="33"/>
+      <c r="J15" s="31"/>
+      <c r="K15" s="42"/>
+      <c r="L15" s="25"/>
     </row>
     <row r="16" spans="1:12" ht="22" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A16" s="33"/>
-      <c r="B16" s="30"/>
-      <c r="C16" s="50"/>
-      <c r="D16" s="42"/>
+      <c r="A16" s="25"/>
+      <c r="B16" s="38"/>
+      <c r="C16" s="49"/>
+      <c r="D16" s="35"/>
       <c r="E16" s="53"/>
       <c r="F16" s="32"/>
       <c r="G16" s="32"/>
       <c r="H16" s="58"/>
-      <c r="I16" s="41"/>
+      <c r="I16" s="43"/>
       <c r="J16" s="32"/>
       <c r="K16" s="57"/>
-      <c r="L16" s="33"/>
+      <c r="L16" s="25"/>
     </row>
     <row r="17" spans="1:12" ht="22" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A17" s="33"/>
-      <c r="B17" s="48"/>
-      <c r="C17" s="50"/>
-      <c r="D17" s="42"/>
+      <c r="A17" s="25"/>
+      <c r="B17" s="50"/>
+      <c r="C17" s="49"/>
+      <c r="D17" s="35"/>
       <c r="E17" s="32"/>
       <c r="F17" s="32"/>
       <c r="G17" s="32"/>
       <c r="H17" s="32"/>
-      <c r="I17" s="41"/>
+      <c r="I17" s="43"/>
       <c r="J17" s="32"/>
       <c r="K17" s="32"/>
-      <c r="L17" s="33"/>
+      <c r="L17" s="25"/>
     </row>
     <row r="18" spans="1:12" ht="22" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A18" s="33"/>
-      <c r="B18" s="36" t="s">
+      <c r="A18" s="25"/>
+      <c r="B18" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="C18" s="35"/>
-      <c r="D18" s="42"/>
+      <c r="C18" s="31"/>
+      <c r="D18" s="35"/>
       <c r="E18" s="32"/>
       <c r="F18" s="32"/>
       <c r="G18" s="32"/>
       <c r="H18" s="32"/>
-      <c r="I18" s="39"/>
-      <c r="J18" s="40"/>
-      <c r="K18" s="38" t="s">
+      <c r="I18" s="42"/>
+      <c r="J18" s="33"/>
+      <c r="K18" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="L18" s="33"/>
+      <c r="L18" s="25"/>
     </row>
     <row r="19" spans="1:12" ht="22" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A19" s="33"/>
-      <c r="B19" s="49"/>
-      <c r="C19" s="36" t="s">
+      <c r="A19" s="25"/>
+      <c r="B19" s="48"/>
+      <c r="C19" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="D19" s="37"/>
+      <c r="D19" s="36"/>
       <c r="E19" s="32"/>
       <c r="F19" s="32"/>
       <c r="G19" s="32"/>
       <c r="H19" s="32"/>
-      <c r="I19" s="35"/>
-      <c r="J19" s="35"/>
-      <c r="K19" s="39"/>
-      <c r="L19" s="33"/>
+      <c r="I19" s="31"/>
+      <c r="J19" s="31"/>
+      <c r="K19" s="42"/>
+      <c r="L19" s="25"/>
     </row>
     <row r="20" spans="1:12" ht="22" customHeight="1" thickTop="1">
-      <c r="A20" s="33"/>
-      <c r="B20" s="43"/>
-      <c r="C20" s="42"/>
+      <c r="A20" s="25"/>
+      <c r="B20" s="40"/>
+      <c r="C20" s="35"/>
       <c r="D20" s="32"/>
       <c r="E20" s="32"/>
       <c r="F20" s="32"/>
@@ -3933,13 +4007,13 @@
       <c r="H20" s="32"/>
       <c r="I20" s="32"/>
       <c r="J20" s="32"/>
-      <c r="K20" s="35"/>
-      <c r="L20" s="33"/>
+      <c r="K20" s="31"/>
+      <c r="L20" s="25"/>
     </row>
     <row r="21" spans="1:12" ht="22" customHeight="1" thickBot="1">
-      <c r="A21" s="33"/>
-      <c r="B21" s="31"/>
-      <c r="C21" s="37"/>
+      <c r="A21" s="25"/>
+      <c r="B21" s="39"/>
+      <c r="C21" s="36"/>
       <c r="D21" s="32"/>
       <c r="E21" s="32"/>
       <c r="F21" s="32"/>
@@ -3948,10 +4022,10 @@
       <c r="I21" s="32"/>
       <c r="J21" s="32"/>
       <c r="K21" s="32"/>
-      <c r="L21" s="33"/>
+      <c r="L21" s="25"/>
     </row>
     <row r="22" spans="1:12" ht="22" customHeight="1" thickTop="1">
-      <c r="A22" s="33"/>
+      <c r="A22" s="25"/>
       <c r="C22" s="1"/>
       <c r="D22" s="32"/>
       <c r="E22" s="32"/>
@@ -3961,10 +4035,69 @@
       <c r="I22" s="32"/>
       <c r="J22" s="32"/>
       <c r="K22" s="32"/>
-      <c r="L22" s="33"/>
+      <c r="L22" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="75">
+    <mergeCell ref="I19:I22"/>
+    <mergeCell ref="J19:J22"/>
+    <mergeCell ref="K20:K22"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="C19:C21"/>
+    <mergeCell ref="J15:J18"/>
+    <mergeCell ref="L15:L16"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="K16:K17"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="E17:E22"/>
+    <mergeCell ref="H17:H22"/>
+    <mergeCell ref="L17:L18"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="K18:K19"/>
+    <mergeCell ref="L19:L20"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="D20:D22"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="L21:L22"/>
+    <mergeCell ref="I15:I18"/>
+    <mergeCell ref="L9:L10"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="K10:K11"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="C11:C14"/>
+    <mergeCell ref="D11:D14"/>
+    <mergeCell ref="I11:I14"/>
+    <mergeCell ref="K12:K13"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="L13:L14"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="K14:K15"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="C15:C18"/>
+    <mergeCell ref="D15:D19"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="L7:L8"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="E8:E16"/>
+    <mergeCell ref="F8:G9"/>
+    <mergeCell ref="H8:H16"/>
+    <mergeCell ref="K8:K9"/>
+    <mergeCell ref="J11:J14"/>
+    <mergeCell ref="L11:L12"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="F12:G13"/>
+    <mergeCell ref="F14:G22"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="C7:C10"/>
+    <mergeCell ref="J7:J10"/>
+    <mergeCell ref="I1:I4"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="C3:C6"/>
+    <mergeCell ref="J3:J6"/>
     <mergeCell ref="L3:L4"/>
     <mergeCell ref="B4:B5"/>
     <mergeCell ref="A1:A2"/>
@@ -3981,65 +4114,6 @@
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="K6:K7"/>
     <mergeCell ref="A7:A8"/>
-    <mergeCell ref="C7:C10"/>
-    <mergeCell ref="J7:J10"/>
-    <mergeCell ref="I1:I4"/>
-    <mergeCell ref="J1:J2"/>
-    <mergeCell ref="C3:C6"/>
-    <mergeCell ref="J3:J6"/>
-    <mergeCell ref="L1:L2"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="K2:K3"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="L7:L8"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="E8:E16"/>
-    <mergeCell ref="F8:G9"/>
-    <mergeCell ref="H8:H16"/>
-    <mergeCell ref="K8:K9"/>
-    <mergeCell ref="J11:J14"/>
-    <mergeCell ref="L11:L12"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="F12:G13"/>
-    <mergeCell ref="F14:G22"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="L9:L10"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="K10:K11"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="C11:C14"/>
-    <mergeCell ref="D11:D14"/>
-    <mergeCell ref="I11:I14"/>
-    <mergeCell ref="K12:K13"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="L13:L14"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="K14:K15"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="C15:C18"/>
-    <mergeCell ref="D15:D19"/>
-    <mergeCell ref="J15:J18"/>
-    <mergeCell ref="L15:L16"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="K16:K17"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="E17:E22"/>
-    <mergeCell ref="H17:H22"/>
-    <mergeCell ref="L17:L18"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="K18:K19"/>
-    <mergeCell ref="L19:L20"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="D20:D22"/>
-    <mergeCell ref="A21:A22"/>
-    <mergeCell ref="L21:L22"/>
-    <mergeCell ref="I15:I18"/>
-    <mergeCell ref="I19:I22"/>
-    <mergeCell ref="J19:J22"/>
-    <mergeCell ref="K20:K22"/>
-    <mergeCell ref="A19:A20"/>
-    <mergeCell ref="C19:C21"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4054,7 +4128,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="22" customHeight="1"/>
   <sheetData>
     <row r="1" spans="1:12" ht="22" customHeight="1" thickBot="1">
-      <c r="A1" s="33"/>
+      <c r="A1" s="25"/>
       <c r="C1" s="32"/>
       <c r="D1" s="32"/>
       <c r="E1" s="32"/>
@@ -4066,11 +4140,11 @@
       <c r="I1" s="32"/>
       <c r="J1" s="32"/>
       <c r="K1" s="1"/>
-      <c r="L1" s="33"/>
+      <c r="L1" s="25"/>
     </row>
     <row r="2" spans="1:12" ht="22" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A2" s="33"/>
-      <c r="B2" s="36" t="s">
+      <c r="A2" s="25"/>
+      <c r="B2" s="34" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="32"/>
@@ -4081,15 +4155,15 @@
       <c r="H2" s="32"/>
       <c r="I2" s="32"/>
       <c r="J2" s="32"/>
-      <c r="K2" s="38" t="s">
+      <c r="K2" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="L2" s="33"/>
+      <c r="L2" s="25"/>
     </row>
     <row r="3" spans="1:12" ht="22" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A3" s="33"/>
-      <c r="B3" s="49"/>
-      <c r="C3" s="36" t="s">
+      <c r="A3" s="25"/>
+      <c r="B3" s="48"/>
+      <c r="C3" s="34" t="s">
         <v>1</v>
       </c>
       <c r="D3" s="32"/>
@@ -4098,146 +4172,146 @@
       <c r="G3" s="44"/>
       <c r="H3" s="32"/>
       <c r="I3" s="32"/>
-      <c r="J3" s="38" t="s">
+      <c r="J3" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="K3" s="39"/>
-      <c r="L3" s="33"/>
+      <c r="K3" s="42"/>
+      <c r="L3" s="25"/>
     </row>
     <row r="4" spans="1:12" ht="22" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A4" s="33"/>
-      <c r="B4" s="30"/>
-      <c r="C4" s="42"/>
+      <c r="A4" s="25"/>
+      <c r="B4" s="38"/>
+      <c r="C4" s="35"/>
       <c r="D4" s="32"/>
       <c r="E4" s="32"/>
       <c r="F4" s="44"/>
       <c r="G4" s="44"/>
       <c r="H4" s="32"/>
       <c r="I4" s="32"/>
-      <c r="J4" s="41"/>
+      <c r="J4" s="43"/>
       <c r="K4" s="57"/>
-      <c r="L4" s="33"/>
+      <c r="L4" s="25"/>
     </row>
     <row r="5" spans="1:12" ht="22" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A5" s="33"/>
-      <c r="B5" s="48"/>
-      <c r="C5" s="42"/>
-      <c r="D5" s="36" t="s">
+      <c r="A5" s="25"/>
+      <c r="B5" s="50"/>
+      <c r="C5" s="35"/>
+      <c r="D5" s="34" t="s">
         <v>2</v>
       </c>
       <c r="E5" s="32"/>
       <c r="F5" s="44"/>
       <c r="G5" s="44"/>
       <c r="H5" s="32"/>
-      <c r="I5" s="38" t="s">
+      <c r="I5" s="41" t="s">
         <v>2</v>
       </c>
-      <c r="J5" s="41"/>
+      <c r="J5" s="43"/>
       <c r="K5" s="32"/>
-      <c r="L5" s="33"/>
+      <c r="L5" s="25"/>
     </row>
     <row r="6" spans="1:12" ht="22" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A6" s="33"/>
-      <c r="B6" s="36" t="s">
+      <c r="A6" s="25"/>
+      <c r="B6" s="34" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="37"/>
-      <c r="D6" s="42"/>
+      <c r="C6" s="36"/>
+      <c r="D6" s="35"/>
       <c r="E6" s="32"/>
       <c r="F6" s="44"/>
       <c r="G6" s="44"/>
       <c r="H6" s="32"/>
-      <c r="I6" s="41"/>
-      <c r="J6" s="39"/>
-      <c r="K6" s="38" t="s">
+      <c r="I6" s="43"/>
+      <c r="J6" s="42"/>
+      <c r="K6" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="L6" s="33"/>
+      <c r="L6" s="25"/>
     </row>
     <row r="7" spans="1:12" ht="22" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A7" s="33"/>
-      <c r="B7" s="49"/>
-      <c r="C7" s="35"/>
-      <c r="D7" s="42"/>
+      <c r="A7" s="25"/>
+      <c r="B7" s="48"/>
+      <c r="C7" s="31"/>
+      <c r="D7" s="35"/>
       <c r="E7" s="32"/>
       <c r="F7" s="44"/>
       <c r="G7" s="44"/>
       <c r="H7" s="32"/>
-      <c r="I7" s="41"/>
-      <c r="J7" s="35"/>
-      <c r="K7" s="39"/>
-      <c r="L7" s="33"/>
+      <c r="I7" s="43"/>
+      <c r="J7" s="31"/>
+      <c r="K7" s="42"/>
+      <c r="L7" s="25"/>
     </row>
     <row r="8" spans="1:12" ht="22" customHeight="1" thickTop="1">
-      <c r="A8" s="33"/>
-      <c r="B8" s="30"/>
+      <c r="A8" s="25"/>
+      <c r="B8" s="38"/>
       <c r="C8" s="32"/>
-      <c r="D8" s="42"/>
+      <c r="D8" s="35"/>
       <c r="E8" s="51" t="s">
         <v>4</v>
       </c>
-      <c r="F8" s="29" t="s">
+      <c r="F8" s="22" t="s">
         <v>5</v>
       </c>
       <c r="G8" s="54"/>
-      <c r="H8" s="35" t="s">
+      <c r="H8" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="I8" s="41"/>
+      <c r="I8" s="43"/>
       <c r="J8" s="32"/>
       <c r="K8" s="57"/>
-      <c r="L8" s="33"/>
+      <c r="L8" s="25"/>
     </row>
     <row r="9" spans="1:12" ht="22" customHeight="1" thickBot="1">
-      <c r="A9" s="33"/>
-      <c r="B9" s="48"/>
+      <c r="A9" s="25"/>
+      <c r="B9" s="50"/>
       <c r="C9" s="32"/>
-      <c r="D9" s="42"/>
+      <c r="D9" s="35"/>
       <c r="E9" s="52"/>
-      <c r="F9" s="29"/>
+      <c r="F9" s="22"/>
       <c r="G9" s="54"/>
       <c r="H9" s="32"/>
-      <c r="I9" s="41"/>
+      <c r="I9" s="43"/>
       <c r="J9" s="32"/>
       <c r="K9" s="32"/>
-      <c r="L9" s="33"/>
+      <c r="L9" s="25"/>
     </row>
     <row r="10" spans="1:12" ht="22" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A10" s="33"/>
-      <c r="B10" s="36" t="s">
+      <c r="A10" s="25"/>
+      <c r="B10" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="40"/>
-      <c r="D10" s="37"/>
+      <c r="C10" s="33"/>
+      <c r="D10" s="36"/>
       <c r="E10" s="52"/>
-      <c r="F10" s="42"/>
-      <c r="G10" s="41"/>
+      <c r="F10" s="35"/>
+      <c r="G10" s="43"/>
       <c r="H10" s="56"/>
-      <c r="I10" s="39"/>
-      <c r="J10" s="40"/>
-      <c r="K10" s="38" t="s">
+      <c r="I10" s="42"/>
+      <c r="J10" s="33"/>
+      <c r="K10" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="L10" s="33"/>
+      <c r="L10" s="25"/>
     </row>
     <row r="11" spans="1:12" ht="22" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A11" s="33"/>
-      <c r="B11" s="49"/>
-      <c r="C11" s="50"/>
+      <c r="A11" s="25"/>
+      <c r="B11" s="48"/>
+      <c r="C11" s="49"/>
       <c r="D11" s="32"/>
       <c r="E11" s="52"/>
-      <c r="F11" s="37"/>
-      <c r="G11" s="39"/>
+      <c r="F11" s="36"/>
+      <c r="G11" s="42"/>
       <c r="H11" s="56"/>
       <c r="I11" s="32"/>
       <c r="J11" s="32"/>
-      <c r="K11" s="39"/>
-      <c r="L11" s="33"/>
+      <c r="K11" s="42"/>
+      <c r="L11" s="25"/>
     </row>
     <row r="12" spans="1:12" ht="22" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A12" s="33"/>
-      <c r="B12" s="30"/>
-      <c r="C12" s="50"/>
+      <c r="A12" s="25"/>
+      <c r="B12" s="38"/>
+      <c r="C12" s="49"/>
       <c r="D12" s="32"/>
       <c r="E12" s="52"/>
       <c r="F12" s="55" t="s">
@@ -4248,12 +4322,12 @@
       <c r="I12" s="32"/>
       <c r="J12" s="32"/>
       <c r="K12" s="57"/>
-      <c r="L12" s="33"/>
+      <c r="L12" s="25"/>
     </row>
     <row r="13" spans="1:12" ht="22" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A13" s="33"/>
-      <c r="B13" s="48"/>
-      <c r="C13" s="50"/>
+      <c r="A13" s="25"/>
+      <c r="B13" s="50"/>
+      <c r="C13" s="49"/>
       <c r="D13" s="32"/>
       <c r="E13" s="52"/>
       <c r="F13" s="56"/>
@@ -4262,14 +4336,14 @@
       <c r="I13" s="32"/>
       <c r="J13" s="32"/>
       <c r="K13" s="32"/>
-      <c r="L13" s="33"/>
+      <c r="L13" s="25"/>
     </row>
     <row r="14" spans="1:12" ht="22" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A14" s="33"/>
-      <c r="B14" s="36" t="s">
+      <c r="A14" s="25"/>
+      <c r="B14" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="50"/>
+      <c r="C14" s="49"/>
       <c r="D14" s="32"/>
       <c r="E14" s="52"/>
       <c r="F14" s="32"/>
@@ -4277,123 +4351,123 @@
       <c r="H14" s="56"/>
       <c r="I14" s="32"/>
       <c r="J14" s="32"/>
-      <c r="K14" s="38" t="s">
+      <c r="K14" s="41" t="s">
         <v>8</v>
       </c>
-      <c r="L14" s="33"/>
+      <c r="L14" s="25"/>
     </row>
     <row r="15" spans="1:12" ht="22" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A15" s="33"/>
-      <c r="B15" s="49"/>
-      <c r="C15" s="50"/>
-      <c r="D15" s="36" t="s">
+      <c r="A15" s="25"/>
+      <c r="B15" s="48"/>
+      <c r="C15" s="49"/>
+      <c r="D15" s="34" t="s">
         <v>9</v>
       </c>
       <c r="E15" s="52"/>
       <c r="F15" s="32"/>
       <c r="G15" s="32"/>
       <c r="H15" s="56"/>
-      <c r="I15" s="38" t="s">
+      <c r="I15" s="41" t="s">
         <v>10</v>
       </c>
-      <c r="J15" s="35"/>
-      <c r="K15" s="39"/>
-      <c r="L15" s="33"/>
+      <c r="J15" s="31"/>
+      <c r="K15" s="42"/>
+      <c r="L15" s="25"/>
     </row>
     <row r="16" spans="1:12" ht="22" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A16" s="33"/>
-      <c r="B16" s="30"/>
-      <c r="C16" s="50"/>
-      <c r="D16" s="42"/>
+      <c r="A16" s="25"/>
+      <c r="B16" s="38"/>
+      <c r="C16" s="49"/>
+      <c r="D16" s="35"/>
       <c r="E16" s="53"/>
       <c r="F16" s="32"/>
       <c r="G16" s="32"/>
       <c r="H16" s="58"/>
-      <c r="I16" s="41"/>
+      <c r="I16" s="43"/>
       <c r="J16" s="32"/>
       <c r="K16" s="57"/>
-      <c r="L16" s="33"/>
+      <c r="L16" s="25"/>
     </row>
     <row r="17" spans="1:12" ht="22" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A17" s="33"/>
-      <c r="B17" s="48"/>
-      <c r="C17" s="50"/>
-      <c r="D17" s="42"/>
+      <c r="A17" s="25"/>
+      <c r="B17" s="50"/>
+      <c r="C17" s="49"/>
+      <c r="D17" s="35"/>
       <c r="E17" s="32"/>
       <c r="F17" s="32"/>
       <c r="G17" s="32"/>
       <c r="H17" s="32"/>
-      <c r="I17" s="41"/>
+      <c r="I17" s="43"/>
       <c r="J17" s="32"/>
       <c r="K17" s="32"/>
-      <c r="L17" s="33"/>
+      <c r="L17" s="25"/>
     </row>
     <row r="18" spans="1:12" ht="22" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A18" s="33"/>
-      <c r="B18" s="36" t="s">
+      <c r="A18" s="25"/>
+      <c r="B18" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="C18" s="35"/>
-      <c r="D18" s="42"/>
+      <c r="C18" s="31"/>
+      <c r="D18" s="35"/>
       <c r="E18" s="32"/>
       <c r="F18" s="32"/>
       <c r="G18" s="32"/>
       <c r="H18" s="32"/>
-      <c r="I18" s="41"/>
-      <c r="J18" s="40"/>
-      <c r="K18" s="38" t="s">
+      <c r="I18" s="43"/>
+      <c r="J18" s="33"/>
+      <c r="K18" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="L18" s="33"/>
+      <c r="L18" s="25"/>
     </row>
     <row r="19" spans="1:12" ht="22" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A19" s="33"/>
-      <c r="B19" s="49"/>
-      <c r="C19" s="36" t="s">
+      <c r="A19" s="25"/>
+      <c r="B19" s="48"/>
+      <c r="C19" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="D19" s="37"/>
+      <c r="D19" s="36"/>
       <c r="E19" s="32"/>
       <c r="F19" s="32"/>
       <c r="G19" s="32"/>
       <c r="H19" s="32"/>
-      <c r="I19" s="39"/>
-      <c r="J19" s="38" t="s">
+      <c r="I19" s="42"/>
+      <c r="J19" s="41" t="s">
         <v>13</v>
       </c>
-      <c r="K19" s="39"/>
-      <c r="L19" s="33"/>
+      <c r="K19" s="42"/>
+      <c r="L19" s="25"/>
     </row>
     <row r="20" spans="1:12" ht="22" customHeight="1" thickTop="1">
-      <c r="A20" s="33"/>
-      <c r="B20" s="43"/>
-      <c r="C20" s="42"/>
+      <c r="A20" s="25"/>
+      <c r="B20" s="40"/>
+      <c r="C20" s="35"/>
       <c r="D20" s="32"/>
       <c r="E20" s="32"/>
       <c r="F20" s="32"/>
       <c r="G20" s="32"/>
       <c r="H20" s="32"/>
       <c r="I20" s="32"/>
-      <c r="J20" s="41"/>
+      <c r="J20" s="43"/>
       <c r="K20" s="32"/>
-      <c r="L20" s="33"/>
+      <c r="L20" s="25"/>
     </row>
     <row r="21" spans="1:12" ht="22" customHeight="1" thickBot="1">
-      <c r="A21" s="33"/>
-      <c r="B21" s="31"/>
-      <c r="C21" s="37"/>
+      <c r="A21" s="25"/>
+      <c r="B21" s="39"/>
+      <c r="C21" s="36"/>
       <c r="D21" s="32"/>
       <c r="E21" s="32"/>
       <c r="F21" s="32"/>
       <c r="G21" s="32"/>
       <c r="H21" s="32"/>
       <c r="I21" s="32"/>
-      <c r="J21" s="39"/>
-      <c r="K21" s="40"/>
-      <c r="L21" s="33"/>
+      <c r="J21" s="42"/>
+      <c r="K21" s="33"/>
+      <c r="L21" s="25"/>
     </row>
     <row r="22" spans="1:12" ht="22" customHeight="1" thickTop="1">
-      <c r="A22" s="33"/>
+      <c r="A22" s="25"/>
       <c r="C22" s="1"/>
       <c r="D22" s="32"/>
       <c r="E22" s="32"/>
@@ -4403,21 +4477,59 @@
       <c r="I22" s="32"/>
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
-      <c r="L22" s="33"/>
+      <c r="L22" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="76">
-    <mergeCell ref="L19:L20"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="D20:D22"/>
-    <mergeCell ref="I20:I22"/>
-    <mergeCell ref="K20:K21"/>
-    <mergeCell ref="L21:L22"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="K18:K19"/>
-    <mergeCell ref="E17:E22"/>
-    <mergeCell ref="H17:H22"/>
-    <mergeCell ref="L17:L18"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="K12:K13"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="F12:G13"/>
+    <mergeCell ref="F14:G22"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="C19:C21"/>
+    <mergeCell ref="J19:J21"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="E8:E16"/>
+    <mergeCell ref="F8:G9"/>
+    <mergeCell ref="H8:H16"/>
+    <mergeCell ref="K8:K9"/>
+    <mergeCell ref="J11:J14"/>
+    <mergeCell ref="K10:K11"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="D5:D10"/>
+    <mergeCell ref="I5:I10"/>
+    <mergeCell ref="L5:L6"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="C7:C10"/>
+    <mergeCell ref="J7:J10"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="C3:C6"/>
+    <mergeCell ref="J3:J6"/>
+    <mergeCell ref="C11:C14"/>
+    <mergeCell ref="D11:D14"/>
+    <mergeCell ref="I11:I14"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="L3:L4"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="D1:D4"/>
+    <mergeCell ref="E1:E7"/>
+    <mergeCell ref="F1:G7"/>
+    <mergeCell ref="H1:H7"/>
+    <mergeCell ref="K4:K5"/>
+    <mergeCell ref="I1:I4"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="L7:L8"/>
     <mergeCell ref="L11:L12"/>
     <mergeCell ref="B12:B13"/>
     <mergeCell ref="A9:A10"/>
@@ -4434,55 +4546,17 @@
     <mergeCell ref="L15:L16"/>
     <mergeCell ref="B16:B17"/>
     <mergeCell ref="K16:K17"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="L1:L2"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="K2:K3"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="L3:L4"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="D1:D4"/>
-    <mergeCell ref="E1:E7"/>
-    <mergeCell ref="F1:G7"/>
-    <mergeCell ref="H1:H7"/>
-    <mergeCell ref="K4:K5"/>
-    <mergeCell ref="I1:I4"/>
-    <mergeCell ref="J1:J2"/>
-    <mergeCell ref="L7:L8"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="D5:D10"/>
-    <mergeCell ref="I5:I10"/>
-    <mergeCell ref="L5:L6"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="C7:C10"/>
-    <mergeCell ref="J7:J10"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="C3:C6"/>
-    <mergeCell ref="J3:J6"/>
-    <mergeCell ref="C11:C14"/>
-    <mergeCell ref="D11:D14"/>
-    <mergeCell ref="I11:I14"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="E8:E16"/>
-    <mergeCell ref="F8:G9"/>
-    <mergeCell ref="H8:H16"/>
-    <mergeCell ref="K8:K9"/>
-    <mergeCell ref="J11:J14"/>
-    <mergeCell ref="K10:K11"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="K12:K13"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="F12:G13"/>
-    <mergeCell ref="F14:G22"/>
-    <mergeCell ref="A19:A20"/>
-    <mergeCell ref="C19:C21"/>
-    <mergeCell ref="J19:J21"/>
-    <mergeCell ref="A21:A22"/>
-    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="L19:L20"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="D20:D22"/>
+    <mergeCell ref="I20:I22"/>
+    <mergeCell ref="K20:K21"/>
+    <mergeCell ref="L21:L22"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="K18:K19"/>
+    <mergeCell ref="E17:E22"/>
+    <mergeCell ref="H17:H22"/>
+    <mergeCell ref="L17:L18"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4497,7 +4571,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="20" customHeight="1"/>
   <sheetData>
     <row r="1" spans="1:12" ht="20" customHeight="1" thickBot="1">
-      <c r="A1" s="33"/>
+      <c r="A1" s="25"/>
       <c r="C1" s="32"/>
       <c r="D1" s="32"/>
       <c r="E1" s="32"/>
@@ -4509,11 +4583,11 @@
       <c r="I1" s="32"/>
       <c r="J1" s="32"/>
       <c r="K1" s="1"/>
-      <c r="L1" s="33"/>
+      <c r="L1" s="25"/>
     </row>
     <row r="2" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A2" s="33"/>
-      <c r="B2" s="36" t="s">
+      <c r="A2" s="25"/>
+      <c r="B2" s="34" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="32"/>
@@ -4524,15 +4598,15 @@
       <c r="H2" s="32"/>
       <c r="I2" s="32"/>
       <c r="J2" s="32"/>
-      <c r="K2" s="38" t="s">
+      <c r="K2" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="L2" s="33"/>
+      <c r="L2" s="25"/>
     </row>
     <row r="3" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A3" s="33"/>
-      <c r="B3" s="49"/>
-      <c r="C3" s="36" t="s">
+      <c r="A3" s="25"/>
+      <c r="B3" s="48"/>
+      <c r="C3" s="34" t="s">
         <v>1</v>
       </c>
       <c r="D3" s="32"/>
@@ -4541,306 +4615,306 @@
       <c r="G3" s="44"/>
       <c r="H3" s="32"/>
       <c r="I3" s="32"/>
-      <c r="J3" s="38" t="s">
+      <c r="J3" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="K3" s="39"/>
-      <c r="L3" s="33"/>
+      <c r="K3" s="42"/>
+      <c r="L3" s="25"/>
     </row>
     <row r="4" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A4" s="33"/>
-      <c r="B4" s="30"/>
-      <c r="C4" s="42"/>
+      <c r="A4" s="25"/>
+      <c r="B4" s="38"/>
+      <c r="C4" s="35"/>
       <c r="D4" s="32"/>
       <c r="E4" s="32"/>
       <c r="F4" s="44"/>
       <c r="G4" s="44"/>
       <c r="H4" s="32"/>
       <c r="I4" s="32"/>
-      <c r="J4" s="41"/>
+      <c r="J4" s="43"/>
       <c r="K4" s="57"/>
-      <c r="L4" s="33"/>
+      <c r="L4" s="25"/>
     </row>
     <row r="5" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A5" s="33"/>
-      <c r="B5" s="48"/>
-      <c r="C5" s="42"/>
-      <c r="D5" s="36" t="s">
+      <c r="A5" s="25"/>
+      <c r="B5" s="50"/>
+      <c r="C5" s="35"/>
+      <c r="D5" s="34" t="s">
         <v>10</v>
       </c>
       <c r="E5" s="32"/>
       <c r="F5" s="44"/>
       <c r="G5" s="44"/>
       <c r="H5" s="32"/>
-      <c r="I5" s="38" t="s">
+      <c r="I5" s="41" t="s">
         <v>2</v>
       </c>
-      <c r="J5" s="41"/>
+      <c r="J5" s="43"/>
       <c r="K5" s="32"/>
-      <c r="L5" s="33"/>
+      <c r="L5" s="25"/>
     </row>
     <row r="6" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A6" s="33"/>
-      <c r="B6" s="36" t="s">
+      <c r="A6" s="25"/>
+      <c r="B6" s="34" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="37"/>
-      <c r="D6" s="42"/>
+      <c r="C6" s="36"/>
+      <c r="D6" s="35"/>
       <c r="E6" s="32"/>
       <c r="F6" s="44"/>
       <c r="G6" s="44"/>
       <c r="H6" s="32"/>
-      <c r="I6" s="41"/>
-      <c r="J6" s="39"/>
-      <c r="K6" s="38" t="s">
+      <c r="I6" s="43"/>
+      <c r="J6" s="42"/>
+      <c r="K6" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="L6" s="33"/>
+      <c r="L6" s="25"/>
     </row>
     <row r="7" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A7" s="33"/>
-      <c r="B7" s="49"/>
-      <c r="C7" s="35"/>
-      <c r="D7" s="42"/>
+      <c r="A7" s="25"/>
+      <c r="B7" s="48"/>
+      <c r="C7" s="31"/>
+      <c r="D7" s="35"/>
       <c r="E7" s="32"/>
       <c r="F7" s="44"/>
       <c r="G7" s="44"/>
       <c r="H7" s="32"/>
-      <c r="I7" s="41"/>
-      <c r="J7" s="35"/>
-      <c r="K7" s="39"/>
-      <c r="L7" s="33"/>
+      <c r="I7" s="43"/>
+      <c r="J7" s="31"/>
+      <c r="K7" s="42"/>
+      <c r="L7" s="25"/>
     </row>
     <row r="8" spans="1:12" ht="20" customHeight="1" thickTop="1">
-      <c r="A8" s="33"/>
-      <c r="B8" s="30"/>
+      <c r="A8" s="25"/>
+      <c r="B8" s="38"/>
       <c r="C8" s="32"/>
-      <c r="D8" s="42"/>
-      <c r="E8" s="36" t="s">
+      <c r="D8" s="35"/>
+      <c r="E8" s="34" t="s">
         <v>7</v>
       </c>
       <c r="F8" s="44"/>
       <c r="G8" s="44"/>
-      <c r="H8" s="38" t="s">
+      <c r="H8" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="I8" s="41"/>
+      <c r="I8" s="43"/>
       <c r="J8" s="32"/>
       <c r="K8" s="57"/>
-      <c r="L8" s="33"/>
+      <c r="L8" s="25"/>
     </row>
     <row r="9" spans="1:12" ht="20" customHeight="1" thickBot="1">
-      <c r="A9" s="33"/>
-      <c r="B9" s="48"/>
+      <c r="A9" s="25"/>
+      <c r="B9" s="50"/>
       <c r="C9" s="32"/>
-      <c r="D9" s="42"/>
-      <c r="E9" s="42"/>
-      <c r="F9" s="29" t="s">
+      <c r="D9" s="35"/>
+      <c r="E9" s="35"/>
+      <c r="F9" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="G9" s="29"/>
-      <c r="H9" s="41"/>
-      <c r="I9" s="41"/>
+      <c r="G9" s="22"/>
+      <c r="H9" s="43"/>
+      <c r="I9" s="43"/>
       <c r="J9" s="32"/>
       <c r="K9" s="32"/>
-      <c r="L9" s="33"/>
+      <c r="L9" s="25"/>
     </row>
     <row r="10" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A10" s="33"/>
-      <c r="B10" s="36" t="s">
+      <c r="A10" s="25"/>
+      <c r="B10" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="40"/>
-      <c r="D10" s="37"/>
-      <c r="E10" s="42"/>
-      <c r="F10" s="29"/>
-      <c r="G10" s="29"/>
-      <c r="H10" s="41"/>
-      <c r="I10" s="39"/>
-      <c r="J10" s="40"/>
-      <c r="K10" s="38" t="s">
+      <c r="C10" s="33"/>
+      <c r="D10" s="36"/>
+      <c r="E10" s="35"/>
+      <c r="F10" s="22"/>
+      <c r="G10" s="22"/>
+      <c r="H10" s="43"/>
+      <c r="I10" s="42"/>
+      <c r="J10" s="33"/>
+      <c r="K10" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="L10" s="33"/>
+      <c r="L10" s="25"/>
     </row>
     <row r="11" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A11" s="33"/>
-      <c r="B11" s="49"/>
-      <c r="C11" s="50"/>
+      <c r="A11" s="25"/>
+      <c r="B11" s="48"/>
+      <c r="C11" s="49"/>
       <c r="D11" s="32"/>
-      <c r="E11" s="42"/>
-      <c r="F11" s="42"/>
-      <c r="G11" s="41"/>
-      <c r="H11" s="41"/>
+      <c r="E11" s="35"/>
+      <c r="F11" s="35"/>
+      <c r="G11" s="43"/>
+      <c r="H11" s="43"/>
       <c r="I11" s="32"/>
       <c r="J11" s="32"/>
-      <c r="K11" s="39"/>
-      <c r="L11" s="33"/>
+      <c r="K11" s="42"/>
+      <c r="L11" s="25"/>
     </row>
     <row r="12" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A12" s="33"/>
-      <c r="B12" s="30"/>
-      <c r="C12" s="50"/>
+      <c r="A12" s="25"/>
+      <c r="B12" s="38"/>
+      <c r="C12" s="49"/>
       <c r="D12" s="32"/>
-      <c r="E12" s="42"/>
-      <c r="F12" s="37"/>
-      <c r="G12" s="39"/>
-      <c r="H12" s="41"/>
+      <c r="E12" s="35"/>
+      <c r="F12" s="36"/>
+      <c r="G12" s="42"/>
+      <c r="H12" s="43"/>
       <c r="I12" s="32"/>
       <c r="J12" s="32"/>
       <c r="K12" s="57"/>
-      <c r="L12" s="33"/>
+      <c r="L12" s="25"/>
     </row>
     <row r="13" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A13" s="33"/>
-      <c r="B13" s="48"/>
-      <c r="C13" s="50"/>
+      <c r="A13" s="25"/>
+      <c r="B13" s="50"/>
+      <c r="C13" s="49"/>
       <c r="D13" s="32"/>
-      <c r="E13" s="42"/>
+      <c r="E13" s="35"/>
       <c r="F13" s="32" t="s">
         <v>15</v>
       </c>
       <c r="G13" s="32"/>
-      <c r="H13" s="41"/>
+      <c r="H13" s="43"/>
       <c r="I13" s="32"/>
       <c r="J13" s="32"/>
       <c r="K13" s="32"/>
-      <c r="L13" s="33"/>
+      <c r="L13" s="25"/>
     </row>
     <row r="14" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A14" s="33"/>
-      <c r="B14" s="36" t="s">
+      <c r="A14" s="25"/>
+      <c r="B14" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="50"/>
+      <c r="C14" s="49"/>
       <c r="D14" s="32"/>
-      <c r="E14" s="42"/>
+      <c r="E14" s="35"/>
       <c r="F14" s="32"/>
       <c r="G14" s="32"/>
-      <c r="H14" s="41"/>
+      <c r="H14" s="43"/>
       <c r="I14" s="32"/>
       <c r="J14" s="32"/>
-      <c r="K14" s="38" t="s">
+      <c r="K14" s="41" t="s">
         <v>8</v>
       </c>
-      <c r="L14" s="33"/>
+      <c r="L14" s="25"/>
     </row>
     <row r="15" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A15" s="33"/>
-      <c r="B15" s="49"/>
-      <c r="C15" s="50"/>
-      <c r="D15" s="36" t="s">
+      <c r="A15" s="25"/>
+      <c r="B15" s="48"/>
+      <c r="C15" s="49"/>
+      <c r="D15" s="34" t="s">
         <v>4</v>
       </c>
-      <c r="E15" s="42"/>
+      <c r="E15" s="35"/>
       <c r="F15" s="32"/>
       <c r="G15" s="32"/>
-      <c r="H15" s="41"/>
-      <c r="I15" s="38" t="s">
+      <c r="H15" s="43"/>
+      <c r="I15" s="41" t="s">
         <v>10</v>
       </c>
-      <c r="J15" s="35"/>
-      <c r="K15" s="39"/>
-      <c r="L15" s="33"/>
+      <c r="J15" s="31"/>
+      <c r="K15" s="42"/>
+      <c r="L15" s="25"/>
     </row>
     <row r="16" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A16" s="33"/>
-      <c r="B16" s="30"/>
-      <c r="C16" s="50"/>
-      <c r="D16" s="42"/>
-      <c r="E16" s="42"/>
+      <c r="A16" s="25"/>
+      <c r="B16" s="38"/>
+      <c r="C16" s="49"/>
+      <c r="D16" s="35"/>
+      <c r="E16" s="35"/>
       <c r="F16" s="32"/>
       <c r="G16" s="32"/>
-      <c r="H16" s="41"/>
-      <c r="I16" s="41"/>
+      <c r="H16" s="43"/>
+      <c r="I16" s="43"/>
       <c r="J16" s="32"/>
       <c r="K16" s="57"/>
-      <c r="L16" s="33"/>
+      <c r="L16" s="25"/>
     </row>
     <row r="17" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A17" s="33"/>
-      <c r="B17" s="48"/>
-      <c r="C17" s="50"/>
-      <c r="D17" s="42"/>
-      <c r="E17" s="37"/>
+      <c r="A17" s="25"/>
+      <c r="B17" s="50"/>
+      <c r="C17" s="49"/>
+      <c r="D17" s="35"/>
+      <c r="E17" s="36"/>
       <c r="F17" s="32"/>
       <c r="G17" s="32"/>
-      <c r="H17" s="39"/>
-      <c r="I17" s="41"/>
+      <c r="H17" s="42"/>
+      <c r="I17" s="43"/>
       <c r="J17" s="32"/>
       <c r="K17" s="32"/>
-      <c r="L17" s="33"/>
+      <c r="L17" s="25"/>
     </row>
     <row r="18" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A18" s="33"/>
-      <c r="B18" s="36" t="s">
+      <c r="A18" s="25"/>
+      <c r="B18" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="C18" s="35"/>
-      <c r="D18" s="42"/>
+      <c r="C18" s="31"/>
+      <c r="D18" s="35"/>
       <c r="E18" s="32"/>
       <c r="F18" s="32"/>
       <c r="G18" s="32"/>
       <c r="H18" s="32"/>
-      <c r="I18" s="41"/>
-      <c r="J18" s="40"/>
-      <c r="K18" s="38" t="s">
+      <c r="I18" s="43"/>
+      <c r="J18" s="33"/>
+      <c r="K18" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="L18" s="33"/>
+      <c r="L18" s="25"/>
     </row>
     <row r="19" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A19" s="33"/>
-      <c r="B19" s="49"/>
-      <c r="C19" s="36" t="s">
+      <c r="A19" s="25"/>
+      <c r="B19" s="48"/>
+      <c r="C19" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="D19" s="42"/>
+      <c r="D19" s="35"/>
       <c r="E19" s="32"/>
       <c r="F19" s="32"/>
       <c r="G19" s="32"/>
       <c r="H19" s="32"/>
-      <c r="I19" s="41"/>
-      <c r="J19" s="38" t="s">
+      <c r="I19" s="43"/>
+      <c r="J19" s="41" t="s">
         <v>13</v>
       </c>
-      <c r="K19" s="39"/>
-      <c r="L19" s="33"/>
+      <c r="K19" s="42"/>
+      <c r="L19" s="25"/>
     </row>
     <row r="20" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A20" s="33"/>
-      <c r="B20" s="43"/>
-      <c r="C20" s="42"/>
-      <c r="D20" s="37"/>
+      <c r="A20" s="25"/>
+      <c r="B20" s="40"/>
+      <c r="C20" s="35"/>
+      <c r="D20" s="36"/>
       <c r="E20" s="32"/>
       <c r="F20" s="32"/>
       <c r="G20" s="32"/>
       <c r="H20" s="32"/>
-      <c r="I20" s="39"/>
-      <c r="J20" s="41"/>
+      <c r="I20" s="42"/>
+      <c r="J20" s="43"/>
       <c r="K20" s="32"/>
-      <c r="L20" s="33"/>
+      <c r="L20" s="25"/>
     </row>
     <row r="21" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A21" s="33"/>
-      <c r="B21" s="30"/>
-      <c r="C21" s="42"/>
+      <c r="A21" s="25"/>
+      <c r="B21" s="38"/>
+      <c r="C21" s="35"/>
       <c r="D21" s="32"/>
       <c r="E21" s="32"/>
       <c r="F21" s="32"/>
       <c r="G21" s="32"/>
       <c r="H21" s="32"/>
       <c r="I21" s="32"/>
-      <c r="J21" s="39"/>
+      <c r="J21" s="42"/>
       <c r="K21" s="32"/>
-      <c r="L21" s="33"/>
+      <c r="L21" s="25"/>
     </row>
     <row r="22" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A22" s="33"/>
-      <c r="B22" s="36" t="s">
+      <c r="A22" s="25"/>
+      <c r="B22" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="C22" s="37"/>
+      <c r="C22" s="36"/>
       <c r="D22" s="32"/>
       <c r="E22" s="32"/>
       <c r="F22" s="32"/>
@@ -4848,13 +4922,13 @@
       <c r="H22" s="32"/>
       <c r="I22" s="32"/>
       <c r="J22" s="32"/>
-      <c r="K22" s="35"/>
-      <c r="L22" s="33"/>
+      <c r="K22" s="31"/>
+      <c r="L22" s="25"/>
     </row>
     <row r="23" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A23" s="33"/>
-      <c r="B23" s="37"/>
-      <c r="C23" s="30"/>
+      <c r="A23" s="25"/>
+      <c r="B23" s="36"/>
+      <c r="C23" s="38"/>
       <c r="D23" s="32"/>
       <c r="E23" s="32"/>
       <c r="F23" s="32"/>
@@ -4863,11 +4937,11 @@
       <c r="I23" s="32"/>
       <c r="J23" s="32"/>
       <c r="K23" s="32"/>
-      <c r="L23" s="33"/>
+      <c r="L23" s="25"/>
     </row>
     <row r="24" spans="1:12" ht="20" customHeight="1" thickTop="1">
-      <c r="A24" s="33"/>
-      <c r="C24" s="30"/>
+      <c r="A24" s="25"/>
+      <c r="C24" s="38"/>
       <c r="D24" s="32"/>
       <c r="E24" s="32"/>
       <c r="F24" s="32"/>
@@ -4876,7 +4950,7 @@
       <c r="I24" s="32"/>
       <c r="J24" s="32"/>
       <c r="K24" s="32"/>
-      <c r="L24" s="33"/>
+      <c r="L24" s="25"/>
     </row>
     <row r="25" spans="1:12" ht="20" customHeight="1">
       <c r="A25" s="4"/>
@@ -4886,6 +4960,72 @@
     </row>
   </sheetData>
   <mergeCells count="82">
+    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="C23:C24"/>
+    <mergeCell ref="L23:L24"/>
+    <mergeCell ref="J22:J24"/>
+    <mergeCell ref="K22:K24"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="C3:C6"/>
+    <mergeCell ref="J3:J6"/>
+    <mergeCell ref="L3:L4"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="D5:D10"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D4"/>
+    <mergeCell ref="E1:E7"/>
+    <mergeCell ref="F1:G8"/>
+    <mergeCell ref="H1:H7"/>
+    <mergeCell ref="I1:I4"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="L7:L8"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="C7:C10"/>
+    <mergeCell ref="J7:J10"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="E8:E17"/>
+    <mergeCell ref="H8:H17"/>
+    <mergeCell ref="K8:K9"/>
+    <mergeCell ref="F9:G10"/>
+    <mergeCell ref="C11:C14"/>
+    <mergeCell ref="D11:D14"/>
+    <mergeCell ref="F11:F12"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="L11:L12"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="L13:L14"/>
+    <mergeCell ref="G11:G12"/>
+    <mergeCell ref="I11:I14"/>
+    <mergeCell ref="J11:J14"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="K12:K13"/>
+    <mergeCell ref="F13:G14"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="K16:K17"/>
+    <mergeCell ref="E18:E24"/>
+    <mergeCell ref="H18:H24"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="K14:K15"/>
+    <mergeCell ref="C15:C18"/>
+    <mergeCell ref="D15:D20"/>
+    <mergeCell ref="F15:G24"/>
+    <mergeCell ref="I15:I20"/>
+    <mergeCell ref="J15:J18"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="K20:K21"/>
+    <mergeCell ref="D21:D24"/>
+    <mergeCell ref="I21:I24"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="I5:I10"/>
+    <mergeCell ref="L5:L6"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="K6:K7"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="K4:K5"/>
     <mergeCell ref="A15:A16"/>
     <mergeCell ref="L15:L16"/>
     <mergeCell ref="A17:A18"/>
@@ -4902,72 +5042,6 @@
     <mergeCell ref="L9:L10"/>
     <mergeCell ref="B10:B11"/>
     <mergeCell ref="K10:K11"/>
-    <mergeCell ref="I5:I10"/>
-    <mergeCell ref="L5:L6"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="K6:K7"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="K4:K5"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="K16:K17"/>
-    <mergeCell ref="E18:E24"/>
-    <mergeCell ref="H18:H24"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="K14:K15"/>
-    <mergeCell ref="C15:C18"/>
-    <mergeCell ref="D15:D20"/>
-    <mergeCell ref="F15:G24"/>
-    <mergeCell ref="I15:I20"/>
-    <mergeCell ref="J15:J18"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="K20:K21"/>
-    <mergeCell ref="D21:D24"/>
-    <mergeCell ref="I21:I24"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="L13:L14"/>
-    <mergeCell ref="G11:G12"/>
-    <mergeCell ref="I11:I14"/>
-    <mergeCell ref="J11:J14"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="K12:K13"/>
-    <mergeCell ref="F13:G14"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="L7:L8"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="C7:C10"/>
-    <mergeCell ref="J7:J10"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="E8:E17"/>
-    <mergeCell ref="H8:H17"/>
-    <mergeCell ref="K8:K9"/>
-    <mergeCell ref="F9:G10"/>
-    <mergeCell ref="C11:C14"/>
-    <mergeCell ref="D11:D14"/>
-    <mergeCell ref="F11:F12"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="L11:L12"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="L1:L2"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="K2:K3"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="C3:C6"/>
-    <mergeCell ref="J3:J6"/>
-    <mergeCell ref="L3:L4"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="D5:D10"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D4"/>
-    <mergeCell ref="E1:E7"/>
-    <mergeCell ref="F1:G8"/>
-    <mergeCell ref="H1:H7"/>
-    <mergeCell ref="I1:I4"/>
-    <mergeCell ref="A23:A24"/>
-    <mergeCell ref="C23:C24"/>
-    <mergeCell ref="L23:L24"/>
-    <mergeCell ref="J22:J24"/>
-    <mergeCell ref="K22:K24"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4982,7 +5056,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="20" customHeight="1"/>
   <sheetData>
     <row r="1" spans="1:12" ht="20" customHeight="1" thickBot="1">
-      <c r="A1" s="33"/>
+      <c r="A1" s="25"/>
       <c r="C1" s="32"/>
       <c r="D1" s="32"/>
       <c r="E1" s="32"/>
@@ -4994,11 +5068,11 @@
       <c r="I1" s="32"/>
       <c r="J1" s="32"/>
       <c r="K1" s="1"/>
-      <c r="L1" s="33"/>
+      <c r="L1" s="25"/>
     </row>
     <row r="2" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A2" s="33"/>
-      <c r="B2" s="36" t="s">
+      <c r="A2" s="25"/>
+      <c r="B2" s="34" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="32"/>
@@ -5009,15 +5083,15 @@
       <c r="H2" s="32"/>
       <c r="I2" s="32"/>
       <c r="J2" s="32"/>
-      <c r="K2" s="38" t="s">
+      <c r="K2" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="L2" s="33"/>
+      <c r="L2" s="25"/>
     </row>
     <row r="3" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A3" s="33"/>
-      <c r="B3" s="49"/>
-      <c r="C3" s="36" t="s">
+      <c r="A3" s="25"/>
+      <c r="B3" s="48"/>
+      <c r="C3" s="34" t="s">
         <v>1</v>
       </c>
       <c r="D3" s="32"/>
@@ -5026,346 +5100,412 @@
       <c r="G3" s="44"/>
       <c r="H3" s="32"/>
       <c r="I3" s="32"/>
-      <c r="J3" s="38" t="s">
+      <c r="J3" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="K3" s="39"/>
-      <c r="L3" s="33"/>
+      <c r="K3" s="42"/>
+      <c r="L3" s="25"/>
     </row>
     <row r="4" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A4" s="33"/>
-      <c r="B4" s="30"/>
-      <c r="C4" s="42"/>
+      <c r="A4" s="25"/>
+      <c r="B4" s="38"/>
+      <c r="C4" s="35"/>
       <c r="D4" s="32"/>
       <c r="E4" s="32"/>
       <c r="F4" s="44"/>
       <c r="G4" s="44"/>
       <c r="H4" s="32"/>
       <c r="I4" s="32"/>
-      <c r="J4" s="41"/>
+      <c r="J4" s="43"/>
       <c r="K4" s="57"/>
-      <c r="L4" s="33"/>
+      <c r="L4" s="25"/>
     </row>
     <row r="5" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A5" s="33"/>
-      <c r="B5" s="48"/>
-      <c r="C5" s="42"/>
-      <c r="D5" s="36" t="s">
+      <c r="A5" s="25"/>
+      <c r="B5" s="50"/>
+      <c r="C5" s="35"/>
+      <c r="D5" s="34" t="s">
         <v>10</v>
       </c>
       <c r="E5" s="32"/>
       <c r="F5" s="44"/>
       <c r="G5" s="44"/>
       <c r="H5" s="32"/>
-      <c r="I5" s="38" t="s">
+      <c r="I5" s="41" t="s">
         <v>10</v>
       </c>
-      <c r="J5" s="41"/>
+      <c r="J5" s="43"/>
       <c r="K5" s="32"/>
-      <c r="L5" s="33"/>
+      <c r="L5" s="25"/>
     </row>
     <row r="6" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A6" s="33"/>
-      <c r="B6" s="36" t="s">
+      <c r="A6" s="25"/>
+      <c r="B6" s="34" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="37"/>
-      <c r="D6" s="42"/>
+      <c r="C6" s="36"/>
+      <c r="D6" s="35"/>
       <c r="E6" s="32"/>
       <c r="F6" s="44"/>
       <c r="G6" s="44"/>
       <c r="H6" s="32"/>
-      <c r="I6" s="41"/>
-      <c r="J6" s="39"/>
-      <c r="K6" s="38" t="s">
+      <c r="I6" s="43"/>
+      <c r="J6" s="42"/>
+      <c r="K6" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="L6" s="33"/>
+      <c r="L6" s="25"/>
     </row>
     <row r="7" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A7" s="33"/>
-      <c r="B7" s="49"/>
-      <c r="C7" s="35"/>
-      <c r="D7" s="42"/>
+      <c r="A7" s="25"/>
+      <c r="B7" s="48"/>
+      <c r="C7" s="31"/>
+      <c r="D7" s="35"/>
       <c r="E7" s="32"/>
       <c r="F7" s="44"/>
       <c r="G7" s="44"/>
       <c r="H7" s="32"/>
-      <c r="I7" s="41"/>
-      <c r="J7" s="35"/>
-      <c r="K7" s="39"/>
-      <c r="L7" s="33"/>
+      <c r="I7" s="43"/>
+      <c r="J7" s="31"/>
+      <c r="K7" s="42"/>
+      <c r="L7" s="25"/>
     </row>
     <row r="8" spans="1:12" ht="20" customHeight="1" thickTop="1">
-      <c r="A8" s="33"/>
-      <c r="B8" s="30"/>
+      <c r="A8" s="25"/>
+      <c r="B8" s="38"/>
       <c r="C8" s="32"/>
-      <c r="D8" s="42"/>
-      <c r="E8" s="36" t="s">
+      <c r="D8" s="35"/>
+      <c r="E8" s="34" t="s">
         <v>7</v>
       </c>
       <c r="F8" s="44"/>
       <c r="G8" s="44"/>
-      <c r="H8" s="38" t="s">
+      <c r="H8" s="41" t="s">
         <v>7</v>
       </c>
-      <c r="I8" s="41"/>
+      <c r="I8" s="43"/>
       <c r="J8" s="32"/>
       <c r="K8" s="57"/>
-      <c r="L8" s="33"/>
+      <c r="L8" s="25"/>
     </row>
     <row r="9" spans="1:12" ht="20" customHeight="1" thickBot="1">
-      <c r="A9" s="33"/>
-      <c r="B9" s="48"/>
+      <c r="A9" s="25"/>
+      <c r="B9" s="50"/>
       <c r="C9" s="32"/>
-      <c r="D9" s="42"/>
-      <c r="E9" s="42"/>
-      <c r="F9" s="29" t="s">
+      <c r="D9" s="35"/>
+      <c r="E9" s="35"/>
+      <c r="F9" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="G9" s="29"/>
-      <c r="H9" s="41"/>
-      <c r="I9" s="41"/>
+      <c r="G9" s="22"/>
+      <c r="H9" s="43"/>
+      <c r="I9" s="43"/>
       <c r="J9" s="32"/>
       <c r="K9" s="32"/>
-      <c r="L9" s="33"/>
+      <c r="L9" s="25"/>
     </row>
     <row r="10" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A10" s="33"/>
-      <c r="B10" s="36" t="s">
+      <c r="A10" s="25"/>
+      <c r="B10" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="40"/>
-      <c r="D10" s="37"/>
-      <c r="E10" s="42"/>
-      <c r="F10" s="29"/>
-      <c r="G10" s="29"/>
-      <c r="H10" s="41"/>
-      <c r="I10" s="39"/>
-      <c r="J10" s="40"/>
-      <c r="K10" s="38" t="s">
+      <c r="C10" s="33"/>
+      <c r="D10" s="36"/>
+      <c r="E10" s="35"/>
+      <c r="F10" s="22"/>
+      <c r="G10" s="22"/>
+      <c r="H10" s="43"/>
+      <c r="I10" s="42"/>
+      <c r="J10" s="33"/>
+      <c r="K10" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="L10" s="33"/>
+      <c r="L10" s="25"/>
     </row>
     <row r="11" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A11" s="33"/>
-      <c r="B11" s="49"/>
-      <c r="C11" s="50"/>
+      <c r="A11" s="25"/>
+      <c r="B11" s="48"/>
+      <c r="C11" s="49"/>
       <c r="D11" s="32"/>
-      <c r="E11" s="42"/>
-      <c r="F11" s="42"/>
-      <c r="G11" s="41"/>
-      <c r="H11" s="41"/>
+      <c r="E11" s="35"/>
+      <c r="F11" s="35"/>
+      <c r="G11" s="43"/>
+      <c r="H11" s="43"/>
       <c r="I11" s="32"/>
       <c r="J11" s="32"/>
-      <c r="K11" s="39"/>
-      <c r="L11" s="33"/>
+      <c r="K11" s="42"/>
+      <c r="L11" s="25"/>
     </row>
     <row r="12" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A12" s="33"/>
-      <c r="B12" s="30"/>
-      <c r="C12" s="50"/>
+      <c r="A12" s="25"/>
+      <c r="B12" s="38"/>
+      <c r="C12" s="49"/>
       <c r="D12" s="32"/>
-      <c r="E12" s="42"/>
-      <c r="F12" s="37"/>
-      <c r="G12" s="39"/>
-      <c r="H12" s="41"/>
+      <c r="E12" s="35"/>
+      <c r="F12" s="36"/>
+      <c r="G12" s="42"/>
+      <c r="H12" s="43"/>
       <c r="I12" s="32"/>
       <c r="J12" s="32"/>
       <c r="K12" s="57"/>
-      <c r="L12" s="33"/>
+      <c r="L12" s="25"/>
     </row>
     <row r="13" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A13" s="33"/>
-      <c r="B13" s="48"/>
-      <c r="C13" s="50"/>
+      <c r="A13" s="25"/>
+      <c r="B13" s="50"/>
+      <c r="C13" s="49"/>
       <c r="D13" s="32"/>
-      <c r="E13" s="42"/>
+      <c r="E13" s="35"/>
       <c r="F13" s="32" t="s">
         <v>15</v>
       </c>
       <c r="G13" s="32"/>
-      <c r="H13" s="41"/>
+      <c r="H13" s="43"/>
       <c r="I13" s="32"/>
       <c r="J13" s="32"/>
       <c r="K13" s="32"/>
-      <c r="L13" s="33"/>
+      <c r="L13" s="25"/>
     </row>
     <row r="14" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A14" s="33"/>
-      <c r="B14" s="36" t="s">
+      <c r="A14" s="25"/>
+      <c r="B14" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="50"/>
+      <c r="C14" s="49"/>
       <c r="D14" s="32"/>
-      <c r="E14" s="42"/>
+      <c r="E14" s="35"/>
       <c r="F14" s="32"/>
       <c r="G14" s="32"/>
-      <c r="H14" s="41"/>
+      <c r="H14" s="43"/>
       <c r="I14" s="32"/>
       <c r="J14" s="32"/>
-      <c r="K14" s="38" t="s">
+      <c r="K14" s="41" t="s">
         <v>8</v>
       </c>
-      <c r="L14" s="33"/>
+      <c r="L14" s="25"/>
     </row>
     <row r="15" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A15" s="33"/>
-      <c r="B15" s="49"/>
-      <c r="C15" s="50"/>
-      <c r="D15" s="36" t="s">
+      <c r="A15" s="25"/>
+      <c r="B15" s="48"/>
+      <c r="C15" s="49"/>
+      <c r="D15" s="34" t="s">
         <v>4</v>
       </c>
-      <c r="E15" s="42"/>
+      <c r="E15" s="35"/>
       <c r="F15" s="32"/>
       <c r="G15" s="32"/>
-      <c r="H15" s="41"/>
-      <c r="I15" s="38" t="s">
+      <c r="H15" s="43"/>
+      <c r="I15" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="J15" s="35"/>
-      <c r="K15" s="39"/>
-      <c r="L15" s="33"/>
+      <c r="J15" s="31"/>
+      <c r="K15" s="42"/>
+      <c r="L15" s="25"/>
     </row>
     <row r="16" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A16" s="33"/>
-      <c r="B16" s="30"/>
-      <c r="C16" s="50"/>
-      <c r="D16" s="42"/>
-      <c r="E16" s="42"/>
+      <c r="A16" s="25"/>
+      <c r="B16" s="38"/>
+      <c r="C16" s="49"/>
+      <c r="D16" s="35"/>
+      <c r="E16" s="35"/>
       <c r="F16" s="32"/>
       <c r="G16" s="32"/>
-      <c r="H16" s="41"/>
-      <c r="I16" s="41"/>
+      <c r="H16" s="43"/>
+      <c r="I16" s="43"/>
       <c r="J16" s="32"/>
       <c r="K16" s="57"/>
-      <c r="L16" s="33"/>
+      <c r="L16" s="25"/>
     </row>
     <row r="17" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A17" s="33"/>
-      <c r="B17" s="48"/>
-      <c r="C17" s="50"/>
-      <c r="D17" s="42"/>
-      <c r="E17" s="37"/>
+      <c r="A17" s="25"/>
+      <c r="B17" s="50"/>
+      <c r="C17" s="49"/>
+      <c r="D17" s="35"/>
+      <c r="E17" s="36"/>
       <c r="F17" s="32"/>
       <c r="G17" s="32"/>
-      <c r="H17" s="39"/>
-      <c r="I17" s="41"/>
+      <c r="H17" s="42"/>
+      <c r="I17" s="43"/>
       <c r="J17" s="32"/>
       <c r="K17" s="32"/>
-      <c r="L17" s="33"/>
+      <c r="L17" s="25"/>
     </row>
     <row r="18" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A18" s="33"/>
-      <c r="B18" s="36" t="s">
+      <c r="A18" s="25"/>
+      <c r="B18" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="C18" s="35"/>
-      <c r="D18" s="42"/>
+      <c r="C18" s="31"/>
+      <c r="D18" s="35"/>
       <c r="E18" s="32"/>
       <c r="F18" s="32"/>
       <c r="G18" s="32"/>
       <c r="H18" s="32"/>
-      <c r="I18" s="41"/>
-      <c r="J18" s="40"/>
-      <c r="K18" s="38" t="s">
+      <c r="I18" s="43"/>
+      <c r="J18" s="33"/>
+      <c r="K18" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="L18" s="33"/>
+      <c r="L18" s="25"/>
     </row>
     <row r="19" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A19" s="33"/>
-      <c r="B19" s="49"/>
-      <c r="C19" s="36" t="s">
+      <c r="A19" s="25"/>
+      <c r="B19" s="48"/>
+      <c r="C19" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="D19" s="42"/>
+      <c r="D19" s="35"/>
       <c r="E19" s="32"/>
       <c r="F19" s="32"/>
       <c r="G19" s="32"/>
       <c r="H19" s="32"/>
-      <c r="I19" s="41"/>
-      <c r="J19" s="38" t="s">
+      <c r="I19" s="43"/>
+      <c r="J19" s="41" t="s">
         <v>2</v>
       </c>
-      <c r="K19" s="39"/>
-      <c r="L19" s="33"/>
+      <c r="K19" s="42"/>
+      <c r="L19" s="25"/>
     </row>
     <row r="20" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A20" s="33"/>
-      <c r="B20" s="43"/>
-      <c r="C20" s="42"/>
-      <c r="D20" s="37"/>
+      <c r="A20" s="25"/>
+      <c r="B20" s="40"/>
+      <c r="C20" s="35"/>
+      <c r="D20" s="36"/>
       <c r="E20" s="32"/>
       <c r="F20" s="32"/>
       <c r="G20" s="32"/>
       <c r="H20" s="32"/>
-      <c r="I20" s="39"/>
-      <c r="J20" s="41"/>
+      <c r="I20" s="42"/>
+      <c r="J20" s="43"/>
       <c r="K20" s="32"/>
-      <c r="L20" s="33"/>
+      <c r="L20" s="25"/>
     </row>
     <row r="21" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A21" s="33"/>
-      <c r="B21" s="30"/>
-      <c r="C21" s="42"/>
+      <c r="A21" s="25"/>
+      <c r="B21" s="38"/>
+      <c r="C21" s="35"/>
       <c r="D21" s="32"/>
       <c r="E21" s="32"/>
       <c r="F21" s="32"/>
       <c r="G21" s="32"/>
       <c r="H21" s="32"/>
       <c r="I21" s="32"/>
-      <c r="J21" s="41"/>
+      <c r="J21" s="43"/>
       <c r="K21" s="32"/>
-      <c r="L21" s="33"/>
+      <c r="L21" s="25"/>
     </row>
     <row r="22" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A22" s="33"/>
-      <c r="B22" s="36" t="s">
+      <c r="A22" s="25"/>
+      <c r="B22" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="C22" s="37"/>
+      <c r="C22" s="36"/>
       <c r="D22" s="32"/>
       <c r="E22" s="32"/>
       <c r="F22" s="32"/>
       <c r="G22" s="32"/>
       <c r="H22" s="32"/>
       <c r="I22" s="32"/>
-      <c r="J22" s="39"/>
-      <c r="K22" s="38" t="s">
+      <c r="J22" s="42"/>
+      <c r="K22" s="41" t="s">
         <v>13</v>
       </c>
-      <c r="L22" s="33"/>
+      <c r="L22" s="25"/>
     </row>
     <row r="23" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A23" s="33"/>
-      <c r="B23" s="37"/>
-      <c r="C23" s="30"/>
+      <c r="A23" s="25"/>
+      <c r="B23" s="36"/>
+      <c r="C23" s="38"/>
       <c r="D23" s="32"/>
       <c r="E23" s="32"/>
       <c r="F23" s="32"/>
       <c r="G23" s="32"/>
       <c r="H23" s="32"/>
       <c r="I23" s="32"/>
-      <c r="J23" s="30"/>
-      <c r="K23" s="39"/>
-      <c r="L23" s="33"/>
+      <c r="J23" s="38"/>
+      <c r="K23" s="42"/>
+      <c r="L23" s="25"/>
     </row>
     <row r="24" spans="1:12" ht="20" customHeight="1" thickTop="1">
-      <c r="A24" s="33"/>
-      <c r="C24" s="30"/>
+      <c r="A24" s="25"/>
+      <c r="C24" s="38"/>
       <c r="D24" s="32"/>
       <c r="E24" s="32"/>
       <c r="F24" s="32"/>
       <c r="G24" s="32"/>
       <c r="H24" s="32"/>
       <c r="I24" s="32"/>
-      <c r="J24" s="30"/>
-      <c r="L24" s="33"/>
+      <c r="J24" s="38"/>
+      <c r="L24" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="82">
+    <mergeCell ref="L23:L24"/>
+    <mergeCell ref="K22:K23"/>
+    <mergeCell ref="J19:J22"/>
+    <mergeCell ref="J23:J24"/>
+    <mergeCell ref="D15:D20"/>
+    <mergeCell ref="I15:I20"/>
+    <mergeCell ref="D21:D24"/>
+    <mergeCell ref="E8:E17"/>
+    <mergeCell ref="H8:H17"/>
+    <mergeCell ref="E18:E24"/>
+    <mergeCell ref="I21:I24"/>
+    <mergeCell ref="H18:H24"/>
+    <mergeCell ref="F13:G14"/>
+    <mergeCell ref="F15:G24"/>
+    <mergeCell ref="F9:G10"/>
+    <mergeCell ref="F11:F12"/>
+    <mergeCell ref="K20:K21"/>
+    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="C19:C22"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="C23:C24"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="L5:L6"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="K6:K7"/>
+    <mergeCell ref="L7:L8"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="C3:C6"/>
+    <mergeCell ref="J3:J6"/>
+    <mergeCell ref="L3:L4"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D4"/>
+    <mergeCell ref="E1:E7"/>
+    <mergeCell ref="H1:H7"/>
+    <mergeCell ref="I1:I4"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="K4:K5"/>
+    <mergeCell ref="C7:C10"/>
+    <mergeCell ref="J7:J10"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="K8:K9"/>
+    <mergeCell ref="F1:G8"/>
+    <mergeCell ref="D5:D10"/>
+    <mergeCell ref="I5:I10"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="L9:L10"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="K10:K11"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="C11:C14"/>
+    <mergeCell ref="D11:D14"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="G11:G12"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="L13:L14"/>
+    <mergeCell ref="L11:L12"/>
+    <mergeCell ref="I11:I14"/>
+    <mergeCell ref="J11:J14"/>
+    <mergeCell ref="K12:K13"/>
     <mergeCell ref="L19:L20"/>
     <mergeCell ref="A21:A22"/>
     <mergeCell ref="L21:L22"/>
@@ -5382,72 +5522,6 @@
     <mergeCell ref="J15:J18"/>
     <mergeCell ref="K16:K17"/>
     <mergeCell ref="B20:B21"/>
-    <mergeCell ref="L9:L10"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="K10:K11"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="C11:C14"/>
-    <mergeCell ref="D11:D14"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="G11:G12"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="L13:L14"/>
-    <mergeCell ref="L11:L12"/>
-    <mergeCell ref="I11:I14"/>
-    <mergeCell ref="J11:J14"/>
-    <mergeCell ref="K12:K13"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="K4:K5"/>
-    <mergeCell ref="C7:C10"/>
-    <mergeCell ref="J7:J10"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="K8:K9"/>
-    <mergeCell ref="F1:G8"/>
-    <mergeCell ref="D5:D10"/>
-    <mergeCell ref="I5:I10"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="L5:L6"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="K6:K7"/>
-    <mergeCell ref="L7:L8"/>
-    <mergeCell ref="L1:L2"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="K2:K3"/>
-    <mergeCell ref="C3:C6"/>
-    <mergeCell ref="J3:J6"/>
-    <mergeCell ref="L3:L4"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D4"/>
-    <mergeCell ref="E1:E7"/>
-    <mergeCell ref="H1:H7"/>
-    <mergeCell ref="I1:I4"/>
-    <mergeCell ref="J1:J2"/>
-    <mergeCell ref="K20:K21"/>
-    <mergeCell ref="A23:A24"/>
-    <mergeCell ref="C19:C22"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="C23:C24"/>
-    <mergeCell ref="A19:A20"/>
-    <mergeCell ref="L23:L24"/>
-    <mergeCell ref="K22:K23"/>
-    <mergeCell ref="J19:J22"/>
-    <mergeCell ref="J23:J24"/>
-    <mergeCell ref="D15:D20"/>
-    <mergeCell ref="I15:I20"/>
-    <mergeCell ref="D21:D24"/>
-    <mergeCell ref="E8:E17"/>
-    <mergeCell ref="H8:H17"/>
-    <mergeCell ref="E18:E24"/>
-    <mergeCell ref="I21:I24"/>
-    <mergeCell ref="H18:H24"/>
-    <mergeCell ref="F13:G14"/>
-    <mergeCell ref="F15:G24"/>
-    <mergeCell ref="F9:G10"/>
-    <mergeCell ref="F11:F12"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5456,49 +5530,711 @@
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB5F6ECB-47B9-CF46-AC56-3264715C5E70}">
+  <dimension ref="A1:L28"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="20" customHeight="1"/>
+  <cols>
+    <col min="4" max="4" width="9.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="20" customHeight="1" thickBot="1">
+      <c r="A1" s="81"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="44" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1" s="44"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="38"/>
+      <c r="J1" s="38"/>
+      <c r="K1" s="38"/>
+    </row>
+    <row r="2" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
+      <c r="A2" s="81"/>
+      <c r="B2" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="39"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="44"/>
+      <c r="G2" s="44"/>
+      <c r="H2" s="38"/>
+      <c r="I2" s="38"/>
+      <c r="J2" s="38"/>
+      <c r="K2" s="39"/>
+      <c r="L2" s="81"/>
+    </row>
+    <row r="3" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
+      <c r="A3" s="81"/>
+      <c r="B3" s="36"/>
+      <c r="C3" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="38"/>
+      <c r="E3" s="38"/>
+      <c r="F3" s="44"/>
+      <c r="G3" s="44"/>
+      <c r="H3" s="38"/>
+      <c r="I3" s="38"/>
+      <c r="J3" s="39"/>
+      <c r="K3" s="41" t="s">
+        <v>0</v>
+      </c>
+      <c r="L3" s="81"/>
+    </row>
+    <row r="4" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
+      <c r="A4" s="81"/>
+      <c r="B4" s="40"/>
+      <c r="C4" s="35"/>
+      <c r="D4" s="39"/>
+      <c r="E4" s="38"/>
+      <c r="F4" s="44"/>
+      <c r="G4" s="44"/>
+      <c r="H4" s="38"/>
+      <c r="I4" s="38"/>
+      <c r="J4" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="K4" s="42"/>
+      <c r="L4" s="81"/>
+    </row>
+    <row r="5" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
+      <c r="A5" s="81"/>
+      <c r="B5" s="39"/>
+      <c r="C5" s="36"/>
+      <c r="D5" s="34" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="38"/>
+      <c r="F5" s="44"/>
+      <c r="G5" s="44"/>
+      <c r="H5" s="38"/>
+      <c r="I5" s="39"/>
+      <c r="J5" s="43"/>
+      <c r="K5" s="31"/>
+      <c r="L5" s="81"/>
+    </row>
+    <row r="6" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
+      <c r="A6" s="81"/>
+      <c r="B6" s="73"/>
+      <c r="C6" s="31"/>
+      <c r="D6" s="35"/>
+      <c r="E6" s="39"/>
+      <c r="F6" s="44"/>
+      <c r="G6" s="44"/>
+      <c r="H6" s="38"/>
+      <c r="I6" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="J6" s="43"/>
+      <c r="K6" s="33"/>
+      <c r="L6" s="81"/>
+    </row>
+    <row r="7" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
+      <c r="A7" s="81"/>
+      <c r="B7" s="73"/>
+      <c r="C7" s="73"/>
+      <c r="D7" s="35"/>
+      <c r="E7" s="34" t="s">
+        <v>15</v>
+      </c>
+      <c r="F7" s="78"/>
+      <c r="G7" s="44"/>
+      <c r="H7" s="38"/>
+      <c r="I7" s="43"/>
+      <c r="J7" s="42"/>
+      <c r="K7" s="41" t="s">
+        <v>3</v>
+      </c>
+      <c r="L7" s="81"/>
+    </row>
+    <row r="8" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
+      <c r="A8" s="81"/>
+      <c r="B8" s="34" t="s">
+        <v>3</v>
+      </c>
+      <c r="C8" s="33"/>
+      <c r="D8" s="36"/>
+      <c r="E8" s="35"/>
+      <c r="F8" s="78"/>
+      <c r="G8" s="44"/>
+      <c r="H8" s="39"/>
+      <c r="I8" s="43"/>
+      <c r="J8" s="31"/>
+      <c r="K8" s="42"/>
+      <c r="L8" s="81"/>
+    </row>
+    <row r="9" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
+      <c r="A9" s="81"/>
+      <c r="B9" s="36"/>
+      <c r="C9" s="73"/>
+      <c r="D9" s="31"/>
+      <c r="E9" s="35"/>
+      <c r="F9" s="78"/>
+      <c r="G9" s="44"/>
+      <c r="H9" s="41" t="s">
+        <v>7</v>
+      </c>
+      <c r="I9" s="43"/>
+      <c r="J9" s="73"/>
+      <c r="K9" s="31"/>
+      <c r="L9" s="81"/>
+    </row>
+    <row r="10" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
+      <c r="A10" s="81"/>
+      <c r="B10" s="73"/>
+      <c r="C10" s="73"/>
+      <c r="D10" s="73"/>
+      <c r="E10" s="35"/>
+      <c r="F10" s="78"/>
+      <c r="G10" s="44"/>
+      <c r="H10" s="43"/>
+      <c r="I10" s="43"/>
+      <c r="J10" s="73"/>
+      <c r="K10" s="33"/>
+      <c r="L10" s="81"/>
+    </row>
+    <row r="11" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
+      <c r="A11" s="81"/>
+      <c r="B11" s="73"/>
+      <c r="C11" s="73"/>
+      <c r="D11" s="73"/>
+      <c r="E11" s="35"/>
+      <c r="F11" s="76" t="s">
+        <v>5</v>
+      </c>
+      <c r="G11" s="77"/>
+      <c r="H11" s="43"/>
+      <c r="I11" s="42"/>
+      <c r="J11" s="33"/>
+      <c r="K11" s="41" t="s">
+        <v>6</v>
+      </c>
+      <c r="L11" s="81"/>
+    </row>
+    <row r="12" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
+      <c r="A12" s="81"/>
+      <c r="B12" s="34" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="73"/>
+      <c r="D12" s="73"/>
+      <c r="E12" s="35"/>
+      <c r="F12" s="76"/>
+      <c r="G12" s="77"/>
+      <c r="H12" s="43"/>
+      <c r="I12" s="31"/>
+      <c r="J12" s="31"/>
+      <c r="K12" s="42"/>
+      <c r="L12" s="81"/>
+    </row>
+    <row r="13" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
+      <c r="A13" s="81"/>
+      <c r="B13" s="36"/>
+      <c r="C13" s="34" t="s">
+        <v>2</v>
+      </c>
+      <c r="D13" s="73"/>
+      <c r="E13" s="35"/>
+      <c r="F13" s="79"/>
+      <c r="G13" s="79"/>
+      <c r="H13" s="43"/>
+      <c r="I13" s="32"/>
+      <c r="J13" s="32"/>
+      <c r="K13" s="31"/>
+      <c r="L13" s="81"/>
+    </row>
+    <row r="14" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
+      <c r="A14" s="81"/>
+      <c r="B14" s="73"/>
+      <c r="C14" s="35"/>
+      <c r="D14" s="33"/>
+      <c r="E14" s="35"/>
+      <c r="F14" s="80"/>
+      <c r="G14" s="80"/>
+      <c r="H14" s="43"/>
+      <c r="I14" s="32"/>
+      <c r="J14" s="32"/>
+      <c r="K14" s="33"/>
+      <c r="L14" s="81"/>
+    </row>
+    <row r="15" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
+      <c r="A15" s="81"/>
+      <c r="B15" s="73"/>
+      <c r="C15" s="35"/>
+      <c r="D15" s="82" t="s">
+        <v>7</v>
+      </c>
+      <c r="E15" s="35"/>
+      <c r="F15" s="41" t="s">
+        <v>64</v>
+      </c>
+      <c r="G15" s="34"/>
+      <c r="H15" s="43"/>
+      <c r="I15" s="33"/>
+      <c r="J15" s="33"/>
+      <c r="K15" s="41" t="s">
+        <v>8</v>
+      </c>
+      <c r="L15" s="81"/>
+    </row>
+    <row r="16" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
+      <c r="A16" s="81"/>
+      <c r="B16" s="34" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="36"/>
+      <c r="D16" s="35"/>
+      <c r="E16" s="35"/>
+      <c r="F16" s="43"/>
+      <c r="G16" s="35"/>
+      <c r="H16" s="43"/>
+      <c r="I16" s="41" t="s">
+        <v>4</v>
+      </c>
+      <c r="J16" s="31"/>
+      <c r="K16" s="42"/>
+      <c r="L16" s="81"/>
+    </row>
+    <row r="17" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
+      <c r="A17" s="81"/>
+      <c r="B17" s="36"/>
+      <c r="C17" s="73"/>
+      <c r="D17" s="35"/>
+      <c r="E17" s="35"/>
+      <c r="F17" s="32"/>
+      <c r="G17" s="32"/>
+      <c r="H17" s="43"/>
+      <c r="I17" s="43"/>
+      <c r="J17" s="73"/>
+      <c r="K17" s="31"/>
+      <c r="L17" s="81"/>
+    </row>
+    <row r="18" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
+      <c r="A18" s="81"/>
+      <c r="B18" s="73"/>
+      <c r="C18" s="73"/>
+      <c r="D18" s="35"/>
+      <c r="E18" s="36"/>
+      <c r="F18" s="32"/>
+      <c r="G18" s="32"/>
+      <c r="H18" s="42"/>
+      <c r="I18" s="43"/>
+      <c r="J18" s="73"/>
+      <c r="K18" s="33"/>
+      <c r="L18" s="81"/>
+    </row>
+    <row r="19" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
+      <c r="A19" s="81"/>
+      <c r="B19" s="73"/>
+      <c r="C19" s="73"/>
+      <c r="D19" s="35"/>
+      <c r="E19" s="31"/>
+      <c r="F19" s="32"/>
+      <c r="G19" s="32"/>
+      <c r="H19" s="31"/>
+      <c r="I19" s="43"/>
+      <c r="J19" s="33"/>
+      <c r="K19" s="41" t="s">
+        <v>11</v>
+      </c>
+      <c r="L19" s="81"/>
+    </row>
+    <row r="20" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
+      <c r="A20" s="81"/>
+      <c r="B20" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="73"/>
+      <c r="D20" s="35"/>
+      <c r="E20" s="73"/>
+      <c r="F20" s="32"/>
+      <c r="G20" s="32"/>
+      <c r="H20" s="73"/>
+      <c r="I20" s="43"/>
+      <c r="J20" s="41" t="s">
+        <v>2</v>
+      </c>
+      <c r="K20" s="42"/>
+      <c r="L20" s="81"/>
+    </row>
+    <row r="21" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
+      <c r="A21" s="81"/>
+      <c r="B21" s="36"/>
+      <c r="C21" s="34" t="s">
+        <v>10</v>
+      </c>
+      <c r="D21" s="35"/>
+      <c r="E21" s="73"/>
+      <c r="F21" s="32"/>
+      <c r="G21" s="32"/>
+      <c r="H21" s="73"/>
+      <c r="I21" s="42"/>
+      <c r="J21" s="43"/>
+      <c r="K21" s="31"/>
+      <c r="L21" s="81"/>
+    </row>
+    <row r="22" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
+      <c r="A22" s="81"/>
+      <c r="B22" s="73"/>
+      <c r="C22" s="35"/>
+      <c r="D22" s="36"/>
+      <c r="E22" s="73"/>
+      <c r="F22" s="32"/>
+      <c r="G22" s="32"/>
+      <c r="H22" s="73"/>
+      <c r="I22" s="31"/>
+      <c r="J22" s="43"/>
+      <c r="K22" s="33"/>
+      <c r="L22" s="81"/>
+    </row>
+    <row r="23" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
+      <c r="A23" s="81"/>
+      <c r="B23" s="73"/>
+      <c r="C23" s="35"/>
+      <c r="D23" s="31"/>
+      <c r="E23" s="73"/>
+      <c r="F23" s="32"/>
+      <c r="G23" s="32"/>
+      <c r="H23" s="73"/>
+      <c r="I23" s="73"/>
+      <c r="J23" s="42"/>
+      <c r="K23" s="41" t="s">
+        <v>13</v>
+      </c>
+      <c r="L23" s="81"/>
+    </row>
+    <row r="24" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
+      <c r="A24" s="81"/>
+      <c r="B24" s="34" t="s">
+        <v>13</v>
+      </c>
+      <c r="C24" s="36"/>
+      <c r="D24" s="73"/>
+      <c r="E24" s="73"/>
+      <c r="F24" s="32"/>
+      <c r="G24" s="32"/>
+      <c r="H24" s="73"/>
+      <c r="I24" s="73"/>
+      <c r="J24" s="40"/>
+      <c r="K24" s="42"/>
+      <c r="L24" s="81"/>
+    </row>
+    <row r="25" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
+      <c r="A25" s="81"/>
+      <c r="B25" s="36"/>
+      <c r="C25" s="40"/>
+      <c r="D25" s="73"/>
+      <c r="E25" s="73"/>
+      <c r="F25" s="32"/>
+      <c r="G25" s="32"/>
+      <c r="H25" s="73"/>
+      <c r="I25" s="73"/>
+      <c r="J25" s="75"/>
+      <c r="K25" s="40"/>
+      <c r="L25" s="81"/>
+    </row>
+    <row r="26" spans="1:12" ht="20" customHeight="1" thickTop="1">
+      <c r="A26" s="81"/>
+      <c r="B26" s="74"/>
+      <c r="C26" s="75"/>
+      <c r="D26" s="73"/>
+      <c r="E26" s="73"/>
+      <c r="F26" s="32"/>
+      <c r="G26" s="32"/>
+      <c r="H26" s="73"/>
+      <c r="I26" s="73"/>
+      <c r="J26" s="75"/>
+      <c r="K26" s="38"/>
+    </row>
+    <row r="27" spans="1:12" ht="20" customHeight="1">
+      <c r="A27" s="72"/>
+      <c r="B27" s="72"/>
+    </row>
+    <row r="28" spans="1:12" ht="20" customHeight="1">
+      <c r="A28" s="72"/>
+    </row>
+  </sheetData>
+  <mergeCells count="88">
+    <mergeCell ref="F7:G10"/>
+    <mergeCell ref="F13:F14"/>
+    <mergeCell ref="G13:G14"/>
+    <mergeCell ref="F17:G26"/>
+    <mergeCell ref="K25:K26"/>
+    <mergeCell ref="J24:J26"/>
+    <mergeCell ref="I22:I26"/>
+    <mergeCell ref="H19:H26"/>
+    <mergeCell ref="H1:H8"/>
+    <mergeCell ref="H9:H18"/>
+    <mergeCell ref="C25:C26"/>
+    <mergeCell ref="D23:D26"/>
+    <mergeCell ref="E19:E26"/>
+    <mergeCell ref="E1:E6"/>
+    <mergeCell ref="D1:D4"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="F1:G6"/>
+    <mergeCell ref="I16:I21"/>
+    <mergeCell ref="I12:I15"/>
+    <mergeCell ref="I6:I11"/>
+    <mergeCell ref="I1:I5"/>
+    <mergeCell ref="J1:J3"/>
+    <mergeCell ref="J4:J7"/>
+    <mergeCell ref="J8:J11"/>
+    <mergeCell ref="J12:J15"/>
+    <mergeCell ref="J16:J19"/>
+    <mergeCell ref="J20:J23"/>
+    <mergeCell ref="K11:K12"/>
+    <mergeCell ref="K9:K10"/>
+    <mergeCell ref="K7:K8"/>
+    <mergeCell ref="K5:K6"/>
+    <mergeCell ref="K3:K4"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="K23:K24"/>
+    <mergeCell ref="K21:K22"/>
+    <mergeCell ref="K19:K20"/>
+    <mergeCell ref="K17:K18"/>
+    <mergeCell ref="K15:K16"/>
+    <mergeCell ref="K13:K14"/>
+    <mergeCell ref="L14:L15"/>
+    <mergeCell ref="L16:L17"/>
+    <mergeCell ref="L18:L19"/>
+    <mergeCell ref="L20:L21"/>
+    <mergeCell ref="L22:L23"/>
+    <mergeCell ref="L24:L25"/>
+    <mergeCell ref="L2:L3"/>
+    <mergeCell ref="L4:L5"/>
+    <mergeCell ref="L6:L7"/>
+    <mergeCell ref="L8:L9"/>
+    <mergeCell ref="L10:L11"/>
+    <mergeCell ref="L12:L13"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="D5:D8"/>
+    <mergeCell ref="C13:C16"/>
+    <mergeCell ref="D15:D22"/>
+    <mergeCell ref="E7:E18"/>
+    <mergeCell ref="D9:D14"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="C21:C24"/>
+    <mergeCell ref="C17:C20"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="F15:G16"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="F11:G12"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="C9:C12"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="A3:A4"/>
+  </mergeCells>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="0" verticalDpi="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D070185-5101-5F42-8DAB-DDF968A40D4E}">
+  <dimension ref="A1:H8"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.7109375" defaultRowHeight="60" customHeight="1"/>
+  <cols>
+    <col min="1" max="16384" width="12.7109375" style="16"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="60" customHeight="1" thickBot="1">
+      <c r="A1" s="25" t="s">
+        <v>63</v>
+      </c>
+      <c r="C1" s="21"/>
+      <c r="D1" s="29" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="29"/>
+      <c r="F1" s="21"/>
+      <c r="H1" s="21"/>
+    </row>
+    <row r="2" spans="1:8" ht="60" customHeight="1" thickTop="1" thickBot="1">
+      <c r="A2" s="25"/>
+      <c r="B2" s="26" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="21"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="H2" s="21"/>
+    </row>
+    <row r="3" spans="1:8" ht="60" customHeight="1" thickTop="1" thickBot="1">
+      <c r="A3" s="21"/>
+      <c r="B3" s="27"/>
+      <c r="C3" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="22" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" s="22"/>
+      <c r="F3" s="23" t="s">
+        <v>6</v>
+      </c>
+      <c r="G3" s="24"/>
+      <c r="H3" s="21"/>
+    </row>
+    <row r="4" spans="1:8" ht="60" customHeight="1" thickTop="1">
+      <c r="A4" s="21"/>
+      <c r="B4" s="21"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="22"/>
+      <c r="F4" s="30"/>
+      <c r="G4" s="21"/>
+      <c r="H4" s="21"/>
+    </row>
+    <row r="5" spans="1:8" ht="60" customHeight="1" thickBot="1">
+      <c r="A5" s="21"/>
+      <c r="B5" s="21"/>
+      <c r="C5" s="28"/>
+      <c r="D5" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="21"/>
+      <c r="F5" s="30"/>
+      <c r="G5" s="21"/>
+      <c r="H5" s="21"/>
+    </row>
+    <row r="6" spans="1:8" ht="60" customHeight="1" thickTop="1" thickBot="1">
+      <c r="A6" s="21"/>
+      <c r="B6" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="27"/>
+      <c r="D6" s="21"/>
+      <c r="E6" s="21"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="H6" s="21"/>
+    </row>
+    <row r="7" spans="1:8" ht="60" customHeight="1" thickTop="1" thickBot="1">
+      <c r="A7" s="21"/>
+      <c r="B7" s="27"/>
+      <c r="C7" s="21"/>
+      <c r="D7" s="21"/>
+      <c r="E7" s="21"/>
+      <c r="F7" s="21"/>
+      <c r="G7" s="24"/>
+      <c r="H7" s="21"/>
+    </row>
+    <row r="8" spans="1:8" ht="60" customHeight="1" thickTop="1">
+      <c r="A8" s="21"/>
+      <c r="C8" s="21"/>
+      <c r="D8" s="21"/>
+      <c r="E8" s="21"/>
+      <c r="F8" s="21"/>
+      <c r="H8" s="21"/>
+    </row>
+  </sheetData>
+  <mergeCells count="24">
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="C3:C6"/>
+    <mergeCell ref="D1:E2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="F3:F6"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="D6:E8"/>
+    <mergeCell ref="D3:E4"/>
+    <mergeCell ref="H7:H8"/>
+    <mergeCell ref="H5:H6"/>
+    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="G6:G7"/>
+  </mergeCells>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="0" verticalDpi="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77A4E167-3852-0542-8EB0-81CB31D49EF8}">
   <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="28" customHeight="1"/>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1" thickTop="1" thickBot="1">
       <c r="A1" s="19"/>
-      <c r="B1" s="59" t="s">
+      <c r="B1" s="66" t="s">
         <v>49</v>
       </c>
-      <c r="C1" s="60"/>
-      <c r="D1" s="59" t="s">
+      <c r="C1" s="67"/>
+      <c r="D1" s="66" t="s">
         <v>50</v>
       </c>
-      <c r="E1" s="61"/>
-      <c r="F1" s="59" t="s">
+      <c r="E1" s="71"/>
+      <c r="F1" s="66" t="s">
         <v>51</v>
       </c>
-      <c r="G1" s="60"/>
-      <c r="H1" s="59" t="s">
+      <c r="G1" s="67"/>
+      <c r="H1" s="66" t="s">
         <v>61</v>
       </c>
-      <c r="I1" s="60"/>
+      <c r="I1" s="67"/>
     </row>
     <row r="2" spans="1:9" ht="28" customHeight="1" thickTop="1" thickBot="1">
       <c r="A2" s="20" t="s">
         <v>52</v>
       </c>
-      <c r="B2" s="71" t="s">
+      <c r="B2" s="61" t="s">
         <v>53</v>
       </c>
-      <c r="C2" s="71"/>
-      <c r="D2" s="71" t="s">
+      <c r="C2" s="61"/>
+      <c r="D2" s="61" t="s">
         <v>54</v>
       </c>
-      <c r="E2" s="71"/>
-      <c r="F2" s="71" t="s">
+      <c r="E2" s="61"/>
+      <c r="F2" s="61" t="s">
         <v>55</v>
       </c>
-      <c r="G2" s="71"/>
-      <c r="H2" s="71" t="s">
+      <c r="G2" s="61"/>
+      <c r="H2" s="61" t="s">
         <v>56</v>
       </c>
-      <c r="I2" s="71"/>
+      <c r="I2" s="61"/>
     </row>
     <row r="3" spans="1:9" ht="28" customHeight="1" thickTop="1">
       <c r="A3" s="18" t="s">
@@ -5664,17 +6400,17 @@
       <c r="I9" s="63"/>
     </row>
     <row r="10" spans="1:9" ht="28" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A10" s="66" t="s">
+      <c r="A10" s="68" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="67"/>
-      <c r="C10" s="67"/>
-      <c r="D10" s="67"/>
-      <c r="E10" s="67"/>
-      <c r="F10" s="67"/>
-      <c r="G10" s="67"/>
-      <c r="H10" s="67"/>
-      <c r="I10" s="68"/>
+      <c r="B10" s="69"/>
+      <c r="C10" s="69"/>
+      <c r="D10" s="69"/>
+      <c r="E10" s="69"/>
+      <c r="F10" s="69"/>
+      <c r="G10" s="69"/>
+      <c r="H10" s="69"/>
+      <c r="I10" s="70"/>
     </row>
     <row r="11" spans="1:9" ht="28" customHeight="1" thickTop="1" thickBot="1">
       <c r="A11" s="11" t="s">
@@ -5764,22 +6500,22 @@
       <c r="A15" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="B15" s="69" t="s">
+      <c r="B15" s="59" t="s">
         <v>4</v>
       </c>
-      <c r="C15" s="70"/>
-      <c r="D15" s="69" t="s">
+      <c r="C15" s="60"/>
+      <c r="D15" s="59" t="s">
         <v>4</v>
       </c>
-      <c r="E15" s="70"/>
-      <c r="F15" s="69" t="s">
+      <c r="E15" s="60"/>
+      <c r="F15" s="59" t="s">
         <v>4</v>
       </c>
-      <c r="G15" s="70"/>
-      <c r="H15" s="69" t="s">
+      <c r="G15" s="60"/>
+      <c r="H15" s="59" t="s">
         <v>4</v>
       </c>
-      <c r="I15" s="70"/>
+      <c r="I15" s="60"/>
     </row>
     <row r="16" spans="1:9" ht="28" customHeight="1" thickTop="1" thickBot="1">
       <c r="A16" s="11" t="s">
@@ -5806,26 +6542,67 @@
       <c r="A17" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="B17" s="69" t="s">
+      <c r="B17" s="59" t="s">
         <v>15</v>
       </c>
-      <c r="C17" s="70"/>
-      <c r="D17" s="69" t="s">
+      <c r="C17" s="60"/>
+      <c r="D17" s="59" t="s">
         <v>15</v>
       </c>
-      <c r="E17" s="70"/>
-      <c r="F17" s="69" t="s">
+      <c r="E17" s="60"/>
+      <c r="F17" s="59" t="s">
         <v>15</v>
       </c>
-      <c r="G17" s="70"/>
-      <c r="H17" s="69" t="s">
+      <c r="G17" s="60"/>
+      <c r="H17" s="59" t="s">
         <v>15</v>
       </c>
-      <c r="I17" s="70"/>
+      <c r="I17" s="60"/>
     </row>
     <row r="18" spans="1:9" ht="28" customHeight="1" thickTop="1"/>
   </sheetData>
   <mergeCells count="57">
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="A10:I10"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="F16:G16"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="D17:E17"/>
     <mergeCell ref="F17:G17"/>
@@ -5842,184 +6619,6 @@
     <mergeCell ref="H12:I12"/>
     <mergeCell ref="H13:I13"/>
     <mergeCell ref="H14:I14"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="A10:I10"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="F5:G5"/>
-  </mergeCells>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="0" verticalDpi="0"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D070185-5101-5F42-8DAB-DDF968A40D4E}">
-  <dimension ref="A1:H8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.7109375" defaultRowHeight="60" customHeight="1"/>
-  <cols>
-    <col min="1" max="16384" width="12.7109375" style="16"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" ht="60" customHeight="1" thickBot="1">
-      <c r="A1" s="33" t="s">
-        <v>63</v>
-      </c>
-      <c r="C1" s="21"/>
-      <c r="D1" s="25" t="s">
-        <v>14</v>
-      </c>
-      <c r="E1" s="25"/>
-      <c r="F1" s="21"/>
-      <c r="H1" s="21"/>
-    </row>
-    <row r="2" spans="1:8" ht="60" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A2" s="33"/>
-      <c r="B2" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="21"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="21"/>
-      <c r="G2" s="26" t="s">
-        <v>0</v>
-      </c>
-      <c r="H2" s="21"/>
-    </row>
-    <row r="3" spans="1:8" ht="60" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A3" s="21"/>
-      <c r="B3" s="23"/>
-      <c r="C3" s="22" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" s="29" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" s="29"/>
-      <c r="F3" s="26" t="s">
-        <v>6</v>
-      </c>
-      <c r="G3" s="28"/>
-      <c r="H3" s="21"/>
-    </row>
-    <row r="4" spans="1:8" ht="60" customHeight="1" thickTop="1">
-      <c r="A4" s="21"/>
-      <c r="B4" s="21"/>
-      <c r="C4" s="24"/>
-      <c r="D4" s="29"/>
-      <c r="E4" s="29"/>
-      <c r="F4" s="27"/>
-      <c r="G4" s="21"/>
-      <c r="H4" s="21"/>
-    </row>
-    <row r="5" spans="1:8" ht="60" customHeight="1" thickBot="1">
-      <c r="A5" s="21"/>
-      <c r="B5" s="21"/>
-      <c r="C5" s="24"/>
-      <c r="D5" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" s="21"/>
-      <c r="F5" s="27"/>
-      <c r="G5" s="21"/>
-      <c r="H5" s="21"/>
-    </row>
-    <row r="6" spans="1:8" ht="60" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A6" s="21"/>
-      <c r="B6" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="C6" s="23"/>
-      <c r="D6" s="21"/>
-      <c r="E6" s="21"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="26" t="s">
-        <v>3</v>
-      </c>
-      <c r="H6" s="21"/>
-    </row>
-    <row r="7" spans="1:8" ht="60" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A7" s="21"/>
-      <c r="B7" s="23"/>
-      <c r="C7" s="21"/>
-      <c r="D7" s="21"/>
-      <c r="E7" s="21"/>
-      <c r="F7" s="21"/>
-      <c r="G7" s="28"/>
-      <c r="H7" s="21"/>
-    </row>
-    <row r="8" spans="1:8" ht="60" customHeight="1" thickTop="1">
-      <c r="A8" s="21"/>
-      <c r="C8" s="21"/>
-      <c r="D8" s="21"/>
-      <c r="E8" s="21"/>
-      <c r="F8" s="21"/>
-      <c r="H8" s="21"/>
-    </row>
-  </sheetData>
-  <mergeCells count="24">
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="D6:E8"/>
-    <mergeCell ref="D3:E4"/>
-    <mergeCell ref="H7:H8"/>
-    <mergeCell ref="H5:H6"/>
-    <mergeCell ref="H3:H4"/>
-    <mergeCell ref="G4:G5"/>
-    <mergeCell ref="G6:G7"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="C3:C6"/>
-    <mergeCell ref="D1:E2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="F3:F6"/>
-    <mergeCell ref="G2:G3"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6033,141 +6632,141 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="46" customHeight="1"/>
   <sheetData>
     <row r="1" spans="1:12" ht="46" customHeight="1" thickBot="1">
-      <c r="A1" s="33"/>
+      <c r="A1" s="25"/>
       <c r="B1" s="10"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="25" t="s">
+      <c r="C1" s="37"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
-      <c r="I1" s="30"/>
-      <c r="J1" s="34"/>
-      <c r="K1" s="30"/>
+      <c r="G1" s="29"/>
+      <c r="H1" s="29"/>
+      <c r="I1" s="38"/>
+      <c r="J1" s="37"/>
+      <c r="K1" s="38"/>
       <c r="L1" s="4"/>
     </row>
     <row r="2" spans="1:12" ht="46" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A2" s="33"/>
-      <c r="B2" s="36" t="s">
+      <c r="A2" s="25"/>
+      <c r="B2" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="34"/>
-      <c r="D2" s="31"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
-      <c r="I2" s="30"/>
-      <c r="J2" s="34"/>
-      <c r="K2" s="31"/>
-      <c r="L2" s="33"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
+      <c r="I2" s="38"/>
+      <c r="J2" s="37"/>
+      <c r="K2" s="39"/>
+      <c r="L2" s="25"/>
     </row>
     <row r="3" spans="1:12" ht="46" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A3" s="33"/>
-      <c r="B3" s="37"/>
-      <c r="C3" s="35"/>
-      <c r="D3" s="36" t="s">
+      <c r="A3" s="25"/>
+      <c r="B3" s="36"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="30"/>
-      <c r="F3" s="29" t="s">
+      <c r="E3" s="38"/>
+      <c r="F3" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="29"/>
-      <c r="H3" s="25"/>
-      <c r="I3" s="30"/>
+      <c r="G3" s="22"/>
+      <c r="H3" s="29"/>
+      <c r="I3" s="38"/>
       <c r="J3" s="10"/>
-      <c r="K3" s="38" t="s">
+      <c r="K3" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="L3" s="33"/>
+      <c r="L3" s="25"/>
     </row>
     <row r="4" spans="1:12" ht="46" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A4" s="33"/>
-      <c r="B4" s="43"/>
+      <c r="A4" s="25"/>
+      <c r="B4" s="40"/>
       <c r="C4" s="32"/>
-      <c r="D4" s="42"/>
-      <c r="E4" s="30"/>
-      <c r="F4" s="29"/>
-      <c r="G4" s="29"/>
-      <c r="H4" s="25"/>
-      <c r="I4" s="30"/>
-      <c r="J4" s="38" t="s">
+      <c r="D4" s="35"/>
+      <c r="E4" s="38"/>
+      <c r="F4" s="22"/>
+      <c r="G4" s="22"/>
+      <c r="H4" s="29"/>
+      <c r="I4" s="38"/>
+      <c r="J4" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="K4" s="39"/>
-      <c r="L4" s="33"/>
+      <c r="K4" s="42"/>
+      <c r="L4" s="25"/>
     </row>
     <row r="5" spans="1:12" ht="46" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A5" s="33"/>
-      <c r="B5" s="31"/>
+      <c r="A5" s="25"/>
+      <c r="B5" s="39"/>
       <c r="C5" s="32"/>
-      <c r="D5" s="42"/>
-      <c r="E5" s="30"/>
+      <c r="D5" s="35"/>
+      <c r="E5" s="38"/>
       <c r="F5" s="15"/>
       <c r="G5" s="17"/>
-      <c r="H5" s="25"/>
-      <c r="I5" s="31"/>
-      <c r="J5" s="41"/>
-      <c r="K5" s="35"/>
-      <c r="L5" s="33"/>
+      <c r="H5" s="29"/>
+      <c r="I5" s="39"/>
+      <c r="J5" s="43"/>
+      <c r="K5" s="31"/>
+      <c r="L5" s="25"/>
     </row>
     <row r="6" spans="1:12" ht="46" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A6" s="33"/>
-      <c r="B6" s="36" t="s">
+      <c r="A6" s="25"/>
+      <c r="B6" s="34" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="40"/>
-      <c r="D6" s="42"/>
-      <c r="E6" s="35"/>
-      <c r="F6" s="35" t="s">
+      <c r="C6" s="33"/>
+      <c r="D6" s="35"/>
+      <c r="E6" s="31"/>
+      <c r="F6" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="G6" s="35"/>
-      <c r="H6" s="35"/>
+      <c r="G6" s="31"/>
+      <c r="H6" s="31"/>
       <c r="I6" s="32"/>
-      <c r="J6" s="41"/>
-      <c r="K6" s="40"/>
-      <c r="L6" s="33"/>
+      <c r="J6" s="43"/>
+      <c r="K6" s="33"/>
+      <c r="L6" s="25"/>
     </row>
     <row r="7" spans="1:12" ht="46" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A7" s="33"/>
-      <c r="B7" s="37"/>
-      <c r="C7" s="36" t="s">
+      <c r="A7" s="25"/>
+      <c r="B7" s="36"/>
+      <c r="C7" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="37"/>
+      <c r="D7" s="36"/>
       <c r="E7" s="32"/>
       <c r="F7" s="32"/>
       <c r="G7" s="32"/>
       <c r="H7" s="32"/>
       <c r="I7" s="32"/>
-      <c r="J7" s="39"/>
-      <c r="K7" s="38" t="s">
+      <c r="J7" s="42"/>
+      <c r="K7" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="L7" s="33"/>
+      <c r="L7" s="25"/>
     </row>
     <row r="8" spans="1:12" ht="46" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A8" s="33"/>
-      <c r="B8" s="43"/>
-      <c r="C8" s="42"/>
+      <c r="A8" s="25"/>
+      <c r="B8" s="40"/>
+      <c r="C8" s="35"/>
       <c r="D8" s="32"/>
       <c r="E8" s="32"/>
       <c r="F8" s="32"/>
       <c r="G8" s="32"/>
       <c r="H8" s="32"/>
       <c r="I8" s="32"/>
-      <c r="J8" s="35"/>
-      <c r="K8" s="39"/>
-      <c r="L8" s="33"/>
+      <c r="J8" s="31"/>
+      <c r="K8" s="42"/>
+      <c r="L8" s="25"/>
     </row>
     <row r="9" spans="1:12" ht="46" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A9" s="33"/>
-      <c r="B9" s="30"/>
-      <c r="C9" s="37"/>
+      <c r="A9" s="25"/>
+      <c r="B9" s="38"/>
+      <c r="C9" s="36"/>
       <c r="D9" s="32"/>
       <c r="E9" s="32"/>
       <c r="F9" s="32"/>
@@ -6175,11 +6774,11 @@
       <c r="H9" s="32"/>
       <c r="I9" s="32"/>
       <c r="J9" s="32"/>
-      <c r="K9" s="35"/>
-      <c r="L9" s="33"/>
+      <c r="K9" s="31"/>
+      <c r="L9" s="25"/>
     </row>
     <row r="10" spans="1:12" ht="46" customHeight="1" thickTop="1">
-      <c r="A10" s="33"/>
+      <c r="A10" s="25"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
       <c r="D10" s="32"/>
@@ -6319,20 +6918,13 @@
     </row>
   </sheetData>
   <mergeCells count="37">
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="C3:C6"/>
-    <mergeCell ref="D3:D7"/>
-    <mergeCell ref="F3:G4"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="E1:E5"/>
-    <mergeCell ref="F1:G2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="E6:E10"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="I1:I5"/>
+    <mergeCell ref="I6:I10"/>
+    <mergeCell ref="L2:L3"/>
+    <mergeCell ref="L4:L5"/>
+    <mergeCell ref="L6:L7"/>
+    <mergeCell ref="L8:L9"/>
+    <mergeCell ref="J1:J2"/>
     <mergeCell ref="H6:H10"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="H1:H5"/>
@@ -6349,13 +6941,20 @@
     <mergeCell ref="F7:G10"/>
     <mergeCell ref="B8:B9"/>
     <mergeCell ref="D8:D10"/>
-    <mergeCell ref="I1:I5"/>
-    <mergeCell ref="I6:I10"/>
-    <mergeCell ref="L2:L3"/>
-    <mergeCell ref="L4:L5"/>
-    <mergeCell ref="L6:L7"/>
-    <mergeCell ref="L8:L9"/>
-    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="C3:C6"/>
+    <mergeCell ref="D3:D7"/>
+    <mergeCell ref="F3:G4"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="E1:E5"/>
+    <mergeCell ref="F1:G2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="E6:E10"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="A5:A6"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6369,155 +6968,155 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="46" customHeight="1"/>
   <sheetData>
     <row r="1" spans="1:12" ht="46" customHeight="1" thickBot="1">
-      <c r="A1" s="33"/>
+      <c r="A1" s="25"/>
       <c r="B1" s="10"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="25" t="s">
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
+      <c r="G1" s="29"/>
+      <c r="H1" s="29"/>
       <c r="I1" s="32"/>
       <c r="J1" s="32"/>
       <c r="K1" s="7"/>
-      <c r="L1" s="33"/>
+      <c r="L1" s="25"/>
     </row>
     <row r="2" spans="1:12" ht="46" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A2" s="33"/>
-      <c r="B2" s="36" t="s">
+      <c r="A2" s="25"/>
+      <c r="B2" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
       <c r="I2" s="32"/>
-      <c r="J2" s="40"/>
-      <c r="K2" s="38" t="s">
+      <c r="J2" s="33"/>
+      <c r="K2" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="L2" s="33"/>
+      <c r="L2" s="25"/>
     </row>
     <row r="3" spans="1:12" ht="46" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A3" s="33"/>
-      <c r="B3" s="37"/>
-      <c r="C3" s="35"/>
-      <c r="D3" s="36" t="s">
+      <c r="A3" s="25"/>
+      <c r="B3" s="36"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="30"/>
-      <c r="F3" s="29" t="s">
+      <c r="E3" s="38"/>
+      <c r="F3" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="29"/>
-      <c r="H3" s="25"/>
-      <c r="I3" s="38" t="s">
+      <c r="G3" s="22"/>
+      <c r="H3" s="29"/>
+      <c r="I3" s="41" t="s">
         <v>8</v>
       </c>
-      <c r="J3" s="35"/>
-      <c r="K3" s="39"/>
-      <c r="L3" s="33"/>
+      <c r="J3" s="31"/>
+      <c r="K3" s="42"/>
+      <c r="L3" s="25"/>
     </row>
     <row r="4" spans="1:12" ht="46" customHeight="1" thickTop="1">
-      <c r="A4" s="33"/>
-      <c r="B4" s="43"/>
+      <c r="A4" s="25"/>
+      <c r="B4" s="40"/>
       <c r="C4" s="32"/>
-      <c r="D4" s="42"/>
-      <c r="E4" s="30"/>
-      <c r="F4" s="29"/>
-      <c r="G4" s="29"/>
-      <c r="H4" s="25"/>
-      <c r="I4" s="41"/>
+      <c r="D4" s="35"/>
+      <c r="E4" s="38"/>
+      <c r="F4" s="22"/>
+      <c r="G4" s="22"/>
+      <c r="H4" s="29"/>
+      <c r="I4" s="43"/>
       <c r="J4" s="32"/>
-      <c r="K4" s="35"/>
-      <c r="L4" s="33"/>
+      <c r="K4" s="31"/>
+      <c r="L4" s="25"/>
     </row>
     <row r="5" spans="1:12" ht="46" customHeight="1" thickBot="1">
-      <c r="A5" s="33"/>
-      <c r="B5" s="31"/>
+      <c r="A5" s="25"/>
+      <c r="B5" s="39"/>
       <c r="C5" s="32"/>
-      <c r="D5" s="42"/>
-      <c r="E5" s="30"/>
+      <c r="D5" s="35"/>
+      <c r="E5" s="38"/>
       <c r="F5" s="15"/>
       <c r="G5" s="17"/>
-      <c r="H5" s="25"/>
-      <c r="I5" s="41"/>
+      <c r="H5" s="29"/>
+      <c r="I5" s="43"/>
       <c r="J5" s="32"/>
-      <c r="K5" s="40"/>
-      <c r="L5" s="33"/>
+      <c r="K5" s="33"/>
+      <c r="L5" s="25"/>
     </row>
     <row r="6" spans="1:12" ht="46" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A6" s="33"/>
-      <c r="B6" s="36" t="s">
+      <c r="A6" s="25"/>
+      <c r="B6" s="34" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="40"/>
-      <c r="D6" s="42"/>
-      <c r="E6" s="35"/>
-      <c r="F6" s="35" t="s">
+      <c r="C6" s="33"/>
+      <c r="D6" s="35"/>
+      <c r="E6" s="31"/>
+      <c r="F6" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="G6" s="35"/>
-      <c r="H6" s="35"/>
-      <c r="I6" s="41"/>
-      <c r="J6" s="40"/>
-      <c r="K6" s="38" t="s">
+      <c r="G6" s="31"/>
+      <c r="H6" s="31"/>
+      <c r="I6" s="43"/>
+      <c r="J6" s="33"/>
+      <c r="K6" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="L6" s="33"/>
+      <c r="L6" s="25"/>
     </row>
     <row r="7" spans="1:12" ht="46" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A7" s="33"/>
-      <c r="B7" s="37"/>
-      <c r="C7" s="36" t="s">
+      <c r="A7" s="25"/>
+      <c r="B7" s="36"/>
+      <c r="C7" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="37"/>
+      <c r="D7" s="36"/>
       <c r="E7" s="32"/>
       <c r="F7" s="32"/>
       <c r="G7" s="32"/>
       <c r="H7" s="32"/>
-      <c r="I7" s="39"/>
-      <c r="J7" s="38" t="s">
+      <c r="I7" s="42"/>
+      <c r="J7" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="K7" s="39"/>
-      <c r="L7" s="33"/>
+      <c r="K7" s="42"/>
+      <c r="L7" s="25"/>
     </row>
     <row r="8" spans="1:12" ht="46" customHeight="1" thickTop="1">
-      <c r="A8" s="33"/>
-      <c r="B8" s="43"/>
-      <c r="C8" s="42"/>
+      <c r="A8" s="25"/>
+      <c r="B8" s="40"/>
+      <c r="C8" s="35"/>
       <c r="D8" s="32"/>
       <c r="E8" s="32"/>
       <c r="F8" s="32"/>
       <c r="G8" s="32"/>
       <c r="H8" s="32"/>
       <c r="I8" s="32"/>
-      <c r="J8" s="41"/>
-      <c r="K8" s="35"/>
-      <c r="L8" s="33"/>
+      <c r="J8" s="43"/>
+      <c r="K8" s="31"/>
+      <c r="L8" s="25"/>
     </row>
     <row r="9" spans="1:12" ht="46" customHeight="1" thickBot="1">
-      <c r="A9" s="33"/>
-      <c r="B9" s="30"/>
-      <c r="C9" s="37"/>
+      <c r="A9" s="25"/>
+      <c r="B9" s="38"/>
+      <c r="C9" s="36"/>
       <c r="D9" s="32"/>
       <c r="E9" s="32"/>
       <c r="F9" s="32"/>
       <c r="G9" s="32"/>
       <c r="H9" s="32"/>
       <c r="I9" s="32"/>
-      <c r="J9" s="39"/>
-      <c r="K9" s="40"/>
-      <c r="L9" s="33"/>
+      <c r="J9" s="42"/>
+      <c r="K9" s="33"/>
+      <c r="L9" s="25"/>
     </row>
     <row r="10" spans="1:12" ht="46" customHeight="1" thickTop="1">
-      <c r="A10" s="33"/>
+      <c r="A10" s="25"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
       <c r="D10" s="32"/>
@@ -6528,7 +7127,7 @@
       <c r="I10" s="32"/>
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
-      <c r="L10" s="33"/>
+      <c r="L10" s="25"/>
     </row>
     <row r="11" spans="1:12" ht="46" customHeight="1">
       <c r="A11" s="4"/>
@@ -6656,17 +7255,17 @@
     </row>
   </sheetData>
   <mergeCells count="38">
-    <mergeCell ref="J1:J2"/>
-    <mergeCell ref="J3:J6"/>
-    <mergeCell ref="C7:C9"/>
-    <mergeCell ref="K2:K3"/>
-    <mergeCell ref="K4:K5"/>
-    <mergeCell ref="K6:K7"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="F1:G2"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="F7:G10"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="L3:L4"/>
+    <mergeCell ref="L5:L6"/>
+    <mergeCell ref="L7:L8"/>
+    <mergeCell ref="L9:L10"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="C3:C6"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="C1:C2"/>
     <mergeCell ref="A9:A10"/>
     <mergeCell ref="B8:B9"/>
     <mergeCell ref="K8:K9"/>
@@ -6683,17 +7282,17 @@
     <mergeCell ref="H1:H5"/>
     <mergeCell ref="H6:H10"/>
     <mergeCell ref="E6:E10"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="C3:C6"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="L1:L2"/>
-    <mergeCell ref="L3:L4"/>
-    <mergeCell ref="L5:L6"/>
-    <mergeCell ref="L7:L8"/>
-    <mergeCell ref="L9:L10"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="J3:J6"/>
+    <mergeCell ref="C7:C9"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="K4:K5"/>
+    <mergeCell ref="K6:K7"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="F1:G2"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="F7:G10"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6707,193 +7306,193 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="38" customHeight="1"/>
   <sheetData>
     <row r="1" spans="1:12" ht="38" customHeight="1" thickBot="1">
-      <c r="A1" s="33"/>
+      <c r="A1" s="25"/>
       <c r="B1" s="10"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="25" t="s">
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="29"/>
+      <c r="H1" s="29"/>
       <c r="I1" s="32"/>
       <c r="J1" s="32"/>
       <c r="K1" s="32"/>
     </row>
     <row r="2" spans="1:12" ht="38" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A2" s="33"/>
-      <c r="B2" s="36" t="s">
+      <c r="A2" s="25"/>
+      <c r="B2" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="31"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
       <c r="I2" s="32"/>
       <c r="J2" s="32"/>
-      <c r="K2" s="40"/>
-      <c r="L2" s="33"/>
+      <c r="K2" s="33"/>
+      <c r="L2" s="25"/>
     </row>
     <row r="3" spans="1:12" ht="38" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A3" s="33"/>
-      <c r="B3" s="37"/>
-      <c r="C3" s="36" t="s">
+      <c r="A3" s="25"/>
+      <c r="B3" s="36"/>
+      <c r="C3" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="30"/>
-      <c r="E3" s="25"/>
-      <c r="F3" s="25"/>
-      <c r="G3" s="25"/>
-      <c r="H3" s="25"/>
-      <c r="I3" s="40"/>
-      <c r="J3" s="40"/>
-      <c r="K3" s="38" t="s">
+      <c r="D3" s="38"/>
+      <c r="E3" s="29"/>
+      <c r="F3" s="29"/>
+      <c r="G3" s="29"/>
+      <c r="H3" s="29"/>
+      <c r="I3" s="33"/>
+      <c r="J3" s="33"/>
+      <c r="K3" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="L3" s="33"/>
+      <c r="L3" s="25"/>
     </row>
     <row r="4" spans="1:12" ht="38" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A4" s="33"/>
-      <c r="B4" s="43"/>
-      <c r="C4" s="42"/>
-      <c r="D4" s="31"/>
+      <c r="A4" s="25"/>
+      <c r="B4" s="40"/>
+      <c r="C4" s="35"/>
+      <c r="D4" s="39"/>
       <c r="E4" s="32"/>
-      <c r="F4" s="29" t="s">
+      <c r="F4" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="G4" s="29"/>
-      <c r="H4" s="42"/>
-      <c r="I4" s="38" t="s">
+      <c r="G4" s="22"/>
+      <c r="H4" s="35"/>
+      <c r="I4" s="41" t="s">
         <v>8</v>
       </c>
-      <c r="J4" s="35"/>
-      <c r="K4" s="39"/>
-      <c r="L4" s="33"/>
+      <c r="J4" s="31"/>
+      <c r="K4" s="42"/>
+      <c r="L4" s="25"/>
     </row>
     <row r="5" spans="1:12" ht="38" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A5" s="33"/>
-      <c r="B5" s="31"/>
-      <c r="C5" s="42"/>
-      <c r="D5" s="36" t="s">
+      <c r="A5" s="25"/>
+      <c r="B5" s="39"/>
+      <c r="C5" s="35"/>
+      <c r="D5" s="34" t="s">
         <v>11</v>
       </c>
       <c r="E5" s="32"/>
-      <c r="F5" s="29"/>
-      <c r="G5" s="29"/>
-      <c r="H5" s="42"/>
-      <c r="I5" s="41"/>
+      <c r="F5" s="22"/>
+      <c r="G5" s="22"/>
+      <c r="H5" s="35"/>
+      <c r="I5" s="43"/>
       <c r="J5" s="32"/>
-      <c r="K5" s="35"/>
-      <c r="L5" s="33"/>
+      <c r="K5" s="31"/>
+      <c r="L5" s="25"/>
     </row>
     <row r="6" spans="1:12" ht="38" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A6" s="33"/>
-      <c r="B6" s="36" t="s">
+      <c r="A6" s="25"/>
+      <c r="B6" s="34" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="37"/>
-      <c r="D6" s="42"/>
+      <c r="C6" s="36"/>
+      <c r="D6" s="35"/>
       <c r="E6" s="32"/>
-      <c r="F6" s="42"/>
-      <c r="G6" s="41"/>
-      <c r="H6" s="42"/>
-      <c r="I6" s="41"/>
+      <c r="F6" s="35"/>
+      <c r="G6" s="43"/>
+      <c r="H6" s="35"/>
+      <c r="I6" s="43"/>
       <c r="J6" s="32"/>
-      <c r="K6" s="40"/>
-      <c r="L6" s="33"/>
+      <c r="K6" s="33"/>
+      <c r="L6" s="25"/>
     </row>
     <row r="7" spans="1:12" ht="38" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A7" s="33"/>
-      <c r="B7" s="37"/>
-      <c r="C7" s="35"/>
-      <c r="D7" s="42"/>
-      <c r="E7" s="40"/>
-      <c r="F7" s="42"/>
-      <c r="G7" s="41"/>
-      <c r="H7" s="37"/>
-      <c r="I7" s="41"/>
-      <c r="J7" s="40"/>
-      <c r="K7" s="38" t="s">
+      <c r="A7" s="25"/>
+      <c r="B7" s="36"/>
+      <c r="C7" s="31"/>
+      <c r="D7" s="35"/>
+      <c r="E7" s="33"/>
+      <c r="F7" s="35"/>
+      <c r="G7" s="43"/>
+      <c r="H7" s="36"/>
+      <c r="I7" s="43"/>
+      <c r="J7" s="33"/>
+      <c r="K7" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="L7" s="33"/>
+      <c r="L7" s="25"/>
     </row>
     <row r="8" spans="1:12" ht="38" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A8" s="33"/>
-      <c r="B8" s="43"/>
+      <c r="A8" s="25"/>
+      <c r="B8" s="40"/>
       <c r="C8" s="32"/>
-      <c r="D8" s="42"/>
-      <c r="E8" s="35"/>
-      <c r="F8" s="35" t="s">
+      <c r="D8" s="35"/>
+      <c r="E8" s="31"/>
+      <c r="F8" s="31" t="s">
         <v>13</v>
       </c>
-      <c r="G8" s="35"/>
-      <c r="H8" s="35"/>
-      <c r="I8" s="39"/>
-      <c r="J8" s="38" t="s">
+      <c r="G8" s="31"/>
+      <c r="H8" s="31"/>
+      <c r="I8" s="42"/>
+      <c r="J8" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="K8" s="39"/>
-      <c r="L8" s="33"/>
+      <c r="K8" s="42"/>
+      <c r="L8" s="25"/>
     </row>
     <row r="9" spans="1:12" ht="38" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A9" s="33"/>
-      <c r="B9" s="31"/>
+      <c r="A9" s="25"/>
+      <c r="B9" s="39"/>
       <c r="C9" s="32"/>
-      <c r="D9" s="42"/>
+      <c r="D9" s="35"/>
       <c r="E9" s="32"/>
       <c r="F9" s="32"/>
       <c r="G9" s="32"/>
       <c r="H9" s="32"/>
-      <c r="I9" s="35"/>
-      <c r="J9" s="41"/>
-      <c r="K9" s="35"/>
-      <c r="L9" s="33"/>
+      <c r="I9" s="31"/>
+      <c r="J9" s="43"/>
+      <c r="K9" s="31"/>
+      <c r="L9" s="25"/>
     </row>
     <row r="10" spans="1:12" ht="38" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A10" s="33"/>
-      <c r="B10" s="36" t="s">
+      <c r="A10" s="25"/>
+      <c r="B10" s="34" t="s">
         <v>6</v>
       </c>
       <c r="C10" s="32"/>
-      <c r="D10" s="42"/>
+      <c r="D10" s="35"/>
       <c r="E10" s="32"/>
-      <c r="F10" s="30"/>
-      <c r="G10" s="30"/>
+      <c r="F10" s="38"/>
+      <c r="G10" s="38"/>
       <c r="H10" s="32"/>
       <c r="I10" s="32"/>
-      <c r="J10" s="39"/>
-      <c r="K10" s="40"/>
-      <c r="L10" s="33"/>
+      <c r="J10" s="42"/>
+      <c r="K10" s="33"/>
+      <c r="L10" s="25"/>
     </row>
     <row r="11" spans="1:12" ht="38" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A11" s="33"/>
-      <c r="B11" s="37"/>
-      <c r="C11" s="35"/>
-      <c r="D11" s="35"/>
+      <c r="A11" s="25"/>
+      <c r="B11" s="36"/>
+      <c r="C11" s="31"/>
+      <c r="D11" s="31"/>
       <c r="E11" s="32"/>
-      <c r="F11" s="30"/>
-      <c r="G11" s="30"/>
+      <c r="F11" s="38"/>
+      <c r="G11" s="38"/>
       <c r="H11" s="32"/>
       <c r="I11" s="32"/>
-      <c r="J11" s="43"/>
-      <c r="K11" s="43"/>
-      <c r="L11" s="33"/>
+      <c r="J11" s="40"/>
+      <c r="K11" s="40"/>
+      <c r="L11" s="25"/>
     </row>
     <row r="12" spans="1:12" ht="38" customHeight="1" thickTop="1">
-      <c r="A12" s="33"/>
+      <c r="A12" s="25"/>
       <c r="C12" s="32"/>
       <c r="D12" s="32"/>
       <c r="E12" s="32"/>
-      <c r="F12" s="30"/>
-      <c r="G12" s="30"/>
+      <c r="F12" s="38"/>
+      <c r="G12" s="38"/>
       <c r="H12" s="32"/>
       <c r="I12" s="32"/>
-      <c r="J12" s="30"/>
-      <c r="K12" s="30"/>
+      <c r="J12" s="38"/>
+      <c r="K12" s="38"/>
     </row>
     <row r="13" spans="1:12" ht="38" customHeight="1">
       <c r="A13" s="4"/>
@@ -7005,6 +7604,36 @@
     </row>
   </sheetData>
   <mergeCells count="46">
+    <mergeCell ref="E1:H3"/>
+    <mergeCell ref="E4:E7"/>
+    <mergeCell ref="H4:H7"/>
+    <mergeCell ref="L6:L7"/>
+    <mergeCell ref="L8:L9"/>
+    <mergeCell ref="L10:L11"/>
+    <mergeCell ref="I1:I3"/>
+    <mergeCell ref="J1:J3"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="K3:K4"/>
+    <mergeCell ref="K5:K6"/>
+    <mergeCell ref="K7:K8"/>
+    <mergeCell ref="K9:K10"/>
+    <mergeCell ref="L2:L3"/>
+    <mergeCell ref="L4:L5"/>
+    <mergeCell ref="J8:J10"/>
+    <mergeCell ref="J4:J7"/>
+    <mergeCell ref="I4:I8"/>
+    <mergeCell ref="I9:I12"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="J11:J12"/>
+    <mergeCell ref="K11:K12"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="E8:E12"/>
+    <mergeCell ref="F8:G9"/>
+    <mergeCell ref="H8:H12"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="F10:G12"/>
     <mergeCell ref="D1:D4"/>
     <mergeCell ref="F4:G5"/>
     <mergeCell ref="C7:C10"/>
@@ -7021,36 +7650,6 @@
     <mergeCell ref="F6:F7"/>
     <mergeCell ref="G6:G7"/>
     <mergeCell ref="A7:A8"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="E8:E12"/>
-    <mergeCell ref="F8:G9"/>
-    <mergeCell ref="H8:H12"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="F10:G12"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="J11:J12"/>
-    <mergeCell ref="K11:K12"/>
-    <mergeCell ref="L10:L11"/>
-    <mergeCell ref="I1:I3"/>
-    <mergeCell ref="J1:J3"/>
-    <mergeCell ref="K1:K2"/>
-    <mergeCell ref="K3:K4"/>
-    <mergeCell ref="K5:K6"/>
-    <mergeCell ref="K7:K8"/>
-    <mergeCell ref="K9:K10"/>
-    <mergeCell ref="L2:L3"/>
-    <mergeCell ref="L4:L5"/>
-    <mergeCell ref="J8:J10"/>
-    <mergeCell ref="J4:J7"/>
-    <mergeCell ref="I4:I8"/>
-    <mergeCell ref="I9:I12"/>
-    <mergeCell ref="E1:H3"/>
-    <mergeCell ref="E4:E7"/>
-    <mergeCell ref="H4:H7"/>
-    <mergeCell ref="L6:L7"/>
-    <mergeCell ref="L8:L9"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7064,197 +7663,197 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="38" customHeight="1"/>
   <sheetData>
     <row r="1" spans="1:12" ht="38" customHeight="1" thickBot="1">
-      <c r="A1" s="33"/>
+      <c r="A1" s="25"/>
       <c r="B1" s="10"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="25" t="s">
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="29"/>
+      <c r="H1" s="29"/>
       <c r="I1" s="32"/>
       <c r="J1" s="32"/>
       <c r="K1" s="7"/>
-      <c r="L1" s="33"/>
+      <c r="L1" s="25"/>
     </row>
     <row r="2" spans="1:12" ht="38" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A2" s="33"/>
-      <c r="B2" s="36" t="s">
+      <c r="A2" s="25"/>
+      <c r="B2" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="31"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
       <c r="I2" s="32"/>
-      <c r="J2" s="40"/>
-      <c r="K2" s="38" t="s">
+      <c r="J2" s="33"/>
+      <c r="K2" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="L2" s="33"/>
+      <c r="L2" s="25"/>
     </row>
     <row r="3" spans="1:12" ht="38" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A3" s="33"/>
-      <c r="B3" s="37"/>
-      <c r="C3" s="36" t="s">
+      <c r="A3" s="25"/>
+      <c r="B3" s="36"/>
+      <c r="C3" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="30"/>
-      <c r="E3" s="25"/>
-      <c r="F3" s="25"/>
-      <c r="G3" s="25"/>
-      <c r="H3" s="25"/>
+      <c r="D3" s="38"/>
+      <c r="E3" s="29"/>
+      <c r="F3" s="29"/>
+      <c r="G3" s="29"/>
+      <c r="H3" s="29"/>
       <c r="I3" s="32"/>
-      <c r="J3" s="38" t="s">
+      <c r="J3" s="41" t="s">
         <v>8</v>
       </c>
-      <c r="K3" s="39"/>
-      <c r="L3" s="33"/>
+      <c r="K3" s="42"/>
+      <c r="L3" s="25"/>
     </row>
     <row r="4" spans="1:12" ht="38" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A4" s="33"/>
-      <c r="B4" s="43"/>
-      <c r="C4" s="42"/>
-      <c r="D4" s="31"/>
+      <c r="A4" s="25"/>
+      <c r="B4" s="40"/>
+      <c r="C4" s="35"/>
+      <c r="D4" s="39"/>
       <c r="E4" s="32"/>
-      <c r="F4" s="29" t="s">
+      <c r="F4" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="G4" s="29"/>
+      <c r="G4" s="22"/>
       <c r="H4" s="32"/>
-      <c r="I4" s="40"/>
-      <c r="J4" s="41"/>
-      <c r="K4" s="35"/>
-      <c r="L4" s="33"/>
+      <c r="I4" s="33"/>
+      <c r="J4" s="43"/>
+      <c r="K4" s="31"/>
+      <c r="L4" s="25"/>
     </row>
     <row r="5" spans="1:12" ht="38" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A5" s="33"/>
-      <c r="B5" s="31"/>
-      <c r="C5" s="42"/>
-      <c r="D5" s="36" t="s">
+      <c r="A5" s="25"/>
+      <c r="B5" s="39"/>
+      <c r="C5" s="35"/>
+      <c r="D5" s="34" t="s">
         <v>11</v>
       </c>
       <c r="E5" s="32"/>
-      <c r="F5" s="29"/>
-      <c r="G5" s="29"/>
+      <c r="F5" s="22"/>
+      <c r="G5" s="22"/>
       <c r="H5" s="32"/>
-      <c r="I5" s="38" t="s">
+      <c r="I5" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="J5" s="41"/>
-      <c r="K5" s="40"/>
-      <c r="L5" s="33"/>
+      <c r="J5" s="43"/>
+      <c r="K5" s="33"/>
+      <c r="L5" s="25"/>
     </row>
     <row r="6" spans="1:12" ht="38" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A6" s="33"/>
-      <c r="B6" s="36" t="s">
+      <c r="A6" s="25"/>
+      <c r="B6" s="34" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="37"/>
-      <c r="D6" s="42"/>
+      <c r="C6" s="36"/>
+      <c r="D6" s="35"/>
       <c r="E6" s="32"/>
-      <c r="F6" s="42"/>
-      <c r="G6" s="41"/>
+      <c r="F6" s="35"/>
+      <c r="G6" s="43"/>
       <c r="H6" s="32"/>
-      <c r="I6" s="41"/>
-      <c r="J6" s="39"/>
-      <c r="K6" s="38" t="s">
+      <c r="I6" s="43"/>
+      <c r="J6" s="42"/>
+      <c r="K6" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="L6" s="33"/>
+      <c r="L6" s="25"/>
     </row>
     <row r="7" spans="1:12" ht="38" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A7" s="33"/>
-      <c r="B7" s="37"/>
-      <c r="C7" s="35"/>
-      <c r="D7" s="42"/>
-      <c r="E7" s="40"/>
-      <c r="F7" s="42"/>
-      <c r="G7" s="41"/>
-      <c r="H7" s="40"/>
-      <c r="I7" s="41"/>
-      <c r="J7" s="35"/>
-      <c r="K7" s="39"/>
-      <c r="L7" s="33"/>
+      <c r="A7" s="25"/>
+      <c r="B7" s="36"/>
+      <c r="C7" s="31"/>
+      <c r="D7" s="35"/>
+      <c r="E7" s="33"/>
+      <c r="F7" s="35"/>
+      <c r="G7" s="43"/>
+      <c r="H7" s="33"/>
+      <c r="I7" s="43"/>
+      <c r="J7" s="31"/>
+      <c r="K7" s="42"/>
+      <c r="L7" s="25"/>
     </row>
     <row r="8" spans="1:12" ht="38" customHeight="1" thickTop="1">
-      <c r="A8" s="33"/>
-      <c r="B8" s="43"/>
+      <c r="A8" s="25"/>
+      <c r="B8" s="40"/>
       <c r="C8" s="32"/>
-      <c r="D8" s="42"/>
-      <c r="E8" s="35"/>
-      <c r="F8" s="35" t="s">
+      <c r="D8" s="35"/>
+      <c r="E8" s="31"/>
+      <c r="F8" s="31" t="s">
         <v>13</v>
       </c>
-      <c r="G8" s="35"/>
-      <c r="H8" s="35"/>
-      <c r="I8" s="41"/>
+      <c r="G8" s="31"/>
+      <c r="H8" s="31"/>
+      <c r="I8" s="43"/>
       <c r="J8" s="32"/>
-      <c r="K8" s="35"/>
-      <c r="L8" s="33"/>
+      <c r="K8" s="31"/>
+      <c r="L8" s="25"/>
     </row>
     <row r="9" spans="1:12" ht="38" customHeight="1" thickBot="1">
-      <c r="A9" s="33"/>
-      <c r="B9" s="31"/>
+      <c r="A9" s="25"/>
+      <c r="B9" s="39"/>
       <c r="C9" s="32"/>
-      <c r="D9" s="42"/>
+      <c r="D9" s="35"/>
       <c r="E9" s="32"/>
       <c r="F9" s="32"/>
       <c r="G9" s="32"/>
       <c r="H9" s="32"/>
-      <c r="I9" s="41"/>
+      <c r="I9" s="43"/>
       <c r="J9" s="32"/>
-      <c r="K9" s="40"/>
-      <c r="L9" s="33"/>
+      <c r="K9" s="33"/>
+      <c r="L9" s="25"/>
     </row>
     <row r="10" spans="1:12" ht="38" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A10" s="33"/>
-      <c r="B10" s="36" t="s">
+      <c r="A10" s="25"/>
+      <c r="B10" s="34" t="s">
         <v>6</v>
       </c>
       <c r="C10" s="32"/>
-      <c r="D10" s="42"/>
+      <c r="D10" s="35"/>
       <c r="E10" s="32"/>
-      <c r="F10" s="30"/>
-      <c r="G10" s="30"/>
+      <c r="F10" s="38"/>
+      <c r="G10" s="38"/>
       <c r="H10" s="32"/>
-      <c r="I10" s="41"/>
+      <c r="I10" s="43"/>
       <c r="J10" s="32"/>
-      <c r="K10" s="38" t="s">
+      <c r="K10" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="L10" s="33"/>
+      <c r="L10" s="25"/>
     </row>
     <row r="11" spans="1:12" ht="38" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A11" s="33"/>
-      <c r="B11" s="37"/>
-      <c r="C11" s="35"/>
-      <c r="D11" s="35"/>
+      <c r="A11" s="25"/>
+      <c r="B11" s="36"/>
+      <c r="C11" s="31"/>
+      <c r="D11" s="31"/>
       <c r="E11" s="32"/>
-      <c r="F11" s="30"/>
-      <c r="G11" s="30"/>
+      <c r="F11" s="38"/>
+      <c r="G11" s="38"/>
       <c r="H11" s="32"/>
-      <c r="I11" s="35"/>
-      <c r="J11" s="35"/>
-      <c r="K11" s="39"/>
-      <c r="L11" s="33"/>
+      <c r="I11" s="31"/>
+      <c r="J11" s="31"/>
+      <c r="K11" s="42"/>
+      <c r="L11" s="25"/>
     </row>
     <row r="12" spans="1:12" ht="38" customHeight="1" thickTop="1">
-      <c r="A12" s="33"/>
+      <c r="A12" s="25"/>
       <c r="C12" s="32"/>
       <c r="D12" s="32"/>
       <c r="E12" s="32"/>
-      <c r="F12" s="30"/>
-      <c r="G12" s="30"/>
+      <c r="F12" s="38"/>
+      <c r="G12" s="38"/>
       <c r="H12" s="32"/>
       <c r="I12" s="32"/>
       <c r="J12" s="32"/>
       <c r="K12" s="1"/>
-      <c r="L12" s="33"/>
+      <c r="L12" s="25"/>
     </row>
     <row r="13" spans="1:12" ht="38" customHeight="1">
       <c r="A13" s="4"/>
@@ -7366,6 +7965,36 @@
     </row>
   </sheetData>
   <mergeCells count="46">
+    <mergeCell ref="L11:L12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="I11:I12"/>
+    <mergeCell ref="J11:J12"/>
+    <mergeCell ref="K10:K11"/>
+    <mergeCell ref="J7:J10"/>
+    <mergeCell ref="L7:L8"/>
+    <mergeCell ref="K8:K9"/>
+    <mergeCell ref="L9:L10"/>
+    <mergeCell ref="F10:G12"/>
+    <mergeCell ref="E8:E12"/>
+    <mergeCell ref="H8:H12"/>
+    <mergeCell ref="E4:E7"/>
+    <mergeCell ref="H4:H7"/>
+    <mergeCell ref="L3:L4"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="D5:D10"/>
+    <mergeCell ref="F4:G5"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="F8:G9"/>
+    <mergeCell ref="K4:K5"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="I5:I10"/>
+    <mergeCell ref="I1:I4"/>
+    <mergeCell ref="J1:J2"/>
     <mergeCell ref="L1:L2"/>
     <mergeCell ref="L5:L6"/>
     <mergeCell ref="B6:B7"/>
@@ -7382,36 +8011,6 @@
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="D1:D4"/>
-    <mergeCell ref="K4:K5"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="I5:I10"/>
-    <mergeCell ref="I1:I4"/>
-    <mergeCell ref="J1:J2"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="D5:D10"/>
-    <mergeCell ref="F4:G5"/>
-    <mergeCell ref="F6:F7"/>
-    <mergeCell ref="G6:G7"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="F8:G9"/>
-    <mergeCell ref="L11:L12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="I11:I12"/>
-    <mergeCell ref="J11:J12"/>
-    <mergeCell ref="K10:K11"/>
-    <mergeCell ref="J7:J10"/>
-    <mergeCell ref="L7:L8"/>
-    <mergeCell ref="K8:K9"/>
-    <mergeCell ref="L9:L10"/>
-    <mergeCell ref="F10:G12"/>
-    <mergeCell ref="E8:E12"/>
-    <mergeCell ref="H8:H12"/>
-    <mergeCell ref="E4:E7"/>
-    <mergeCell ref="H4:H7"/>
-    <mergeCell ref="L3:L4"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7425,10 +8024,10 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="34" customHeight="1"/>
   <sheetData>
     <row r="1" spans="1:12" ht="34" customHeight="1" thickBot="1">
-      <c r="A1" s="33"/>
+      <c r="A1" s="25"/>
       <c r="B1" s="10"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
       <c r="E1" s="32"/>
       <c r="F1" s="44" t="s">
         <v>14</v>
@@ -7438,215 +8037,215 @@
       <c r="I1" s="32"/>
       <c r="J1" s="32"/>
       <c r="K1" s="7"/>
-      <c r="L1" s="33"/>
+      <c r="L1" s="25"/>
     </row>
     <row r="2" spans="1:12" ht="34" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A2" s="33"/>
-      <c r="B2" s="36" t="s">
+      <c r="A2" s="25"/>
+      <c r="B2" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="31"/>
-      <c r="D2" s="30"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="38"/>
       <c r="E2" s="32"/>
       <c r="F2" s="44"/>
       <c r="G2" s="44"/>
       <c r="H2" s="32"/>
       <c r="I2" s="32"/>
-      <c r="J2" s="40"/>
-      <c r="K2" s="38" t="s">
+      <c r="J2" s="33"/>
+      <c r="K2" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="L2" s="33"/>
+      <c r="L2" s="25"/>
     </row>
     <row r="3" spans="1:12" ht="34" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A3" s="33"/>
-      <c r="B3" s="37"/>
-      <c r="C3" s="36" t="s">
+      <c r="A3" s="25"/>
+      <c r="B3" s="36"/>
+      <c r="C3" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="30"/>
+      <c r="D3" s="38"/>
       <c r="E3" s="32"/>
       <c r="F3" s="44"/>
       <c r="G3" s="44"/>
       <c r="H3" s="32"/>
       <c r="I3" s="32"/>
-      <c r="J3" s="38" t="s">
+      <c r="J3" s="41" t="s">
         <v>8</v>
       </c>
-      <c r="K3" s="39"/>
-      <c r="L3" s="33"/>
+      <c r="K3" s="42"/>
+      <c r="L3" s="25"/>
     </row>
     <row r="4" spans="1:12" ht="34" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A4" s="33"/>
-      <c r="B4" s="43"/>
-      <c r="C4" s="42"/>
-      <c r="D4" s="31"/>
+      <c r="A4" s="25"/>
+      <c r="B4" s="40"/>
+      <c r="C4" s="35"/>
+      <c r="D4" s="39"/>
       <c r="E4" s="32"/>
       <c r="F4" s="44"/>
       <c r="G4" s="44"/>
       <c r="H4" s="32"/>
-      <c r="I4" s="40"/>
-      <c r="J4" s="41"/>
-      <c r="K4" s="35"/>
-      <c r="L4" s="33"/>
+      <c r="I4" s="33"/>
+      <c r="J4" s="43"/>
+      <c r="K4" s="31"/>
+      <c r="L4" s="25"/>
     </row>
     <row r="5" spans="1:12" ht="34" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A5" s="33"/>
-      <c r="B5" s="31"/>
-      <c r="C5" s="42"/>
-      <c r="D5" s="36" t="s">
+      <c r="A5" s="25"/>
+      <c r="B5" s="39"/>
+      <c r="C5" s="35"/>
+      <c r="D5" s="34" t="s">
         <v>13</v>
       </c>
       <c r="E5" s="32"/>
-      <c r="F5" s="29" t="s">
+      <c r="F5" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="G5" s="29"/>
+      <c r="G5" s="22"/>
       <c r="H5" s="32"/>
-      <c r="I5" s="38" t="s">
+      <c r="I5" s="41" t="s">
         <v>13</v>
       </c>
-      <c r="J5" s="41"/>
-      <c r="K5" s="40"/>
-      <c r="L5" s="33"/>
+      <c r="J5" s="43"/>
+      <c r="K5" s="33"/>
+      <c r="L5" s="25"/>
     </row>
     <row r="6" spans="1:12" ht="34" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A6" s="33"/>
-      <c r="B6" s="36" t="s">
+      <c r="A6" s="25"/>
+      <c r="B6" s="34" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="37"/>
-      <c r="D6" s="42"/>
+      <c r="C6" s="36"/>
+      <c r="D6" s="35"/>
       <c r="E6" s="32"/>
-      <c r="F6" s="29"/>
-      <c r="G6" s="29"/>
+      <c r="F6" s="22"/>
+      <c r="G6" s="22"/>
       <c r="H6" s="32"/>
-      <c r="I6" s="41"/>
-      <c r="J6" s="39"/>
-      <c r="K6" s="38" t="s">
+      <c r="I6" s="43"/>
+      <c r="J6" s="42"/>
+      <c r="K6" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="L6" s="33"/>
+      <c r="L6" s="25"/>
     </row>
     <row r="7" spans="1:12" ht="34" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A7" s="33"/>
-      <c r="B7" s="37"/>
-      <c r="C7" s="35"/>
-      <c r="D7" s="42"/>
+      <c r="A7" s="25"/>
+      <c r="B7" s="36"/>
+      <c r="C7" s="31"/>
+      <c r="D7" s="35"/>
       <c r="E7" s="32"/>
-      <c r="F7" s="42"/>
-      <c r="G7" s="41"/>
+      <c r="F7" s="35"/>
+      <c r="G7" s="43"/>
       <c r="H7" s="32"/>
-      <c r="I7" s="41"/>
-      <c r="J7" s="35"/>
-      <c r="K7" s="39"/>
-      <c r="L7" s="33"/>
+      <c r="I7" s="43"/>
+      <c r="J7" s="31"/>
+      <c r="K7" s="42"/>
+      <c r="L7" s="25"/>
     </row>
     <row r="8" spans="1:12" ht="34" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A8" s="33"/>
-      <c r="B8" s="43"/>
+      <c r="A8" s="25"/>
+      <c r="B8" s="40"/>
       <c r="C8" s="32"/>
-      <c r="D8" s="42"/>
+      <c r="D8" s="35"/>
       <c r="E8" s="32"/>
-      <c r="F8" s="37"/>
-      <c r="G8" s="39"/>
+      <c r="F8" s="36"/>
+      <c r="G8" s="42"/>
       <c r="H8" s="32"/>
-      <c r="I8" s="41"/>
+      <c r="I8" s="43"/>
       <c r="J8" s="32"/>
-      <c r="K8" s="35"/>
-      <c r="L8" s="33"/>
+      <c r="K8" s="31"/>
+      <c r="L8" s="25"/>
     </row>
     <row r="9" spans="1:12" ht="34" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A9" s="33"/>
-      <c r="B9" s="31"/>
+      <c r="A9" s="25"/>
+      <c r="B9" s="39"/>
       <c r="C9" s="32"/>
-      <c r="D9" s="42"/>
-      <c r="E9" s="35"/>
-      <c r="F9" s="35" t="s">
+      <c r="D9" s="35"/>
+      <c r="E9" s="31"/>
+      <c r="F9" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="G9" s="35"/>
-      <c r="H9" s="35"/>
-      <c r="I9" s="41"/>
+      <c r="G9" s="31"/>
+      <c r="H9" s="31"/>
+      <c r="I9" s="43"/>
       <c r="J9" s="32"/>
-      <c r="K9" s="40"/>
-      <c r="L9" s="33"/>
+      <c r="K9" s="33"/>
+      <c r="L9" s="25"/>
     </row>
     <row r="10" spans="1:12" ht="34" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A10" s="33"/>
-      <c r="B10" s="36" t="s">
+      <c r="A10" s="25"/>
+      <c r="B10" s="34" t="s">
         <v>6</v>
       </c>
       <c r="C10" s="32"/>
-      <c r="D10" s="42"/>
+      <c r="D10" s="35"/>
       <c r="E10" s="32"/>
       <c r="F10" s="32"/>
       <c r="G10" s="32"/>
       <c r="H10" s="32"/>
-      <c r="I10" s="41"/>
+      <c r="I10" s="43"/>
       <c r="J10" s="32"/>
-      <c r="K10" s="38" t="s">
+      <c r="K10" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="L10" s="33"/>
+      <c r="L10" s="25"/>
     </row>
     <row r="11" spans="1:12" ht="34" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A11" s="33"/>
-      <c r="B11" s="37"/>
-      <c r="C11" s="36" t="s">
+      <c r="A11" s="25"/>
+      <c r="B11" s="36"/>
+      <c r="C11" s="34" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="42"/>
+      <c r="D11" s="35"/>
       <c r="E11" s="32"/>
-      <c r="F11" s="30"/>
-      <c r="G11" s="30"/>
+      <c r="F11" s="38"/>
+      <c r="G11" s="38"/>
       <c r="H11" s="32"/>
-      <c r="I11" s="35"/>
-      <c r="J11" s="35"/>
-      <c r="K11" s="39"/>
-      <c r="L11" s="33"/>
+      <c r="I11" s="31"/>
+      <c r="J11" s="31"/>
+      <c r="K11" s="42"/>
+      <c r="L11" s="25"/>
     </row>
     <row r="12" spans="1:12" ht="34" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A12" s="33"/>
-      <c r="B12" s="43"/>
-      <c r="C12" s="42"/>
-      <c r="D12" s="37"/>
+      <c r="A12" s="25"/>
+      <c r="B12" s="40"/>
+      <c r="C12" s="35"/>
+      <c r="D12" s="36"/>
       <c r="E12" s="32"/>
-      <c r="F12" s="30"/>
-      <c r="G12" s="30"/>
+      <c r="F12" s="38"/>
+      <c r="G12" s="38"/>
       <c r="H12" s="32"/>
       <c r="I12" s="32"/>
       <c r="J12" s="32"/>
       <c r="K12" s="32"/>
-      <c r="L12" s="33"/>
+      <c r="L12" s="25"/>
     </row>
     <row r="13" spans="1:12" ht="34" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A13" s="33"/>
-      <c r="B13" s="31"/>
-      <c r="C13" s="37"/>
-      <c r="D13" s="35"/>
+      <c r="A13" s="25"/>
+      <c r="B13" s="39"/>
+      <c r="C13" s="36"/>
+      <c r="D13" s="31"/>
       <c r="E13" s="32"/>
-      <c r="F13" s="30"/>
-      <c r="G13" s="30"/>
+      <c r="F13" s="38"/>
+      <c r="G13" s="38"/>
       <c r="H13" s="32"/>
       <c r="I13" s="32"/>
       <c r="J13" s="32"/>
       <c r="K13" s="32"/>
-      <c r="L13" s="33"/>
+      <c r="L13" s="25"/>
     </row>
     <row r="14" spans="1:12" ht="34" customHeight="1" thickTop="1">
-      <c r="A14" s="33"/>
+      <c r="A14" s="25"/>
       <c r="B14" s="2"/>
       <c r="C14" s="1"/>
       <c r="D14" s="32"/>
       <c r="E14" s="32"/>
-      <c r="F14" s="30"/>
-      <c r="G14" s="30"/>
+      <c r="F14" s="38"/>
+      <c r="G14" s="38"/>
       <c r="H14" s="32"/>
       <c r="I14" s="32"/>
       <c r="J14" s="32"/>
       <c r="K14" s="32"/>
-      <c r="L14" s="33"/>
+      <c r="L14" s="25"/>
     </row>
     <row r="15" spans="1:12" ht="34" customHeight="1">
       <c r="A15" s="4"/>
@@ -7736,6 +8335,40 @@
     </row>
   </sheetData>
   <mergeCells count="50">
+    <mergeCell ref="I5:I10"/>
+    <mergeCell ref="K10:K11"/>
+    <mergeCell ref="J7:J10"/>
+    <mergeCell ref="L7:L8"/>
+    <mergeCell ref="L9:L10"/>
+    <mergeCell ref="K4:K5"/>
+    <mergeCell ref="I1:I4"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="L3:L4"/>
+    <mergeCell ref="L11:L12"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="L13:L14"/>
+    <mergeCell ref="K12:K14"/>
+    <mergeCell ref="J11:J14"/>
+    <mergeCell ref="I11:I14"/>
+    <mergeCell ref="F5:G6"/>
+    <mergeCell ref="L5:L6"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="K6:K7"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="C7:C10"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="K8:K9"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="E9:E14"/>
+    <mergeCell ref="F9:G10"/>
+    <mergeCell ref="H9:H14"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="C11:C13"/>
+    <mergeCell ref="F11:G14"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="K2:K3"/>
     <mergeCell ref="A3:A4"/>
@@ -7752,40 +8385,6 @@
     <mergeCell ref="G7:G8"/>
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="D5:D12"/>
-    <mergeCell ref="F5:G6"/>
-    <mergeCell ref="L5:L6"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="K6:K7"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="C7:C10"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="K8:K9"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="E9:E14"/>
-    <mergeCell ref="F9:G10"/>
-    <mergeCell ref="H9:H14"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="C11:C13"/>
-    <mergeCell ref="F11:G14"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="D13:D14"/>
-    <mergeCell ref="L13:L14"/>
-    <mergeCell ref="K12:K14"/>
-    <mergeCell ref="J11:J14"/>
-    <mergeCell ref="I11:I14"/>
-    <mergeCell ref="I5:I10"/>
-    <mergeCell ref="K10:K11"/>
-    <mergeCell ref="J7:J10"/>
-    <mergeCell ref="L7:L8"/>
-    <mergeCell ref="L9:L10"/>
-    <mergeCell ref="K4:K5"/>
-    <mergeCell ref="I1:I4"/>
-    <mergeCell ref="J1:J2"/>
-    <mergeCell ref="L1:L2"/>
-    <mergeCell ref="L3:L4"/>
-    <mergeCell ref="L11:L12"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7799,10 +8398,10 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="34" customHeight="1"/>
   <sheetData>
     <row r="1" spans="1:12" ht="34" customHeight="1" thickBot="1">
-      <c r="A1" s="33"/>
+      <c r="A1" s="25"/>
       <c r="B1" s="10"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
       <c r="E1" s="32"/>
       <c r="F1" s="44" t="s">
         <v>14</v>
@@ -7812,217 +8411,217 @@
       <c r="I1" s="32"/>
       <c r="J1" s="32"/>
       <c r="K1" s="7"/>
-      <c r="L1" s="33"/>
+      <c r="L1" s="25"/>
     </row>
     <row r="2" spans="1:12" ht="34" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A2" s="33"/>
-      <c r="B2" s="36" t="s">
+      <c r="A2" s="25"/>
+      <c r="B2" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="31"/>
-      <c r="D2" s="30"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="38"/>
       <c r="E2" s="32"/>
       <c r="F2" s="44"/>
       <c r="G2" s="44"/>
       <c r="H2" s="32"/>
       <c r="I2" s="32"/>
-      <c r="J2" s="40"/>
-      <c r="K2" s="38" t="s">
+      <c r="J2" s="33"/>
+      <c r="K2" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="L2" s="33"/>
+      <c r="L2" s="25"/>
     </row>
     <row r="3" spans="1:12" ht="34" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A3" s="33"/>
-      <c r="B3" s="37"/>
-      <c r="C3" s="36" t="s">
+      <c r="A3" s="25"/>
+      <c r="B3" s="36"/>
+      <c r="C3" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="30"/>
+      <c r="D3" s="38"/>
       <c r="E3" s="32"/>
       <c r="F3" s="44"/>
       <c r="G3" s="44"/>
       <c r="H3" s="32"/>
       <c r="I3" s="32"/>
-      <c r="J3" s="38" t="s">
+      <c r="J3" s="41" t="s">
         <v>8</v>
       </c>
-      <c r="K3" s="39"/>
-      <c r="L3" s="33"/>
+      <c r="K3" s="42"/>
+      <c r="L3" s="25"/>
     </row>
     <row r="4" spans="1:12" ht="34" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A4" s="33"/>
-      <c r="B4" s="43"/>
-      <c r="C4" s="42"/>
-      <c r="D4" s="31"/>
+      <c r="A4" s="25"/>
+      <c r="B4" s="40"/>
+      <c r="C4" s="35"/>
+      <c r="D4" s="39"/>
       <c r="E4" s="32"/>
       <c r="F4" s="44"/>
       <c r="G4" s="44"/>
       <c r="H4" s="32"/>
-      <c r="I4" s="40"/>
-      <c r="J4" s="41"/>
-      <c r="K4" s="35"/>
-      <c r="L4" s="33"/>
+      <c r="I4" s="33"/>
+      <c r="J4" s="43"/>
+      <c r="K4" s="31"/>
+      <c r="L4" s="25"/>
     </row>
     <row r="5" spans="1:12" ht="34" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A5" s="33"/>
-      <c r="B5" s="31"/>
-      <c r="C5" s="42"/>
-      <c r="D5" s="36">
+      <c r="A5" s="25"/>
+      <c r="B5" s="39"/>
+      <c r="C5" s="35"/>
+      <c r="D5" s="34">
         <v>14</v>
       </c>
       <c r="E5" s="32"/>
-      <c r="F5" s="29" t="s">
+      <c r="F5" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="G5" s="29"/>
+      <c r="G5" s="22"/>
       <c r="H5" s="32"/>
-      <c r="I5" s="38" t="s">
+      <c r="I5" s="41" t="s">
         <v>13</v>
       </c>
-      <c r="J5" s="41"/>
-      <c r="K5" s="40"/>
-      <c r="L5" s="33"/>
+      <c r="J5" s="43"/>
+      <c r="K5" s="33"/>
+      <c r="L5" s="25"/>
     </row>
     <row r="6" spans="1:12" ht="34" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A6" s="33"/>
-      <c r="B6" s="36" t="s">
+      <c r="A6" s="25"/>
+      <c r="B6" s="34" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="37"/>
-      <c r="D6" s="42"/>
+      <c r="C6" s="36"/>
+      <c r="D6" s="35"/>
       <c r="E6" s="32"/>
-      <c r="F6" s="29"/>
-      <c r="G6" s="29"/>
+      <c r="F6" s="22"/>
+      <c r="G6" s="22"/>
       <c r="H6" s="32"/>
-      <c r="I6" s="41"/>
-      <c r="J6" s="39"/>
-      <c r="K6" s="38" t="s">
+      <c r="I6" s="43"/>
+      <c r="J6" s="42"/>
+      <c r="K6" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="L6" s="33"/>
+      <c r="L6" s="25"/>
     </row>
     <row r="7" spans="1:12" ht="34" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A7" s="33"/>
-      <c r="B7" s="37"/>
-      <c r="C7" s="35"/>
-      <c r="D7" s="42"/>
+      <c r="A7" s="25"/>
+      <c r="B7" s="36"/>
+      <c r="C7" s="31"/>
+      <c r="D7" s="35"/>
       <c r="E7" s="32"/>
-      <c r="F7" s="42"/>
-      <c r="G7" s="41"/>
+      <c r="F7" s="35"/>
+      <c r="G7" s="43"/>
       <c r="H7" s="32"/>
-      <c r="I7" s="41"/>
-      <c r="J7" s="35"/>
-      <c r="K7" s="39"/>
-      <c r="L7" s="33"/>
+      <c r="I7" s="43"/>
+      <c r="J7" s="31"/>
+      <c r="K7" s="42"/>
+      <c r="L7" s="25"/>
     </row>
     <row r="8" spans="1:12" ht="34" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A8" s="33"/>
-      <c r="B8" s="43"/>
+      <c r="A8" s="25"/>
+      <c r="B8" s="40"/>
       <c r="C8" s="32"/>
-      <c r="D8" s="42"/>
+      <c r="D8" s="35"/>
       <c r="E8" s="32"/>
-      <c r="F8" s="37"/>
-      <c r="G8" s="39"/>
+      <c r="F8" s="36"/>
+      <c r="G8" s="42"/>
       <c r="H8" s="32"/>
-      <c r="I8" s="41"/>
+      <c r="I8" s="43"/>
       <c r="J8" s="32"/>
-      <c r="K8" s="35"/>
-      <c r="L8" s="33"/>
+      <c r="K8" s="31"/>
+      <c r="L8" s="25"/>
     </row>
     <row r="9" spans="1:12" ht="34" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A9" s="33"/>
-      <c r="B9" s="31"/>
+      <c r="A9" s="25"/>
+      <c r="B9" s="39"/>
       <c r="C9" s="32"/>
-      <c r="D9" s="42"/>
-      <c r="E9" s="35"/>
-      <c r="F9" s="35" t="s">
+      <c r="D9" s="35"/>
+      <c r="E9" s="31"/>
+      <c r="F9" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="G9" s="35"/>
-      <c r="H9" s="35"/>
-      <c r="I9" s="41"/>
+      <c r="G9" s="31"/>
+      <c r="H9" s="31"/>
+      <c r="I9" s="43"/>
       <c r="J9" s="32"/>
-      <c r="K9" s="40"/>
-      <c r="L9" s="33"/>
+      <c r="K9" s="33"/>
+      <c r="L9" s="25"/>
     </row>
     <row r="10" spans="1:12" ht="34" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A10" s="33"/>
-      <c r="B10" s="36" t="s">
+      <c r="A10" s="25"/>
+      <c r="B10" s="34" t="s">
         <v>6</v>
       </c>
       <c r="C10" s="32"/>
-      <c r="D10" s="42"/>
+      <c r="D10" s="35"/>
       <c r="E10" s="32"/>
       <c r="F10" s="32"/>
       <c r="G10" s="32"/>
       <c r="H10" s="32"/>
-      <c r="I10" s="41"/>
-      <c r="J10" s="40"/>
-      <c r="K10" s="38" t="s">
+      <c r="I10" s="43"/>
+      <c r="J10" s="33"/>
+      <c r="K10" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="L10" s="33"/>
+      <c r="L10" s="25"/>
     </row>
     <row r="11" spans="1:12" ht="34" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A11" s="33"/>
-      <c r="B11" s="37"/>
-      <c r="C11" s="36" t="s">
+      <c r="A11" s="25"/>
+      <c r="B11" s="36"/>
+      <c r="C11" s="34" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="42"/>
+      <c r="D11" s="35"/>
       <c r="E11" s="32"/>
-      <c r="F11" s="30"/>
-      <c r="G11" s="30"/>
+      <c r="F11" s="38"/>
+      <c r="G11" s="38"/>
       <c r="H11" s="32"/>
-      <c r="I11" s="41"/>
-      <c r="J11" s="38" t="s">
+      <c r="I11" s="43"/>
+      <c r="J11" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="K11" s="39"/>
-      <c r="L11" s="33"/>
+      <c r="K11" s="42"/>
+      <c r="L11" s="25"/>
     </row>
     <row r="12" spans="1:12" ht="34" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A12" s="33"/>
-      <c r="B12" s="43"/>
-      <c r="C12" s="42"/>
-      <c r="D12" s="37"/>
+      <c r="A12" s="25"/>
+      <c r="B12" s="40"/>
+      <c r="C12" s="35"/>
+      <c r="D12" s="36"/>
       <c r="E12" s="32"/>
-      <c r="F12" s="30"/>
-      <c r="G12" s="30"/>
+      <c r="F12" s="38"/>
+      <c r="G12" s="38"/>
       <c r="H12" s="32"/>
-      <c r="I12" s="39"/>
-      <c r="J12" s="41"/>
-      <c r="K12" s="35"/>
-      <c r="L12" s="33"/>
+      <c r="I12" s="42"/>
+      <c r="J12" s="43"/>
+      <c r="K12" s="31"/>
+      <c r="L12" s="25"/>
     </row>
     <row r="13" spans="1:12" ht="34" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A13" s="33"/>
-      <c r="B13" s="31"/>
-      <c r="C13" s="37"/>
-      <c r="D13" s="35"/>
+      <c r="A13" s="25"/>
+      <c r="B13" s="39"/>
+      <c r="C13" s="36"/>
+      <c r="D13" s="31"/>
       <c r="E13" s="32"/>
-      <c r="F13" s="30"/>
-      <c r="G13" s="30"/>
+      <c r="F13" s="38"/>
+      <c r="G13" s="38"/>
       <c r="H13" s="32"/>
-      <c r="I13" s="35"/>
-      <c r="J13" s="39"/>
-      <c r="K13" s="40"/>
-      <c r="L13" s="33"/>
+      <c r="I13" s="31"/>
+      <c r="J13" s="42"/>
+      <c r="K13" s="33"/>
+      <c r="L13" s="25"/>
     </row>
     <row r="14" spans="1:12" ht="34" customHeight="1" thickTop="1">
-      <c r="A14" s="33"/>
+      <c r="A14" s="25"/>
       <c r="B14" s="2"/>
       <c r="C14" s="1"/>
       <c r="D14" s="32"/>
       <c r="E14" s="32"/>
-      <c r="F14" s="30"/>
-      <c r="G14" s="30"/>
+      <c r="F14" s="38"/>
+      <c r="G14" s="38"/>
       <c r="H14" s="32"/>
       <c r="I14" s="32"/>
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
-      <c r="L14" s="33"/>
+      <c r="L14" s="25"/>
     </row>
     <row r="15" spans="1:12" ht="34" customHeight="1">
       <c r="A15" s="4"/>
@@ -8112,12 +8711,34 @@
     </row>
   </sheetData>
   <mergeCells count="50">
-    <mergeCell ref="D13:D14"/>
-    <mergeCell ref="L9:L10"/>
-    <mergeCell ref="I13:I14"/>
-    <mergeCell ref="H9:H14"/>
-    <mergeCell ref="F11:G14"/>
-    <mergeCell ref="E9:E14"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D4"/>
+    <mergeCell ref="E1:E8"/>
+    <mergeCell ref="F1:G4"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="G7:G8"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="C3:C6"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="J3:J6"/>
+    <mergeCell ref="L3:L4"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="H1:H8"/>
+    <mergeCell ref="L5:L6"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="K6:K7"/>
+    <mergeCell ref="C7:C10"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="K4:K5"/>
+    <mergeCell ref="D5:D12"/>
+    <mergeCell ref="F5:G6"/>
+    <mergeCell ref="I5:I12"/>
+    <mergeCell ref="I1:I4"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="L1:L2"/>
     <mergeCell ref="K2:K3"/>
     <mergeCell ref="L13:L14"/>
     <mergeCell ref="C11:C13"/>
@@ -8134,34 +8755,12 @@
     <mergeCell ref="K8:K9"/>
     <mergeCell ref="A9:A10"/>
     <mergeCell ref="F9:G10"/>
-    <mergeCell ref="J3:J6"/>
-    <mergeCell ref="L3:L4"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="H1:H8"/>
-    <mergeCell ref="L5:L6"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="K6:K7"/>
-    <mergeCell ref="C7:C10"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="K4:K5"/>
-    <mergeCell ref="D5:D12"/>
-    <mergeCell ref="F5:G6"/>
-    <mergeCell ref="I5:I12"/>
-    <mergeCell ref="I1:I4"/>
-    <mergeCell ref="J1:J2"/>
-    <mergeCell ref="L1:L2"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D4"/>
-    <mergeCell ref="E1:E8"/>
-    <mergeCell ref="F1:G4"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="G7:G8"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="C3:C6"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="L9:L10"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="H9:H14"/>
+    <mergeCell ref="F11:G14"/>
+    <mergeCell ref="E9:E14"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8175,10 +8774,10 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="30" customHeight="1"/>
   <sheetData>
     <row r="1" spans="1:12" ht="30" customHeight="1" thickBot="1">
-      <c r="A1" s="33"/>
+      <c r="A1" s="25"/>
       <c r="B1" s="10"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
       <c r="E1" s="32"/>
       <c r="F1" s="46" t="s">
         <v>14</v>
@@ -8191,225 +8790,225 @@
       <c r="L1" s="45"/>
     </row>
     <row r="2" spans="1:12" ht="30" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A2" s="33"/>
-      <c r="B2" s="36" t="s">
+      <c r="A2" s="25"/>
+      <c r="B2" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="31"/>
-      <c r="D2" s="30"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="38"/>
       <c r="E2" s="32"/>
       <c r="F2" s="47"/>
       <c r="G2" s="47"/>
       <c r="H2" s="32"/>
       <c r="I2" s="32"/>
-      <c r="J2" s="40"/>
-      <c r="K2" s="38" t="s">
+      <c r="J2" s="33"/>
+      <c r="K2" s="41" t="s">
         <v>0</v>
       </c>
       <c r="L2" s="45"/>
     </row>
     <row r="3" spans="1:12" ht="30" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A3" s="33"/>
-      <c r="B3" s="37"/>
-      <c r="C3" s="36" t="s">
+      <c r="A3" s="25"/>
+      <c r="B3" s="36"/>
+      <c r="C3" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="30"/>
+      <c r="D3" s="38"/>
       <c r="E3" s="32"/>
       <c r="F3" s="47"/>
       <c r="G3" s="47"/>
       <c r="H3" s="32"/>
       <c r="I3" s="32"/>
-      <c r="J3" s="38" t="s">
+      <c r="J3" s="41" t="s">
         <v>8</v>
       </c>
-      <c r="K3" s="39"/>
+      <c r="K3" s="42"/>
       <c r="L3" s="45"/>
     </row>
     <row r="4" spans="1:12" ht="30" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A4" s="33"/>
-      <c r="B4" s="43"/>
-      <c r="C4" s="42"/>
-      <c r="D4" s="31"/>
+      <c r="A4" s="25"/>
+      <c r="B4" s="40"/>
+      <c r="C4" s="35"/>
+      <c r="D4" s="39"/>
       <c r="E4" s="32"/>
       <c r="F4" s="47"/>
       <c r="G4" s="47"/>
       <c r="H4" s="32"/>
-      <c r="I4" s="40"/>
-      <c r="J4" s="41"/>
-      <c r="K4" s="35"/>
+      <c r="I4" s="33"/>
+      <c r="J4" s="43"/>
+      <c r="K4" s="31"/>
       <c r="L4" s="45"/>
     </row>
     <row r="5" spans="1:12" ht="30" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A5" s="33"/>
-      <c r="B5" s="31"/>
-      <c r="C5" s="42"/>
-      <c r="D5" s="36" t="s">
+      <c r="A5" s="25"/>
+      <c r="B5" s="39"/>
+      <c r="C5" s="35"/>
+      <c r="D5" s="34" t="s">
         <v>1</v>
       </c>
       <c r="E5" s="32"/>
-      <c r="F5" s="29" t="s">
+      <c r="F5" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="G5" s="29"/>
+      <c r="G5" s="22"/>
       <c r="H5" s="32"/>
-      <c r="I5" s="38" t="s">
+      <c r="I5" s="41" t="s">
         <v>13</v>
       </c>
-      <c r="J5" s="41"/>
-      <c r="K5" s="40"/>
+      <c r="J5" s="43"/>
+      <c r="K5" s="33"/>
       <c r="L5" s="45"/>
     </row>
     <row r="6" spans="1:12" ht="30" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A6" s="33"/>
-      <c r="B6" s="36" t="s">
+      <c r="A6" s="25"/>
+      <c r="B6" s="34" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="37"/>
-      <c r="D6" s="42"/>
+      <c r="C6" s="36"/>
+      <c r="D6" s="35"/>
       <c r="E6" s="32"/>
-      <c r="F6" s="29"/>
-      <c r="G6" s="29"/>
+      <c r="F6" s="22"/>
+      <c r="G6" s="22"/>
       <c r="H6" s="32"/>
-      <c r="I6" s="41"/>
-      <c r="J6" s="39"/>
-      <c r="K6" s="38" t="s">
+      <c r="I6" s="43"/>
+      <c r="J6" s="42"/>
+      <c r="K6" s="41" t="s">
         <v>3</v>
       </c>
       <c r="L6" s="45"/>
     </row>
     <row r="7" spans="1:12" ht="30" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A7" s="33"/>
-      <c r="B7" s="37"/>
-      <c r="C7" s="35"/>
-      <c r="D7" s="42"/>
+      <c r="A7" s="25"/>
+      <c r="B7" s="36"/>
+      <c r="C7" s="31"/>
+      <c r="D7" s="35"/>
       <c r="E7" s="32"/>
-      <c r="F7" s="42"/>
-      <c r="G7" s="41"/>
+      <c r="F7" s="35"/>
+      <c r="G7" s="43"/>
       <c r="H7" s="32"/>
-      <c r="I7" s="41"/>
-      <c r="J7" s="35"/>
-      <c r="K7" s="39"/>
+      <c r="I7" s="43"/>
+      <c r="J7" s="31"/>
+      <c r="K7" s="42"/>
       <c r="L7" s="45"/>
     </row>
     <row r="8" spans="1:12" ht="30" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A8" s="33"/>
-      <c r="B8" s="43"/>
+      <c r="A8" s="25"/>
+      <c r="B8" s="40"/>
       <c r="C8" s="32"/>
-      <c r="D8" s="42"/>
+      <c r="D8" s="35"/>
       <c r="E8" s="32"/>
-      <c r="F8" s="37"/>
-      <c r="G8" s="39"/>
+      <c r="F8" s="36"/>
+      <c r="G8" s="42"/>
       <c r="H8" s="32"/>
-      <c r="I8" s="41"/>
+      <c r="I8" s="43"/>
       <c r="J8" s="32"/>
-      <c r="K8" s="35"/>
+      <c r="K8" s="31"/>
       <c r="L8" s="45"/>
     </row>
     <row r="9" spans="1:12" ht="30" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A9" s="33"/>
-      <c r="B9" s="31"/>
+      <c r="A9" s="25"/>
+      <c r="B9" s="39"/>
       <c r="C9" s="32"/>
-      <c r="D9" s="42"/>
-      <c r="E9" s="35"/>
-      <c r="F9" s="35" t="s">
+      <c r="D9" s="35"/>
+      <c r="E9" s="31"/>
+      <c r="F9" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="G9" s="35"/>
-      <c r="H9" s="35"/>
-      <c r="I9" s="41"/>
+      <c r="G9" s="31"/>
+      <c r="H9" s="31"/>
+      <c r="I9" s="43"/>
       <c r="J9" s="32"/>
-      <c r="K9" s="40"/>
+      <c r="K9" s="33"/>
       <c r="L9" s="45"/>
     </row>
     <row r="10" spans="1:12" ht="30" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A10" s="33"/>
-      <c r="B10" s="36" t="s">
+      <c r="A10" s="25"/>
+      <c r="B10" s="34" t="s">
         <v>6</v>
       </c>
       <c r="C10" s="32"/>
-      <c r="D10" s="42"/>
+      <c r="D10" s="35"/>
       <c r="E10" s="32"/>
       <c r="F10" s="32"/>
       <c r="G10" s="32"/>
       <c r="H10" s="32"/>
-      <c r="I10" s="41"/>
-      <c r="J10" s="40"/>
-      <c r="K10" s="38" t="s">
+      <c r="I10" s="43"/>
+      <c r="J10" s="33"/>
+      <c r="K10" s="41" t="s">
         <v>6</v>
       </c>
       <c r="L10" s="45"/>
     </row>
     <row r="11" spans="1:12" ht="30" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A11" s="33"/>
-      <c r="B11" s="37"/>
-      <c r="C11" s="36" t="s">
+      <c r="A11" s="25"/>
+      <c r="B11" s="36"/>
+      <c r="C11" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="D11" s="42"/>
+      <c r="D11" s="35"/>
       <c r="E11" s="32"/>
-      <c r="F11" s="30"/>
-      <c r="G11" s="30"/>
+      <c r="F11" s="38"/>
+      <c r="G11" s="38"/>
       <c r="H11" s="32"/>
-      <c r="I11" s="41"/>
-      <c r="J11" s="38" t="s">
+      <c r="I11" s="43"/>
+      <c r="J11" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="K11" s="39"/>
+      <c r="K11" s="42"/>
       <c r="L11" s="45"/>
     </row>
     <row r="12" spans="1:12" ht="30" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A12" s="33"/>
-      <c r="B12" s="43"/>
-      <c r="C12" s="42"/>
-      <c r="D12" s="37"/>
+      <c r="A12" s="25"/>
+      <c r="B12" s="40"/>
+      <c r="C12" s="35"/>
+      <c r="D12" s="36"/>
       <c r="E12" s="32"/>
-      <c r="F12" s="30"/>
-      <c r="G12" s="30"/>
+      <c r="F12" s="38"/>
+      <c r="G12" s="38"/>
       <c r="H12" s="32"/>
-      <c r="I12" s="39"/>
-      <c r="J12" s="41"/>
-      <c r="K12" s="35"/>
+      <c r="I12" s="42"/>
+      <c r="J12" s="43"/>
+      <c r="K12" s="31"/>
       <c r="L12" s="45"/>
     </row>
     <row r="13" spans="1:12" ht="30" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A13" s="33"/>
-      <c r="B13" s="31"/>
-      <c r="C13" s="42"/>
+      <c r="A13" s="25"/>
+      <c r="B13" s="39"/>
+      <c r="C13" s="35"/>
       <c r="D13" s="32"/>
       <c r="E13" s="32"/>
-      <c r="F13" s="30"/>
-      <c r="G13" s="30"/>
+      <c r="F13" s="38"/>
+      <c r="G13" s="38"/>
       <c r="H13" s="32"/>
-      <c r="I13" s="35"/>
-      <c r="J13" s="39"/>
-      <c r="K13" s="40"/>
+      <c r="I13" s="31"/>
+      <c r="J13" s="42"/>
+      <c r="K13" s="33"/>
       <c r="L13" s="45"/>
     </row>
     <row r="14" spans="1:12" ht="30" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A14" s="33"/>
-      <c r="B14" s="36" t="s">
+      <c r="A14" s="25"/>
+      <c r="B14" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="37"/>
+      <c r="C14" s="36"/>
       <c r="D14" s="32"/>
       <c r="E14" s="32"/>
-      <c r="F14" s="30"/>
-      <c r="G14" s="30"/>
+      <c r="F14" s="38"/>
+      <c r="G14" s="38"/>
       <c r="H14" s="32"/>
       <c r="I14" s="32"/>
-      <c r="J14" s="35"/>
-      <c r="K14" s="35"/>
+      <c r="J14" s="31"/>
+      <c r="K14" s="31"/>
       <c r="L14" s="45"/>
     </row>
     <row r="15" spans="1:12" ht="30" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A15" s="33"/>
-      <c r="B15" s="37"/>
+      <c r="A15" s="25"/>
+      <c r="B15" s="36"/>
       <c r="C15" s="32"/>
       <c r="D15" s="32"/>
       <c r="E15" s="32"/>
-      <c r="F15" s="30"/>
-      <c r="G15" s="30"/>
+      <c r="F15" s="38"/>
+      <c r="G15" s="38"/>
       <c r="H15" s="32"/>
       <c r="I15" s="32"/>
       <c r="J15" s="32"/>
@@ -8417,12 +9016,12 @@
       <c r="L15" s="45"/>
     </row>
     <row r="16" spans="1:12" ht="30" customHeight="1" thickTop="1">
-      <c r="A16" s="33"/>
+      <c r="A16" s="25"/>
       <c r="C16" s="32"/>
       <c r="D16" s="32"/>
       <c r="E16" s="32"/>
-      <c r="F16" s="30"/>
-      <c r="G16" s="30"/>
+      <c r="F16" s="38"/>
+      <c r="G16" s="38"/>
       <c r="H16" s="32"/>
       <c r="I16" s="32"/>
       <c r="J16" s="32"/>
@@ -8495,6 +9094,46 @@
     </row>
   </sheetData>
   <mergeCells count="56">
+    <mergeCell ref="F1:G4"/>
+    <mergeCell ref="H1:H8"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="G7:G8"/>
+    <mergeCell ref="L5:L6"/>
+    <mergeCell ref="K6:K7"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D4"/>
+    <mergeCell ref="E1:E8"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="L9:L10"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="C7:C10"/>
+    <mergeCell ref="K4:K5"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="D5:D12"/>
+    <mergeCell ref="F5:G6"/>
+    <mergeCell ref="I5:I12"/>
+    <mergeCell ref="I1:I4"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="C3:C6"/>
+    <mergeCell ref="J3:J6"/>
+    <mergeCell ref="L3:L4"/>
+    <mergeCell ref="K14:K16"/>
+    <mergeCell ref="I13:I16"/>
+    <mergeCell ref="L13:L14"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="K8:K9"/>
+    <mergeCell ref="E9:E16"/>
+    <mergeCell ref="F9:G10"/>
+    <mergeCell ref="H9:H16"/>
     <mergeCell ref="A15:A16"/>
     <mergeCell ref="C15:C16"/>
     <mergeCell ref="L15:L16"/>
@@ -8511,46 +9150,6 @@
     <mergeCell ref="D13:D16"/>
     <mergeCell ref="J7:J10"/>
     <mergeCell ref="L7:L8"/>
-    <mergeCell ref="K14:K16"/>
-    <mergeCell ref="I13:I16"/>
-    <mergeCell ref="L13:L14"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="K8:K9"/>
-    <mergeCell ref="E9:E16"/>
-    <mergeCell ref="F9:G10"/>
-    <mergeCell ref="H9:H16"/>
-    <mergeCell ref="K2:K3"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="L9:L10"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="C7:C10"/>
-    <mergeCell ref="K4:K5"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="D5:D12"/>
-    <mergeCell ref="F5:G6"/>
-    <mergeCell ref="I5:I12"/>
-    <mergeCell ref="I1:I4"/>
-    <mergeCell ref="J1:J2"/>
-    <mergeCell ref="C3:C6"/>
-    <mergeCell ref="J3:J6"/>
-    <mergeCell ref="L3:L4"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D4"/>
-    <mergeCell ref="E1:E8"/>
-    <mergeCell ref="F1:G4"/>
-    <mergeCell ref="H1:H8"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="G7:G8"/>
-    <mergeCell ref="L5:L6"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="K6:K7"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="L1:L2"/>
-    <mergeCell ref="B2:B3"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/tornament_standard.xlsx
+++ b/tornament_standard.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ayumu/Desktop/programming/Python/classmach/tournament/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ayumu/Desktop/Python/classmach/tornament/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A92443D-A36B-924C-8B2D-8780B47359B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{250CEEB5-03A2-D541-A3C3-0F0685720DAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17420" firstSheet="3" activeTab="18" xr2:uid="{ACC25020-1812-3D45-8CD3-466514F5749C}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="17420" firstSheet="3" activeTab="13" xr2:uid="{ACC25020-1812-3D45-8CD3-466514F5749C}"/>
   </bookViews>
   <sheets>
     <sheet name="仕様書" sheetId="7" r:id="rId1"/>
@@ -31,8 +31,7 @@
     <sheet name="22" sheetId="1" r:id="rId16"/>
     <sheet name="23" sheetId="3" r:id="rId17"/>
     <sheet name="24" sheetId="2" r:id="rId18"/>
-    <sheet name="25" sheetId="23" r:id="rId19"/>
-    <sheet name="timetable" sheetId="14" r:id="rId20"/>
+    <sheet name="timetable" sheetId="14" r:id="rId19"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -55,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="64">
   <si>
     <t>①</t>
     <phoneticPr fontId="1"/>
@@ -452,13 +451,6 @@
     <t>1S</t>
     <phoneticPr fontId="1"/>
   </si>
-  <si>
-    <t>⑬</t>
-    <rPh sb="0" eb="1">
-      <t>⑩サンマル</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
 </sst>
 </file>
 
@@ -467,7 +459,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="h:mm;@"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="19">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -618,15 +610,6 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="16"/>
-      <color rgb="FF000000"/>
-      <name val="游ゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -636,7 +619,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="28">
+  <borders count="26">
     <border>
       <left/>
       <right/>
@@ -919,37 +902,13 @@
         <color rgb="FF000000"/>
       </diagonal>
     </border>
-    <border>
-      <left style="thick">
-        <color auto="1"/>
-      </left>
-      <right style="thick">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color auto="1"/>
-      </left>
-      <right style="thick">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thick">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1016,18 +975,6 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1040,28 +987,16 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1070,7 +1005,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1079,7 +1029,16 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1094,13 +1053,13 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1127,13 +1086,13 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1148,12 +1107,6 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1163,40 +1116,13 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1602,10 +1528,10 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="30" customHeight="1"/>
   <sheetData>
     <row r="1" spans="1:12" ht="30" customHeight="1" thickBot="1">
-      <c r="A1" s="25"/>
+      <c r="A1" s="33"/>
       <c r="B1" s="10"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
       <c r="E1" s="32"/>
       <c r="F1" s="44" t="s">
         <v>14</v>
@@ -1615,246 +1541,246 @@
       <c r="I1" s="32"/>
       <c r="J1" s="32"/>
       <c r="K1" s="7"/>
-      <c r="L1" s="38"/>
+      <c r="L1" s="30"/>
     </row>
     <row r="2" spans="1:12" ht="30" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A2" s="25"/>
-      <c r="B2" s="34" t="s">
+      <c r="A2" s="33"/>
+      <c r="B2" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="39"/>
-      <c r="D2" s="38"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="30"/>
       <c r="E2" s="32"/>
       <c r="F2" s="44"/>
       <c r="G2" s="44"/>
       <c r="H2" s="32"/>
       <c r="I2" s="32"/>
-      <c r="J2" s="33"/>
-      <c r="K2" s="41" t="s">
+      <c r="J2" s="40"/>
+      <c r="K2" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="L2" s="38"/>
+      <c r="L2" s="30"/>
     </row>
     <row r="3" spans="1:12" ht="30" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A3" s="25"/>
-      <c r="B3" s="36"/>
-      <c r="C3" s="34" t="s">
+      <c r="A3" s="33"/>
+      <c r="B3" s="37"/>
+      <c r="C3" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="38"/>
+      <c r="D3" s="30"/>
       <c r="E3" s="32"/>
       <c r="F3" s="44"/>
       <c r="G3" s="44"/>
       <c r="H3" s="32"/>
       <c r="I3" s="32"/>
-      <c r="J3" s="41" t="s">
+      <c r="J3" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="K3" s="42"/>
-      <c r="L3" s="25"/>
+      <c r="K3" s="39"/>
+      <c r="L3" s="33"/>
     </row>
     <row r="4" spans="1:12" ht="30" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A4" s="25"/>
-      <c r="B4" s="40"/>
-      <c r="C4" s="35"/>
-      <c r="D4" s="39"/>
+      <c r="A4" s="33"/>
+      <c r="B4" s="43"/>
+      <c r="C4" s="42"/>
+      <c r="D4" s="31"/>
       <c r="E4" s="32"/>
       <c r="F4" s="44"/>
       <c r="G4" s="44"/>
       <c r="H4" s="32"/>
-      <c r="I4" s="33"/>
-      <c r="J4" s="43"/>
-      <c r="K4" s="31"/>
-      <c r="L4" s="25"/>
+      <c r="I4" s="40"/>
+      <c r="J4" s="41"/>
+      <c r="K4" s="35"/>
+      <c r="L4" s="33"/>
     </row>
     <row r="5" spans="1:12" ht="30" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A5" s="25"/>
-      <c r="B5" s="39"/>
-      <c r="C5" s="35"/>
-      <c r="D5" s="34" t="s">
+      <c r="A5" s="33"/>
+      <c r="B5" s="31"/>
+      <c r="C5" s="42"/>
+      <c r="D5" s="36" t="s">
         <v>1</v>
       </c>
       <c r="E5" s="32"/>
-      <c r="F5" s="22" t="s">
+      <c r="F5" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="G5" s="22"/>
+      <c r="G5" s="29"/>
       <c r="H5" s="32"/>
-      <c r="I5" s="41" t="s">
+      <c r="I5" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="J5" s="43"/>
-      <c r="K5" s="33"/>
-      <c r="L5" s="38"/>
+      <c r="J5" s="41"/>
+      <c r="K5" s="40"/>
+      <c r="L5" s="30"/>
     </row>
     <row r="6" spans="1:12" ht="30" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A6" s="25"/>
-      <c r="B6" s="34" t="s">
+      <c r="A6" s="33"/>
+      <c r="B6" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="36"/>
-      <c r="D6" s="35"/>
+      <c r="C6" s="37"/>
+      <c r="D6" s="42"/>
       <c r="E6" s="32"/>
-      <c r="F6" s="22"/>
-      <c r="G6" s="22"/>
+      <c r="F6" s="29"/>
+      <c r="G6" s="29"/>
       <c r="H6" s="32"/>
-      <c r="I6" s="43"/>
-      <c r="J6" s="42"/>
-      <c r="K6" s="41" t="s">
+      <c r="I6" s="41"/>
+      <c r="J6" s="39"/>
+      <c r="K6" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="L6" s="38"/>
+      <c r="L6" s="30"/>
     </row>
     <row r="7" spans="1:12" ht="30" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A7" s="25"/>
-      <c r="B7" s="36"/>
-      <c r="C7" s="31"/>
-      <c r="D7" s="35"/>
+      <c r="A7" s="33"/>
+      <c r="B7" s="37"/>
+      <c r="C7" s="35"/>
+      <c r="D7" s="42"/>
       <c r="E7" s="32"/>
-      <c r="F7" s="35"/>
-      <c r="G7" s="43"/>
+      <c r="F7" s="42"/>
+      <c r="G7" s="41"/>
       <c r="H7" s="32"/>
-      <c r="I7" s="43"/>
-      <c r="J7" s="31"/>
-      <c r="K7" s="42"/>
-      <c r="L7" s="38"/>
+      <c r="I7" s="41"/>
+      <c r="J7" s="35"/>
+      <c r="K7" s="39"/>
+      <c r="L7" s="30"/>
     </row>
     <row r="8" spans="1:12" ht="30" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A8" s="25"/>
-      <c r="B8" s="40"/>
+      <c r="A8" s="33"/>
+      <c r="B8" s="43"/>
       <c r="C8" s="32"/>
-      <c r="D8" s="35"/>
+      <c r="D8" s="42"/>
       <c r="E8" s="32"/>
-      <c r="F8" s="36"/>
-      <c r="G8" s="42"/>
+      <c r="F8" s="37"/>
+      <c r="G8" s="39"/>
       <c r="H8" s="32"/>
-      <c r="I8" s="43"/>
+      <c r="I8" s="41"/>
       <c r="J8" s="32"/>
-      <c r="K8" s="31"/>
-      <c r="L8" s="38"/>
+      <c r="K8" s="35"/>
+      <c r="L8" s="30"/>
     </row>
     <row r="9" spans="1:12" ht="30" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A9" s="25"/>
-      <c r="B9" s="39"/>
+      <c r="A9" s="33"/>
+      <c r="B9" s="31"/>
       <c r="C9" s="32"/>
-      <c r="D9" s="35"/>
-      <c r="E9" s="31"/>
-      <c r="F9" s="31" t="s">
+      <c r="D9" s="42"/>
+      <c r="E9" s="35"/>
+      <c r="F9" s="35" t="s">
         <v>2</v>
       </c>
-      <c r="G9" s="31"/>
-      <c r="H9" s="31"/>
-      <c r="I9" s="43"/>
+      <c r="G9" s="35"/>
+      <c r="H9" s="35"/>
+      <c r="I9" s="41"/>
       <c r="J9" s="32"/>
-      <c r="K9" s="33"/>
-      <c r="L9" s="38"/>
+      <c r="K9" s="40"/>
+      <c r="L9" s="30"/>
     </row>
     <row r="10" spans="1:12" ht="30" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A10" s="25"/>
-      <c r="B10" s="34" t="s">
+      <c r="A10" s="33"/>
+      <c r="B10" s="36" t="s">
         <v>6</v>
       </c>
       <c r="C10" s="32"/>
-      <c r="D10" s="35"/>
+      <c r="D10" s="42"/>
       <c r="E10" s="32"/>
       <c r="F10" s="32"/>
       <c r="G10" s="32"/>
       <c r="H10" s="32"/>
-      <c r="I10" s="43"/>
-      <c r="J10" s="33"/>
-      <c r="K10" s="41" t="s">
+      <c r="I10" s="41"/>
+      <c r="J10" s="40"/>
+      <c r="K10" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="L10" s="38"/>
+      <c r="L10" s="30"/>
     </row>
     <row r="11" spans="1:12" ht="30" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A11" s="25"/>
-      <c r="B11" s="36"/>
-      <c r="C11" s="34"/>
-      <c r="D11" s="35"/>
+      <c r="A11" s="33"/>
+      <c r="B11" s="37"/>
+      <c r="C11" s="36"/>
+      <c r="D11" s="42"/>
       <c r="E11" s="32"/>
-      <c r="F11" s="38"/>
-      <c r="G11" s="38"/>
+      <c r="F11" s="30"/>
+      <c r="G11" s="30"/>
       <c r="H11" s="32"/>
-      <c r="I11" s="43"/>
-      <c r="J11" s="41" t="s">
+      <c r="I11" s="41"/>
+      <c r="J11" s="38" t="s">
         <v>13</v>
       </c>
-      <c r="K11" s="42"/>
-      <c r="L11" s="38"/>
+      <c r="K11" s="39"/>
+      <c r="L11" s="30"/>
     </row>
     <row r="12" spans="1:12" ht="30" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A12" s="25"/>
-      <c r="B12" s="40"/>
-      <c r="C12" s="35"/>
-      <c r="D12" s="36"/>
+      <c r="A12" s="33"/>
+      <c r="B12" s="43"/>
+      <c r="C12" s="42"/>
+      <c r="D12" s="37"/>
       <c r="E12" s="32"/>
-      <c r="F12" s="38"/>
-      <c r="G12" s="38"/>
+      <c r="F12" s="30"/>
+      <c r="G12" s="30"/>
       <c r="H12" s="32"/>
-      <c r="I12" s="42"/>
-      <c r="J12" s="43"/>
-      <c r="K12" s="31"/>
-      <c r="L12" s="38"/>
+      <c r="I12" s="39"/>
+      <c r="J12" s="41"/>
+      <c r="K12" s="35"/>
+      <c r="L12" s="30"/>
     </row>
     <row r="13" spans="1:12" ht="30" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A13" s="25"/>
-      <c r="B13" s="39"/>
-      <c r="C13" s="35"/>
+      <c r="A13" s="33"/>
+      <c r="B13" s="31"/>
+      <c r="C13" s="42"/>
       <c r="D13" s="32"/>
       <c r="E13" s="32"/>
-      <c r="F13" s="38"/>
-      <c r="G13" s="38"/>
+      <c r="F13" s="30"/>
+      <c r="G13" s="30"/>
       <c r="H13" s="32"/>
-      <c r="I13" s="31"/>
-      <c r="J13" s="43"/>
-      <c r="K13" s="33"/>
-      <c r="L13" s="38"/>
+      <c r="I13" s="35"/>
+      <c r="J13" s="41"/>
+      <c r="K13" s="40"/>
+      <c r="L13" s="30"/>
     </row>
     <row r="14" spans="1:12" ht="30" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A14" s="25"/>
-      <c r="B14" s="34" t="s">
+      <c r="A14" s="33"/>
+      <c r="B14" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="36"/>
+      <c r="C14" s="37"/>
       <c r="D14" s="32"/>
       <c r="E14" s="32"/>
-      <c r="F14" s="38"/>
-      <c r="G14" s="38"/>
+      <c r="F14" s="30"/>
+      <c r="G14" s="30"/>
       <c r="H14" s="32"/>
       <c r="I14" s="32"/>
-      <c r="J14" s="42"/>
-      <c r="K14" s="41" t="s">
+      <c r="J14" s="39"/>
+      <c r="K14" s="38" t="s">
         <v>8</v>
       </c>
-      <c r="L14" s="38"/>
+      <c r="L14" s="30"/>
     </row>
     <row r="15" spans="1:12" ht="30" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A15" s="25"/>
-      <c r="B15" s="36"/>
+      <c r="A15" s="33"/>
+      <c r="B15" s="37"/>
       <c r="C15" s="32"/>
       <c r="D15" s="32"/>
       <c r="E15" s="32"/>
-      <c r="F15" s="38"/>
-      <c r="G15" s="38"/>
+      <c r="F15" s="30"/>
+      <c r="G15" s="30"/>
       <c r="H15" s="32"/>
       <c r="I15" s="32"/>
-      <c r="J15" s="31"/>
-      <c r="K15" s="42"/>
-      <c r="L15" s="38"/>
+      <c r="J15" s="35"/>
+      <c r="K15" s="39"/>
+      <c r="L15" s="30"/>
     </row>
     <row r="16" spans="1:12" ht="30" customHeight="1" thickTop="1">
-      <c r="A16" s="25"/>
+      <c r="A16" s="33"/>
       <c r="C16" s="32"/>
       <c r="D16" s="32"/>
       <c r="E16" s="32"/>
-      <c r="F16" s="38"/>
-      <c r="G16" s="38"/>
+      <c r="F16" s="30"/>
+      <c r="G16" s="30"/>
       <c r="H16" s="32"/>
       <c r="I16" s="32"/>
       <c r="J16" s="32"/>
       <c r="K16" s="2"/>
-      <c r="L16" s="38"/>
+      <c r="L16" s="30"/>
     </row>
     <row r="18" spans="1:12" ht="30" customHeight="1">
       <c r="A18" s="4"/>
@@ -1922,6 +1848,47 @@
     </row>
   </sheetData>
   <mergeCells count="56">
+    <mergeCell ref="K12:K13"/>
+    <mergeCell ref="K14:K15"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="L3:L4"/>
+    <mergeCell ref="L5:L6"/>
+    <mergeCell ref="L7:L8"/>
+    <mergeCell ref="L9:L10"/>
+    <mergeCell ref="L11:L12"/>
+    <mergeCell ref="L13:L14"/>
+    <mergeCell ref="L15:L16"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="K4:K5"/>
+    <mergeCell ref="K6:K7"/>
+    <mergeCell ref="K8:K9"/>
+    <mergeCell ref="K10:K11"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="J3:J6"/>
+    <mergeCell ref="J7:J10"/>
+    <mergeCell ref="J11:J14"/>
+    <mergeCell ref="J15:J16"/>
+    <mergeCell ref="F11:G16"/>
+    <mergeCell ref="H1:H8"/>
+    <mergeCell ref="H9:H16"/>
+    <mergeCell ref="I1:I4"/>
+    <mergeCell ref="I5:I12"/>
+    <mergeCell ref="I13:I16"/>
+    <mergeCell ref="F1:G4"/>
+    <mergeCell ref="F5:G6"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="G7:G8"/>
+    <mergeCell ref="F9:G10"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="D5:D12"/>
+    <mergeCell ref="D13:D16"/>
+    <mergeCell ref="E1:E8"/>
+    <mergeCell ref="E9:E16"/>
+    <mergeCell ref="C3:C6"/>
+    <mergeCell ref="C7:C10"/>
+    <mergeCell ref="C11:C14"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D4"/>
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="A7:A8"/>
     <mergeCell ref="A9:A10"/>
@@ -1937,47 +1904,6 @@
     <mergeCell ref="A15:A16"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="A3:A4"/>
-    <mergeCell ref="C15:C16"/>
-    <mergeCell ref="D5:D12"/>
-    <mergeCell ref="D13:D16"/>
-    <mergeCell ref="E1:E8"/>
-    <mergeCell ref="E9:E16"/>
-    <mergeCell ref="C3:C6"/>
-    <mergeCell ref="C7:C10"/>
-    <mergeCell ref="C11:C14"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D4"/>
-    <mergeCell ref="F11:G16"/>
-    <mergeCell ref="H1:H8"/>
-    <mergeCell ref="H9:H16"/>
-    <mergeCell ref="I1:I4"/>
-    <mergeCell ref="I5:I12"/>
-    <mergeCell ref="I13:I16"/>
-    <mergeCell ref="F1:G4"/>
-    <mergeCell ref="F5:G6"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="G7:G8"/>
-    <mergeCell ref="F9:G10"/>
-    <mergeCell ref="J1:J2"/>
-    <mergeCell ref="J3:J6"/>
-    <mergeCell ref="J7:J10"/>
-    <mergeCell ref="J11:J14"/>
-    <mergeCell ref="J15:J16"/>
-    <mergeCell ref="K12:K13"/>
-    <mergeCell ref="K14:K15"/>
-    <mergeCell ref="L1:L2"/>
-    <mergeCell ref="L3:L4"/>
-    <mergeCell ref="L5:L6"/>
-    <mergeCell ref="L7:L8"/>
-    <mergeCell ref="L9:L10"/>
-    <mergeCell ref="L11:L12"/>
-    <mergeCell ref="L13:L14"/>
-    <mergeCell ref="L15:L16"/>
-    <mergeCell ref="K2:K3"/>
-    <mergeCell ref="K4:K5"/>
-    <mergeCell ref="K6:K7"/>
-    <mergeCell ref="K8:K9"/>
-    <mergeCell ref="K10:K11"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1991,7 +1917,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="26" customHeight="1"/>
   <sheetData>
     <row r="1" spans="1:12" ht="26" customHeight="1" thickBot="1">
-      <c r="A1" s="25"/>
+      <c r="A1" s="33"/>
       <c r="C1" s="32"/>
       <c r="D1" s="32"/>
       <c r="E1" s="32"/>
@@ -2006,8 +1932,8 @@
       <c r="L1" s="4"/>
     </row>
     <row r="2" spans="1:12" ht="26" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A2" s="25"/>
-      <c r="B2" s="34" t="s">
+      <c r="A2" s="33"/>
+      <c r="B2" s="36" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="32"/>
@@ -2018,13 +1944,13 @@
       <c r="H2" s="32"/>
       <c r="I2" s="32"/>
       <c r="J2" s="32"/>
-      <c r="K2" s="33"/>
-      <c r="L2" s="38"/>
+      <c r="K2" s="40"/>
+      <c r="L2" s="30"/>
     </row>
     <row r="3" spans="1:12" ht="26" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A3" s="25"/>
-      <c r="B3" s="48"/>
-      <c r="C3" s="34" t="s">
+      <c r="A3" s="33"/>
+      <c r="B3" s="49"/>
+      <c r="C3" s="36" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="32"/>
@@ -2033,244 +1959,244 @@
       <c r="G3" s="44"/>
       <c r="H3" s="32"/>
       <c r="I3" s="32"/>
-      <c r="J3" s="33"/>
-      <c r="K3" s="41" t="s">
+      <c r="J3" s="40"/>
+      <c r="K3" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="L3" s="38"/>
+      <c r="L3" s="30"/>
     </row>
     <row r="4" spans="1:12" ht="26" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A4" s="25"/>
-      <c r="B4" s="38"/>
-      <c r="C4" s="35"/>
+      <c r="A4" s="33"/>
+      <c r="B4" s="30"/>
+      <c r="C4" s="42"/>
       <c r="D4" s="32"/>
-      <c r="E4" s="33"/>
+      <c r="E4" s="40"/>
       <c r="F4" s="44"/>
       <c r="G4" s="44"/>
       <c r="H4" s="32"/>
       <c r="I4" s="32"/>
-      <c r="J4" s="41" t="s">
+      <c r="J4" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="K4" s="42"/>
-      <c r="L4" s="38"/>
+      <c r="K4" s="39"/>
+      <c r="L4" s="30"/>
     </row>
     <row r="5" spans="1:12" ht="26" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A5" s="25"/>
-      <c r="B5" s="50"/>
-      <c r="C5" s="35"/>
-      <c r="D5" s="31"/>
-      <c r="E5" s="34" t="s">
+      <c r="A5" s="33"/>
+      <c r="B5" s="48"/>
+      <c r="C5" s="42"/>
+      <c r="D5" s="35"/>
+      <c r="E5" s="36" t="s">
         <v>2</v>
       </c>
       <c r="F5" s="44"/>
       <c r="G5" s="44"/>
       <c r="H5" s="32"/>
-      <c r="I5" s="33"/>
-      <c r="J5" s="43"/>
-      <c r="K5" s="31"/>
-      <c r="L5" s="38"/>
+      <c r="I5" s="40"/>
+      <c r="J5" s="41"/>
+      <c r="K5" s="35"/>
+      <c r="L5" s="30"/>
     </row>
     <row r="6" spans="1:12" ht="26" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A6" s="25"/>
-      <c r="B6" s="34" t="s">
+      <c r="A6" s="33"/>
+      <c r="B6" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="36"/>
+      <c r="C6" s="37"/>
       <c r="D6" s="32"/>
-      <c r="E6" s="35"/>
+      <c r="E6" s="42"/>
       <c r="F6" s="44"/>
       <c r="G6" s="44"/>
       <c r="H6" s="32"/>
-      <c r="I6" s="41" t="s">
+      <c r="I6" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="J6" s="43"/>
-      <c r="K6" s="33"/>
-      <c r="L6" s="38"/>
+      <c r="J6" s="41"/>
+      <c r="K6" s="40"/>
+      <c r="L6" s="30"/>
     </row>
     <row r="7" spans="1:12" ht="26" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A7" s="25"/>
-      <c r="B7" s="48"/>
-      <c r="C7" s="31"/>
+      <c r="A7" s="33"/>
+      <c r="B7" s="49"/>
+      <c r="C7" s="35"/>
       <c r="D7" s="32"/>
-      <c r="E7" s="35"/>
-      <c r="F7" s="22" t="s">
+      <c r="E7" s="42"/>
+      <c r="F7" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="G7" s="22"/>
+      <c r="G7" s="29"/>
       <c r="H7" s="32"/>
-      <c r="I7" s="43"/>
-      <c r="J7" s="42"/>
-      <c r="K7" s="41" t="s">
+      <c r="I7" s="41"/>
+      <c r="J7" s="39"/>
+      <c r="K7" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="L7" s="38"/>
+      <c r="L7" s="30"/>
     </row>
     <row r="8" spans="1:12" ht="26" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A8" s="25"/>
-      <c r="B8" s="38"/>
+      <c r="A8" s="33"/>
+      <c r="B8" s="30"/>
       <c r="C8" s="32"/>
       <c r="D8" s="32"/>
-      <c r="E8" s="35"/>
-      <c r="F8" s="22"/>
-      <c r="G8" s="22"/>
+      <c r="E8" s="42"/>
+      <c r="F8" s="29"/>
+      <c r="G8" s="29"/>
       <c r="H8" s="32"/>
-      <c r="I8" s="43"/>
-      <c r="J8" s="31"/>
-      <c r="K8" s="42"/>
-      <c r="L8" s="38"/>
+      <c r="I8" s="41"/>
+      <c r="J8" s="35"/>
+      <c r="K8" s="39"/>
+      <c r="L8" s="30"/>
     </row>
     <row r="9" spans="1:12" ht="26" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A9" s="25"/>
-      <c r="B9" s="50"/>
+      <c r="A9" s="33"/>
+      <c r="B9" s="48"/>
       <c r="C9" s="32"/>
       <c r="D9" s="32"/>
-      <c r="E9" s="35"/>
-      <c r="F9" s="35"/>
-      <c r="G9" s="43"/>
+      <c r="E9" s="42"/>
+      <c r="F9" s="42"/>
+      <c r="G9" s="41"/>
       <c r="H9" s="32"/>
-      <c r="I9" s="43"/>
+      <c r="I9" s="41"/>
       <c r="J9" s="32"/>
-      <c r="K9" s="31"/>
-      <c r="L9" s="38"/>
+      <c r="K9" s="35"/>
+      <c r="L9" s="30"/>
     </row>
     <row r="10" spans="1:12" ht="26" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A10" s="25"/>
-      <c r="B10" s="34" t="s">
+      <c r="A10" s="33"/>
+      <c r="B10" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="33"/>
+      <c r="C10" s="40"/>
       <c r="D10" s="32"/>
-      <c r="E10" s="35"/>
-      <c r="F10" s="36"/>
-      <c r="G10" s="42"/>
+      <c r="E10" s="42"/>
+      <c r="F10" s="37"/>
+      <c r="G10" s="39"/>
       <c r="H10" s="32"/>
-      <c r="I10" s="43"/>
+      <c r="I10" s="41"/>
       <c r="J10" s="32"/>
-      <c r="K10" s="33"/>
-      <c r="L10" s="38"/>
+      <c r="K10" s="40"/>
+      <c r="L10" s="30"/>
     </row>
     <row r="11" spans="1:12" ht="26" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A11" s="25"/>
-      <c r="B11" s="48"/>
-      <c r="C11" s="49"/>
-      <c r="D11" s="34" t="s">
+      <c r="A11" s="33"/>
+      <c r="B11" s="49"/>
+      <c r="C11" s="50"/>
+      <c r="D11" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="E11" s="35"/>
-      <c r="F11" s="31" t="s">
+      <c r="E11" s="42"/>
+      <c r="F11" s="35" t="s">
         <v>10</v>
       </c>
-      <c r="G11" s="31"/>
-      <c r="H11" s="31"/>
-      <c r="I11" s="43"/>
-      <c r="J11" s="33"/>
-      <c r="K11" s="41" t="s">
+      <c r="G11" s="35"/>
+      <c r="H11" s="35"/>
+      <c r="I11" s="41"/>
+      <c r="J11" s="40"/>
+      <c r="K11" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="L11" s="38"/>
+      <c r="L11" s="30"/>
     </row>
     <row r="12" spans="1:12" ht="26" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A12" s="25"/>
-      <c r="B12" s="38"/>
-      <c r="C12" s="49"/>
-      <c r="D12" s="35"/>
-      <c r="E12" s="35"/>
+      <c r="A12" s="33"/>
+      <c r="B12" s="30"/>
+      <c r="C12" s="50"/>
+      <c r="D12" s="42"/>
+      <c r="E12" s="42"/>
       <c r="F12" s="32"/>
       <c r="G12" s="32"/>
       <c r="H12" s="32"/>
-      <c r="I12" s="43"/>
-      <c r="J12" s="41" t="s">
+      <c r="I12" s="41"/>
+      <c r="J12" s="38" t="s">
         <v>13</v>
       </c>
-      <c r="K12" s="42"/>
-      <c r="L12" s="38"/>
+      <c r="K12" s="39"/>
+      <c r="L12" s="30"/>
     </row>
     <row r="13" spans="1:12" ht="26" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A13" s="25"/>
-      <c r="B13" s="50"/>
-      <c r="C13" s="49"/>
-      <c r="D13" s="35"/>
-      <c r="E13" s="36"/>
-      <c r="F13" s="38"/>
-      <c r="G13" s="38"/>
+      <c r="A13" s="33"/>
+      <c r="B13" s="48"/>
+      <c r="C13" s="50"/>
+      <c r="D13" s="42"/>
+      <c r="E13" s="37"/>
+      <c r="F13" s="30"/>
+      <c r="G13" s="30"/>
       <c r="H13" s="32"/>
-      <c r="I13" s="42"/>
-      <c r="J13" s="43"/>
-      <c r="K13" s="31"/>
-      <c r="L13" s="38"/>
+      <c r="I13" s="39"/>
+      <c r="J13" s="41"/>
+      <c r="K13" s="35"/>
+      <c r="L13" s="30"/>
     </row>
     <row r="14" spans="1:12" ht="26" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A14" s="25"/>
-      <c r="B14" s="34" t="s">
+      <c r="A14" s="33"/>
+      <c r="B14" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="49"/>
-      <c r="D14" s="35"/>
-      <c r="E14" s="31"/>
-      <c r="F14" s="38"/>
-      <c r="G14" s="38"/>
+      <c r="C14" s="50"/>
+      <c r="D14" s="42"/>
+      <c r="E14" s="35"/>
+      <c r="F14" s="30"/>
+      <c r="G14" s="30"/>
       <c r="H14" s="32"/>
       <c r="I14" s="32"/>
-      <c r="J14" s="43"/>
-      <c r="K14" s="33"/>
-      <c r="L14" s="38"/>
+      <c r="J14" s="41"/>
+      <c r="K14" s="40"/>
+      <c r="L14" s="30"/>
     </row>
     <row r="15" spans="1:12" ht="26" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A15" s="25"/>
-      <c r="B15" s="48"/>
-      <c r="C15" s="34" t="s">
+      <c r="A15" s="33"/>
+      <c r="B15" s="49"/>
+      <c r="C15" s="36" t="s">
         <v>62</v>
       </c>
-      <c r="D15" s="36"/>
+      <c r="D15" s="37"/>
       <c r="E15" s="32"/>
-      <c r="F15" s="38"/>
-      <c r="G15" s="38"/>
+      <c r="F15" s="30"/>
+      <c r="G15" s="30"/>
       <c r="H15" s="32"/>
       <c r="I15" s="32"/>
-      <c r="J15" s="42"/>
-      <c r="K15" s="41" t="s">
+      <c r="J15" s="39"/>
+      <c r="K15" s="38" t="s">
         <v>8</v>
       </c>
-      <c r="L15" s="38"/>
+      <c r="L15" s="30"/>
     </row>
     <row r="16" spans="1:12" ht="26" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A16" s="25"/>
-      <c r="B16" s="40"/>
-      <c r="C16" s="35"/>
-      <c r="D16" s="31"/>
+      <c r="A16" s="33"/>
+      <c r="B16" s="43"/>
+      <c r="C16" s="42"/>
+      <c r="D16" s="35"/>
       <c r="E16" s="32"/>
-      <c r="F16" s="38"/>
-      <c r="G16" s="38"/>
+      <c r="F16" s="30"/>
+      <c r="G16" s="30"/>
       <c r="H16" s="32"/>
       <c r="I16" s="32"/>
-      <c r="J16" s="31"/>
-      <c r="K16" s="42"/>
-      <c r="L16" s="38"/>
+      <c r="J16" s="35"/>
+      <c r="K16" s="39"/>
+      <c r="L16" s="30"/>
     </row>
     <row r="17" spans="1:12" ht="26" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A17" s="25"/>
-      <c r="B17" s="39"/>
-      <c r="C17" s="36"/>
+      <c r="A17" s="33"/>
+      <c r="B17" s="31"/>
+      <c r="C17" s="37"/>
       <c r="D17" s="32"/>
       <c r="E17" s="32"/>
-      <c r="F17" s="38"/>
-      <c r="G17" s="38"/>
+      <c r="F17" s="30"/>
+      <c r="G17" s="30"/>
       <c r="H17" s="32"/>
       <c r="I17" s="32"/>
       <c r="J17" s="32"/>
-      <c r="K17" s="31"/>
-      <c r="L17" s="38"/>
+      <c r="K17" s="35"/>
+      <c r="L17" s="30"/>
     </row>
     <row r="18" spans="1:12" ht="26" customHeight="1" thickTop="1">
-      <c r="A18" s="25"/>
+      <c r="A18" s="33"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
       <c r="D18" s="32"/>
       <c r="E18" s="32"/>
-      <c r="F18" s="38"/>
-      <c r="G18" s="38"/>
+      <c r="F18" s="30"/>
+      <c r="G18" s="30"/>
       <c r="H18" s="32"/>
       <c r="I18" s="32"/>
       <c r="J18" s="32"/>
@@ -2332,6 +2258,52 @@
     </row>
   </sheetData>
   <mergeCells count="62">
+    <mergeCell ref="E1:E4"/>
+    <mergeCell ref="E14:E18"/>
+    <mergeCell ref="D16:D18"/>
+    <mergeCell ref="H1:H10"/>
+    <mergeCell ref="H11:H18"/>
+    <mergeCell ref="F1:G6"/>
+    <mergeCell ref="F7:G8"/>
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="G9:G10"/>
+    <mergeCell ref="F11:G12"/>
+    <mergeCell ref="F13:G18"/>
+    <mergeCell ref="J4:J7"/>
+    <mergeCell ref="J8:J11"/>
+    <mergeCell ref="J12:J15"/>
+    <mergeCell ref="J16:J18"/>
+    <mergeCell ref="I1:I5"/>
+    <mergeCell ref="I6:I13"/>
+    <mergeCell ref="I14:I18"/>
+    <mergeCell ref="J1:J3"/>
+    <mergeCell ref="K15:K16"/>
+    <mergeCell ref="K17:K18"/>
+    <mergeCell ref="L2:L3"/>
+    <mergeCell ref="L4:L5"/>
+    <mergeCell ref="L6:L7"/>
+    <mergeCell ref="L8:L9"/>
+    <mergeCell ref="L10:L11"/>
+    <mergeCell ref="L12:L13"/>
+    <mergeCell ref="K5:K6"/>
+    <mergeCell ref="K7:K8"/>
+    <mergeCell ref="K9:K10"/>
+    <mergeCell ref="K11:K12"/>
+    <mergeCell ref="K13:K14"/>
+    <mergeCell ref="L14:L15"/>
+    <mergeCell ref="L16:L17"/>
+    <mergeCell ref="K3:K4"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C15:C17"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="C11:C14"/>
+    <mergeCell ref="B8:B9"/>
     <mergeCell ref="K1:K2"/>
     <mergeCell ref="B12:B13"/>
     <mergeCell ref="A5:A6"/>
@@ -2348,52 +2320,6 @@
     <mergeCell ref="D5:D10"/>
     <mergeCell ref="E5:E13"/>
     <mergeCell ref="D1:D4"/>
-    <mergeCell ref="C15:C17"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="C11:C14"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="K15:K16"/>
-    <mergeCell ref="K17:K18"/>
-    <mergeCell ref="L2:L3"/>
-    <mergeCell ref="L4:L5"/>
-    <mergeCell ref="L6:L7"/>
-    <mergeCell ref="L8:L9"/>
-    <mergeCell ref="L10:L11"/>
-    <mergeCell ref="L12:L13"/>
-    <mergeCell ref="K5:K6"/>
-    <mergeCell ref="K7:K8"/>
-    <mergeCell ref="K9:K10"/>
-    <mergeCell ref="K11:K12"/>
-    <mergeCell ref="K13:K14"/>
-    <mergeCell ref="L14:L15"/>
-    <mergeCell ref="L16:L17"/>
-    <mergeCell ref="K3:K4"/>
-    <mergeCell ref="J4:J7"/>
-    <mergeCell ref="J8:J11"/>
-    <mergeCell ref="J12:J15"/>
-    <mergeCell ref="J16:J18"/>
-    <mergeCell ref="I1:I5"/>
-    <mergeCell ref="I6:I13"/>
-    <mergeCell ref="I14:I18"/>
-    <mergeCell ref="J1:J3"/>
-    <mergeCell ref="E1:E4"/>
-    <mergeCell ref="E14:E18"/>
-    <mergeCell ref="D16:D18"/>
-    <mergeCell ref="H1:H10"/>
-    <mergeCell ref="H11:H18"/>
-    <mergeCell ref="F1:G6"/>
-    <mergeCell ref="F7:G8"/>
-    <mergeCell ref="F9:F10"/>
-    <mergeCell ref="G9:G10"/>
-    <mergeCell ref="F11:G12"/>
-    <mergeCell ref="F13:G18"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2407,293 +2333,293 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="26" customHeight="1"/>
   <sheetData>
     <row r="1" spans="1:12" ht="26" customHeight="1" thickBot="1">
-      <c r="A1" s="25"/>
+      <c r="A1" s="33"/>
       <c r="C1" s="32"/>
       <c r="D1" s="32"/>
       <c r="E1" s="32"/>
-      <c r="F1" s="29" t="s">
+      <c r="F1" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="G1" s="29"/>
+      <c r="G1" s="25"/>
       <c r="H1" s="32"/>
       <c r="I1" s="32"/>
       <c r="J1" s="32"/>
       <c r="K1" s="7"/>
-      <c r="L1" s="25"/>
+      <c r="L1" s="33"/>
     </row>
     <row r="2" spans="1:12" ht="26" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A2" s="25"/>
-      <c r="B2" s="34" t="s">
+      <c r="A2" s="33"/>
+      <c r="B2" s="36" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="32"/>
       <c r="D2" s="32"/>
       <c r="E2" s="32"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="29"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
       <c r="H2" s="32"/>
       <c r="I2" s="32"/>
-      <c r="J2" s="33"/>
-      <c r="K2" s="41" t="s">
+      <c r="J2" s="40"/>
+      <c r="K2" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="L2" s="25"/>
+      <c r="L2" s="33"/>
     </row>
     <row r="3" spans="1:12" ht="26" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A3" s="25"/>
-      <c r="B3" s="48"/>
-      <c r="C3" s="34" t="s">
+      <c r="A3" s="33"/>
+      <c r="B3" s="49"/>
+      <c r="C3" s="36" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="32"/>
       <c r="E3" s="32"/>
-      <c r="F3" s="29"/>
-      <c r="G3" s="29"/>
+      <c r="F3" s="25"/>
+      <c r="G3" s="25"/>
       <c r="H3" s="32"/>
       <c r="I3" s="32"/>
-      <c r="J3" s="41" t="s">
+      <c r="J3" s="38" t="s">
         <v>13</v>
       </c>
-      <c r="K3" s="42"/>
-      <c r="L3" s="25"/>
+      <c r="K3" s="39"/>
+      <c r="L3" s="33"/>
     </row>
     <row r="4" spans="1:12" ht="26" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A4" s="25"/>
-      <c r="B4" s="38"/>
-      <c r="C4" s="35"/>
+      <c r="A4" s="33"/>
+      <c r="B4" s="30"/>
+      <c r="C4" s="42"/>
       <c r="D4" s="32"/>
-      <c r="E4" s="33"/>
-      <c r="F4" s="29"/>
-      <c r="G4" s="29"/>
-      <c r="H4" s="33"/>
-      <c r="I4" s="33"/>
-      <c r="J4" s="43"/>
-      <c r="K4" s="31"/>
-      <c r="L4" s="25"/>
+      <c r="E4" s="40"/>
+      <c r="F4" s="25"/>
+      <c r="G4" s="25"/>
+      <c r="H4" s="40"/>
+      <c r="I4" s="40"/>
+      <c r="J4" s="41"/>
+      <c r="K4" s="35"/>
+      <c r="L4" s="33"/>
     </row>
     <row r="5" spans="1:12" ht="26" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A5" s="25"/>
-      <c r="B5" s="50"/>
-      <c r="C5" s="35"/>
-      <c r="D5" s="31"/>
-      <c r="E5" s="34" t="s">
+      <c r="A5" s="33"/>
+      <c r="B5" s="48"/>
+      <c r="C5" s="42"/>
+      <c r="D5" s="35"/>
+      <c r="E5" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="F5" s="29"/>
-      <c r="G5" s="29"/>
-      <c r="H5" s="41" t="s">
+      <c r="F5" s="25"/>
+      <c r="G5" s="25"/>
+      <c r="H5" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="I5" s="31"/>
-      <c r="J5" s="43"/>
-      <c r="K5" s="33"/>
-      <c r="L5" s="25"/>
+      <c r="I5" s="35"/>
+      <c r="J5" s="41"/>
+      <c r="K5" s="40"/>
+      <c r="L5" s="33"/>
     </row>
     <row r="6" spans="1:12" ht="26" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A6" s="25"/>
-      <c r="B6" s="34" t="s">
+      <c r="A6" s="33"/>
+      <c r="B6" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="36"/>
+      <c r="C6" s="37"/>
       <c r="D6" s="32"/>
-      <c r="E6" s="35"/>
-      <c r="F6" s="29"/>
-      <c r="G6" s="29"/>
-      <c r="H6" s="43"/>
+      <c r="E6" s="42"/>
+      <c r="F6" s="25"/>
+      <c r="G6" s="25"/>
+      <c r="H6" s="41"/>
       <c r="I6" s="32"/>
-      <c r="J6" s="42"/>
-      <c r="K6" s="41" t="s">
+      <c r="J6" s="39"/>
+      <c r="K6" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="L6" s="25"/>
+      <c r="L6" s="33"/>
     </row>
     <row r="7" spans="1:12" ht="26" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A7" s="25"/>
-      <c r="B7" s="48"/>
-      <c r="C7" s="31"/>
+      <c r="A7" s="33"/>
+      <c r="B7" s="49"/>
+      <c r="C7" s="35"/>
       <c r="D7" s="32"/>
-      <c r="E7" s="35"/>
-      <c r="F7" s="22" t="s">
+      <c r="E7" s="42"/>
+      <c r="F7" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="G7" s="22"/>
-      <c r="H7" s="43"/>
+      <c r="G7" s="29"/>
+      <c r="H7" s="41"/>
       <c r="I7" s="32"/>
       <c r="J7" s="32"/>
-      <c r="K7" s="42"/>
-      <c r="L7" s="25"/>
+      <c r="K7" s="39"/>
+      <c r="L7" s="33"/>
     </row>
     <row r="8" spans="1:12" ht="26" customHeight="1" thickTop="1">
-      <c r="A8" s="25"/>
-      <c r="B8" s="38"/>
+      <c r="A8" s="33"/>
+      <c r="B8" s="30"/>
       <c r="C8" s="32"/>
       <c r="D8" s="32"/>
-      <c r="E8" s="35"/>
-      <c r="F8" s="22"/>
-      <c r="G8" s="22"/>
-      <c r="H8" s="43"/>
+      <c r="E8" s="42"/>
+      <c r="F8" s="29"/>
+      <c r="G8" s="29"/>
+      <c r="H8" s="41"/>
       <c r="I8" s="32"/>
       <c r="J8" s="32"/>
-      <c r="K8" s="31"/>
-      <c r="L8" s="25"/>
+      <c r="K8" s="35"/>
+      <c r="L8" s="33"/>
     </row>
     <row r="9" spans="1:12" ht="26" customHeight="1" thickBot="1">
-      <c r="A9" s="25"/>
-      <c r="B9" s="50"/>
+      <c r="A9" s="33"/>
+      <c r="B9" s="48"/>
       <c r="C9" s="32"/>
       <c r="D9" s="32"/>
-      <c r="E9" s="35"/>
-      <c r="F9" s="35"/>
-      <c r="G9" s="43"/>
-      <c r="H9" s="43"/>
+      <c r="E9" s="42"/>
+      <c r="F9" s="42"/>
+      <c r="G9" s="41"/>
+      <c r="H9" s="41"/>
       <c r="I9" s="32"/>
       <c r="J9" s="32"/>
-      <c r="K9" s="33"/>
-      <c r="L9" s="25"/>
+      <c r="K9" s="40"/>
+      <c r="L9" s="33"/>
     </row>
     <row r="10" spans="1:12" ht="26" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A10" s="25"/>
-      <c r="B10" s="34" t="s">
+      <c r="A10" s="33"/>
+      <c r="B10" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="33"/>
+      <c r="C10" s="40"/>
       <c r="D10" s="32"/>
-      <c r="E10" s="35"/>
-      <c r="F10" s="36"/>
-      <c r="G10" s="42"/>
-      <c r="H10" s="43"/>
-      <c r="I10" s="33"/>
+      <c r="E10" s="42"/>
+      <c r="F10" s="37"/>
+      <c r="G10" s="39"/>
+      <c r="H10" s="41"/>
+      <c r="I10" s="40"/>
       <c r="J10" s="32"/>
-      <c r="K10" s="41" t="s">
+      <c r="K10" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="L10" s="25"/>
+      <c r="L10" s="33"/>
     </row>
     <row r="11" spans="1:12" ht="26" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A11" s="25"/>
-      <c r="B11" s="48"/>
-      <c r="C11" s="49"/>
-      <c r="D11" s="34" t="s">
+      <c r="A11" s="33"/>
+      <c r="B11" s="49"/>
+      <c r="C11" s="50"/>
+      <c r="D11" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="E11" s="35"/>
-      <c r="F11" s="31" t="s">
+      <c r="E11" s="42"/>
+      <c r="F11" s="35" t="s">
         <v>10</v>
       </c>
-      <c r="G11" s="31"/>
-      <c r="H11" s="43"/>
-      <c r="I11" s="41" t="s">
+      <c r="G11" s="35"/>
+      <c r="H11" s="41"/>
+      <c r="I11" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="J11" s="31"/>
-      <c r="K11" s="42"/>
-      <c r="L11" s="25"/>
+      <c r="J11" s="35"/>
+      <c r="K11" s="39"/>
+      <c r="L11" s="33"/>
     </row>
     <row r="12" spans="1:12" ht="26" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A12" s="25"/>
-      <c r="B12" s="38"/>
-      <c r="C12" s="49"/>
-      <c r="D12" s="35"/>
-      <c r="E12" s="35"/>
+      <c r="A12" s="33"/>
+      <c r="B12" s="30"/>
+      <c r="C12" s="50"/>
+      <c r="D12" s="42"/>
+      <c r="E12" s="42"/>
       <c r="F12" s="32"/>
       <c r="G12" s="32"/>
-      <c r="H12" s="43"/>
-      <c r="I12" s="43"/>
+      <c r="H12" s="41"/>
+      <c r="I12" s="41"/>
       <c r="J12" s="32"/>
-      <c r="K12" s="31"/>
-      <c r="L12" s="25"/>
+      <c r="K12" s="35"/>
+      <c r="L12" s="33"/>
     </row>
     <row r="13" spans="1:12" ht="26" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A13" s="25"/>
-      <c r="B13" s="50"/>
-      <c r="C13" s="49"/>
-      <c r="D13" s="35"/>
-      <c r="E13" s="36"/>
-      <c r="F13" s="38"/>
-      <c r="G13" s="38"/>
-      <c r="H13" s="42"/>
-      <c r="I13" s="43"/>
+      <c r="A13" s="33"/>
+      <c r="B13" s="48"/>
+      <c r="C13" s="50"/>
+      <c r="D13" s="42"/>
+      <c r="E13" s="37"/>
+      <c r="F13" s="30"/>
+      <c r="G13" s="30"/>
+      <c r="H13" s="39"/>
+      <c r="I13" s="41"/>
       <c r="J13" s="32"/>
-      <c r="K13" s="33"/>
-      <c r="L13" s="25"/>
+      <c r="K13" s="40"/>
+      <c r="L13" s="33"/>
     </row>
     <row r="14" spans="1:12" ht="26" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A14" s="25"/>
-      <c r="B14" s="34" t="s">
+      <c r="A14" s="33"/>
+      <c r="B14" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="49"/>
-      <c r="D14" s="35"/>
-      <c r="E14" s="31"/>
-      <c r="F14" s="38"/>
-      <c r="G14" s="38"/>
-      <c r="H14" s="31"/>
-      <c r="I14" s="43"/>
-      <c r="J14" s="33"/>
-      <c r="K14" s="41" t="s">
+      <c r="C14" s="50"/>
+      <c r="D14" s="42"/>
+      <c r="E14" s="35"/>
+      <c r="F14" s="30"/>
+      <c r="G14" s="30"/>
+      <c r="H14" s="35"/>
+      <c r="I14" s="41"/>
+      <c r="J14" s="40"/>
+      <c r="K14" s="38" t="s">
         <v>8</v>
       </c>
-      <c r="L14" s="25"/>
+      <c r="L14" s="33"/>
     </row>
     <row r="15" spans="1:12" ht="26" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A15" s="25"/>
-      <c r="B15" s="48"/>
-      <c r="C15" s="34" t="s">
+      <c r="A15" s="33"/>
+      <c r="B15" s="49"/>
+      <c r="C15" s="36" t="s">
         <v>62</v>
       </c>
-      <c r="D15" s="36"/>
+      <c r="D15" s="37"/>
       <c r="E15" s="32"/>
-      <c r="F15" s="38"/>
-      <c r="G15" s="38"/>
+      <c r="F15" s="30"/>
+      <c r="G15" s="30"/>
       <c r="H15" s="32"/>
-      <c r="I15" s="42"/>
-      <c r="J15" s="41" t="s">
+      <c r="I15" s="39"/>
+      <c r="J15" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="K15" s="42"/>
-      <c r="L15" s="25"/>
+      <c r="K15" s="39"/>
+      <c r="L15" s="33"/>
     </row>
     <row r="16" spans="1:12" ht="26" customHeight="1" thickTop="1">
-      <c r="A16" s="25"/>
-      <c r="B16" s="40"/>
-      <c r="C16" s="35"/>
-      <c r="D16" s="31"/>
+      <c r="A16" s="33"/>
+      <c r="B16" s="43"/>
+      <c r="C16" s="42"/>
+      <c r="D16" s="35"/>
       <c r="E16" s="32"/>
-      <c r="F16" s="38"/>
-      <c r="G16" s="38"/>
+      <c r="F16" s="30"/>
+      <c r="G16" s="30"/>
       <c r="H16" s="32"/>
-      <c r="I16" s="31"/>
-      <c r="J16" s="43"/>
-      <c r="K16" s="31"/>
-      <c r="L16" s="25"/>
+      <c r="I16" s="35"/>
+      <c r="J16" s="41"/>
+      <c r="K16" s="35"/>
+      <c r="L16" s="33"/>
     </row>
     <row r="17" spans="1:12" ht="26" customHeight="1" thickBot="1">
-      <c r="A17" s="25"/>
-      <c r="B17" s="39"/>
-      <c r="C17" s="36"/>
+      <c r="A17" s="33"/>
+      <c r="B17" s="31"/>
+      <c r="C17" s="37"/>
       <c r="D17" s="32"/>
       <c r="E17" s="32"/>
-      <c r="F17" s="38"/>
-      <c r="G17" s="38"/>
+      <c r="F17" s="30"/>
+      <c r="G17" s="30"/>
       <c r="H17" s="32"/>
       <c r="I17" s="32"/>
-      <c r="J17" s="42"/>
-      <c r="K17" s="33"/>
-      <c r="L17" s="25"/>
+      <c r="J17" s="39"/>
+      <c r="K17" s="40"/>
+      <c r="L17" s="33"/>
     </row>
     <row r="18" spans="1:12" ht="26" customHeight="1" thickTop="1">
-      <c r="A18" s="25"/>
+      <c r="A18" s="33"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
       <c r="D18" s="32"/>
       <c r="E18" s="32"/>
-      <c r="F18" s="38"/>
-      <c r="G18" s="38"/>
+      <c r="F18" s="30"/>
+      <c r="G18" s="30"/>
       <c r="H18" s="32"/>
       <c r="I18" s="32"/>
       <c r="J18" s="1"/>
       <c r="K18" s="1"/>
-      <c r="L18" s="25"/>
+      <c r="L18" s="33"/>
     </row>
     <row r="19" spans="1:12" ht="26" customHeight="1">
       <c r="A19" s="4"/>
@@ -2750,26 +2676,34 @@
     </row>
   </sheetData>
   <mergeCells count="64">
-    <mergeCell ref="L1:L2"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="K2:K3"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="I1:I4"/>
-    <mergeCell ref="L3:L4"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D4"/>
-    <mergeCell ref="K4:K5"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="D5:D10"/>
-    <mergeCell ref="I5:I10"/>
-    <mergeCell ref="J1:J2"/>
-    <mergeCell ref="C3:C6"/>
-    <mergeCell ref="J3:J6"/>
-    <mergeCell ref="E1:E4"/>
-    <mergeCell ref="F1:G6"/>
-    <mergeCell ref="H1:H4"/>
-    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="L17:L18"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="K16:K17"/>
+    <mergeCell ref="L15:L16"/>
+    <mergeCell ref="E5:E13"/>
+    <mergeCell ref="H5:H13"/>
+    <mergeCell ref="F7:G8"/>
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="G9:G10"/>
+    <mergeCell ref="F11:G12"/>
+    <mergeCell ref="I11:I15"/>
+    <mergeCell ref="F13:G18"/>
+    <mergeCell ref="E14:E18"/>
+    <mergeCell ref="H14:H18"/>
+    <mergeCell ref="L11:L12"/>
+    <mergeCell ref="L5:L6"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="K12:K13"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="K14:K15"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="C15:C17"/>
+    <mergeCell ref="J15:J17"/>
+    <mergeCell ref="D16:D18"/>
+    <mergeCell ref="I16:I18"/>
+    <mergeCell ref="J11:J14"/>
+    <mergeCell ref="B12:B13"/>
     <mergeCell ref="A9:A10"/>
     <mergeCell ref="L9:L10"/>
     <mergeCell ref="B10:B11"/>
@@ -2786,34 +2720,26 @@
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="K6:K7"/>
     <mergeCell ref="A7:A8"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="K12:K13"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="K14:K15"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="C15:C17"/>
-    <mergeCell ref="J15:J17"/>
-    <mergeCell ref="D16:D18"/>
-    <mergeCell ref="I16:I18"/>
-    <mergeCell ref="J11:J14"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="L17:L18"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="K16:K17"/>
-    <mergeCell ref="L15:L16"/>
-    <mergeCell ref="E5:E13"/>
-    <mergeCell ref="H5:H13"/>
-    <mergeCell ref="F7:G8"/>
-    <mergeCell ref="F9:F10"/>
-    <mergeCell ref="G9:G10"/>
-    <mergeCell ref="F11:G12"/>
-    <mergeCell ref="I11:I15"/>
-    <mergeCell ref="F13:G18"/>
-    <mergeCell ref="E14:E18"/>
-    <mergeCell ref="H14:H18"/>
-    <mergeCell ref="L11:L12"/>
-    <mergeCell ref="L5:L6"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D4"/>
+    <mergeCell ref="K4:K5"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="D5:D10"/>
+    <mergeCell ref="I5:I10"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="C3:C6"/>
+    <mergeCell ref="J3:J6"/>
+    <mergeCell ref="E1:E4"/>
+    <mergeCell ref="F1:G6"/>
+    <mergeCell ref="H1:H4"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="I1:I4"/>
+    <mergeCell ref="L3:L4"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2827,7 +2753,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="24" customHeight="1"/>
   <sheetData>
     <row r="1" spans="1:12" ht="24" customHeight="1" thickBot="1">
-      <c r="A1" s="25"/>
+      <c r="A1" s="33"/>
       <c r="C1" s="32"/>
       <c r="D1" s="32"/>
       <c r="E1" s="32"/>
@@ -2839,11 +2765,11 @@
       <c r="I1" s="32"/>
       <c r="J1" s="32"/>
       <c r="K1" s="7"/>
-      <c r="L1" s="25"/>
+      <c r="L1" s="33"/>
     </row>
     <row r="2" spans="1:12" ht="24" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A2" s="25"/>
-      <c r="B2" s="34" t="s">
+      <c r="A2" s="33"/>
+      <c r="B2" s="36" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="32"/>
@@ -2853,16 +2779,16 @@
       <c r="G2" s="44"/>
       <c r="H2" s="32"/>
       <c r="I2" s="32"/>
-      <c r="J2" s="33"/>
-      <c r="K2" s="41" t="s">
+      <c r="J2" s="40"/>
+      <c r="K2" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="L2" s="25"/>
+      <c r="L2" s="33"/>
     </row>
     <row r="3" spans="1:12" ht="24" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A3" s="25"/>
-      <c r="B3" s="48"/>
-      <c r="C3" s="34" t="s">
+      <c r="A3" s="33"/>
+      <c r="B3" s="49"/>
+      <c r="C3" s="36" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="32"/>
@@ -2871,243 +2797,243 @@
       <c r="G3" s="44"/>
       <c r="H3" s="32"/>
       <c r="I3" s="32"/>
-      <c r="J3" s="41" t="s">
+      <c r="J3" s="38" t="s">
         <v>13</v>
       </c>
-      <c r="K3" s="42"/>
-      <c r="L3" s="25"/>
+      <c r="K3" s="39"/>
+      <c r="L3" s="33"/>
     </row>
     <row r="4" spans="1:12" ht="24" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A4" s="25"/>
-      <c r="B4" s="38"/>
-      <c r="C4" s="35"/>
+      <c r="A4" s="33"/>
+      <c r="B4" s="30"/>
+      <c r="C4" s="42"/>
       <c r="D4" s="32"/>
       <c r="E4" s="32"/>
       <c r="F4" s="44"/>
       <c r="G4" s="44"/>
-      <c r="H4" s="33"/>
-      <c r="I4" s="33"/>
-      <c r="J4" s="43"/>
-      <c r="K4" s="31"/>
-      <c r="L4" s="25"/>
+      <c r="H4" s="40"/>
+      <c r="I4" s="40"/>
+      <c r="J4" s="41"/>
+      <c r="K4" s="35"/>
+      <c r="L4" s="33"/>
     </row>
     <row r="5" spans="1:12" ht="24" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A5" s="25"/>
-      <c r="B5" s="50"/>
-      <c r="C5" s="35"/>
-      <c r="D5" s="34" t="s">
+      <c r="A5" s="33"/>
+      <c r="B5" s="48"/>
+      <c r="C5" s="42"/>
+      <c r="D5" s="36" t="s">
         <v>2</v>
       </c>
       <c r="E5" s="32"/>
       <c r="F5" s="44"/>
       <c r="G5" s="44"/>
-      <c r="H5" s="41" t="s">
+      <c r="H5" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="I5" s="31"/>
-      <c r="J5" s="43"/>
-      <c r="K5" s="33"/>
-      <c r="L5" s="25"/>
+      <c r="I5" s="35"/>
+      <c r="J5" s="41"/>
+      <c r="K5" s="40"/>
+      <c r="L5" s="33"/>
     </row>
     <row r="6" spans="1:12" ht="24" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A6" s="25"/>
-      <c r="B6" s="34" t="s">
+      <c r="A6" s="33"/>
+      <c r="B6" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="36"/>
-      <c r="D6" s="35"/>
+      <c r="C6" s="37"/>
+      <c r="D6" s="42"/>
       <c r="E6" s="32"/>
       <c r="F6" s="44"/>
       <c r="G6" s="44"/>
-      <c r="H6" s="43"/>
+      <c r="H6" s="41"/>
       <c r="I6" s="32"/>
-      <c r="J6" s="42"/>
-      <c r="K6" s="41" t="s">
+      <c r="J6" s="39"/>
+      <c r="K6" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="L6" s="25"/>
+      <c r="L6" s="33"/>
     </row>
     <row r="7" spans="1:12" ht="24" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A7" s="25"/>
-      <c r="B7" s="48"/>
-      <c r="C7" s="31"/>
-      <c r="D7" s="35"/>
+      <c r="A7" s="33"/>
+      <c r="B7" s="49"/>
+      <c r="C7" s="35"/>
+      <c r="D7" s="42"/>
       <c r="E7" s="32"/>
       <c r="F7" s="44"/>
       <c r="G7" s="44"/>
-      <c r="H7" s="43"/>
+      <c r="H7" s="41"/>
       <c r="I7" s="32"/>
       <c r="J7" s="32"/>
-      <c r="K7" s="42"/>
-      <c r="L7" s="25"/>
+      <c r="K7" s="39"/>
+      <c r="L7" s="33"/>
     </row>
     <row r="8" spans="1:12" ht="24" customHeight="1" thickTop="1">
-      <c r="A8" s="25"/>
-      <c r="B8" s="38"/>
+      <c r="A8" s="33"/>
+      <c r="B8" s="30"/>
       <c r="C8" s="32"/>
-      <c r="D8" s="35"/>
+      <c r="D8" s="42"/>
       <c r="E8" s="51" t="s">
         <v>10</v>
       </c>
-      <c r="F8" s="22" t="s">
+      <c r="F8" s="29" t="s">
         <v>5</v>
       </c>
       <c r="G8" s="54"/>
-      <c r="H8" s="43"/>
+      <c r="H8" s="41"/>
       <c r="I8" s="32"/>
       <c r="J8" s="32"/>
-      <c r="K8" s="31"/>
-      <c r="L8" s="25"/>
+      <c r="K8" s="35"/>
+      <c r="L8" s="33"/>
     </row>
     <row r="9" spans="1:12" ht="24" customHeight="1" thickBot="1">
-      <c r="A9" s="25"/>
-      <c r="B9" s="50"/>
+      <c r="A9" s="33"/>
+      <c r="B9" s="48"/>
       <c r="C9" s="32"/>
-      <c r="D9" s="35"/>
+      <c r="D9" s="42"/>
       <c r="E9" s="52"/>
-      <c r="F9" s="22"/>
+      <c r="F9" s="29"/>
       <c r="G9" s="54"/>
-      <c r="H9" s="43"/>
+      <c r="H9" s="41"/>
       <c r="I9" s="32"/>
       <c r="J9" s="32"/>
-      <c r="K9" s="33"/>
-      <c r="L9" s="25"/>
+      <c r="K9" s="40"/>
+      <c r="L9" s="33"/>
     </row>
     <row r="10" spans="1:12" ht="24" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A10" s="25"/>
-      <c r="B10" s="34" t="s">
+      <c r="A10" s="33"/>
+      <c r="B10" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="33"/>
-      <c r="D10" s="36"/>
+      <c r="C10" s="40"/>
+      <c r="D10" s="37"/>
       <c r="E10" s="52"/>
-      <c r="F10" s="35"/>
-      <c r="G10" s="43"/>
-      <c r="H10" s="43"/>
-      <c r="I10" s="33"/>
+      <c r="F10" s="42"/>
+      <c r="G10" s="41"/>
+      <c r="H10" s="41"/>
+      <c r="I10" s="40"/>
       <c r="J10" s="32"/>
-      <c r="K10" s="41" t="s">
+      <c r="K10" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="L10" s="25"/>
+      <c r="L10" s="33"/>
     </row>
     <row r="11" spans="1:12" ht="24" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A11" s="25"/>
-      <c r="B11" s="48"/>
-      <c r="C11" s="49"/>
+      <c r="A11" s="33"/>
+      <c r="B11" s="49"/>
+      <c r="C11" s="50"/>
       <c r="D11" s="32"/>
       <c r="E11" s="52"/>
-      <c r="F11" s="36"/>
-      <c r="G11" s="42"/>
-      <c r="H11" s="43"/>
-      <c r="I11" s="41" t="s">
+      <c r="F11" s="37"/>
+      <c r="G11" s="39"/>
+      <c r="H11" s="41"/>
+      <c r="I11" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="J11" s="31"/>
-      <c r="K11" s="42"/>
-      <c r="L11" s="25"/>
+      <c r="J11" s="35"/>
+      <c r="K11" s="39"/>
+      <c r="L11" s="33"/>
     </row>
     <row r="12" spans="1:12" ht="24" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A12" s="25"/>
-      <c r="B12" s="38"/>
-      <c r="C12" s="49"/>
+      <c r="A12" s="33"/>
+      <c r="B12" s="30"/>
+      <c r="C12" s="50"/>
       <c r="D12" s="32"/>
       <c r="E12" s="52"/>
       <c r="F12" s="55" t="s">
         <v>4</v>
       </c>
       <c r="G12" s="51"/>
-      <c r="H12" s="43"/>
-      <c r="I12" s="43"/>
+      <c r="H12" s="41"/>
+      <c r="I12" s="41"/>
       <c r="J12" s="32"/>
-      <c r="K12" s="31"/>
-      <c r="L12" s="25"/>
+      <c r="K12" s="35"/>
+      <c r="L12" s="33"/>
     </row>
     <row r="13" spans="1:12" ht="24" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A13" s="25"/>
-      <c r="B13" s="50"/>
-      <c r="C13" s="49"/>
+      <c r="A13" s="33"/>
+      <c r="B13" s="48"/>
+      <c r="C13" s="50"/>
       <c r="D13" s="32"/>
       <c r="E13" s="52"/>
       <c r="F13" s="56"/>
       <c r="G13" s="52"/>
-      <c r="H13" s="42"/>
-      <c r="I13" s="43"/>
+      <c r="H13" s="39"/>
+      <c r="I13" s="41"/>
       <c r="J13" s="32"/>
-      <c r="K13" s="33"/>
-      <c r="L13" s="25"/>
+      <c r="K13" s="40"/>
+      <c r="L13" s="33"/>
     </row>
     <row r="14" spans="1:12" ht="24" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A14" s="25"/>
-      <c r="B14" s="34" t="s">
+      <c r="A14" s="33"/>
+      <c r="B14" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="49"/>
+      <c r="C14" s="50"/>
       <c r="D14" s="32"/>
       <c r="E14" s="52"/>
       <c r="F14" s="32"/>
       <c r="G14" s="32"/>
-      <c r="H14" s="31"/>
-      <c r="I14" s="43"/>
-      <c r="J14" s="33"/>
-      <c r="K14" s="41" t="s">
+      <c r="H14" s="35"/>
+      <c r="I14" s="41"/>
+      <c r="J14" s="40"/>
+      <c r="K14" s="38" t="s">
         <v>8</v>
       </c>
-      <c r="L14" s="25"/>
+      <c r="L14" s="33"/>
     </row>
     <row r="15" spans="1:12" ht="24" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A15" s="25"/>
-      <c r="B15" s="48"/>
-      <c r="C15" s="49"/>
-      <c r="D15" s="34" t="s">
+      <c r="A15" s="33"/>
+      <c r="B15" s="49"/>
+      <c r="C15" s="50"/>
+      <c r="D15" s="36" t="s">
         <v>1</v>
       </c>
       <c r="E15" s="52"/>
       <c r="F15" s="32"/>
       <c r="G15" s="32"/>
       <c r="H15" s="32"/>
-      <c r="I15" s="42"/>
-      <c r="J15" s="41" t="s">
+      <c r="I15" s="39"/>
+      <c r="J15" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="K15" s="42"/>
-      <c r="L15" s="25"/>
+      <c r="K15" s="39"/>
+      <c r="L15" s="33"/>
     </row>
     <row r="16" spans="1:12" ht="24" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A16" s="25"/>
-      <c r="B16" s="38"/>
-      <c r="C16" s="49"/>
-      <c r="D16" s="35"/>
+      <c r="A16" s="33"/>
+      <c r="B16" s="30"/>
+      <c r="C16" s="50"/>
+      <c r="D16" s="42"/>
       <c r="E16" s="53"/>
       <c r="F16" s="32"/>
       <c r="G16" s="32"/>
       <c r="H16" s="32"/>
-      <c r="I16" s="31"/>
-      <c r="J16" s="43"/>
-      <c r="K16" s="31"/>
-      <c r="L16" s="25"/>
+      <c r="I16" s="35"/>
+      <c r="J16" s="41"/>
+      <c r="K16" s="35"/>
+      <c r="L16" s="33"/>
     </row>
     <row r="17" spans="1:12" ht="24" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A17" s="25"/>
-      <c r="B17" s="50"/>
-      <c r="C17" s="49"/>
-      <c r="D17" s="35"/>
-      <c r="E17" s="31"/>
+      <c r="A17" s="33"/>
+      <c r="B17" s="48"/>
+      <c r="C17" s="50"/>
+      <c r="D17" s="42"/>
+      <c r="E17" s="35"/>
       <c r="F17" s="32"/>
       <c r="G17" s="32"/>
       <c r="H17" s="32"/>
       <c r="I17" s="32"/>
-      <c r="J17" s="42"/>
-      <c r="K17" s="33"/>
-      <c r="L17" s="25"/>
+      <c r="J17" s="39"/>
+      <c r="K17" s="40"/>
+      <c r="L17" s="33"/>
     </row>
     <row r="18" spans="1:12" ht="24" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A18" s="25"/>
-      <c r="B18" s="34" t="s">
+      <c r="A18" s="33"/>
+      <c r="B18" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="C18" s="31"/>
-      <c r="D18" s="36"/>
+      <c r="C18" s="35"/>
+      <c r="D18" s="37"/>
       <c r="E18" s="32"/>
       <c r="F18" s="32"/>
       <c r="G18" s="32"/>
@@ -3115,13 +3041,13 @@
       <c r="I18" s="32"/>
       <c r="J18" s="1"/>
       <c r="K18" s="1"/>
-      <c r="L18" s="25"/>
+      <c r="L18" s="33"/>
     </row>
     <row r="19" spans="1:12" ht="24" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A19" s="25"/>
-      <c r="B19" s="48"/>
-      <c r="C19" s="31"/>
-      <c r="D19" s="31"/>
+      <c r="A19" s="33"/>
+      <c r="B19" s="49"/>
+      <c r="C19" s="35"/>
+      <c r="D19" s="35"/>
       <c r="E19" s="32"/>
       <c r="F19" s="32"/>
       <c r="G19" s="32"/>
@@ -3129,10 +3055,10 @@
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
-      <c r="L19" s="25"/>
+      <c r="L19" s="33"/>
     </row>
     <row r="20" spans="1:12" ht="24" customHeight="1" thickTop="1">
-      <c r="A20" s="25"/>
+      <c r="A20" s="33"/>
       <c r="B20" s="3"/>
       <c r="C20" s="32"/>
       <c r="D20" s="32"/>
@@ -3143,7 +3069,7 @@
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
-      <c r="L20" s="25"/>
+      <c r="L20" s="33"/>
     </row>
     <row r="21" spans="1:12" ht="24" customHeight="1">
       <c r="A21" s="4"/>
@@ -3173,6 +3099,59 @@
     </row>
   </sheetData>
   <mergeCells count="69">
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D4"/>
+    <mergeCell ref="E1:E7"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="D5:D10"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="I1:I4"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="C3:C6"/>
+    <mergeCell ref="J3:J6"/>
+    <mergeCell ref="L3:L4"/>
+    <mergeCell ref="F1:G7"/>
+    <mergeCell ref="K4:K5"/>
+    <mergeCell ref="I5:I10"/>
+    <mergeCell ref="L5:L6"/>
+    <mergeCell ref="K6:K7"/>
+    <mergeCell ref="H1:H4"/>
+    <mergeCell ref="H5:H13"/>
+    <mergeCell ref="I11:I15"/>
+    <mergeCell ref="H14:H18"/>
+    <mergeCell ref="J15:J17"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="L7:L8"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="E8:E16"/>
+    <mergeCell ref="F8:G9"/>
+    <mergeCell ref="K8:K9"/>
+    <mergeCell ref="J11:J14"/>
+    <mergeCell ref="L11:L12"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="F12:G13"/>
+    <mergeCell ref="F14:G20"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="L9:L10"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="C11:C14"/>
+    <mergeCell ref="D11:D14"/>
+    <mergeCell ref="K12:K13"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="E17:E20"/>
+    <mergeCell ref="I16:I18"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="K10:K11"/>
+    <mergeCell ref="C7:C10"/>
+    <mergeCell ref="J7:J10"/>
     <mergeCell ref="L13:L14"/>
     <mergeCell ref="B14:B15"/>
     <mergeCell ref="K14:K15"/>
@@ -3189,59 +3168,6 @@
     <mergeCell ref="L19:L20"/>
     <mergeCell ref="C19:C20"/>
     <mergeCell ref="D19:D20"/>
-    <mergeCell ref="E17:E20"/>
-    <mergeCell ref="I16:I18"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="K10:K11"/>
-    <mergeCell ref="C7:C10"/>
-    <mergeCell ref="J7:J10"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="C11:C14"/>
-    <mergeCell ref="D11:D14"/>
-    <mergeCell ref="K12:K13"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="K2:K3"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="L7:L8"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="E8:E16"/>
-    <mergeCell ref="F8:G9"/>
-    <mergeCell ref="K8:K9"/>
-    <mergeCell ref="J11:J14"/>
-    <mergeCell ref="L11:L12"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="F12:G13"/>
-    <mergeCell ref="F14:G20"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="L9:L10"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="I1:I4"/>
-    <mergeCell ref="J1:J2"/>
-    <mergeCell ref="C3:C6"/>
-    <mergeCell ref="J3:J6"/>
-    <mergeCell ref="L3:L4"/>
-    <mergeCell ref="F1:G7"/>
-    <mergeCell ref="K4:K5"/>
-    <mergeCell ref="I5:I10"/>
-    <mergeCell ref="L5:L6"/>
-    <mergeCell ref="K6:K7"/>
-    <mergeCell ref="H1:H4"/>
-    <mergeCell ref="H5:H13"/>
-    <mergeCell ref="I11:I15"/>
-    <mergeCell ref="H14:H18"/>
-    <mergeCell ref="J15:J17"/>
-    <mergeCell ref="L1:L2"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D4"/>
-    <mergeCell ref="E1:E7"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="D5:D10"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="B2:B3"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3255,7 +3181,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="24" customHeight="1"/>
   <sheetData>
     <row r="1" spans="1:12" ht="24" customHeight="1" thickBot="1">
-      <c r="A1" s="25"/>
+      <c r="A1" s="33"/>
       <c r="C1" s="32"/>
       <c r="D1" s="32"/>
       <c r="E1" s="32"/>
@@ -3267,11 +3193,11 @@
       <c r="I1" s="32"/>
       <c r="J1" s="32"/>
       <c r="K1" s="1"/>
-      <c r="L1" s="25"/>
+      <c r="L1" s="33"/>
     </row>
     <row r="2" spans="1:12" ht="24" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A2" s="25"/>
-      <c r="B2" s="34" t="s">
+      <c r="A2" s="33"/>
+      <c r="B2" s="36" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="32"/>
@@ -3282,15 +3208,15 @@
       <c r="H2" s="32"/>
       <c r="I2" s="32"/>
       <c r="J2" s="32"/>
-      <c r="K2" s="41" t="s">
+      <c r="K2" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="L2" s="25"/>
+      <c r="L2" s="33"/>
     </row>
     <row r="3" spans="1:12" ht="24" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A3" s="25"/>
-      <c r="B3" s="48"/>
-      <c r="C3" s="34" t="s">
+      <c r="A3" s="33"/>
+      <c r="B3" s="49"/>
+      <c r="C3" s="36" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="32"/>
@@ -3299,146 +3225,146 @@
       <c r="G3" s="44"/>
       <c r="H3" s="32"/>
       <c r="I3" s="32"/>
-      <c r="J3" s="41" t="s">
+      <c r="J3" s="38" t="s">
         <v>13</v>
       </c>
-      <c r="K3" s="42"/>
-      <c r="L3" s="25"/>
+      <c r="K3" s="39"/>
+      <c r="L3" s="33"/>
     </row>
     <row r="4" spans="1:12" ht="24" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A4" s="25"/>
-      <c r="B4" s="38"/>
-      <c r="C4" s="35"/>
+      <c r="A4" s="33"/>
+      <c r="B4" s="30"/>
+      <c r="C4" s="42"/>
       <c r="D4" s="32"/>
       <c r="E4" s="32"/>
       <c r="F4" s="44"/>
       <c r="G4" s="44"/>
       <c r="H4" s="32"/>
       <c r="I4" s="32"/>
-      <c r="J4" s="43"/>
+      <c r="J4" s="41"/>
       <c r="K4" s="57"/>
-      <c r="L4" s="25"/>
+      <c r="L4" s="33"/>
     </row>
     <row r="5" spans="1:12" ht="24" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A5" s="25"/>
-      <c r="B5" s="50"/>
-      <c r="C5" s="35"/>
-      <c r="D5" s="34" t="s">
+      <c r="A5" s="33"/>
+      <c r="B5" s="48"/>
+      <c r="C5" s="42"/>
+      <c r="D5" s="36" t="s">
         <v>2</v>
       </c>
       <c r="E5" s="32"/>
       <c r="F5" s="44"/>
       <c r="G5" s="44"/>
       <c r="H5" s="32"/>
-      <c r="I5" s="41" t="s">
+      <c r="I5" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="J5" s="43"/>
+      <c r="J5" s="41"/>
       <c r="K5" s="32"/>
-      <c r="L5" s="25"/>
+      <c r="L5" s="33"/>
     </row>
     <row r="6" spans="1:12" ht="24" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A6" s="25"/>
-      <c r="B6" s="34" t="s">
+      <c r="A6" s="33"/>
+      <c r="B6" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="36"/>
-      <c r="D6" s="35"/>
+      <c r="C6" s="37"/>
+      <c r="D6" s="42"/>
       <c r="E6" s="32"/>
       <c r="F6" s="44"/>
       <c r="G6" s="44"/>
       <c r="H6" s="32"/>
-      <c r="I6" s="43"/>
-      <c r="J6" s="42"/>
-      <c r="K6" s="41" t="s">
+      <c r="I6" s="41"/>
+      <c r="J6" s="39"/>
+      <c r="K6" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="L6" s="25"/>
+      <c r="L6" s="33"/>
     </row>
     <row r="7" spans="1:12" ht="24" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A7" s="25"/>
-      <c r="B7" s="48"/>
-      <c r="C7" s="31"/>
-      <c r="D7" s="35"/>
+      <c r="A7" s="33"/>
+      <c r="B7" s="49"/>
+      <c r="C7" s="35"/>
+      <c r="D7" s="42"/>
       <c r="E7" s="32"/>
       <c r="F7" s="44"/>
       <c r="G7" s="44"/>
       <c r="H7" s="32"/>
-      <c r="I7" s="43"/>
-      <c r="J7" s="31"/>
-      <c r="K7" s="42"/>
-      <c r="L7" s="25"/>
+      <c r="I7" s="41"/>
+      <c r="J7" s="35"/>
+      <c r="K7" s="39"/>
+      <c r="L7" s="33"/>
     </row>
     <row r="8" spans="1:12" ht="24" customHeight="1" thickTop="1">
-      <c r="A8" s="25"/>
-      <c r="B8" s="38"/>
+      <c r="A8" s="33"/>
+      <c r="B8" s="30"/>
       <c r="C8" s="32"/>
-      <c r="D8" s="35"/>
+      <c r="D8" s="42"/>
       <c r="E8" s="51" t="s">
         <v>10</v>
       </c>
-      <c r="F8" s="22" t="s">
+      <c r="F8" s="29" t="s">
         <v>5</v>
       </c>
       <c r="G8" s="54"/>
-      <c r="H8" s="31" t="s">
+      <c r="H8" s="35" t="s">
         <v>10</v>
       </c>
-      <c r="I8" s="43"/>
+      <c r="I8" s="41"/>
       <c r="J8" s="32"/>
       <c r="K8" s="57"/>
-      <c r="L8" s="25"/>
+      <c r="L8" s="33"/>
     </row>
     <row r="9" spans="1:12" ht="24" customHeight="1" thickBot="1">
-      <c r="A9" s="25"/>
-      <c r="B9" s="50"/>
+      <c r="A9" s="33"/>
+      <c r="B9" s="48"/>
       <c r="C9" s="32"/>
-      <c r="D9" s="35"/>
+      <c r="D9" s="42"/>
       <c r="E9" s="52"/>
-      <c r="F9" s="22"/>
+      <c r="F9" s="29"/>
       <c r="G9" s="54"/>
       <c r="H9" s="32"/>
-      <c r="I9" s="43"/>
+      <c r="I9" s="41"/>
       <c r="J9" s="32"/>
       <c r="K9" s="32"/>
-      <c r="L9" s="25"/>
+      <c r="L9" s="33"/>
     </row>
     <row r="10" spans="1:12" ht="24" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A10" s="25"/>
-      <c r="B10" s="34" t="s">
+      <c r="A10" s="33"/>
+      <c r="B10" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="33"/>
-      <c r="D10" s="36"/>
+      <c r="C10" s="40"/>
+      <c r="D10" s="37"/>
       <c r="E10" s="52"/>
-      <c r="F10" s="35"/>
-      <c r="G10" s="43"/>
+      <c r="F10" s="42"/>
+      <c r="G10" s="41"/>
       <c r="H10" s="56"/>
-      <c r="I10" s="42"/>
-      <c r="J10" s="33"/>
-      <c r="K10" s="41" t="s">
+      <c r="I10" s="39"/>
+      <c r="J10" s="40"/>
+      <c r="K10" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="L10" s="25"/>
+      <c r="L10" s="33"/>
     </row>
     <row r="11" spans="1:12" ht="24" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A11" s="25"/>
-      <c r="B11" s="48"/>
-      <c r="C11" s="49"/>
+      <c r="A11" s="33"/>
+      <c r="B11" s="49"/>
+      <c r="C11" s="50"/>
       <c r="D11" s="32"/>
       <c r="E11" s="52"/>
-      <c r="F11" s="36"/>
-      <c r="G11" s="42"/>
+      <c r="F11" s="37"/>
+      <c r="G11" s="39"/>
       <c r="H11" s="56"/>
       <c r="I11" s="32"/>
       <c r="J11" s="32"/>
-      <c r="K11" s="42"/>
-      <c r="L11" s="25"/>
+      <c r="K11" s="39"/>
+      <c r="L11" s="33"/>
     </row>
     <row r="12" spans="1:12" ht="24" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A12" s="25"/>
-      <c r="B12" s="38"/>
-      <c r="C12" s="49"/>
+      <c r="A12" s="33"/>
+      <c r="B12" s="30"/>
+      <c r="C12" s="50"/>
       <c r="D12" s="32"/>
       <c r="E12" s="52"/>
       <c r="F12" s="55" t="s">
@@ -3449,12 +3375,12 @@
       <c r="I12" s="32"/>
       <c r="J12" s="32"/>
       <c r="K12" s="57"/>
-      <c r="L12" s="25"/>
+      <c r="L12" s="33"/>
     </row>
     <row r="13" spans="1:12" ht="24" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A13" s="25"/>
-      <c r="B13" s="50"/>
-      <c r="C13" s="49"/>
+      <c r="A13" s="33"/>
+      <c r="B13" s="48"/>
+      <c r="C13" s="50"/>
       <c r="D13" s="32"/>
       <c r="E13" s="52"/>
       <c r="F13" s="56"/>
@@ -3463,14 +3389,14 @@
       <c r="I13" s="32"/>
       <c r="J13" s="32"/>
       <c r="K13" s="32"/>
-      <c r="L13" s="25"/>
+      <c r="L13" s="33"/>
     </row>
     <row r="14" spans="1:12" ht="24" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A14" s="25"/>
-      <c r="B14" s="34" t="s">
+      <c r="A14" s="33"/>
+      <c r="B14" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="49"/>
+      <c r="C14" s="50"/>
       <c r="D14" s="32"/>
       <c r="E14" s="52"/>
       <c r="F14" s="32"/>
@@ -3478,91 +3404,91 @@
       <c r="H14" s="56"/>
       <c r="I14" s="32"/>
       <c r="J14" s="32"/>
-      <c r="K14" s="41" t="s">
+      <c r="K14" s="38" t="s">
         <v>8</v>
       </c>
-      <c r="L14" s="25"/>
+      <c r="L14" s="33"/>
     </row>
     <row r="15" spans="1:12" ht="24" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A15" s="25"/>
-      <c r="B15" s="48"/>
-      <c r="C15" s="49"/>
-      <c r="D15" s="34" t="s">
+      <c r="A15" s="33"/>
+      <c r="B15" s="49"/>
+      <c r="C15" s="50"/>
+      <c r="D15" s="36" t="s">
         <v>1</v>
       </c>
       <c r="E15" s="52"/>
       <c r="F15" s="32"/>
       <c r="G15" s="32"/>
       <c r="H15" s="56"/>
-      <c r="I15" s="41" t="s">
+      <c r="I15" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="J15" s="31"/>
-      <c r="K15" s="42"/>
-      <c r="L15" s="25"/>
+      <c r="J15" s="35"/>
+      <c r="K15" s="39"/>
+      <c r="L15" s="33"/>
     </row>
     <row r="16" spans="1:12" ht="24" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A16" s="25"/>
-      <c r="B16" s="38"/>
-      <c r="C16" s="49"/>
-      <c r="D16" s="35"/>
+      <c r="A16" s="33"/>
+      <c r="B16" s="30"/>
+      <c r="C16" s="50"/>
+      <c r="D16" s="42"/>
       <c r="E16" s="53"/>
       <c r="F16" s="32"/>
       <c r="G16" s="32"/>
       <c r="H16" s="58"/>
-      <c r="I16" s="43"/>
+      <c r="I16" s="41"/>
       <c r="J16" s="32"/>
       <c r="K16" s="57"/>
-      <c r="L16" s="25"/>
+      <c r="L16" s="33"/>
     </row>
     <row r="17" spans="1:12" ht="24" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A17" s="25"/>
-      <c r="B17" s="50"/>
-      <c r="C17" s="49"/>
-      <c r="D17" s="35"/>
-      <c r="E17" s="31"/>
+      <c r="A17" s="33"/>
+      <c r="B17" s="48"/>
+      <c r="C17" s="50"/>
+      <c r="D17" s="42"/>
+      <c r="E17" s="35"/>
       <c r="F17" s="32"/>
       <c r="G17" s="32"/>
-      <c r="H17" s="31"/>
-      <c r="I17" s="43"/>
+      <c r="H17" s="35"/>
+      <c r="I17" s="41"/>
       <c r="J17" s="32"/>
       <c r="K17" s="32"/>
-      <c r="L17" s="25"/>
+      <c r="L17" s="33"/>
     </row>
     <row r="18" spans="1:12" ht="24" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A18" s="25"/>
-      <c r="B18" s="34" t="s">
+      <c r="A18" s="33"/>
+      <c r="B18" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="C18" s="31"/>
-      <c r="D18" s="36"/>
+      <c r="C18" s="35"/>
+      <c r="D18" s="37"/>
       <c r="E18" s="32"/>
       <c r="F18" s="32"/>
       <c r="G18" s="32"/>
       <c r="H18" s="32"/>
-      <c r="I18" s="42"/>
-      <c r="J18" s="33"/>
-      <c r="K18" s="41" t="s">
+      <c r="I18" s="39"/>
+      <c r="J18" s="40"/>
+      <c r="K18" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="L18" s="25"/>
+      <c r="L18" s="33"/>
     </row>
     <row r="19" spans="1:12" ht="24" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A19" s="25"/>
-      <c r="B19" s="48"/>
-      <c r="C19" s="31"/>
-      <c r="D19" s="31"/>
+      <c r="A19" s="33"/>
+      <c r="B19" s="49"/>
+      <c r="C19" s="35"/>
+      <c r="D19" s="35"/>
       <c r="E19" s="32"/>
       <c r="F19" s="32"/>
       <c r="G19" s="32"/>
       <c r="H19" s="32"/>
-      <c r="I19" s="31"/>
-      <c r="J19" s="31"/>
-      <c r="K19" s="42"/>
-      <c r="L19" s="25"/>
+      <c r="I19" s="35"/>
+      <c r="J19" s="35"/>
+      <c r="K19" s="39"/>
+      <c r="L19" s="33"/>
     </row>
     <row r="20" spans="1:12" ht="24" customHeight="1" thickTop="1">
-      <c r="A20" s="25"/>
+      <c r="A20" s="33"/>
       <c r="B20" s="3"/>
       <c r="C20" s="32"/>
       <c r="D20" s="32"/>
@@ -3573,7 +3499,7 @@
       <c r="I20" s="32"/>
       <c r="J20" s="32"/>
       <c r="K20" s="2"/>
-      <c r="L20" s="25"/>
+      <c r="L20" s="33"/>
     </row>
     <row r="21" spans="1:12" ht="24" customHeight="1">
       <c r="A21" s="4"/>
@@ -3603,6 +3529,62 @@
     </row>
   </sheetData>
   <mergeCells count="72">
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D4"/>
+    <mergeCell ref="E1:E7"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="D5:D10"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="I1:I4"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="C3:C6"/>
+    <mergeCell ref="J3:J6"/>
+    <mergeCell ref="L3:L4"/>
+    <mergeCell ref="F1:G7"/>
+    <mergeCell ref="H1:H7"/>
+    <mergeCell ref="K4:K5"/>
+    <mergeCell ref="I5:I10"/>
+    <mergeCell ref="L5:L6"/>
+    <mergeCell ref="K6:K7"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="L7:L8"/>
+    <mergeCell ref="E8:E16"/>
+    <mergeCell ref="F8:G9"/>
+    <mergeCell ref="L11:L12"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="F12:G13"/>
+    <mergeCell ref="F14:G20"/>
+    <mergeCell ref="L9:L10"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="K10:K11"/>
+    <mergeCell ref="C7:C10"/>
+    <mergeCell ref="J7:J10"/>
+    <mergeCell ref="L13:L14"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="C11:C14"/>
+    <mergeCell ref="D11:D14"/>
+    <mergeCell ref="I11:I14"/>
+    <mergeCell ref="K12:K13"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="K14:K15"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="C15:C18"/>
+    <mergeCell ref="I15:I18"/>
+    <mergeCell ref="J15:J18"/>
+    <mergeCell ref="H8:H16"/>
+    <mergeCell ref="K8:K9"/>
+    <mergeCell ref="J11:J14"/>
     <mergeCell ref="A19:A20"/>
     <mergeCell ref="L19:L20"/>
     <mergeCell ref="L15:L16"/>
@@ -3619,62 +3601,6 @@
     <mergeCell ref="D19:D20"/>
     <mergeCell ref="E17:E20"/>
     <mergeCell ref="H17:H20"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="C11:C14"/>
-    <mergeCell ref="D11:D14"/>
-    <mergeCell ref="I11:I14"/>
-    <mergeCell ref="K12:K13"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="K14:K15"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="C15:C18"/>
-    <mergeCell ref="I15:I18"/>
-    <mergeCell ref="J15:J18"/>
-    <mergeCell ref="H8:H16"/>
-    <mergeCell ref="K8:K9"/>
-    <mergeCell ref="J11:J14"/>
-    <mergeCell ref="L11:L12"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="F12:G13"/>
-    <mergeCell ref="F14:G20"/>
-    <mergeCell ref="L9:L10"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="K10:K11"/>
-    <mergeCell ref="C7:C10"/>
-    <mergeCell ref="J7:J10"/>
-    <mergeCell ref="L13:L14"/>
-    <mergeCell ref="I1:I4"/>
-    <mergeCell ref="J1:J2"/>
-    <mergeCell ref="C3:C6"/>
-    <mergeCell ref="J3:J6"/>
-    <mergeCell ref="L3:L4"/>
-    <mergeCell ref="F1:G7"/>
-    <mergeCell ref="H1:H7"/>
-    <mergeCell ref="K4:K5"/>
-    <mergeCell ref="I5:I10"/>
-    <mergeCell ref="L5:L6"/>
-    <mergeCell ref="K6:K7"/>
-    <mergeCell ref="L1:L2"/>
-    <mergeCell ref="K2:K3"/>
-    <mergeCell ref="L7:L8"/>
-    <mergeCell ref="E8:E16"/>
-    <mergeCell ref="F8:G9"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D4"/>
-    <mergeCell ref="E1:E7"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="D5:D10"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="A9:A10"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3688,7 +3614,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="22" customHeight="1"/>
   <sheetData>
     <row r="1" spans="1:12" ht="22" customHeight="1" thickBot="1">
-      <c r="A1" s="25"/>
+      <c r="A1" s="33"/>
       <c r="C1" s="32"/>
       <c r="D1" s="32"/>
       <c r="E1" s="32"/>
@@ -3700,11 +3626,11 @@
       <c r="I1" s="32"/>
       <c r="J1" s="32"/>
       <c r="K1" s="1"/>
-      <c r="L1" s="25"/>
+      <c r="L1" s="33"/>
     </row>
     <row r="2" spans="1:12" ht="22" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A2" s="25"/>
-      <c r="B2" s="34" t="s">
+      <c r="A2" s="33"/>
+      <c r="B2" s="36" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="32"/>
@@ -3715,15 +3641,15 @@
       <c r="H2" s="32"/>
       <c r="I2" s="32"/>
       <c r="J2" s="32"/>
-      <c r="K2" s="41" t="s">
+      <c r="K2" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="L2" s="25"/>
+      <c r="L2" s="33"/>
     </row>
     <row r="3" spans="1:12" ht="22" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A3" s="25"/>
-      <c r="B3" s="48"/>
-      <c r="C3" s="34" t="s">
+      <c r="A3" s="33"/>
+      <c r="B3" s="49"/>
+      <c r="C3" s="36" t="s">
         <v>1</v>
       </c>
       <c r="D3" s="32"/>
@@ -3732,146 +3658,146 @@
       <c r="G3" s="44"/>
       <c r="H3" s="32"/>
       <c r="I3" s="32"/>
-      <c r="J3" s="41" t="s">
+      <c r="J3" s="38" t="s">
         <v>13</v>
       </c>
-      <c r="K3" s="42"/>
-      <c r="L3" s="25"/>
+      <c r="K3" s="39"/>
+      <c r="L3" s="33"/>
     </row>
     <row r="4" spans="1:12" ht="22" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A4" s="25"/>
-      <c r="B4" s="38"/>
-      <c r="C4" s="35"/>
+      <c r="A4" s="33"/>
+      <c r="B4" s="30"/>
+      <c r="C4" s="42"/>
       <c r="D4" s="32"/>
       <c r="E4" s="32"/>
       <c r="F4" s="44"/>
       <c r="G4" s="44"/>
       <c r="H4" s="32"/>
       <c r="I4" s="32"/>
-      <c r="J4" s="43"/>
+      <c r="J4" s="41"/>
       <c r="K4" s="57"/>
-      <c r="L4" s="25"/>
+      <c r="L4" s="33"/>
     </row>
     <row r="5" spans="1:12" ht="22" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A5" s="25"/>
-      <c r="B5" s="50"/>
-      <c r="C5" s="35"/>
-      <c r="D5" s="34" t="s">
+      <c r="A5" s="33"/>
+      <c r="B5" s="48"/>
+      <c r="C5" s="42"/>
+      <c r="D5" s="36" t="s">
         <v>2</v>
       </c>
       <c r="E5" s="32"/>
       <c r="F5" s="44"/>
       <c r="G5" s="44"/>
       <c r="H5" s="32"/>
-      <c r="I5" s="41" t="s">
+      <c r="I5" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="J5" s="43"/>
+      <c r="J5" s="41"/>
       <c r="K5" s="32"/>
-      <c r="L5" s="25"/>
+      <c r="L5" s="33"/>
     </row>
     <row r="6" spans="1:12" ht="22" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A6" s="25"/>
-      <c r="B6" s="34" t="s">
+      <c r="A6" s="33"/>
+      <c r="B6" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="36"/>
-      <c r="D6" s="35"/>
+      <c r="C6" s="37"/>
+      <c r="D6" s="42"/>
       <c r="E6" s="32"/>
       <c r="F6" s="44"/>
       <c r="G6" s="44"/>
       <c r="H6" s="32"/>
-      <c r="I6" s="43"/>
-      <c r="J6" s="42"/>
-      <c r="K6" s="41" t="s">
+      <c r="I6" s="41"/>
+      <c r="J6" s="39"/>
+      <c r="K6" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="L6" s="25"/>
+      <c r="L6" s="33"/>
     </row>
     <row r="7" spans="1:12" ht="22" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A7" s="25"/>
-      <c r="B7" s="48"/>
-      <c r="C7" s="31"/>
-      <c r="D7" s="35"/>
+      <c r="A7" s="33"/>
+      <c r="B7" s="49"/>
+      <c r="C7" s="35"/>
+      <c r="D7" s="42"/>
       <c r="E7" s="32"/>
       <c r="F7" s="44"/>
       <c r="G7" s="44"/>
       <c r="H7" s="32"/>
-      <c r="I7" s="43"/>
-      <c r="J7" s="31"/>
-      <c r="K7" s="42"/>
-      <c r="L7" s="25"/>
+      <c r="I7" s="41"/>
+      <c r="J7" s="35"/>
+      <c r="K7" s="39"/>
+      <c r="L7" s="33"/>
     </row>
     <row r="8" spans="1:12" ht="22" customHeight="1" thickTop="1">
-      <c r="A8" s="25"/>
-      <c r="B8" s="38"/>
+      <c r="A8" s="33"/>
+      <c r="B8" s="30"/>
       <c r="C8" s="32"/>
-      <c r="D8" s="35"/>
+      <c r="D8" s="42"/>
       <c r="E8" s="51" t="s">
         <v>4</v>
       </c>
-      <c r="F8" s="22" t="s">
+      <c r="F8" s="29" t="s">
         <v>5</v>
       </c>
       <c r="G8" s="54"/>
-      <c r="H8" s="31" t="s">
+      <c r="H8" s="35" t="s">
         <v>10</v>
       </c>
-      <c r="I8" s="43"/>
+      <c r="I8" s="41"/>
       <c r="J8" s="32"/>
       <c r="K8" s="57"/>
-      <c r="L8" s="25"/>
+      <c r="L8" s="33"/>
     </row>
     <row r="9" spans="1:12" ht="22" customHeight="1" thickBot="1">
-      <c r="A9" s="25"/>
-      <c r="B9" s="50"/>
+      <c r="A9" s="33"/>
+      <c r="B9" s="48"/>
       <c r="C9" s="32"/>
-      <c r="D9" s="35"/>
+      <c r="D9" s="42"/>
       <c r="E9" s="52"/>
-      <c r="F9" s="22"/>
+      <c r="F9" s="29"/>
       <c r="G9" s="54"/>
       <c r="H9" s="32"/>
-      <c r="I9" s="43"/>
+      <c r="I9" s="41"/>
       <c r="J9" s="32"/>
       <c r="K9" s="32"/>
-      <c r="L9" s="25"/>
+      <c r="L9" s="33"/>
     </row>
     <row r="10" spans="1:12" ht="22" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A10" s="25"/>
-      <c r="B10" s="34" t="s">
+      <c r="A10" s="33"/>
+      <c r="B10" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="33"/>
-      <c r="D10" s="36"/>
+      <c r="C10" s="40"/>
+      <c r="D10" s="37"/>
       <c r="E10" s="52"/>
       <c r="F10" s="8"/>
-      <c r="G10" s="43"/>
+      <c r="G10" s="41"/>
       <c r="H10" s="56"/>
-      <c r="I10" s="42"/>
-      <c r="J10" s="33"/>
-      <c r="K10" s="41" t="s">
+      <c r="I10" s="39"/>
+      <c r="J10" s="40"/>
+      <c r="K10" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="L10" s="25"/>
+      <c r="L10" s="33"/>
     </row>
     <row r="11" spans="1:12" ht="22" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A11" s="25"/>
-      <c r="B11" s="48"/>
-      <c r="C11" s="49"/>
+      <c r="A11" s="33"/>
+      <c r="B11" s="49"/>
+      <c r="C11" s="50"/>
       <c r="D11" s="32"/>
       <c r="E11" s="52"/>
       <c r="F11" s="9"/>
-      <c r="G11" s="42"/>
+      <c r="G11" s="39"/>
       <c r="H11" s="56"/>
       <c r="I11" s="32"/>
       <c r="J11" s="32"/>
-      <c r="K11" s="42"/>
-      <c r="L11" s="25"/>
+      <c r="K11" s="39"/>
+      <c r="L11" s="33"/>
     </row>
     <row r="12" spans="1:12" ht="22" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A12" s="25"/>
-      <c r="B12" s="38"/>
-      <c r="C12" s="49"/>
+      <c r="A12" s="33"/>
+      <c r="B12" s="30"/>
+      <c r="C12" s="50"/>
       <c r="D12" s="32"/>
       <c r="E12" s="52"/>
       <c r="F12" s="55" t="s">
@@ -3882,12 +3808,12 @@
       <c r="I12" s="32"/>
       <c r="J12" s="32"/>
       <c r="K12" s="57"/>
-      <c r="L12" s="25"/>
+      <c r="L12" s="33"/>
     </row>
     <row r="13" spans="1:12" ht="22" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A13" s="25"/>
-      <c r="B13" s="50"/>
-      <c r="C13" s="49"/>
+      <c r="A13" s="33"/>
+      <c r="B13" s="48"/>
+      <c r="C13" s="50"/>
       <c r="D13" s="32"/>
       <c r="E13" s="52"/>
       <c r="F13" s="56"/>
@@ -3896,14 +3822,14 @@
       <c r="I13" s="32"/>
       <c r="J13" s="32"/>
       <c r="K13" s="32"/>
-      <c r="L13" s="25"/>
+      <c r="L13" s="33"/>
     </row>
     <row r="14" spans="1:12" ht="22" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A14" s="25"/>
-      <c r="B14" s="34" t="s">
+      <c r="A14" s="33"/>
+      <c r="B14" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="49"/>
+      <c r="C14" s="50"/>
       <c r="D14" s="32"/>
       <c r="E14" s="52"/>
       <c r="F14" s="32"/>
@@ -3911,95 +3837,95 @@
       <c r="H14" s="56"/>
       <c r="I14" s="32"/>
       <c r="J14" s="32"/>
-      <c r="K14" s="41" t="s">
+      <c r="K14" s="38" t="s">
         <v>8</v>
       </c>
-      <c r="L14" s="25"/>
+      <c r="L14" s="33"/>
     </row>
     <row r="15" spans="1:12" ht="22" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A15" s="25"/>
-      <c r="B15" s="48"/>
-      <c r="C15" s="49"/>
-      <c r="D15" s="34" t="s">
+      <c r="A15" s="33"/>
+      <c r="B15" s="49"/>
+      <c r="C15" s="50"/>
+      <c r="D15" s="36" t="s">
         <v>9</v>
       </c>
       <c r="E15" s="52"/>
       <c r="F15" s="32"/>
       <c r="G15" s="32"/>
       <c r="H15" s="56"/>
-      <c r="I15" s="41" t="s">
+      <c r="I15" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="J15" s="31"/>
-      <c r="K15" s="42"/>
-      <c r="L15" s="25"/>
+      <c r="J15" s="35"/>
+      <c r="K15" s="39"/>
+      <c r="L15" s="33"/>
     </row>
     <row r="16" spans="1:12" ht="22" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A16" s="25"/>
-      <c r="B16" s="38"/>
-      <c r="C16" s="49"/>
-      <c r="D16" s="35"/>
+      <c r="A16" s="33"/>
+      <c r="B16" s="30"/>
+      <c r="C16" s="50"/>
+      <c r="D16" s="42"/>
       <c r="E16" s="53"/>
       <c r="F16" s="32"/>
       <c r="G16" s="32"/>
       <c r="H16" s="58"/>
-      <c r="I16" s="43"/>
+      <c r="I16" s="41"/>
       <c r="J16" s="32"/>
       <c r="K16" s="57"/>
-      <c r="L16" s="25"/>
+      <c r="L16" s="33"/>
     </row>
     <row r="17" spans="1:12" ht="22" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A17" s="25"/>
-      <c r="B17" s="50"/>
-      <c r="C17" s="49"/>
-      <c r="D17" s="35"/>
+      <c r="A17" s="33"/>
+      <c r="B17" s="48"/>
+      <c r="C17" s="50"/>
+      <c r="D17" s="42"/>
       <c r="E17" s="32"/>
       <c r="F17" s="32"/>
       <c r="G17" s="32"/>
       <c r="H17" s="32"/>
-      <c r="I17" s="43"/>
+      <c r="I17" s="41"/>
       <c r="J17" s="32"/>
       <c r="K17" s="32"/>
-      <c r="L17" s="25"/>
+      <c r="L17" s="33"/>
     </row>
     <row r="18" spans="1:12" ht="22" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A18" s="25"/>
-      <c r="B18" s="34" t="s">
+      <c r="A18" s="33"/>
+      <c r="B18" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="C18" s="31"/>
-      <c r="D18" s="35"/>
+      <c r="C18" s="35"/>
+      <c r="D18" s="42"/>
       <c r="E18" s="32"/>
       <c r="F18" s="32"/>
       <c r="G18" s="32"/>
       <c r="H18" s="32"/>
-      <c r="I18" s="42"/>
-      <c r="J18" s="33"/>
-      <c r="K18" s="41" t="s">
+      <c r="I18" s="39"/>
+      <c r="J18" s="40"/>
+      <c r="K18" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="L18" s="25"/>
+      <c r="L18" s="33"/>
     </row>
     <row r="19" spans="1:12" ht="22" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A19" s="25"/>
-      <c r="B19" s="48"/>
-      <c r="C19" s="34" t="s">
+      <c r="A19" s="33"/>
+      <c r="B19" s="49"/>
+      <c r="C19" s="36" t="s">
         <v>12</v>
       </c>
-      <c r="D19" s="36"/>
+      <c r="D19" s="37"/>
       <c r="E19" s="32"/>
       <c r="F19" s="32"/>
       <c r="G19" s="32"/>
       <c r="H19" s="32"/>
-      <c r="I19" s="31"/>
-      <c r="J19" s="31"/>
-      <c r="K19" s="42"/>
-      <c r="L19" s="25"/>
+      <c r="I19" s="35"/>
+      <c r="J19" s="35"/>
+      <c r="K19" s="39"/>
+      <c r="L19" s="33"/>
     </row>
     <row r="20" spans="1:12" ht="22" customHeight="1" thickTop="1">
-      <c r="A20" s="25"/>
-      <c r="B20" s="40"/>
-      <c r="C20" s="35"/>
+      <c r="A20" s="33"/>
+      <c r="B20" s="43"/>
+      <c r="C20" s="42"/>
       <c r="D20" s="32"/>
       <c r="E20" s="32"/>
       <c r="F20" s="32"/>
@@ -4007,13 +3933,13 @@
       <c r="H20" s="32"/>
       <c r="I20" s="32"/>
       <c r="J20" s="32"/>
-      <c r="K20" s="31"/>
-      <c r="L20" s="25"/>
+      <c r="K20" s="35"/>
+      <c r="L20" s="33"/>
     </row>
     <row r="21" spans="1:12" ht="22" customHeight="1" thickBot="1">
-      <c r="A21" s="25"/>
-      <c r="B21" s="39"/>
-      <c r="C21" s="36"/>
+      <c r="A21" s="33"/>
+      <c r="B21" s="31"/>
+      <c r="C21" s="37"/>
       <c r="D21" s="32"/>
       <c r="E21" s="32"/>
       <c r="F21" s="32"/>
@@ -4022,10 +3948,10 @@
       <c r="I21" s="32"/>
       <c r="J21" s="32"/>
       <c r="K21" s="32"/>
-      <c r="L21" s="25"/>
+      <c r="L21" s="33"/>
     </row>
     <row r="22" spans="1:12" ht="22" customHeight="1" thickTop="1">
-      <c r="A22" s="25"/>
+      <c r="A22" s="33"/>
       <c r="C22" s="1"/>
       <c r="D22" s="32"/>
       <c r="E22" s="32"/>
@@ -4035,15 +3961,64 @@
       <c r="I22" s="32"/>
       <c r="J22" s="32"/>
       <c r="K22" s="32"/>
-      <c r="L22" s="25"/>
+      <c r="L22" s="33"/>
     </row>
   </sheetData>
   <mergeCells count="75">
-    <mergeCell ref="I19:I22"/>
-    <mergeCell ref="J19:J22"/>
-    <mergeCell ref="K20:K22"/>
-    <mergeCell ref="A19:A20"/>
-    <mergeCell ref="C19:C21"/>
+    <mergeCell ref="L3:L4"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D4"/>
+    <mergeCell ref="E1:E7"/>
+    <mergeCell ref="F1:G7"/>
+    <mergeCell ref="H1:H7"/>
+    <mergeCell ref="K4:K5"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="D5:D10"/>
+    <mergeCell ref="I5:I10"/>
+    <mergeCell ref="L5:L6"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="K6:K7"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="C7:C10"/>
+    <mergeCell ref="J7:J10"/>
+    <mergeCell ref="I1:I4"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="C3:C6"/>
+    <mergeCell ref="J3:J6"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="L7:L8"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="E8:E16"/>
+    <mergeCell ref="F8:G9"/>
+    <mergeCell ref="H8:H16"/>
+    <mergeCell ref="K8:K9"/>
+    <mergeCell ref="J11:J14"/>
+    <mergeCell ref="L11:L12"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="F12:G13"/>
+    <mergeCell ref="F14:G22"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="L9:L10"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="K10:K11"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="C11:C14"/>
+    <mergeCell ref="D11:D14"/>
+    <mergeCell ref="I11:I14"/>
+    <mergeCell ref="K12:K13"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="L13:L14"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="K14:K15"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="C15:C18"/>
+    <mergeCell ref="D15:D19"/>
     <mergeCell ref="J15:J18"/>
     <mergeCell ref="L15:L16"/>
     <mergeCell ref="B16:B17"/>
@@ -4060,60 +4035,11 @@
     <mergeCell ref="A21:A22"/>
     <mergeCell ref="L21:L22"/>
     <mergeCell ref="I15:I18"/>
-    <mergeCell ref="L9:L10"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="K10:K11"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="C11:C14"/>
-    <mergeCell ref="D11:D14"/>
-    <mergeCell ref="I11:I14"/>
-    <mergeCell ref="K12:K13"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="L13:L14"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="K14:K15"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="C15:C18"/>
-    <mergeCell ref="D15:D19"/>
-    <mergeCell ref="L1:L2"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="K2:K3"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="L7:L8"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="E8:E16"/>
-    <mergeCell ref="F8:G9"/>
-    <mergeCell ref="H8:H16"/>
-    <mergeCell ref="K8:K9"/>
-    <mergeCell ref="J11:J14"/>
-    <mergeCell ref="L11:L12"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="F12:G13"/>
-    <mergeCell ref="F14:G22"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="C7:C10"/>
-    <mergeCell ref="J7:J10"/>
-    <mergeCell ref="I1:I4"/>
-    <mergeCell ref="J1:J2"/>
-    <mergeCell ref="C3:C6"/>
-    <mergeCell ref="J3:J6"/>
-    <mergeCell ref="L3:L4"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D4"/>
-    <mergeCell ref="E1:E7"/>
-    <mergeCell ref="F1:G7"/>
-    <mergeCell ref="H1:H7"/>
-    <mergeCell ref="K4:K5"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="D5:D10"/>
-    <mergeCell ref="I5:I10"/>
-    <mergeCell ref="L5:L6"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="K6:K7"/>
-    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="I19:I22"/>
+    <mergeCell ref="J19:J22"/>
+    <mergeCell ref="K20:K22"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="C19:C21"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4128,7 +4054,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="22" customHeight="1"/>
   <sheetData>
     <row r="1" spans="1:12" ht="22" customHeight="1" thickBot="1">
-      <c r="A1" s="25"/>
+      <c r="A1" s="33"/>
       <c r="C1" s="32"/>
       <c r="D1" s="32"/>
       <c r="E1" s="32"/>
@@ -4140,11 +4066,11 @@
       <c r="I1" s="32"/>
       <c r="J1" s="32"/>
       <c r="K1" s="1"/>
-      <c r="L1" s="25"/>
+      <c r="L1" s="33"/>
     </row>
     <row r="2" spans="1:12" ht="22" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A2" s="25"/>
-      <c r="B2" s="34" t="s">
+      <c r="A2" s="33"/>
+      <c r="B2" s="36" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="32"/>
@@ -4155,15 +4081,15 @@
       <c r="H2" s="32"/>
       <c r="I2" s="32"/>
       <c r="J2" s="32"/>
-      <c r="K2" s="41" t="s">
+      <c r="K2" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="L2" s="25"/>
+      <c r="L2" s="33"/>
     </row>
     <row r="3" spans="1:12" ht="22" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A3" s="25"/>
-      <c r="B3" s="48"/>
-      <c r="C3" s="34" t="s">
+      <c r="A3" s="33"/>
+      <c r="B3" s="49"/>
+      <c r="C3" s="36" t="s">
         <v>1</v>
       </c>
       <c r="D3" s="32"/>
@@ -4172,146 +4098,146 @@
       <c r="G3" s="44"/>
       <c r="H3" s="32"/>
       <c r="I3" s="32"/>
-      <c r="J3" s="41" t="s">
+      <c r="J3" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="K3" s="42"/>
-      <c r="L3" s="25"/>
+      <c r="K3" s="39"/>
+      <c r="L3" s="33"/>
     </row>
     <row r="4" spans="1:12" ht="22" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A4" s="25"/>
-      <c r="B4" s="38"/>
-      <c r="C4" s="35"/>
+      <c r="A4" s="33"/>
+      <c r="B4" s="30"/>
+      <c r="C4" s="42"/>
       <c r="D4" s="32"/>
       <c r="E4" s="32"/>
       <c r="F4" s="44"/>
       <c r="G4" s="44"/>
       <c r="H4" s="32"/>
       <c r="I4" s="32"/>
-      <c r="J4" s="43"/>
+      <c r="J4" s="41"/>
       <c r="K4" s="57"/>
-      <c r="L4" s="25"/>
+      <c r="L4" s="33"/>
     </row>
     <row r="5" spans="1:12" ht="22" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A5" s="25"/>
-      <c r="B5" s="50"/>
-      <c r="C5" s="35"/>
-      <c r="D5" s="34" t="s">
+      <c r="A5" s="33"/>
+      <c r="B5" s="48"/>
+      <c r="C5" s="42"/>
+      <c r="D5" s="36" t="s">
         <v>2</v>
       </c>
       <c r="E5" s="32"/>
       <c r="F5" s="44"/>
       <c r="G5" s="44"/>
       <c r="H5" s="32"/>
-      <c r="I5" s="41" t="s">
+      <c r="I5" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="J5" s="43"/>
+      <c r="J5" s="41"/>
       <c r="K5" s="32"/>
-      <c r="L5" s="25"/>
+      <c r="L5" s="33"/>
     </row>
     <row r="6" spans="1:12" ht="22" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A6" s="25"/>
-      <c r="B6" s="34" t="s">
+      <c r="A6" s="33"/>
+      <c r="B6" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="36"/>
-      <c r="D6" s="35"/>
+      <c r="C6" s="37"/>
+      <c r="D6" s="42"/>
       <c r="E6" s="32"/>
       <c r="F6" s="44"/>
       <c r="G6" s="44"/>
       <c r="H6" s="32"/>
-      <c r="I6" s="43"/>
-      <c r="J6" s="42"/>
-      <c r="K6" s="41" t="s">
+      <c r="I6" s="41"/>
+      <c r="J6" s="39"/>
+      <c r="K6" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="L6" s="25"/>
+      <c r="L6" s="33"/>
     </row>
     <row r="7" spans="1:12" ht="22" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A7" s="25"/>
-      <c r="B7" s="48"/>
-      <c r="C7" s="31"/>
-      <c r="D7" s="35"/>
+      <c r="A7" s="33"/>
+      <c r="B7" s="49"/>
+      <c r="C7" s="35"/>
+      <c r="D7" s="42"/>
       <c r="E7" s="32"/>
       <c r="F7" s="44"/>
       <c r="G7" s="44"/>
       <c r="H7" s="32"/>
-      <c r="I7" s="43"/>
-      <c r="J7" s="31"/>
-      <c r="K7" s="42"/>
-      <c r="L7" s="25"/>
+      <c r="I7" s="41"/>
+      <c r="J7" s="35"/>
+      <c r="K7" s="39"/>
+      <c r="L7" s="33"/>
     </row>
     <row r="8" spans="1:12" ht="22" customHeight="1" thickTop="1">
-      <c r="A8" s="25"/>
-      <c r="B8" s="38"/>
+      <c r="A8" s="33"/>
+      <c r="B8" s="30"/>
       <c r="C8" s="32"/>
-      <c r="D8" s="35"/>
+      <c r="D8" s="42"/>
       <c r="E8" s="51" t="s">
         <v>4</v>
       </c>
-      <c r="F8" s="22" t="s">
+      <c r="F8" s="29" t="s">
         <v>5</v>
       </c>
       <c r="G8" s="54"/>
-      <c r="H8" s="31" t="s">
+      <c r="H8" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="I8" s="43"/>
+      <c r="I8" s="41"/>
       <c r="J8" s="32"/>
       <c r="K8" s="57"/>
-      <c r="L8" s="25"/>
+      <c r="L8" s="33"/>
     </row>
     <row r="9" spans="1:12" ht="22" customHeight="1" thickBot="1">
-      <c r="A9" s="25"/>
-      <c r="B9" s="50"/>
+      <c r="A9" s="33"/>
+      <c r="B9" s="48"/>
       <c r="C9" s="32"/>
-      <c r="D9" s="35"/>
+      <c r="D9" s="42"/>
       <c r="E9" s="52"/>
-      <c r="F9" s="22"/>
+      <c r="F9" s="29"/>
       <c r="G9" s="54"/>
       <c r="H9" s="32"/>
-      <c r="I9" s="43"/>
+      <c r="I9" s="41"/>
       <c r="J9" s="32"/>
       <c r="K9" s="32"/>
-      <c r="L9" s="25"/>
+      <c r="L9" s="33"/>
     </row>
     <row r="10" spans="1:12" ht="22" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A10" s="25"/>
-      <c r="B10" s="34" t="s">
+      <c r="A10" s="33"/>
+      <c r="B10" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="33"/>
-      <c r="D10" s="36"/>
+      <c r="C10" s="40"/>
+      <c r="D10" s="37"/>
       <c r="E10" s="52"/>
-      <c r="F10" s="35"/>
-      <c r="G10" s="43"/>
+      <c r="F10" s="42"/>
+      <c r="G10" s="41"/>
       <c r="H10" s="56"/>
-      <c r="I10" s="42"/>
-      <c r="J10" s="33"/>
-      <c r="K10" s="41" t="s">
+      <c r="I10" s="39"/>
+      <c r="J10" s="40"/>
+      <c r="K10" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="L10" s="25"/>
+      <c r="L10" s="33"/>
     </row>
     <row r="11" spans="1:12" ht="22" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A11" s="25"/>
-      <c r="B11" s="48"/>
-      <c r="C11" s="49"/>
+      <c r="A11" s="33"/>
+      <c r="B11" s="49"/>
+      <c r="C11" s="50"/>
       <c r="D11" s="32"/>
       <c r="E11" s="52"/>
-      <c r="F11" s="36"/>
-      <c r="G11" s="42"/>
+      <c r="F11" s="37"/>
+      <c r="G11" s="39"/>
       <c r="H11" s="56"/>
       <c r="I11" s="32"/>
       <c r="J11" s="32"/>
-      <c r="K11" s="42"/>
-      <c r="L11" s="25"/>
+      <c r="K11" s="39"/>
+      <c r="L11" s="33"/>
     </row>
     <row r="12" spans="1:12" ht="22" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A12" s="25"/>
-      <c r="B12" s="38"/>
-      <c r="C12" s="49"/>
+      <c r="A12" s="33"/>
+      <c r="B12" s="30"/>
+      <c r="C12" s="50"/>
       <c r="D12" s="32"/>
       <c r="E12" s="52"/>
       <c r="F12" s="55" t="s">
@@ -4322,12 +4248,12 @@
       <c r="I12" s="32"/>
       <c r="J12" s="32"/>
       <c r="K12" s="57"/>
-      <c r="L12" s="25"/>
+      <c r="L12" s="33"/>
     </row>
     <row r="13" spans="1:12" ht="22" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A13" s="25"/>
-      <c r="B13" s="50"/>
-      <c r="C13" s="49"/>
+      <c r="A13" s="33"/>
+      <c r="B13" s="48"/>
+      <c r="C13" s="50"/>
       <c r="D13" s="32"/>
       <c r="E13" s="52"/>
       <c r="F13" s="56"/>
@@ -4336,14 +4262,14 @@
       <c r="I13" s="32"/>
       <c r="J13" s="32"/>
       <c r="K13" s="32"/>
-      <c r="L13" s="25"/>
+      <c r="L13" s="33"/>
     </row>
     <row r="14" spans="1:12" ht="22" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A14" s="25"/>
-      <c r="B14" s="34" t="s">
+      <c r="A14" s="33"/>
+      <c r="B14" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="49"/>
+      <c r="C14" s="50"/>
       <c r="D14" s="32"/>
       <c r="E14" s="52"/>
       <c r="F14" s="32"/>
@@ -4351,123 +4277,123 @@
       <c r="H14" s="56"/>
       <c r="I14" s="32"/>
       <c r="J14" s="32"/>
-      <c r="K14" s="41" t="s">
+      <c r="K14" s="38" t="s">
         <v>8</v>
       </c>
-      <c r="L14" s="25"/>
+      <c r="L14" s="33"/>
     </row>
     <row r="15" spans="1:12" ht="22" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A15" s="25"/>
-      <c r="B15" s="48"/>
-      <c r="C15" s="49"/>
-      <c r="D15" s="34" t="s">
+      <c r="A15" s="33"/>
+      <c r="B15" s="49"/>
+      <c r="C15" s="50"/>
+      <c r="D15" s="36" t="s">
         <v>9</v>
       </c>
       <c r="E15" s="52"/>
       <c r="F15" s="32"/>
       <c r="G15" s="32"/>
       <c r="H15" s="56"/>
-      <c r="I15" s="41" t="s">
+      <c r="I15" s="38" t="s">
         <v>10</v>
       </c>
-      <c r="J15" s="31"/>
-      <c r="K15" s="42"/>
-      <c r="L15" s="25"/>
+      <c r="J15" s="35"/>
+      <c r="K15" s="39"/>
+      <c r="L15" s="33"/>
     </row>
     <row r="16" spans="1:12" ht="22" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A16" s="25"/>
-      <c r="B16" s="38"/>
-      <c r="C16" s="49"/>
-      <c r="D16" s="35"/>
+      <c r="A16" s="33"/>
+      <c r="B16" s="30"/>
+      <c r="C16" s="50"/>
+      <c r="D16" s="42"/>
       <c r="E16" s="53"/>
       <c r="F16" s="32"/>
       <c r="G16" s="32"/>
       <c r="H16" s="58"/>
-      <c r="I16" s="43"/>
+      <c r="I16" s="41"/>
       <c r="J16" s="32"/>
       <c r="K16" s="57"/>
-      <c r="L16" s="25"/>
+      <c r="L16" s="33"/>
     </row>
     <row r="17" spans="1:12" ht="22" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A17" s="25"/>
-      <c r="B17" s="50"/>
-      <c r="C17" s="49"/>
-      <c r="D17" s="35"/>
+      <c r="A17" s="33"/>
+      <c r="B17" s="48"/>
+      <c r="C17" s="50"/>
+      <c r="D17" s="42"/>
       <c r="E17" s="32"/>
       <c r="F17" s="32"/>
       <c r="G17" s="32"/>
       <c r="H17" s="32"/>
-      <c r="I17" s="43"/>
+      <c r="I17" s="41"/>
       <c r="J17" s="32"/>
       <c r="K17" s="32"/>
-      <c r="L17" s="25"/>
+      <c r="L17" s="33"/>
     </row>
     <row r="18" spans="1:12" ht="22" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A18" s="25"/>
-      <c r="B18" s="34" t="s">
+      <c r="A18" s="33"/>
+      <c r="B18" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="C18" s="31"/>
-      <c r="D18" s="35"/>
+      <c r="C18" s="35"/>
+      <c r="D18" s="42"/>
       <c r="E18" s="32"/>
       <c r="F18" s="32"/>
       <c r="G18" s="32"/>
       <c r="H18" s="32"/>
-      <c r="I18" s="43"/>
-      <c r="J18" s="33"/>
-      <c r="K18" s="41" t="s">
+      <c r="I18" s="41"/>
+      <c r="J18" s="40"/>
+      <c r="K18" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="L18" s="25"/>
+      <c r="L18" s="33"/>
     </row>
     <row r="19" spans="1:12" ht="22" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A19" s="25"/>
-      <c r="B19" s="48"/>
-      <c r="C19" s="34" t="s">
+      <c r="A19" s="33"/>
+      <c r="B19" s="49"/>
+      <c r="C19" s="36" t="s">
         <v>12</v>
       </c>
-      <c r="D19" s="36"/>
+      <c r="D19" s="37"/>
       <c r="E19" s="32"/>
       <c r="F19" s="32"/>
       <c r="G19" s="32"/>
       <c r="H19" s="32"/>
-      <c r="I19" s="42"/>
-      <c r="J19" s="41" t="s">
+      <c r="I19" s="39"/>
+      <c r="J19" s="38" t="s">
         <v>13</v>
       </c>
-      <c r="K19" s="42"/>
-      <c r="L19" s="25"/>
+      <c r="K19" s="39"/>
+      <c r="L19" s="33"/>
     </row>
     <row r="20" spans="1:12" ht="22" customHeight="1" thickTop="1">
-      <c r="A20" s="25"/>
-      <c r="B20" s="40"/>
-      <c r="C20" s="35"/>
+      <c r="A20" s="33"/>
+      <c r="B20" s="43"/>
+      <c r="C20" s="42"/>
       <c r="D20" s="32"/>
       <c r="E20" s="32"/>
       <c r="F20" s="32"/>
       <c r="G20" s="32"/>
       <c r="H20" s="32"/>
       <c r="I20" s="32"/>
-      <c r="J20" s="43"/>
+      <c r="J20" s="41"/>
       <c r="K20" s="32"/>
-      <c r="L20" s="25"/>
+      <c r="L20" s="33"/>
     </row>
     <row r="21" spans="1:12" ht="22" customHeight="1" thickBot="1">
-      <c r="A21" s="25"/>
-      <c r="B21" s="39"/>
-      <c r="C21" s="36"/>
+      <c r="A21" s="33"/>
+      <c r="B21" s="31"/>
+      <c r="C21" s="37"/>
       <c r="D21" s="32"/>
       <c r="E21" s="32"/>
       <c r="F21" s="32"/>
       <c r="G21" s="32"/>
       <c r="H21" s="32"/>
       <c r="I21" s="32"/>
-      <c r="J21" s="42"/>
-      <c r="K21" s="33"/>
-      <c r="L21" s="25"/>
+      <c r="J21" s="39"/>
+      <c r="K21" s="40"/>
+      <c r="L21" s="33"/>
     </row>
     <row r="22" spans="1:12" ht="22" customHeight="1" thickTop="1">
-      <c r="A22" s="25"/>
+      <c r="A22" s="33"/>
       <c r="C22" s="1"/>
       <c r="D22" s="32"/>
       <c r="E22" s="32"/>
@@ -4477,27 +4403,53 @@
       <c r="I22" s="32"/>
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
-      <c r="L22" s="25"/>
+      <c r="L22" s="33"/>
     </row>
   </sheetData>
   <mergeCells count="76">
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="K12:K13"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="F12:G13"/>
-    <mergeCell ref="F14:G22"/>
-    <mergeCell ref="A19:A20"/>
-    <mergeCell ref="C19:C21"/>
-    <mergeCell ref="J19:J21"/>
-    <mergeCell ref="A21:A22"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="E8:E16"/>
-    <mergeCell ref="F8:G9"/>
-    <mergeCell ref="H8:H16"/>
-    <mergeCell ref="K8:K9"/>
-    <mergeCell ref="J11:J14"/>
-    <mergeCell ref="K10:K11"/>
+    <mergeCell ref="L19:L20"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="D20:D22"/>
+    <mergeCell ref="I20:I22"/>
+    <mergeCell ref="K20:K21"/>
+    <mergeCell ref="L21:L22"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="K18:K19"/>
+    <mergeCell ref="E17:E22"/>
+    <mergeCell ref="H17:H22"/>
+    <mergeCell ref="L17:L18"/>
+    <mergeCell ref="L11:L12"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="L9:L10"/>
+    <mergeCell ref="K6:K7"/>
+    <mergeCell ref="L13:L14"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="K14:K15"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="C15:C18"/>
+    <mergeCell ref="D15:D19"/>
+    <mergeCell ref="I15:I19"/>
+    <mergeCell ref="J15:J18"/>
+    <mergeCell ref="L15:L16"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="K16:K17"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="L3:L4"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="D1:D4"/>
+    <mergeCell ref="E1:E7"/>
+    <mergeCell ref="F1:G7"/>
+    <mergeCell ref="H1:H7"/>
+    <mergeCell ref="K4:K5"/>
+    <mergeCell ref="I1:I4"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="L7:L8"/>
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="D5:D10"/>
     <mergeCell ref="I5:I10"/>
@@ -4514,49 +4466,23 @@
     <mergeCell ref="C11:C14"/>
     <mergeCell ref="D11:D14"/>
     <mergeCell ref="I11:I14"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="L1:L2"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="K2:K3"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="L3:L4"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="D1:D4"/>
-    <mergeCell ref="E1:E7"/>
-    <mergeCell ref="F1:G7"/>
-    <mergeCell ref="H1:H7"/>
-    <mergeCell ref="K4:K5"/>
-    <mergeCell ref="I1:I4"/>
-    <mergeCell ref="J1:J2"/>
-    <mergeCell ref="L7:L8"/>
-    <mergeCell ref="L11:L12"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="L9:L10"/>
-    <mergeCell ref="K6:K7"/>
-    <mergeCell ref="L13:L14"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="K14:K15"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="C15:C18"/>
-    <mergeCell ref="D15:D19"/>
-    <mergeCell ref="I15:I19"/>
-    <mergeCell ref="J15:J18"/>
-    <mergeCell ref="L15:L16"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="K16:K17"/>
-    <mergeCell ref="L19:L20"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="D20:D22"/>
-    <mergeCell ref="I20:I22"/>
-    <mergeCell ref="K20:K21"/>
-    <mergeCell ref="L21:L22"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="K18:K19"/>
-    <mergeCell ref="E17:E22"/>
-    <mergeCell ref="H17:H22"/>
-    <mergeCell ref="L17:L18"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="E8:E16"/>
+    <mergeCell ref="F8:G9"/>
+    <mergeCell ref="H8:H16"/>
+    <mergeCell ref="K8:K9"/>
+    <mergeCell ref="J11:J14"/>
+    <mergeCell ref="K10:K11"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="K12:K13"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="F12:G13"/>
+    <mergeCell ref="F14:G22"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="C19:C21"/>
+    <mergeCell ref="J19:J21"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="A17:A18"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4571,7 +4497,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="20" customHeight="1"/>
   <sheetData>
     <row r="1" spans="1:12" ht="20" customHeight="1" thickBot="1">
-      <c r="A1" s="25"/>
+      <c r="A1" s="33"/>
       <c r="C1" s="32"/>
       <c r="D1" s="32"/>
       <c r="E1" s="32"/>
@@ -4583,11 +4509,11 @@
       <c r="I1" s="32"/>
       <c r="J1" s="32"/>
       <c r="K1" s="1"/>
-      <c r="L1" s="25"/>
+      <c r="L1" s="33"/>
     </row>
     <row r="2" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A2" s="25"/>
-      <c r="B2" s="34" t="s">
+      <c r="A2" s="33"/>
+      <c r="B2" s="36" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="32"/>
@@ -4598,15 +4524,15 @@
       <c r="H2" s="32"/>
       <c r="I2" s="32"/>
       <c r="J2" s="32"/>
-      <c r="K2" s="41" t="s">
+      <c r="K2" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="L2" s="25"/>
+      <c r="L2" s="33"/>
     </row>
     <row r="3" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A3" s="25"/>
-      <c r="B3" s="48"/>
-      <c r="C3" s="34" t="s">
+      <c r="A3" s="33"/>
+      <c r="B3" s="49"/>
+      <c r="C3" s="36" t="s">
         <v>1</v>
       </c>
       <c r="D3" s="32"/>
@@ -4615,306 +4541,306 @@
       <c r="G3" s="44"/>
       <c r="H3" s="32"/>
       <c r="I3" s="32"/>
-      <c r="J3" s="41" t="s">
+      <c r="J3" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="K3" s="42"/>
-      <c r="L3" s="25"/>
+      <c r="K3" s="39"/>
+      <c r="L3" s="33"/>
     </row>
     <row r="4" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A4" s="25"/>
-      <c r="B4" s="38"/>
-      <c r="C4" s="35"/>
+      <c r="A4" s="33"/>
+      <c r="B4" s="30"/>
+      <c r="C4" s="42"/>
       <c r="D4" s="32"/>
       <c r="E4" s="32"/>
       <c r="F4" s="44"/>
       <c r="G4" s="44"/>
       <c r="H4" s="32"/>
       <c r="I4" s="32"/>
-      <c r="J4" s="43"/>
+      <c r="J4" s="41"/>
       <c r="K4" s="57"/>
-      <c r="L4" s="25"/>
+      <c r="L4" s="33"/>
     </row>
     <row r="5" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A5" s="25"/>
-      <c r="B5" s="50"/>
-      <c r="C5" s="35"/>
-      <c r="D5" s="34" t="s">
+      <c r="A5" s="33"/>
+      <c r="B5" s="48"/>
+      <c r="C5" s="42"/>
+      <c r="D5" s="36" t="s">
         <v>10</v>
       </c>
       <c r="E5" s="32"/>
       <c r="F5" s="44"/>
       <c r="G5" s="44"/>
       <c r="H5" s="32"/>
-      <c r="I5" s="41" t="s">
+      <c r="I5" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="J5" s="43"/>
+      <c r="J5" s="41"/>
       <c r="K5" s="32"/>
-      <c r="L5" s="25"/>
+      <c r="L5" s="33"/>
     </row>
     <row r="6" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A6" s="25"/>
-      <c r="B6" s="34" t="s">
+      <c r="A6" s="33"/>
+      <c r="B6" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="36"/>
-      <c r="D6" s="35"/>
+      <c r="C6" s="37"/>
+      <c r="D6" s="42"/>
       <c r="E6" s="32"/>
       <c r="F6" s="44"/>
       <c r="G6" s="44"/>
       <c r="H6" s="32"/>
-      <c r="I6" s="43"/>
-      <c r="J6" s="42"/>
-      <c r="K6" s="41" t="s">
+      <c r="I6" s="41"/>
+      <c r="J6" s="39"/>
+      <c r="K6" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="L6" s="25"/>
+      <c r="L6" s="33"/>
     </row>
     <row r="7" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A7" s="25"/>
-      <c r="B7" s="48"/>
-      <c r="C7" s="31"/>
-      <c r="D7" s="35"/>
+      <c r="A7" s="33"/>
+      <c r="B7" s="49"/>
+      <c r="C7" s="35"/>
+      <c r="D7" s="42"/>
       <c r="E7" s="32"/>
       <c r="F7" s="44"/>
       <c r="G7" s="44"/>
       <c r="H7" s="32"/>
-      <c r="I7" s="43"/>
-      <c r="J7" s="31"/>
-      <c r="K7" s="42"/>
-      <c r="L7" s="25"/>
+      <c r="I7" s="41"/>
+      <c r="J7" s="35"/>
+      <c r="K7" s="39"/>
+      <c r="L7" s="33"/>
     </row>
     <row r="8" spans="1:12" ht="20" customHeight="1" thickTop="1">
-      <c r="A8" s="25"/>
-      <c r="B8" s="38"/>
+      <c r="A8" s="33"/>
+      <c r="B8" s="30"/>
       <c r="C8" s="32"/>
-      <c r="D8" s="35"/>
-      <c r="E8" s="34" t="s">
+      <c r="D8" s="42"/>
+      <c r="E8" s="36" t="s">
         <v>7</v>
       </c>
       <c r="F8" s="44"/>
       <c r="G8" s="44"/>
-      <c r="H8" s="41" t="s">
+      <c r="H8" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="I8" s="43"/>
+      <c r="I8" s="41"/>
       <c r="J8" s="32"/>
       <c r="K8" s="57"/>
-      <c r="L8" s="25"/>
+      <c r="L8" s="33"/>
     </row>
     <row r="9" spans="1:12" ht="20" customHeight="1" thickBot="1">
-      <c r="A9" s="25"/>
-      <c r="B9" s="50"/>
+      <c r="A9" s="33"/>
+      <c r="B9" s="48"/>
       <c r="C9" s="32"/>
-      <c r="D9" s="35"/>
-      <c r="E9" s="35"/>
-      <c r="F9" s="22" t="s">
+      <c r="D9" s="42"/>
+      <c r="E9" s="42"/>
+      <c r="F9" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="G9" s="22"/>
-      <c r="H9" s="43"/>
-      <c r="I9" s="43"/>
+      <c r="G9" s="29"/>
+      <c r="H9" s="41"/>
+      <c r="I9" s="41"/>
       <c r="J9" s="32"/>
       <c r="K9" s="32"/>
-      <c r="L9" s="25"/>
+      <c r="L9" s="33"/>
     </row>
     <row r="10" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A10" s="25"/>
-      <c r="B10" s="34" t="s">
+      <c r="A10" s="33"/>
+      <c r="B10" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="33"/>
-      <c r="D10" s="36"/>
-      <c r="E10" s="35"/>
-      <c r="F10" s="22"/>
-      <c r="G10" s="22"/>
-      <c r="H10" s="43"/>
-      <c r="I10" s="42"/>
-      <c r="J10" s="33"/>
-      <c r="K10" s="41" t="s">
+      <c r="C10" s="40"/>
+      <c r="D10" s="37"/>
+      <c r="E10" s="42"/>
+      <c r="F10" s="29"/>
+      <c r="G10" s="29"/>
+      <c r="H10" s="41"/>
+      <c r="I10" s="39"/>
+      <c r="J10" s="40"/>
+      <c r="K10" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="L10" s="25"/>
+      <c r="L10" s="33"/>
     </row>
     <row r="11" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A11" s="25"/>
-      <c r="B11" s="48"/>
-      <c r="C11" s="49"/>
+      <c r="A11" s="33"/>
+      <c r="B11" s="49"/>
+      <c r="C11" s="50"/>
       <c r="D11" s="32"/>
-      <c r="E11" s="35"/>
-      <c r="F11" s="35"/>
-      <c r="G11" s="43"/>
-      <c r="H11" s="43"/>
+      <c r="E11" s="42"/>
+      <c r="F11" s="42"/>
+      <c r="G11" s="41"/>
+      <c r="H11" s="41"/>
       <c r="I11" s="32"/>
       <c r="J11" s="32"/>
-      <c r="K11" s="42"/>
-      <c r="L11" s="25"/>
+      <c r="K11" s="39"/>
+      <c r="L11" s="33"/>
     </row>
     <row r="12" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A12" s="25"/>
-      <c r="B12" s="38"/>
-      <c r="C12" s="49"/>
+      <c r="A12" s="33"/>
+      <c r="B12" s="30"/>
+      <c r="C12" s="50"/>
       <c r="D12" s="32"/>
-      <c r="E12" s="35"/>
-      <c r="F12" s="36"/>
-      <c r="G12" s="42"/>
-      <c r="H12" s="43"/>
+      <c r="E12" s="42"/>
+      <c r="F12" s="37"/>
+      <c r="G12" s="39"/>
+      <c r="H12" s="41"/>
       <c r="I12" s="32"/>
       <c r="J12" s="32"/>
       <c r="K12" s="57"/>
-      <c r="L12" s="25"/>
+      <c r="L12" s="33"/>
     </row>
     <row r="13" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A13" s="25"/>
-      <c r="B13" s="50"/>
-      <c r="C13" s="49"/>
+      <c r="A13" s="33"/>
+      <c r="B13" s="48"/>
+      <c r="C13" s="50"/>
       <c r="D13" s="32"/>
-      <c r="E13" s="35"/>
+      <c r="E13" s="42"/>
       <c r="F13" s="32" t="s">
         <v>15</v>
       </c>
       <c r="G13" s="32"/>
-      <c r="H13" s="43"/>
+      <c r="H13" s="41"/>
       <c r="I13" s="32"/>
       <c r="J13" s="32"/>
       <c r="K13" s="32"/>
-      <c r="L13" s="25"/>
+      <c r="L13" s="33"/>
     </row>
     <row r="14" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A14" s="25"/>
-      <c r="B14" s="34" t="s">
+      <c r="A14" s="33"/>
+      <c r="B14" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="49"/>
+      <c r="C14" s="50"/>
       <c r="D14" s="32"/>
-      <c r="E14" s="35"/>
+      <c r="E14" s="42"/>
       <c r="F14" s="32"/>
       <c r="G14" s="32"/>
-      <c r="H14" s="43"/>
+      <c r="H14" s="41"/>
       <c r="I14" s="32"/>
       <c r="J14" s="32"/>
-      <c r="K14" s="41" t="s">
+      <c r="K14" s="38" t="s">
         <v>8</v>
       </c>
-      <c r="L14" s="25"/>
+      <c r="L14" s="33"/>
     </row>
     <row r="15" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A15" s="25"/>
-      <c r="B15" s="48"/>
-      <c r="C15" s="49"/>
-      <c r="D15" s="34" t="s">
+      <c r="A15" s="33"/>
+      <c r="B15" s="49"/>
+      <c r="C15" s="50"/>
+      <c r="D15" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="E15" s="35"/>
+      <c r="E15" s="42"/>
       <c r="F15" s="32"/>
       <c r="G15" s="32"/>
-      <c r="H15" s="43"/>
-      <c r="I15" s="41" t="s">
+      <c r="H15" s="41"/>
+      <c r="I15" s="38" t="s">
         <v>10</v>
       </c>
-      <c r="J15" s="31"/>
-      <c r="K15" s="42"/>
-      <c r="L15" s="25"/>
+      <c r="J15" s="35"/>
+      <c r="K15" s="39"/>
+      <c r="L15" s="33"/>
     </row>
     <row r="16" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A16" s="25"/>
-      <c r="B16" s="38"/>
-      <c r="C16" s="49"/>
-      <c r="D16" s="35"/>
-      <c r="E16" s="35"/>
+      <c r="A16" s="33"/>
+      <c r="B16" s="30"/>
+      <c r="C16" s="50"/>
+      <c r="D16" s="42"/>
+      <c r="E16" s="42"/>
       <c r="F16" s="32"/>
       <c r="G16" s="32"/>
-      <c r="H16" s="43"/>
-      <c r="I16" s="43"/>
+      <c r="H16" s="41"/>
+      <c r="I16" s="41"/>
       <c r="J16" s="32"/>
       <c r="K16" s="57"/>
-      <c r="L16" s="25"/>
+      <c r="L16" s="33"/>
     </row>
     <row r="17" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A17" s="25"/>
-      <c r="B17" s="50"/>
-      <c r="C17" s="49"/>
-      <c r="D17" s="35"/>
-      <c r="E17" s="36"/>
+      <c r="A17" s="33"/>
+      <c r="B17" s="48"/>
+      <c r="C17" s="50"/>
+      <c r="D17" s="42"/>
+      <c r="E17" s="37"/>
       <c r="F17" s="32"/>
       <c r="G17" s="32"/>
-      <c r="H17" s="42"/>
-      <c r="I17" s="43"/>
+      <c r="H17" s="39"/>
+      <c r="I17" s="41"/>
       <c r="J17" s="32"/>
       <c r="K17" s="32"/>
-      <c r="L17" s="25"/>
+      <c r="L17" s="33"/>
     </row>
     <row r="18" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A18" s="25"/>
-      <c r="B18" s="34" t="s">
+      <c r="A18" s="33"/>
+      <c r="B18" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="C18" s="31"/>
-      <c r="D18" s="35"/>
+      <c r="C18" s="35"/>
+      <c r="D18" s="42"/>
       <c r="E18" s="32"/>
       <c r="F18" s="32"/>
       <c r="G18" s="32"/>
       <c r="H18" s="32"/>
-      <c r="I18" s="43"/>
-      <c r="J18" s="33"/>
-      <c r="K18" s="41" t="s">
+      <c r="I18" s="41"/>
+      <c r="J18" s="40"/>
+      <c r="K18" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="L18" s="25"/>
+      <c r="L18" s="33"/>
     </row>
     <row r="19" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A19" s="25"/>
-      <c r="B19" s="48"/>
-      <c r="C19" s="34" t="s">
+      <c r="A19" s="33"/>
+      <c r="B19" s="49"/>
+      <c r="C19" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="D19" s="35"/>
+      <c r="D19" s="42"/>
       <c r="E19" s="32"/>
       <c r="F19" s="32"/>
       <c r="G19" s="32"/>
       <c r="H19" s="32"/>
-      <c r="I19" s="43"/>
-      <c r="J19" s="41" t="s">
+      <c r="I19" s="41"/>
+      <c r="J19" s="38" t="s">
         <v>13</v>
       </c>
-      <c r="K19" s="42"/>
-      <c r="L19" s="25"/>
+      <c r="K19" s="39"/>
+      <c r="L19" s="33"/>
     </row>
     <row r="20" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A20" s="25"/>
-      <c r="B20" s="40"/>
-      <c r="C20" s="35"/>
-      <c r="D20" s="36"/>
+      <c r="A20" s="33"/>
+      <c r="B20" s="43"/>
+      <c r="C20" s="42"/>
+      <c r="D20" s="37"/>
       <c r="E20" s="32"/>
       <c r="F20" s="32"/>
       <c r="G20" s="32"/>
       <c r="H20" s="32"/>
-      <c r="I20" s="42"/>
-      <c r="J20" s="43"/>
+      <c r="I20" s="39"/>
+      <c r="J20" s="41"/>
       <c r="K20" s="32"/>
-      <c r="L20" s="25"/>
+      <c r="L20" s="33"/>
     </row>
     <row r="21" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A21" s="25"/>
-      <c r="B21" s="38"/>
-      <c r="C21" s="35"/>
+      <c r="A21" s="33"/>
+      <c r="B21" s="30"/>
+      <c r="C21" s="42"/>
       <c r="D21" s="32"/>
       <c r="E21" s="32"/>
       <c r="F21" s="32"/>
       <c r="G21" s="32"/>
       <c r="H21" s="32"/>
       <c r="I21" s="32"/>
-      <c r="J21" s="42"/>
+      <c r="J21" s="39"/>
       <c r="K21" s="32"/>
-      <c r="L21" s="25"/>
+      <c r="L21" s="33"/>
     </row>
     <row r="22" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A22" s="25"/>
-      <c r="B22" s="34" t="s">
+      <c r="A22" s="33"/>
+      <c r="B22" s="36" t="s">
         <v>13</v>
       </c>
-      <c r="C22" s="36"/>
+      <c r="C22" s="37"/>
       <c r="D22" s="32"/>
       <c r="E22" s="32"/>
       <c r="F22" s="32"/>
@@ -4922,13 +4848,13 @@
       <c r="H22" s="32"/>
       <c r="I22" s="32"/>
       <c r="J22" s="32"/>
-      <c r="K22" s="31"/>
-      <c r="L22" s="25"/>
+      <c r="K22" s="35"/>
+      <c r="L22" s="33"/>
     </row>
     <row r="23" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A23" s="25"/>
-      <c r="B23" s="36"/>
-      <c r="C23" s="38"/>
+      <c r="A23" s="33"/>
+      <c r="B23" s="37"/>
+      <c r="C23" s="30"/>
       <c r="D23" s="32"/>
       <c r="E23" s="32"/>
       <c r="F23" s="32"/>
@@ -4937,11 +4863,11 @@
       <c r="I23" s="32"/>
       <c r="J23" s="32"/>
       <c r="K23" s="32"/>
-      <c r="L23" s="25"/>
+      <c r="L23" s="33"/>
     </row>
     <row r="24" spans="1:12" ht="20" customHeight="1" thickTop="1">
-      <c r="A24" s="25"/>
-      <c r="C24" s="38"/>
+      <c r="A24" s="33"/>
+      <c r="C24" s="30"/>
       <c r="D24" s="32"/>
       <c r="E24" s="32"/>
       <c r="F24" s="32"/>
@@ -4950,7 +4876,7 @@
       <c r="I24" s="32"/>
       <c r="J24" s="32"/>
       <c r="K24" s="32"/>
-      <c r="L24" s="25"/>
+      <c r="L24" s="33"/>
     </row>
     <row r="25" spans="1:12" ht="20" customHeight="1">
       <c r="A25" s="4"/>
@@ -4960,11 +4886,67 @@
     </row>
   </sheetData>
   <mergeCells count="82">
-    <mergeCell ref="A23:A24"/>
-    <mergeCell ref="C23:C24"/>
-    <mergeCell ref="L23:L24"/>
-    <mergeCell ref="J22:J24"/>
-    <mergeCell ref="K22:K24"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="L15:L16"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="L17:L18"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C19:C22"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="J19:J21"/>
+    <mergeCell ref="L19:L20"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="L21:L22"/>
+    <mergeCell ref="K18:K19"/>
+    <mergeCell ref="L9:L10"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="K10:K11"/>
+    <mergeCell ref="I5:I10"/>
+    <mergeCell ref="L5:L6"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="K6:K7"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="K4:K5"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="K16:K17"/>
+    <mergeCell ref="E18:E24"/>
+    <mergeCell ref="H18:H24"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="K14:K15"/>
+    <mergeCell ref="C15:C18"/>
+    <mergeCell ref="D15:D20"/>
+    <mergeCell ref="F15:G24"/>
+    <mergeCell ref="I15:I20"/>
+    <mergeCell ref="J15:J18"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="K20:K21"/>
+    <mergeCell ref="D21:D24"/>
+    <mergeCell ref="I21:I24"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="L13:L14"/>
+    <mergeCell ref="G11:G12"/>
+    <mergeCell ref="I11:I14"/>
+    <mergeCell ref="J11:J14"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="K12:K13"/>
+    <mergeCell ref="F13:G14"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="L7:L8"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="C7:C10"/>
+    <mergeCell ref="J7:J10"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="E8:E17"/>
+    <mergeCell ref="H8:H17"/>
+    <mergeCell ref="K8:K9"/>
+    <mergeCell ref="F9:G10"/>
+    <mergeCell ref="C11:C14"/>
+    <mergeCell ref="D11:D14"/>
+    <mergeCell ref="F11:F12"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="L11:L12"/>
+    <mergeCell ref="A13:A14"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="L1:L2"/>
     <mergeCell ref="B2:B3"/>
@@ -4981,67 +4963,11 @@
     <mergeCell ref="F1:G8"/>
     <mergeCell ref="H1:H7"/>
     <mergeCell ref="I1:I4"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="L7:L8"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="C7:C10"/>
-    <mergeCell ref="J7:J10"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="E8:E17"/>
-    <mergeCell ref="H8:H17"/>
-    <mergeCell ref="K8:K9"/>
-    <mergeCell ref="F9:G10"/>
-    <mergeCell ref="C11:C14"/>
-    <mergeCell ref="D11:D14"/>
-    <mergeCell ref="F11:F12"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="L11:L12"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="L13:L14"/>
-    <mergeCell ref="G11:G12"/>
-    <mergeCell ref="I11:I14"/>
-    <mergeCell ref="J11:J14"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="K12:K13"/>
-    <mergeCell ref="F13:G14"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="K16:K17"/>
-    <mergeCell ref="E18:E24"/>
-    <mergeCell ref="H18:H24"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="K14:K15"/>
-    <mergeCell ref="C15:C18"/>
-    <mergeCell ref="D15:D20"/>
-    <mergeCell ref="F15:G24"/>
-    <mergeCell ref="I15:I20"/>
-    <mergeCell ref="J15:J18"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="K20:K21"/>
-    <mergeCell ref="D21:D24"/>
-    <mergeCell ref="I21:I24"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="I5:I10"/>
-    <mergeCell ref="L5:L6"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="K6:K7"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="K4:K5"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="L15:L16"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="L17:L18"/>
-    <mergeCell ref="J1:J2"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="C19:C22"/>
-    <mergeCell ref="A19:A20"/>
-    <mergeCell ref="J19:J21"/>
-    <mergeCell ref="L19:L20"/>
-    <mergeCell ref="A21:A22"/>
-    <mergeCell ref="L21:L22"/>
-    <mergeCell ref="K18:K19"/>
-    <mergeCell ref="L9:L10"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="K10:K11"/>
+    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="C23:C24"/>
+    <mergeCell ref="L23:L24"/>
+    <mergeCell ref="J22:J24"/>
+    <mergeCell ref="K22:K24"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5056,7 +4982,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="20" customHeight="1"/>
   <sheetData>
     <row r="1" spans="1:12" ht="20" customHeight="1" thickBot="1">
-      <c r="A1" s="25"/>
+      <c r="A1" s="33"/>
       <c r="C1" s="32"/>
       <c r="D1" s="32"/>
       <c r="E1" s="32"/>
@@ -5068,11 +4994,11 @@
       <c r="I1" s="32"/>
       <c r="J1" s="32"/>
       <c r="K1" s="1"/>
-      <c r="L1" s="25"/>
+      <c r="L1" s="33"/>
     </row>
     <row r="2" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A2" s="25"/>
-      <c r="B2" s="34" t="s">
+      <c r="A2" s="33"/>
+      <c r="B2" s="36" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="32"/>
@@ -5083,15 +5009,15 @@
       <c r="H2" s="32"/>
       <c r="I2" s="32"/>
       <c r="J2" s="32"/>
-      <c r="K2" s="41" t="s">
+      <c r="K2" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="L2" s="25"/>
+      <c r="L2" s="33"/>
     </row>
     <row r="3" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A3" s="25"/>
-      <c r="B3" s="48"/>
-      <c r="C3" s="34" t="s">
+      <c r="A3" s="33"/>
+      <c r="B3" s="49"/>
+      <c r="C3" s="36" t="s">
         <v>1</v>
       </c>
       <c r="D3" s="32"/>
@@ -5100,346 +5026,412 @@
       <c r="G3" s="44"/>
       <c r="H3" s="32"/>
       <c r="I3" s="32"/>
-      <c r="J3" s="41" t="s">
+      <c r="J3" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="K3" s="42"/>
-      <c r="L3" s="25"/>
+      <c r="K3" s="39"/>
+      <c r="L3" s="33"/>
     </row>
     <row r="4" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A4" s="25"/>
-      <c r="B4" s="38"/>
-      <c r="C4" s="35"/>
+      <c r="A4" s="33"/>
+      <c r="B4" s="30"/>
+      <c r="C4" s="42"/>
       <c r="D4" s="32"/>
       <c r="E4" s="32"/>
       <c r="F4" s="44"/>
       <c r="G4" s="44"/>
       <c r="H4" s="32"/>
       <c r="I4" s="32"/>
-      <c r="J4" s="43"/>
+      <c r="J4" s="41"/>
       <c r="K4" s="57"/>
-      <c r="L4" s="25"/>
+      <c r="L4" s="33"/>
     </row>
     <row r="5" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A5" s="25"/>
-      <c r="B5" s="50"/>
-      <c r="C5" s="35"/>
-      <c r="D5" s="34" t="s">
+      <c r="A5" s="33"/>
+      <c r="B5" s="48"/>
+      <c r="C5" s="42"/>
+      <c r="D5" s="36" t="s">
         <v>10</v>
       </c>
       <c r="E5" s="32"/>
       <c r="F5" s="44"/>
       <c r="G5" s="44"/>
       <c r="H5" s="32"/>
-      <c r="I5" s="41" t="s">
+      <c r="I5" s="38" t="s">
         <v>10</v>
       </c>
-      <c r="J5" s="43"/>
+      <c r="J5" s="41"/>
       <c r="K5" s="32"/>
-      <c r="L5" s="25"/>
+      <c r="L5" s="33"/>
     </row>
     <row r="6" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A6" s="25"/>
-      <c r="B6" s="34" t="s">
+      <c r="A6" s="33"/>
+      <c r="B6" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="36"/>
-      <c r="D6" s="35"/>
+      <c r="C6" s="37"/>
+      <c r="D6" s="42"/>
       <c r="E6" s="32"/>
       <c r="F6" s="44"/>
       <c r="G6" s="44"/>
       <c r="H6" s="32"/>
-      <c r="I6" s="43"/>
-      <c r="J6" s="42"/>
-      <c r="K6" s="41" t="s">
+      <c r="I6" s="41"/>
+      <c r="J6" s="39"/>
+      <c r="K6" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="L6" s="25"/>
+      <c r="L6" s="33"/>
     </row>
     <row r="7" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A7" s="25"/>
-      <c r="B7" s="48"/>
-      <c r="C7" s="31"/>
-      <c r="D7" s="35"/>
+      <c r="A7" s="33"/>
+      <c r="B7" s="49"/>
+      <c r="C7" s="35"/>
+      <c r="D7" s="42"/>
       <c r="E7" s="32"/>
       <c r="F7" s="44"/>
       <c r="G7" s="44"/>
       <c r="H7" s="32"/>
-      <c r="I7" s="43"/>
-      <c r="J7" s="31"/>
-      <c r="K7" s="42"/>
-      <c r="L7" s="25"/>
+      <c r="I7" s="41"/>
+      <c r="J7" s="35"/>
+      <c r="K7" s="39"/>
+      <c r="L7" s="33"/>
     </row>
     <row r="8" spans="1:12" ht="20" customHeight="1" thickTop="1">
-      <c r="A8" s="25"/>
-      <c r="B8" s="38"/>
+      <c r="A8" s="33"/>
+      <c r="B8" s="30"/>
       <c r="C8" s="32"/>
-      <c r="D8" s="35"/>
-      <c r="E8" s="34" t="s">
+      <c r="D8" s="42"/>
+      <c r="E8" s="36" t="s">
         <v>7</v>
       </c>
       <c r="F8" s="44"/>
       <c r="G8" s="44"/>
-      <c r="H8" s="41" t="s">
+      <c r="H8" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="I8" s="43"/>
+      <c r="I8" s="41"/>
       <c r="J8" s="32"/>
       <c r="K8" s="57"/>
-      <c r="L8" s="25"/>
+      <c r="L8" s="33"/>
     </row>
     <row r="9" spans="1:12" ht="20" customHeight="1" thickBot="1">
-      <c r="A9" s="25"/>
-      <c r="B9" s="50"/>
+      <c r="A9" s="33"/>
+      <c r="B9" s="48"/>
       <c r="C9" s="32"/>
-      <c r="D9" s="35"/>
-      <c r="E9" s="35"/>
-      <c r="F9" s="22" t="s">
+      <c r="D9" s="42"/>
+      <c r="E9" s="42"/>
+      <c r="F9" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="G9" s="22"/>
-      <c r="H9" s="43"/>
-      <c r="I9" s="43"/>
+      <c r="G9" s="29"/>
+      <c r="H9" s="41"/>
+      <c r="I9" s="41"/>
       <c r="J9" s="32"/>
       <c r="K9" s="32"/>
-      <c r="L9" s="25"/>
+      <c r="L9" s="33"/>
     </row>
     <row r="10" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A10" s="25"/>
-      <c r="B10" s="34" t="s">
+      <c r="A10" s="33"/>
+      <c r="B10" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="33"/>
-      <c r="D10" s="36"/>
-      <c r="E10" s="35"/>
-      <c r="F10" s="22"/>
-      <c r="G10" s="22"/>
-      <c r="H10" s="43"/>
-      <c r="I10" s="42"/>
-      <c r="J10" s="33"/>
-      <c r="K10" s="41" t="s">
+      <c r="C10" s="40"/>
+      <c r="D10" s="37"/>
+      <c r="E10" s="42"/>
+      <c r="F10" s="29"/>
+      <c r="G10" s="29"/>
+      <c r="H10" s="41"/>
+      <c r="I10" s="39"/>
+      <c r="J10" s="40"/>
+      <c r="K10" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="L10" s="25"/>
+      <c r="L10" s="33"/>
     </row>
     <row r="11" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A11" s="25"/>
-      <c r="B11" s="48"/>
-      <c r="C11" s="49"/>
+      <c r="A11" s="33"/>
+      <c r="B11" s="49"/>
+      <c r="C11" s="50"/>
       <c r="D11" s="32"/>
-      <c r="E11" s="35"/>
-      <c r="F11" s="35"/>
-      <c r="G11" s="43"/>
-      <c r="H11" s="43"/>
+      <c r="E11" s="42"/>
+      <c r="F11" s="42"/>
+      <c r="G11" s="41"/>
+      <c r="H11" s="41"/>
       <c r="I11" s="32"/>
       <c r="J11" s="32"/>
-      <c r="K11" s="42"/>
-      <c r="L11" s="25"/>
+      <c r="K11" s="39"/>
+      <c r="L11" s="33"/>
     </row>
     <row r="12" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A12" s="25"/>
-      <c r="B12" s="38"/>
-      <c r="C12" s="49"/>
+      <c r="A12" s="33"/>
+      <c r="B12" s="30"/>
+      <c r="C12" s="50"/>
       <c r="D12" s="32"/>
-      <c r="E12" s="35"/>
-      <c r="F12" s="36"/>
-      <c r="G12" s="42"/>
-      <c r="H12" s="43"/>
+      <c r="E12" s="42"/>
+      <c r="F12" s="37"/>
+      <c r="G12" s="39"/>
+      <c r="H12" s="41"/>
       <c r="I12" s="32"/>
       <c r="J12" s="32"/>
       <c r="K12" s="57"/>
-      <c r="L12" s="25"/>
+      <c r="L12" s="33"/>
     </row>
     <row r="13" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A13" s="25"/>
-      <c r="B13" s="50"/>
-      <c r="C13" s="49"/>
+      <c r="A13" s="33"/>
+      <c r="B13" s="48"/>
+      <c r="C13" s="50"/>
       <c r="D13" s="32"/>
-      <c r="E13" s="35"/>
+      <c r="E13" s="42"/>
       <c r="F13" s="32" t="s">
         <v>15</v>
       </c>
       <c r="G13" s="32"/>
-      <c r="H13" s="43"/>
+      <c r="H13" s="41"/>
       <c r="I13" s="32"/>
       <c r="J13" s="32"/>
       <c r="K13" s="32"/>
-      <c r="L13" s="25"/>
+      <c r="L13" s="33"/>
     </row>
     <row r="14" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A14" s="25"/>
-      <c r="B14" s="34" t="s">
+      <c r="A14" s="33"/>
+      <c r="B14" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="49"/>
+      <c r="C14" s="50"/>
       <c r="D14" s="32"/>
-      <c r="E14" s="35"/>
+      <c r="E14" s="42"/>
       <c r="F14" s="32"/>
       <c r="G14" s="32"/>
-      <c r="H14" s="43"/>
+      <c r="H14" s="41"/>
       <c r="I14" s="32"/>
       <c r="J14" s="32"/>
-      <c r="K14" s="41" t="s">
+      <c r="K14" s="38" t="s">
         <v>8</v>
       </c>
-      <c r="L14" s="25"/>
+      <c r="L14" s="33"/>
     </row>
     <row r="15" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A15" s="25"/>
-      <c r="B15" s="48"/>
-      <c r="C15" s="49"/>
-      <c r="D15" s="34" t="s">
+      <c r="A15" s="33"/>
+      <c r="B15" s="49"/>
+      <c r="C15" s="50"/>
+      <c r="D15" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="E15" s="35"/>
+      <c r="E15" s="42"/>
       <c r="F15" s="32"/>
       <c r="G15" s="32"/>
-      <c r="H15" s="43"/>
-      <c r="I15" s="41" t="s">
+      <c r="H15" s="41"/>
+      <c r="I15" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="J15" s="31"/>
-      <c r="K15" s="42"/>
-      <c r="L15" s="25"/>
+      <c r="J15" s="35"/>
+      <c r="K15" s="39"/>
+      <c r="L15" s="33"/>
     </row>
     <row r="16" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A16" s="25"/>
-      <c r="B16" s="38"/>
-      <c r="C16" s="49"/>
-      <c r="D16" s="35"/>
-      <c r="E16" s="35"/>
+      <c r="A16" s="33"/>
+      <c r="B16" s="30"/>
+      <c r="C16" s="50"/>
+      <c r="D16" s="42"/>
+      <c r="E16" s="42"/>
       <c r="F16" s="32"/>
       <c r="G16" s="32"/>
-      <c r="H16" s="43"/>
-      <c r="I16" s="43"/>
+      <c r="H16" s="41"/>
+      <c r="I16" s="41"/>
       <c r="J16" s="32"/>
       <c r="K16" s="57"/>
-      <c r="L16" s="25"/>
+      <c r="L16" s="33"/>
     </row>
     <row r="17" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A17" s="25"/>
-      <c r="B17" s="50"/>
-      <c r="C17" s="49"/>
-      <c r="D17" s="35"/>
-      <c r="E17" s="36"/>
+      <c r="A17" s="33"/>
+      <c r="B17" s="48"/>
+      <c r="C17" s="50"/>
+      <c r="D17" s="42"/>
+      <c r="E17" s="37"/>
       <c r="F17" s="32"/>
       <c r="G17" s="32"/>
-      <c r="H17" s="42"/>
-      <c r="I17" s="43"/>
+      <c r="H17" s="39"/>
+      <c r="I17" s="41"/>
       <c r="J17" s="32"/>
       <c r="K17" s="32"/>
-      <c r="L17" s="25"/>
+      <c r="L17" s="33"/>
     </row>
     <row r="18" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A18" s="25"/>
-      <c r="B18" s="34" t="s">
+      <c r="A18" s="33"/>
+      <c r="B18" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="C18" s="31"/>
-      <c r="D18" s="35"/>
+      <c r="C18" s="35"/>
+      <c r="D18" s="42"/>
       <c r="E18" s="32"/>
       <c r="F18" s="32"/>
       <c r="G18" s="32"/>
       <c r="H18" s="32"/>
-      <c r="I18" s="43"/>
-      <c r="J18" s="33"/>
-      <c r="K18" s="41" t="s">
+      <c r="I18" s="41"/>
+      <c r="J18" s="40"/>
+      <c r="K18" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="L18" s="25"/>
+      <c r="L18" s="33"/>
     </row>
     <row r="19" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A19" s="25"/>
-      <c r="B19" s="48"/>
-      <c r="C19" s="34" t="s">
+      <c r="A19" s="33"/>
+      <c r="B19" s="49"/>
+      <c r="C19" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="D19" s="35"/>
+      <c r="D19" s="42"/>
       <c r="E19" s="32"/>
       <c r="F19" s="32"/>
       <c r="G19" s="32"/>
       <c r="H19" s="32"/>
-      <c r="I19" s="43"/>
-      <c r="J19" s="41" t="s">
+      <c r="I19" s="41"/>
+      <c r="J19" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="K19" s="42"/>
-      <c r="L19" s="25"/>
+      <c r="K19" s="39"/>
+      <c r="L19" s="33"/>
     </row>
     <row r="20" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A20" s="25"/>
-      <c r="B20" s="40"/>
-      <c r="C20" s="35"/>
-      <c r="D20" s="36"/>
+      <c r="A20" s="33"/>
+      <c r="B20" s="43"/>
+      <c r="C20" s="42"/>
+      <c r="D20" s="37"/>
       <c r="E20" s="32"/>
       <c r="F20" s="32"/>
       <c r="G20" s="32"/>
       <c r="H20" s="32"/>
-      <c r="I20" s="42"/>
-      <c r="J20" s="43"/>
+      <c r="I20" s="39"/>
+      <c r="J20" s="41"/>
       <c r="K20" s="32"/>
-      <c r="L20" s="25"/>
+      <c r="L20" s="33"/>
     </row>
     <row r="21" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A21" s="25"/>
-      <c r="B21" s="38"/>
-      <c r="C21" s="35"/>
+      <c r="A21" s="33"/>
+      <c r="B21" s="30"/>
+      <c r="C21" s="42"/>
       <c r="D21" s="32"/>
       <c r="E21" s="32"/>
       <c r="F21" s="32"/>
       <c r="G21" s="32"/>
       <c r="H21" s="32"/>
       <c r="I21" s="32"/>
-      <c r="J21" s="43"/>
+      <c r="J21" s="41"/>
       <c r="K21" s="32"/>
-      <c r="L21" s="25"/>
+      <c r="L21" s="33"/>
     </row>
     <row r="22" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A22" s="25"/>
-      <c r="B22" s="34" t="s">
+      <c r="A22" s="33"/>
+      <c r="B22" s="36" t="s">
         <v>13</v>
       </c>
-      <c r="C22" s="36"/>
+      <c r="C22" s="37"/>
       <c r="D22" s="32"/>
       <c r="E22" s="32"/>
       <c r="F22" s="32"/>
       <c r="G22" s="32"/>
       <c r="H22" s="32"/>
       <c r="I22" s="32"/>
-      <c r="J22" s="42"/>
-      <c r="K22" s="41" t="s">
+      <c r="J22" s="39"/>
+      <c r="K22" s="38" t="s">
         <v>13</v>
       </c>
-      <c r="L22" s="25"/>
+      <c r="L22" s="33"/>
     </row>
     <row r="23" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A23" s="25"/>
-      <c r="B23" s="36"/>
-      <c r="C23" s="38"/>
+      <c r="A23" s="33"/>
+      <c r="B23" s="37"/>
+      <c r="C23" s="30"/>
       <c r="D23" s="32"/>
       <c r="E23" s="32"/>
       <c r="F23" s="32"/>
       <c r="G23" s="32"/>
       <c r="H23" s="32"/>
       <c r="I23" s="32"/>
-      <c r="J23" s="38"/>
-      <c r="K23" s="42"/>
-      <c r="L23" s="25"/>
+      <c r="J23" s="30"/>
+      <c r="K23" s="39"/>
+      <c r="L23" s="33"/>
     </row>
     <row r="24" spans="1:12" ht="20" customHeight="1" thickTop="1">
-      <c r="A24" s="25"/>
-      <c r="C24" s="38"/>
+      <c r="A24" s="33"/>
+      <c r="C24" s="30"/>
       <c r="D24" s="32"/>
       <c r="E24" s="32"/>
       <c r="F24" s="32"/>
       <c r="G24" s="32"/>
       <c r="H24" s="32"/>
       <c r="I24" s="32"/>
-      <c r="J24" s="38"/>
-      <c r="L24" s="25"/>
+      <c r="J24" s="30"/>
+      <c r="L24" s="33"/>
     </row>
   </sheetData>
   <mergeCells count="82">
+    <mergeCell ref="L19:L20"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="L21:L22"/>
+    <mergeCell ref="L15:L16"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="L17:L18"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="K18:K19"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="K14:K15"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="C15:C18"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="J15:J18"/>
+    <mergeCell ref="K16:K17"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="L9:L10"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="K10:K11"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="C11:C14"/>
+    <mergeCell ref="D11:D14"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="G11:G12"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="L13:L14"/>
+    <mergeCell ref="L11:L12"/>
+    <mergeCell ref="I11:I14"/>
+    <mergeCell ref="J11:J14"/>
+    <mergeCell ref="K12:K13"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="K4:K5"/>
+    <mergeCell ref="C7:C10"/>
+    <mergeCell ref="J7:J10"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="K8:K9"/>
+    <mergeCell ref="F1:G8"/>
+    <mergeCell ref="D5:D10"/>
+    <mergeCell ref="I5:I10"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="L5:L6"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="K6:K7"/>
+    <mergeCell ref="L7:L8"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="C3:C6"/>
+    <mergeCell ref="J3:J6"/>
+    <mergeCell ref="L3:L4"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D4"/>
+    <mergeCell ref="E1:E7"/>
+    <mergeCell ref="H1:H7"/>
+    <mergeCell ref="I1:I4"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="K20:K21"/>
+    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="C19:C22"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="C23:C24"/>
+    <mergeCell ref="A19:A20"/>
     <mergeCell ref="L23:L24"/>
     <mergeCell ref="K22:K23"/>
     <mergeCell ref="J19:J22"/>
@@ -5456,72 +5448,6 @@
     <mergeCell ref="F15:G24"/>
     <mergeCell ref="F9:G10"/>
     <mergeCell ref="F11:F12"/>
-    <mergeCell ref="K20:K21"/>
-    <mergeCell ref="A23:A24"/>
-    <mergeCell ref="C19:C22"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="C23:C24"/>
-    <mergeCell ref="A19:A20"/>
-    <mergeCell ref="L5:L6"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="K6:K7"/>
-    <mergeCell ref="L7:L8"/>
-    <mergeCell ref="L1:L2"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="K2:K3"/>
-    <mergeCell ref="C3:C6"/>
-    <mergeCell ref="J3:J6"/>
-    <mergeCell ref="L3:L4"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D4"/>
-    <mergeCell ref="E1:E7"/>
-    <mergeCell ref="H1:H7"/>
-    <mergeCell ref="I1:I4"/>
-    <mergeCell ref="J1:J2"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="K4:K5"/>
-    <mergeCell ref="C7:C10"/>
-    <mergeCell ref="J7:J10"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="K8:K9"/>
-    <mergeCell ref="F1:G8"/>
-    <mergeCell ref="D5:D10"/>
-    <mergeCell ref="I5:I10"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="L9:L10"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="K10:K11"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="C11:C14"/>
-    <mergeCell ref="D11:D14"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="G11:G12"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="L13:L14"/>
-    <mergeCell ref="L11:L12"/>
-    <mergeCell ref="I11:I14"/>
-    <mergeCell ref="J11:J14"/>
-    <mergeCell ref="K12:K13"/>
-    <mergeCell ref="L19:L20"/>
-    <mergeCell ref="A21:A22"/>
-    <mergeCell ref="L21:L22"/>
-    <mergeCell ref="L15:L16"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="L17:L18"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="K18:K19"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="K14:K15"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="C15:C18"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="J15:J18"/>
-    <mergeCell ref="K16:K17"/>
-    <mergeCell ref="B20:B21"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5530,523 +5456,433 @@
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB5F6ECB-47B9-CF46-AC56-3264715C5E70}">
-  <dimension ref="A1:L28"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="20" customHeight="1"/>
-  <cols>
-    <col min="4" max="4" width="9.140625" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77A4E167-3852-0542-8EB0-81CB31D49EF8}">
+  <dimension ref="A1:I18"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="28" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:12" ht="20" customHeight="1" thickBot="1">
-      <c r="A1" s="81"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="44" t="s">
-        <v>14</v>
-      </c>
-      <c r="G1" s="44"/>
-      <c r="H1" s="38"/>
-      <c r="I1" s="38"/>
-      <c r="J1" s="38"/>
-      <c r="K1" s="38"/>
-    </row>
-    <row r="2" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A2" s="81"/>
-      <c r="B2" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="39"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="44"/>
-      <c r="G2" s="44"/>
-      <c r="H2" s="38"/>
-      <c r="I2" s="38"/>
-      <c r="J2" s="38"/>
-      <c r="K2" s="39"/>
-      <c r="L2" s="81"/>
-    </row>
-    <row r="3" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A3" s="81"/>
-      <c r="B3" s="36"/>
-      <c r="C3" s="34" t="s">
+    <row r="1" spans="1:9" ht="28" customHeight="1" thickTop="1" thickBot="1">
+      <c r="A1" s="19"/>
+      <c r="B1" s="59" t="s">
+        <v>49</v>
+      </c>
+      <c r="C1" s="60"/>
+      <c r="D1" s="59" t="s">
+        <v>50</v>
+      </c>
+      <c r="E1" s="61"/>
+      <c r="F1" s="59" t="s">
+        <v>51</v>
+      </c>
+      <c r="G1" s="60"/>
+      <c r="H1" s="59" t="s">
+        <v>61</v>
+      </c>
+      <c r="I1" s="60"/>
+    </row>
+    <row r="2" spans="1:9" ht="28" customHeight="1" thickTop="1" thickBot="1">
+      <c r="A2" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="B2" s="71" t="s">
+        <v>53</v>
+      </c>
+      <c r="C2" s="71"/>
+      <c r="D2" s="71" t="s">
+        <v>54</v>
+      </c>
+      <c r="E2" s="71"/>
+      <c r="F2" s="71" t="s">
+        <v>55</v>
+      </c>
+      <c r="G2" s="71"/>
+      <c r="H2" s="71" t="s">
+        <v>56</v>
+      </c>
+      <c r="I2" s="71"/>
+    </row>
+    <row r="3" spans="1:9" ht="28" customHeight="1" thickTop="1">
+      <c r="A3" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="E3" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="F3" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="G3" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="I3" s="13" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="28" customHeight="1" thickBot="1">
+      <c r="A4" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="E4" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="F4" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="G4" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="H4" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="I4" s="13" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="28" customHeight="1" thickTop="1" thickBot="1">
+      <c r="A5" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" s="62" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" s="63"/>
+      <c r="D5" s="62" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" s="63"/>
+      <c r="F5" s="62" t="s">
+        <v>30</v>
+      </c>
+      <c r="G5" s="63"/>
+      <c r="H5" s="62" t="s">
+        <v>30</v>
+      </c>
+      <c r="I5" s="63"/>
+    </row>
+    <row r="6" spans="1:9" ht="28" customHeight="1" thickTop="1" thickBot="1">
+      <c r="A6" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" s="62" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" s="63"/>
+      <c r="D6" s="62" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6" s="63"/>
+      <c r="F6" s="62" t="s">
+        <v>32</v>
+      </c>
+      <c r="G6" s="63"/>
+      <c r="H6" s="62" t="s">
+        <v>32</v>
+      </c>
+      <c r="I6" s="63"/>
+    </row>
+    <row r="7" spans="1:9" ht="28" customHeight="1" thickTop="1" thickBot="1">
+      <c r="A7" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" s="62" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" s="63"/>
+      <c r="D7" s="62" t="s">
+        <v>34</v>
+      </c>
+      <c r="E7" s="63"/>
+      <c r="F7" s="62" t="s">
+        <v>34</v>
+      </c>
+      <c r="G7" s="63"/>
+      <c r="H7" s="62" t="s">
+        <v>34</v>
+      </c>
+      <c r="I7" s="63"/>
+    </row>
+    <row r="8" spans="1:9" ht="28" customHeight="1" thickTop="1" thickBot="1">
+      <c r="A8" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" s="62" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="63"/>
+      <c r="D8" s="62" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" s="63"/>
+      <c r="F8" s="62" t="s">
+        <v>25</v>
+      </c>
+      <c r="G8" s="63"/>
+      <c r="H8" s="62" t="s">
+        <v>25</v>
+      </c>
+      <c r="I8" s="63"/>
+    </row>
+    <row r="9" spans="1:9" ht="28" customHeight="1" thickTop="1" thickBot="1">
+      <c r="A9" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B9" s="62" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" s="63"/>
+      <c r="D9" s="62" t="s">
+        <v>24</v>
+      </c>
+      <c r="E9" s="63"/>
+      <c r="F9" s="62" t="s">
+        <v>24</v>
+      </c>
+      <c r="G9" s="63"/>
+      <c r="H9" s="62" t="s">
+        <v>24</v>
+      </c>
+      <c r="I9" s="63"/>
+    </row>
+    <row r="10" spans="1:9" ht="28" customHeight="1" thickTop="1" thickBot="1">
+      <c r="A10" s="66" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" s="67"/>
+      <c r="C10" s="67"/>
+      <c r="D10" s="67"/>
+      <c r="E10" s="67"/>
+      <c r="F10" s="67"/>
+      <c r="G10" s="67"/>
+      <c r="H10" s="67"/>
+      <c r="I10" s="68"/>
+    </row>
+    <row r="11" spans="1:9" ht="28" customHeight="1" thickTop="1" thickBot="1">
+      <c r="A11" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" s="64" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11" s="65"/>
+      <c r="D11" s="64" t="s">
+        <v>13</v>
+      </c>
+      <c r="E11" s="65"/>
+      <c r="F11" s="64" t="s">
+        <v>13</v>
+      </c>
+      <c r="G11" s="65"/>
+      <c r="H11" s="64" t="s">
+        <v>13</v>
+      </c>
+      <c r="I11" s="65"/>
+    </row>
+    <row r="12" spans="1:9" ht="28" customHeight="1" thickTop="1" thickBot="1">
+      <c r="A12" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="44"/>
-      <c r="G3" s="44"/>
-      <c r="H3" s="38"/>
-      <c r="I3" s="38"/>
-      <c r="J3" s="39"/>
-      <c r="K3" s="41" t="s">
-        <v>0</v>
-      </c>
-      <c r="L3" s="81"/>
-    </row>
-    <row r="4" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A4" s="81"/>
-      <c r="B4" s="40"/>
-      <c r="C4" s="35"/>
-      <c r="D4" s="39"/>
-      <c r="E4" s="38"/>
-      <c r="F4" s="44"/>
-      <c r="G4" s="44"/>
-      <c r="H4" s="38"/>
-      <c r="I4" s="38"/>
-      <c r="J4" s="41" t="s">
+      <c r="C12" s="65"/>
+      <c r="D12" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="K4" s="42"/>
-      <c r="L4" s="81"/>
-    </row>
-    <row r="5" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A5" s="81"/>
-      <c r="B5" s="39"/>
-      <c r="C5" s="36"/>
-      <c r="D5" s="34" t="s">
+      <c r="E12" s="65"/>
+      <c r="F12" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="G12" s="65"/>
+      <c r="H12" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="I12" s="65"/>
+    </row>
+    <row r="13" spans="1:9" ht="28" customHeight="1" thickTop="1" thickBot="1">
+      <c r="A13" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="B13" s="64" t="s">
+        <v>2</v>
+      </c>
+      <c r="C13" s="65"/>
+      <c r="D13" s="64" t="s">
+        <v>2</v>
+      </c>
+      <c r="E13" s="65"/>
+      <c r="F13" s="64" t="s">
+        <v>2</v>
+      </c>
+      <c r="G13" s="65"/>
+      <c r="H13" s="64" t="s">
+        <v>2</v>
+      </c>
+      <c r="I13" s="65"/>
+    </row>
+    <row r="14" spans="1:9" ht="28" customHeight="1" thickTop="1" thickBot="1">
+      <c r="A14" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="B14" s="64" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" s="65"/>
+      <c r="D14" s="64" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14" s="65"/>
+      <c r="F14" s="64" t="s">
+        <v>10</v>
+      </c>
+      <c r="G14" s="65"/>
+      <c r="H14" s="64" t="s">
+        <v>10</v>
+      </c>
+      <c r="I14" s="65"/>
+    </row>
+    <row r="15" spans="1:9" ht="28" customHeight="1" thickTop="1" thickBot="1">
+      <c r="A15" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" s="69" t="s">
         <v>4</v>
       </c>
-      <c r="E5" s="38"/>
-      <c r="F5" s="44"/>
-      <c r="G5" s="44"/>
-      <c r="H5" s="38"/>
-      <c r="I5" s="39"/>
-      <c r="J5" s="43"/>
-      <c r="K5" s="31"/>
-      <c r="L5" s="81"/>
-    </row>
-    <row r="6" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A6" s="81"/>
-      <c r="B6" s="73"/>
-      <c r="C6" s="31"/>
-      <c r="D6" s="35"/>
-      <c r="E6" s="39"/>
-      <c r="F6" s="44"/>
-      <c r="G6" s="44"/>
-      <c r="H6" s="38"/>
-      <c r="I6" s="41" t="s">
-        <v>10</v>
-      </c>
-      <c r="J6" s="43"/>
-      <c r="K6" s="33"/>
-      <c r="L6" s="81"/>
-    </row>
-    <row r="7" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A7" s="81"/>
-      <c r="B7" s="73"/>
-      <c r="C7" s="73"/>
-      <c r="D7" s="35"/>
-      <c r="E7" s="34" t="s">
+      <c r="C15" s="70"/>
+      <c r="D15" s="69" t="s">
+        <v>4</v>
+      </c>
+      <c r="E15" s="70"/>
+      <c r="F15" s="69" t="s">
+        <v>4</v>
+      </c>
+      <c r="G15" s="70"/>
+      <c r="H15" s="69" t="s">
+        <v>4</v>
+      </c>
+      <c r="I15" s="70"/>
+    </row>
+    <row r="16" spans="1:9" ht="28" customHeight="1" thickTop="1" thickBot="1">
+      <c r="A16" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="B16" s="64" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="65"/>
+      <c r="D16" s="64" t="s">
+        <v>7</v>
+      </c>
+      <c r="E16" s="65"/>
+      <c r="F16" s="64" t="s">
+        <v>7</v>
+      </c>
+      <c r="G16" s="65"/>
+      <c r="H16" s="64" t="s">
+        <v>7</v>
+      </c>
+      <c r="I16" s="65"/>
+    </row>
+    <row r="17" spans="1:9" ht="28" customHeight="1" thickTop="1" thickBot="1">
+      <c r="A17" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" s="69" t="s">
         <v>15</v>
       </c>
-      <c r="F7" s="78"/>
-      <c r="G7" s="44"/>
-      <c r="H7" s="38"/>
-      <c r="I7" s="43"/>
-      <c r="J7" s="42"/>
-      <c r="K7" s="41" t="s">
-        <v>3</v>
-      </c>
-      <c r="L7" s="81"/>
-    </row>
-    <row r="8" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A8" s="81"/>
-      <c r="B8" s="34" t="s">
-        <v>3</v>
-      </c>
-      <c r="C8" s="33"/>
-      <c r="D8" s="36"/>
-      <c r="E8" s="35"/>
-      <c r="F8" s="78"/>
-      <c r="G8" s="44"/>
-      <c r="H8" s="39"/>
-      <c r="I8" s="43"/>
-      <c r="J8" s="31"/>
-      <c r="K8" s="42"/>
-      <c r="L8" s="81"/>
-    </row>
-    <row r="9" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A9" s="81"/>
-      <c r="B9" s="36"/>
-      <c r="C9" s="73"/>
-      <c r="D9" s="31"/>
-      <c r="E9" s="35"/>
-      <c r="F9" s="78"/>
-      <c r="G9" s="44"/>
-      <c r="H9" s="41" t="s">
-        <v>7</v>
-      </c>
-      <c r="I9" s="43"/>
-      <c r="J9" s="73"/>
-      <c r="K9" s="31"/>
-      <c r="L9" s="81"/>
-    </row>
-    <row r="10" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A10" s="81"/>
-      <c r="B10" s="73"/>
-      <c r="C10" s="73"/>
-      <c r="D10" s="73"/>
-      <c r="E10" s="35"/>
-      <c r="F10" s="78"/>
-      <c r="G10" s="44"/>
-      <c r="H10" s="43"/>
-      <c r="I10" s="43"/>
-      <c r="J10" s="73"/>
-      <c r="K10" s="33"/>
-      <c r="L10" s="81"/>
-    </row>
-    <row r="11" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A11" s="81"/>
-      <c r="B11" s="73"/>
-      <c r="C11" s="73"/>
-      <c r="D11" s="73"/>
-      <c r="E11" s="35"/>
-      <c r="F11" s="76" t="s">
-        <v>5</v>
-      </c>
-      <c r="G11" s="77"/>
-      <c r="H11" s="43"/>
-      <c r="I11" s="42"/>
-      <c r="J11" s="33"/>
-      <c r="K11" s="41" t="s">
-        <v>6</v>
-      </c>
-      <c r="L11" s="81"/>
-    </row>
-    <row r="12" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A12" s="81"/>
-      <c r="B12" s="34" t="s">
-        <v>6</v>
-      </c>
-      <c r="C12" s="73"/>
-      <c r="D12" s="73"/>
-      <c r="E12" s="35"/>
-      <c r="F12" s="76"/>
-      <c r="G12" s="77"/>
-      <c r="H12" s="43"/>
-      <c r="I12" s="31"/>
-      <c r="J12" s="31"/>
-      <c r="K12" s="42"/>
-      <c r="L12" s="81"/>
-    </row>
-    <row r="13" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A13" s="81"/>
-      <c r="B13" s="36"/>
-      <c r="C13" s="34" t="s">
-        <v>2</v>
-      </c>
-      <c r="D13" s="73"/>
-      <c r="E13" s="35"/>
-      <c r="F13" s="79"/>
-      <c r="G13" s="79"/>
-      <c r="H13" s="43"/>
-      <c r="I13" s="32"/>
-      <c r="J13" s="32"/>
-      <c r="K13" s="31"/>
-      <c r="L13" s="81"/>
-    </row>
-    <row r="14" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A14" s="81"/>
-      <c r="B14" s="73"/>
-      <c r="C14" s="35"/>
-      <c r="D14" s="33"/>
-      <c r="E14" s="35"/>
-      <c r="F14" s="80"/>
-      <c r="G14" s="80"/>
-      <c r="H14" s="43"/>
-      <c r="I14" s="32"/>
-      <c r="J14" s="32"/>
-      <c r="K14" s="33"/>
-      <c r="L14" s="81"/>
-    </row>
-    <row r="15" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A15" s="81"/>
-      <c r="B15" s="73"/>
-      <c r="C15" s="35"/>
-      <c r="D15" s="82" t="s">
-        <v>7</v>
-      </c>
-      <c r="E15" s="35"/>
-      <c r="F15" s="41" t="s">
-        <v>64</v>
-      </c>
-      <c r="G15" s="34"/>
-      <c r="H15" s="43"/>
-      <c r="I15" s="33"/>
-      <c r="J15" s="33"/>
-      <c r="K15" s="41" t="s">
-        <v>8</v>
-      </c>
-      <c r="L15" s="81"/>
-    </row>
-    <row r="16" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A16" s="81"/>
-      <c r="B16" s="34" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="36"/>
-      <c r="D16" s="35"/>
-      <c r="E16" s="35"/>
-      <c r="F16" s="43"/>
-      <c r="G16" s="35"/>
-      <c r="H16" s="43"/>
-      <c r="I16" s="41" t="s">
-        <v>4</v>
-      </c>
-      <c r="J16" s="31"/>
-      <c r="K16" s="42"/>
-      <c r="L16" s="81"/>
-    </row>
-    <row r="17" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A17" s="81"/>
-      <c r="B17" s="36"/>
-      <c r="C17" s="73"/>
-      <c r="D17" s="35"/>
-      <c r="E17" s="35"/>
-      <c r="F17" s="32"/>
-      <c r="G17" s="32"/>
-      <c r="H17" s="43"/>
-      <c r="I17" s="43"/>
-      <c r="J17" s="73"/>
-      <c r="K17" s="31"/>
-      <c r="L17" s="81"/>
-    </row>
-    <row r="18" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A18" s="81"/>
-      <c r="B18" s="73"/>
-      <c r="C18" s="73"/>
-      <c r="D18" s="35"/>
-      <c r="E18" s="36"/>
-      <c r="F18" s="32"/>
-      <c r="G18" s="32"/>
-      <c r="H18" s="42"/>
-      <c r="I18" s="43"/>
-      <c r="J18" s="73"/>
-      <c r="K18" s="33"/>
-      <c r="L18" s="81"/>
-    </row>
-    <row r="19" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A19" s="81"/>
-      <c r="B19" s="73"/>
-      <c r="C19" s="73"/>
-      <c r="D19" s="35"/>
-      <c r="E19" s="31"/>
-      <c r="F19" s="32"/>
-      <c r="G19" s="32"/>
-      <c r="H19" s="31"/>
-      <c r="I19" s="43"/>
-      <c r="J19" s="33"/>
-      <c r="K19" s="41" t="s">
-        <v>11</v>
-      </c>
-      <c r="L19" s="81"/>
-    </row>
-    <row r="20" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A20" s="81"/>
-      <c r="B20" s="34" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="73"/>
-      <c r="D20" s="35"/>
-      <c r="E20" s="73"/>
-      <c r="F20" s="32"/>
-      <c r="G20" s="32"/>
-      <c r="H20" s="73"/>
-      <c r="I20" s="43"/>
-      <c r="J20" s="41" t="s">
-        <v>2</v>
-      </c>
-      <c r="K20" s="42"/>
-      <c r="L20" s="81"/>
-    </row>
-    <row r="21" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A21" s="81"/>
-      <c r="B21" s="36"/>
-      <c r="C21" s="34" t="s">
-        <v>10</v>
-      </c>
-      <c r="D21" s="35"/>
-      <c r="E21" s="73"/>
-      <c r="F21" s="32"/>
-      <c r="G21" s="32"/>
-      <c r="H21" s="73"/>
-      <c r="I21" s="42"/>
-      <c r="J21" s="43"/>
-      <c r="K21" s="31"/>
-      <c r="L21" s="81"/>
-    </row>
-    <row r="22" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A22" s="81"/>
-      <c r="B22" s="73"/>
-      <c r="C22" s="35"/>
-      <c r="D22" s="36"/>
-      <c r="E22" s="73"/>
-      <c r="F22" s="32"/>
-      <c r="G22" s="32"/>
-      <c r="H22" s="73"/>
-      <c r="I22" s="31"/>
-      <c r="J22" s="43"/>
-      <c r="K22" s="33"/>
-      <c r="L22" s="81"/>
-    </row>
-    <row r="23" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A23" s="81"/>
-      <c r="B23" s="73"/>
-      <c r="C23" s="35"/>
-      <c r="D23" s="31"/>
-      <c r="E23" s="73"/>
-      <c r="F23" s="32"/>
-      <c r="G23" s="32"/>
-      <c r="H23" s="73"/>
-      <c r="I23" s="73"/>
-      <c r="J23" s="42"/>
-      <c r="K23" s="41" t="s">
-        <v>13</v>
-      </c>
-      <c r="L23" s="81"/>
-    </row>
-    <row r="24" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A24" s="81"/>
-      <c r="B24" s="34" t="s">
-        <v>13</v>
-      </c>
-      <c r="C24" s="36"/>
-      <c r="D24" s="73"/>
-      <c r="E24" s="73"/>
-      <c r="F24" s="32"/>
-      <c r="G24" s="32"/>
-      <c r="H24" s="73"/>
-      <c r="I24" s="73"/>
-      <c r="J24" s="40"/>
-      <c r="K24" s="42"/>
-      <c r="L24" s="81"/>
-    </row>
-    <row r="25" spans="1:12" ht="20" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A25" s="81"/>
-      <c r="B25" s="36"/>
-      <c r="C25" s="40"/>
-      <c r="D25" s="73"/>
-      <c r="E25" s="73"/>
-      <c r="F25" s="32"/>
-      <c r="G25" s="32"/>
-      <c r="H25" s="73"/>
-      <c r="I25" s="73"/>
-      <c r="J25" s="75"/>
-      <c r="K25" s="40"/>
-      <c r="L25" s="81"/>
-    </row>
-    <row r="26" spans="1:12" ht="20" customHeight="1" thickTop="1">
-      <c r="A26" s="81"/>
-      <c r="B26" s="74"/>
-      <c r="C26" s="75"/>
-      <c r="D26" s="73"/>
-      <c r="E26" s="73"/>
-      <c r="F26" s="32"/>
-      <c r="G26" s="32"/>
-      <c r="H26" s="73"/>
-      <c r="I26" s="73"/>
-      <c r="J26" s="75"/>
-      <c r="K26" s="38"/>
-    </row>
-    <row r="27" spans="1:12" ht="20" customHeight="1">
-      <c r="A27" s="72"/>
-      <c r="B27" s="72"/>
-    </row>
-    <row r="28" spans="1:12" ht="20" customHeight="1">
-      <c r="A28" s="72"/>
-    </row>
+      <c r="C17" s="70"/>
+      <c r="D17" s="69" t="s">
+        <v>15</v>
+      </c>
+      <c r="E17" s="70"/>
+      <c r="F17" s="69" t="s">
+        <v>15</v>
+      </c>
+      <c r="G17" s="70"/>
+      <c r="H17" s="69" t="s">
+        <v>15</v>
+      </c>
+      <c r="I17" s="70"/>
+    </row>
+    <row r="18" spans="1:9" ht="28" customHeight="1" thickTop="1"/>
   </sheetData>
-  <mergeCells count="88">
-    <mergeCell ref="F7:G10"/>
-    <mergeCell ref="F13:F14"/>
-    <mergeCell ref="G13:G14"/>
-    <mergeCell ref="F17:G26"/>
-    <mergeCell ref="K25:K26"/>
-    <mergeCell ref="J24:J26"/>
-    <mergeCell ref="I22:I26"/>
-    <mergeCell ref="H19:H26"/>
-    <mergeCell ref="H1:H8"/>
-    <mergeCell ref="H9:H18"/>
-    <mergeCell ref="C25:C26"/>
-    <mergeCell ref="D23:D26"/>
-    <mergeCell ref="E19:E26"/>
-    <mergeCell ref="E1:E6"/>
-    <mergeCell ref="D1:D4"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="F1:G6"/>
-    <mergeCell ref="I16:I21"/>
-    <mergeCell ref="I12:I15"/>
-    <mergeCell ref="I6:I11"/>
-    <mergeCell ref="I1:I5"/>
-    <mergeCell ref="J1:J3"/>
-    <mergeCell ref="J4:J7"/>
-    <mergeCell ref="J8:J11"/>
-    <mergeCell ref="J12:J15"/>
-    <mergeCell ref="J16:J19"/>
-    <mergeCell ref="J20:J23"/>
-    <mergeCell ref="K11:K12"/>
-    <mergeCell ref="K9:K10"/>
-    <mergeCell ref="K7:K8"/>
-    <mergeCell ref="K5:K6"/>
-    <mergeCell ref="K3:K4"/>
-    <mergeCell ref="K1:K2"/>
-    <mergeCell ref="K23:K24"/>
-    <mergeCell ref="K21:K22"/>
-    <mergeCell ref="K19:K20"/>
-    <mergeCell ref="K17:K18"/>
-    <mergeCell ref="K15:K16"/>
-    <mergeCell ref="K13:K14"/>
-    <mergeCell ref="L14:L15"/>
-    <mergeCell ref="L16:L17"/>
-    <mergeCell ref="L18:L19"/>
-    <mergeCell ref="L20:L21"/>
-    <mergeCell ref="L22:L23"/>
-    <mergeCell ref="L24:L25"/>
-    <mergeCell ref="L2:L3"/>
-    <mergeCell ref="L4:L5"/>
-    <mergeCell ref="L6:L7"/>
-    <mergeCell ref="L8:L9"/>
-    <mergeCell ref="L10:L11"/>
-    <mergeCell ref="L12:L13"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="D5:D8"/>
-    <mergeCell ref="C13:C16"/>
-    <mergeCell ref="D15:D22"/>
-    <mergeCell ref="E7:E18"/>
-    <mergeCell ref="D9:D14"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="A23:A24"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="A25:A26"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="A19:A20"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="A21:A22"/>
-    <mergeCell ref="C21:C24"/>
-    <mergeCell ref="C17:C20"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="F15:G16"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="F11:G12"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="C9:C12"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="A3:A4"/>
+  <mergeCells count="57">
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="H17:I17"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="A10:I10"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F5:G5"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6063,91 +5899,91 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="60" customHeight="1" thickBot="1">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="33" t="s">
         <v>63</v>
       </c>
       <c r="C1" s="21"/>
-      <c r="D1" s="29" t="s">
+      <c r="D1" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="E1" s="29"/>
+      <c r="E1" s="25"/>
       <c r="F1" s="21"/>
       <c r="H1" s="21"/>
     </row>
     <row r="2" spans="1:8" ht="60" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A2" s="25"/>
-      <c r="B2" s="26" t="s">
+      <c r="A2" s="33"/>
+      <c r="B2" s="22" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="21"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
       <c r="F2" s="21"/>
-      <c r="G2" s="23" t="s">
+      <c r="G2" s="26" t="s">
         <v>0</v>
       </c>
       <c r="H2" s="21"/>
     </row>
     <row r="3" spans="1:8" ht="60" customHeight="1" thickTop="1" thickBot="1">
       <c r="A3" s="21"/>
-      <c r="B3" s="27"/>
-      <c r="C3" s="26" t="s">
+      <c r="B3" s="23"/>
+      <c r="C3" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="22" t="s">
+      <c r="D3" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="22"/>
-      <c r="F3" s="23" t="s">
+      <c r="E3" s="29"/>
+      <c r="F3" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="24"/>
+      <c r="G3" s="28"/>
       <c r="H3" s="21"/>
     </row>
     <row r="4" spans="1:8" ht="60" customHeight="1" thickTop="1">
       <c r="A4" s="21"/>
       <c r="B4" s="21"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="22"/>
-      <c r="F4" s="30"/>
+      <c r="C4" s="24"/>
+      <c r="D4" s="29"/>
+      <c r="E4" s="29"/>
+      <c r="F4" s="27"/>
       <c r="G4" s="21"/>
       <c r="H4" s="21"/>
     </row>
     <row r="5" spans="1:8" ht="60" customHeight="1" thickBot="1">
       <c r="A5" s="21"/>
       <c r="B5" s="21"/>
-      <c r="C5" s="28"/>
+      <c r="C5" s="24"/>
       <c r="D5" s="21" t="s">
         <v>8</v>
       </c>
       <c r="E5" s="21"/>
-      <c r="F5" s="30"/>
+      <c r="F5" s="27"/>
       <c r="G5" s="21"/>
       <c r="H5" s="21"/>
     </row>
     <row r="6" spans="1:8" ht="60" customHeight="1" thickTop="1" thickBot="1">
       <c r="A6" s="21"/>
-      <c r="B6" s="26" t="s">
+      <c r="B6" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="27"/>
+      <c r="C6" s="23"/>
       <c r="D6" s="21"/>
       <c r="E6" s="21"/>
-      <c r="F6" s="24"/>
-      <c r="G6" s="23" t="s">
+      <c r="F6" s="28"/>
+      <c r="G6" s="26" t="s">
         <v>3</v>
       </c>
       <c r="H6" s="21"/>
     </row>
     <row r="7" spans="1:8" ht="60" customHeight="1" thickTop="1" thickBot="1">
       <c r="A7" s="21"/>
-      <c r="B7" s="27"/>
+      <c r="B7" s="23"/>
       <c r="C7" s="21"/>
       <c r="D7" s="21"/>
       <c r="E7" s="21"/>
       <c r="F7" s="21"/>
-      <c r="G7" s="24"/>
+      <c r="G7" s="28"/>
       <c r="H7" s="21"/>
     </row>
     <row r="8" spans="1:8" ht="60" customHeight="1" thickTop="1">
@@ -6160,6 +5996,14 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="D6:E8"/>
+    <mergeCell ref="D3:E4"/>
+    <mergeCell ref="H7:H8"/>
+    <mergeCell ref="H5:H6"/>
+    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="G6:G7"/>
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="A3:A4"/>
@@ -6176,449 +6020,6 @@
     <mergeCell ref="F1:F2"/>
     <mergeCell ref="F3:F6"/>
     <mergeCell ref="G2:G3"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="D6:E8"/>
-    <mergeCell ref="D3:E4"/>
-    <mergeCell ref="H7:H8"/>
-    <mergeCell ref="H5:H6"/>
-    <mergeCell ref="H3:H4"/>
-    <mergeCell ref="G4:G5"/>
-    <mergeCell ref="G6:G7"/>
-  </mergeCells>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="0" verticalDpi="0"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77A4E167-3852-0542-8EB0-81CB31D49EF8}">
-  <dimension ref="A1:I18"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="28" customHeight="1"/>
-  <sheetData>
-    <row r="1" spans="1:9" ht="28" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A1" s="19"/>
-      <c r="B1" s="66" t="s">
-        <v>49</v>
-      </c>
-      <c r="C1" s="67"/>
-      <c r="D1" s="66" t="s">
-        <v>50</v>
-      </c>
-      <c r="E1" s="71"/>
-      <c r="F1" s="66" t="s">
-        <v>51</v>
-      </c>
-      <c r="G1" s="67"/>
-      <c r="H1" s="66" t="s">
-        <v>61</v>
-      </c>
-      <c r="I1" s="67"/>
-    </row>
-    <row r="2" spans="1:9" ht="28" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A2" s="20" t="s">
-        <v>52</v>
-      </c>
-      <c r="B2" s="61" t="s">
-        <v>53</v>
-      </c>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61" t="s">
-        <v>54</v>
-      </c>
-      <c r="E2" s="61"/>
-      <c r="F2" s="61" t="s">
-        <v>55</v>
-      </c>
-      <c r="G2" s="61"/>
-      <c r="H2" s="61" t="s">
-        <v>56</v>
-      </c>
-      <c r="I2" s="61"/>
-    </row>
-    <row r="3" spans="1:9" ht="28" customHeight="1" thickTop="1">
-      <c r="A3" s="18" t="s">
-        <v>47</v>
-      </c>
-      <c r="B3" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="C3" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="E3" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="F3" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="G3" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="H3" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="I3" s="13" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="28" customHeight="1" thickBot="1">
-      <c r="A4" s="18" t="s">
-        <v>48</v>
-      </c>
-      <c r="B4" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="C4" s="14" t="s">
-        <v>60</v>
-      </c>
-      <c r="D4" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="E4" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="F4" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="G4" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="H4" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="I4" s="13" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="28" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A5" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="B5" s="62" t="s">
-        <v>30</v>
-      </c>
-      <c r="C5" s="63"/>
-      <c r="D5" s="62" t="s">
-        <v>30</v>
-      </c>
-      <c r="E5" s="63"/>
-      <c r="F5" s="62" t="s">
-        <v>30</v>
-      </c>
-      <c r="G5" s="63"/>
-      <c r="H5" s="62" t="s">
-        <v>30</v>
-      </c>
-      <c r="I5" s="63"/>
-    </row>
-    <row r="6" spans="1:9" ht="28" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A6" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="B6" s="62" t="s">
-        <v>32</v>
-      </c>
-      <c r="C6" s="63"/>
-      <c r="D6" s="62" t="s">
-        <v>32</v>
-      </c>
-      <c r="E6" s="63"/>
-      <c r="F6" s="62" t="s">
-        <v>32</v>
-      </c>
-      <c r="G6" s="63"/>
-      <c r="H6" s="62" t="s">
-        <v>32</v>
-      </c>
-      <c r="I6" s="63"/>
-    </row>
-    <row r="7" spans="1:9" ht="28" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A7" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="B7" s="62" t="s">
-        <v>34</v>
-      </c>
-      <c r="C7" s="63"/>
-      <c r="D7" s="62" t="s">
-        <v>34</v>
-      </c>
-      <c r="E7" s="63"/>
-      <c r="F7" s="62" t="s">
-        <v>34</v>
-      </c>
-      <c r="G7" s="63"/>
-      <c r="H7" s="62" t="s">
-        <v>34</v>
-      </c>
-      <c r="I7" s="63"/>
-    </row>
-    <row r="8" spans="1:9" ht="28" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A8" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="B8" s="62" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" s="63"/>
-      <c r="D8" s="62" t="s">
-        <v>25</v>
-      </c>
-      <c r="E8" s="63"/>
-      <c r="F8" s="62" t="s">
-        <v>25</v>
-      </c>
-      <c r="G8" s="63"/>
-      <c r="H8" s="62" t="s">
-        <v>25</v>
-      </c>
-      <c r="I8" s="63"/>
-    </row>
-    <row r="9" spans="1:9" ht="28" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A9" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="B9" s="62" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" s="63"/>
-      <c r="D9" s="62" t="s">
-        <v>24</v>
-      </c>
-      <c r="E9" s="63"/>
-      <c r="F9" s="62" t="s">
-        <v>24</v>
-      </c>
-      <c r="G9" s="63"/>
-      <c r="H9" s="62" t="s">
-        <v>24</v>
-      </c>
-      <c r="I9" s="63"/>
-    </row>
-    <row r="10" spans="1:9" ht="28" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A10" s="68" t="s">
-        <v>37</v>
-      </c>
-      <c r="B10" s="69"/>
-      <c r="C10" s="69"/>
-      <c r="D10" s="69"/>
-      <c r="E10" s="69"/>
-      <c r="F10" s="69"/>
-      <c r="G10" s="69"/>
-      <c r="H10" s="69"/>
-      <c r="I10" s="70"/>
-    </row>
-    <row r="11" spans="1:9" ht="28" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A11" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="B11" s="64" t="s">
-        <v>13</v>
-      </c>
-      <c r="C11" s="65"/>
-      <c r="D11" s="64" t="s">
-        <v>13</v>
-      </c>
-      <c r="E11" s="65"/>
-      <c r="F11" s="64" t="s">
-        <v>13</v>
-      </c>
-      <c r="G11" s="65"/>
-      <c r="H11" s="64" t="s">
-        <v>13</v>
-      </c>
-      <c r="I11" s="65"/>
-    </row>
-    <row r="12" spans="1:9" ht="28" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A12" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="B12" s="64" t="s">
-        <v>1</v>
-      </c>
-      <c r="C12" s="65"/>
-      <c r="D12" s="64" t="s">
-        <v>1</v>
-      </c>
-      <c r="E12" s="65"/>
-      <c r="F12" s="64" t="s">
-        <v>1</v>
-      </c>
-      <c r="G12" s="65"/>
-      <c r="H12" s="64" t="s">
-        <v>1</v>
-      </c>
-      <c r="I12" s="65"/>
-    </row>
-    <row r="13" spans="1:9" ht="28" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A13" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="B13" s="64" t="s">
-        <v>2</v>
-      </c>
-      <c r="C13" s="65"/>
-      <c r="D13" s="64" t="s">
-        <v>2</v>
-      </c>
-      <c r="E13" s="65"/>
-      <c r="F13" s="64" t="s">
-        <v>2</v>
-      </c>
-      <c r="G13" s="65"/>
-      <c r="H13" s="64" t="s">
-        <v>2</v>
-      </c>
-      <c r="I13" s="65"/>
-    </row>
-    <row r="14" spans="1:9" ht="28" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A14" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="B14" s="64" t="s">
-        <v>10</v>
-      </c>
-      <c r="C14" s="65"/>
-      <c r="D14" s="64" t="s">
-        <v>10</v>
-      </c>
-      <c r="E14" s="65"/>
-      <c r="F14" s="64" t="s">
-        <v>10</v>
-      </c>
-      <c r="G14" s="65"/>
-      <c r="H14" s="64" t="s">
-        <v>10</v>
-      </c>
-      <c r="I14" s="65"/>
-    </row>
-    <row r="15" spans="1:9" ht="28" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A15" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="B15" s="59" t="s">
-        <v>4</v>
-      </c>
-      <c r="C15" s="60"/>
-      <c r="D15" s="59" t="s">
-        <v>4</v>
-      </c>
-      <c r="E15" s="60"/>
-      <c r="F15" s="59" t="s">
-        <v>4</v>
-      </c>
-      <c r="G15" s="60"/>
-      <c r="H15" s="59" t="s">
-        <v>4</v>
-      </c>
-      <c r="I15" s="60"/>
-    </row>
-    <row r="16" spans="1:9" ht="28" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A16" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="B16" s="64" t="s">
-        <v>7</v>
-      </c>
-      <c r="C16" s="65"/>
-      <c r="D16" s="64" t="s">
-        <v>7</v>
-      </c>
-      <c r="E16" s="65"/>
-      <c r="F16" s="64" t="s">
-        <v>7</v>
-      </c>
-      <c r="G16" s="65"/>
-      <c r="H16" s="64" t="s">
-        <v>7</v>
-      </c>
-      <c r="I16" s="65"/>
-    </row>
-    <row r="17" spans="1:9" ht="28" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A17" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="B17" s="59" t="s">
-        <v>15</v>
-      </c>
-      <c r="C17" s="60"/>
-      <c r="D17" s="59" t="s">
-        <v>15</v>
-      </c>
-      <c r="E17" s="60"/>
-      <c r="F17" s="59" t="s">
-        <v>15</v>
-      </c>
-      <c r="G17" s="60"/>
-      <c r="H17" s="59" t="s">
-        <v>15</v>
-      </c>
-      <c r="I17" s="60"/>
-    </row>
-    <row r="18" spans="1:9" ht="28" customHeight="1" thickTop="1"/>
-  </sheetData>
-  <mergeCells count="57">
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="A10:I10"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="H17:I17"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="H9:I9"/>
-    <mergeCell ref="H11:I11"/>
-    <mergeCell ref="H12:I12"/>
-    <mergeCell ref="H13:I13"/>
-    <mergeCell ref="H14:I14"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6632,141 +6033,141 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="46" customHeight="1"/>
   <sheetData>
     <row r="1" spans="1:12" ht="46" customHeight="1" thickBot="1">
-      <c r="A1" s="25"/>
+      <c r="A1" s="33"/>
       <c r="B1" s="10"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="29" t="s">
+      <c r="C1" s="34"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="G1" s="29"/>
-      <c r="H1" s="29"/>
-      <c r="I1" s="38"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="38"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="30"/>
+      <c r="J1" s="34"/>
+      <c r="K1" s="30"/>
       <c r="L1" s="4"/>
     </row>
     <row r="2" spans="1:12" ht="46" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A2" s="25"/>
-      <c r="B2" s="34" t="s">
+      <c r="A2" s="33"/>
+      <c r="B2" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="37"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="29"/>
-      <c r="H2" s="29"/>
-      <c r="I2" s="38"/>
-      <c r="J2" s="37"/>
-      <c r="K2" s="39"/>
-      <c r="L2" s="25"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="25"/>
+      <c r="I2" s="30"/>
+      <c r="J2" s="34"/>
+      <c r="K2" s="31"/>
+      <c r="L2" s="33"/>
     </row>
     <row r="3" spans="1:12" ht="46" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A3" s="25"/>
-      <c r="B3" s="36"/>
-      <c r="C3" s="31"/>
-      <c r="D3" s="34" t="s">
+      <c r="A3" s="33"/>
+      <c r="B3" s="37"/>
+      <c r="C3" s="35"/>
+      <c r="D3" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="38"/>
-      <c r="F3" s="22" t="s">
+      <c r="E3" s="30"/>
+      <c r="F3" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="22"/>
-      <c r="H3" s="29"/>
-      <c r="I3" s="38"/>
+      <c r="G3" s="29"/>
+      <c r="H3" s="25"/>
+      <c r="I3" s="30"/>
       <c r="J3" s="10"/>
-      <c r="K3" s="41" t="s">
+      <c r="K3" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="L3" s="25"/>
+      <c r="L3" s="33"/>
     </row>
     <row r="4" spans="1:12" ht="46" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A4" s="25"/>
-      <c r="B4" s="40"/>
+      <c r="A4" s="33"/>
+      <c r="B4" s="43"/>
       <c r="C4" s="32"/>
-      <c r="D4" s="35"/>
-      <c r="E4" s="38"/>
-      <c r="F4" s="22"/>
-      <c r="G4" s="22"/>
-      <c r="H4" s="29"/>
-      <c r="I4" s="38"/>
-      <c r="J4" s="41" t="s">
+      <c r="D4" s="42"/>
+      <c r="E4" s="30"/>
+      <c r="F4" s="29"/>
+      <c r="G4" s="29"/>
+      <c r="H4" s="25"/>
+      <c r="I4" s="30"/>
+      <c r="J4" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="K4" s="42"/>
-      <c r="L4" s="25"/>
+      <c r="K4" s="39"/>
+      <c r="L4" s="33"/>
     </row>
     <row r="5" spans="1:12" ht="46" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A5" s="25"/>
-      <c r="B5" s="39"/>
+      <c r="A5" s="33"/>
+      <c r="B5" s="31"/>
       <c r="C5" s="32"/>
-      <c r="D5" s="35"/>
-      <c r="E5" s="38"/>
+      <c r="D5" s="42"/>
+      <c r="E5" s="30"/>
       <c r="F5" s="15"/>
       <c r="G5" s="17"/>
-      <c r="H5" s="29"/>
-      <c r="I5" s="39"/>
-      <c r="J5" s="43"/>
-      <c r="K5" s="31"/>
-      <c r="L5" s="25"/>
+      <c r="H5" s="25"/>
+      <c r="I5" s="31"/>
+      <c r="J5" s="41"/>
+      <c r="K5" s="35"/>
+      <c r="L5" s="33"/>
     </row>
     <row r="6" spans="1:12" ht="46" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A6" s="25"/>
-      <c r="B6" s="34" t="s">
+      <c r="A6" s="33"/>
+      <c r="B6" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="33"/>
-      <c r="D6" s="35"/>
-      <c r="E6" s="31"/>
-      <c r="F6" s="31" t="s">
+      <c r="C6" s="40"/>
+      <c r="D6" s="42"/>
+      <c r="E6" s="35"/>
+      <c r="F6" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="G6" s="31"/>
-      <c r="H6" s="31"/>
+      <c r="G6" s="35"/>
+      <c r="H6" s="35"/>
       <c r="I6" s="32"/>
-      <c r="J6" s="43"/>
-      <c r="K6" s="33"/>
-      <c r="L6" s="25"/>
+      <c r="J6" s="41"/>
+      <c r="K6" s="40"/>
+      <c r="L6" s="33"/>
     </row>
     <row r="7" spans="1:12" ht="46" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A7" s="25"/>
-      <c r="B7" s="36"/>
-      <c r="C7" s="34" t="s">
+      <c r="A7" s="33"/>
+      <c r="B7" s="37"/>
+      <c r="C7" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="36"/>
+      <c r="D7" s="37"/>
       <c r="E7" s="32"/>
       <c r="F7" s="32"/>
       <c r="G7" s="32"/>
       <c r="H7" s="32"/>
       <c r="I7" s="32"/>
-      <c r="J7" s="42"/>
-      <c r="K7" s="41" t="s">
+      <c r="J7" s="39"/>
+      <c r="K7" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="L7" s="25"/>
+      <c r="L7" s="33"/>
     </row>
     <row r="8" spans="1:12" ht="46" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A8" s="25"/>
-      <c r="B8" s="40"/>
-      <c r="C8" s="35"/>
+      <c r="A8" s="33"/>
+      <c r="B8" s="43"/>
+      <c r="C8" s="42"/>
       <c r="D8" s="32"/>
       <c r="E8" s="32"/>
       <c r="F8" s="32"/>
       <c r="G8" s="32"/>
       <c r="H8" s="32"/>
       <c r="I8" s="32"/>
-      <c r="J8" s="31"/>
-      <c r="K8" s="42"/>
-      <c r="L8" s="25"/>
+      <c r="J8" s="35"/>
+      <c r="K8" s="39"/>
+      <c r="L8" s="33"/>
     </row>
     <row r="9" spans="1:12" ht="46" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A9" s="25"/>
-      <c r="B9" s="38"/>
-      <c r="C9" s="36"/>
+      <c r="A9" s="33"/>
+      <c r="B9" s="30"/>
+      <c r="C9" s="37"/>
       <c r="D9" s="32"/>
       <c r="E9" s="32"/>
       <c r="F9" s="32"/>
@@ -6774,11 +6175,11 @@
       <c r="H9" s="32"/>
       <c r="I9" s="32"/>
       <c r="J9" s="32"/>
-      <c r="K9" s="31"/>
-      <c r="L9" s="25"/>
+      <c r="K9" s="35"/>
+      <c r="L9" s="33"/>
     </row>
     <row r="10" spans="1:12" ht="46" customHeight="1" thickTop="1">
-      <c r="A10" s="25"/>
+      <c r="A10" s="33"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
       <c r="D10" s="32"/>
@@ -6918,13 +6319,20 @@
     </row>
   </sheetData>
   <mergeCells count="37">
-    <mergeCell ref="I1:I5"/>
-    <mergeCell ref="I6:I10"/>
-    <mergeCell ref="L2:L3"/>
-    <mergeCell ref="L4:L5"/>
-    <mergeCell ref="L6:L7"/>
-    <mergeCell ref="L8:L9"/>
-    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="C3:C6"/>
+    <mergeCell ref="D3:D7"/>
+    <mergeCell ref="F3:G4"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="E1:E5"/>
+    <mergeCell ref="F1:G2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="E6:E10"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="A5:A6"/>
     <mergeCell ref="H6:H10"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="H1:H5"/>
@@ -6941,20 +6349,13 @@
     <mergeCell ref="F7:G10"/>
     <mergeCell ref="B8:B9"/>
     <mergeCell ref="D8:D10"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="C3:C6"/>
-    <mergeCell ref="D3:D7"/>
-    <mergeCell ref="F3:G4"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="E1:E5"/>
-    <mergeCell ref="F1:G2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="E6:E10"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="I1:I5"/>
+    <mergeCell ref="I6:I10"/>
+    <mergeCell ref="L2:L3"/>
+    <mergeCell ref="L4:L5"/>
+    <mergeCell ref="L6:L7"/>
+    <mergeCell ref="L8:L9"/>
+    <mergeCell ref="J1:J2"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6968,155 +6369,155 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="46" customHeight="1"/>
   <sheetData>
     <row r="1" spans="1:12" ht="46" customHeight="1" thickBot="1">
-      <c r="A1" s="25"/>
+      <c r="A1" s="33"/>
       <c r="B1" s="10"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="29" t="s">
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="G1" s="29"/>
-      <c r="H1" s="29"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
       <c r="I1" s="32"/>
       <c r="J1" s="32"/>
       <c r="K1" s="7"/>
-      <c r="L1" s="25"/>
+      <c r="L1" s="33"/>
     </row>
     <row r="2" spans="1:12" ht="46" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A2" s="25"/>
-      <c r="B2" s="34" t="s">
+      <c r="A2" s="33"/>
+      <c r="B2" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="29"/>
-      <c r="H2" s="29"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="25"/>
       <c r="I2" s="32"/>
-      <c r="J2" s="33"/>
-      <c r="K2" s="41" t="s">
+      <c r="J2" s="40"/>
+      <c r="K2" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="L2" s="25"/>
+      <c r="L2" s="33"/>
     </row>
     <row r="3" spans="1:12" ht="46" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A3" s="25"/>
-      <c r="B3" s="36"/>
-      <c r="C3" s="31"/>
-      <c r="D3" s="34" t="s">
+      <c r="A3" s="33"/>
+      <c r="B3" s="37"/>
+      <c r="C3" s="35"/>
+      <c r="D3" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="38"/>
-      <c r="F3" s="22" t="s">
+      <c r="E3" s="30"/>
+      <c r="F3" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="22"/>
-      <c r="H3" s="29"/>
-      <c r="I3" s="41" t="s">
+      <c r="G3" s="29"/>
+      <c r="H3" s="25"/>
+      <c r="I3" s="38" t="s">
         <v>8</v>
       </c>
-      <c r="J3" s="31"/>
-      <c r="K3" s="42"/>
-      <c r="L3" s="25"/>
+      <c r="J3" s="35"/>
+      <c r="K3" s="39"/>
+      <c r="L3" s="33"/>
     </row>
     <row r="4" spans="1:12" ht="46" customHeight="1" thickTop="1">
-      <c r="A4" s="25"/>
-      <c r="B4" s="40"/>
+      <c r="A4" s="33"/>
+      <c r="B4" s="43"/>
       <c r="C4" s="32"/>
-      <c r="D4" s="35"/>
-      <c r="E4" s="38"/>
-      <c r="F4" s="22"/>
-      <c r="G4" s="22"/>
-      <c r="H4" s="29"/>
-      <c r="I4" s="43"/>
+      <c r="D4" s="42"/>
+      <c r="E4" s="30"/>
+      <c r="F4" s="29"/>
+      <c r="G4" s="29"/>
+      <c r="H4" s="25"/>
+      <c r="I4" s="41"/>
       <c r="J4" s="32"/>
-      <c r="K4" s="31"/>
-      <c r="L4" s="25"/>
+      <c r="K4" s="35"/>
+      <c r="L4" s="33"/>
     </row>
     <row r="5" spans="1:12" ht="46" customHeight="1" thickBot="1">
-      <c r="A5" s="25"/>
-      <c r="B5" s="39"/>
+      <c r="A5" s="33"/>
+      <c r="B5" s="31"/>
       <c r="C5" s="32"/>
-      <c r="D5" s="35"/>
-      <c r="E5" s="38"/>
+      <c r="D5" s="42"/>
+      <c r="E5" s="30"/>
       <c r="F5" s="15"/>
       <c r="G5" s="17"/>
-      <c r="H5" s="29"/>
-      <c r="I5" s="43"/>
+      <c r="H5" s="25"/>
+      <c r="I5" s="41"/>
       <c r="J5" s="32"/>
-      <c r="K5" s="33"/>
-      <c r="L5" s="25"/>
+      <c r="K5" s="40"/>
+      <c r="L5" s="33"/>
     </row>
     <row r="6" spans="1:12" ht="46" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A6" s="25"/>
-      <c r="B6" s="34" t="s">
+      <c r="A6" s="33"/>
+      <c r="B6" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="33"/>
-      <c r="D6" s="35"/>
-      <c r="E6" s="31"/>
-      <c r="F6" s="31" t="s">
+      <c r="C6" s="40"/>
+      <c r="D6" s="42"/>
+      <c r="E6" s="35"/>
+      <c r="F6" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="G6" s="31"/>
-      <c r="H6" s="31"/>
-      <c r="I6" s="43"/>
-      <c r="J6" s="33"/>
-      <c r="K6" s="41" t="s">
+      <c r="G6" s="35"/>
+      <c r="H6" s="35"/>
+      <c r="I6" s="41"/>
+      <c r="J6" s="40"/>
+      <c r="K6" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="L6" s="25"/>
+      <c r="L6" s="33"/>
     </row>
     <row r="7" spans="1:12" ht="46" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A7" s="25"/>
-      <c r="B7" s="36"/>
-      <c r="C7" s="34" t="s">
+      <c r="A7" s="33"/>
+      <c r="B7" s="37"/>
+      <c r="C7" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="36"/>
+      <c r="D7" s="37"/>
       <c r="E7" s="32"/>
       <c r="F7" s="32"/>
       <c r="G7" s="32"/>
       <c r="H7" s="32"/>
-      <c r="I7" s="42"/>
-      <c r="J7" s="41" t="s">
+      <c r="I7" s="39"/>
+      <c r="J7" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="K7" s="42"/>
-      <c r="L7" s="25"/>
+      <c r="K7" s="39"/>
+      <c r="L7" s="33"/>
     </row>
     <row r="8" spans="1:12" ht="46" customHeight="1" thickTop="1">
-      <c r="A8" s="25"/>
-      <c r="B8" s="40"/>
-      <c r="C8" s="35"/>
+      <c r="A8" s="33"/>
+      <c r="B8" s="43"/>
+      <c r="C8" s="42"/>
       <c r="D8" s="32"/>
       <c r="E8" s="32"/>
       <c r="F8" s="32"/>
       <c r="G8" s="32"/>
       <c r="H8" s="32"/>
       <c r="I8" s="32"/>
-      <c r="J8" s="43"/>
-      <c r="K8" s="31"/>
-      <c r="L8" s="25"/>
+      <c r="J8" s="41"/>
+      <c r="K8" s="35"/>
+      <c r="L8" s="33"/>
     </row>
     <row r="9" spans="1:12" ht="46" customHeight="1" thickBot="1">
-      <c r="A9" s="25"/>
-      <c r="B9" s="38"/>
-      <c r="C9" s="36"/>
+      <c r="A9" s="33"/>
+      <c r="B9" s="30"/>
+      <c r="C9" s="37"/>
       <c r="D9" s="32"/>
       <c r="E9" s="32"/>
       <c r="F9" s="32"/>
       <c r="G9" s="32"/>
       <c r="H9" s="32"/>
       <c r="I9" s="32"/>
-      <c r="J9" s="42"/>
-      <c r="K9" s="33"/>
-      <c r="L9" s="25"/>
+      <c r="J9" s="39"/>
+      <c r="K9" s="40"/>
+      <c r="L9" s="33"/>
     </row>
     <row r="10" spans="1:12" ht="46" customHeight="1" thickTop="1">
-      <c r="A10" s="25"/>
+      <c r="A10" s="33"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
       <c r="D10" s="32"/>
@@ -7127,7 +6528,7 @@
       <c r="I10" s="32"/>
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
-      <c r="L10" s="25"/>
+      <c r="L10" s="33"/>
     </row>
     <row r="11" spans="1:12" ht="46" customHeight="1">
       <c r="A11" s="4"/>
@@ -7255,17 +6656,17 @@
     </row>
   </sheetData>
   <mergeCells count="38">
-    <mergeCell ref="L1:L2"/>
-    <mergeCell ref="L3:L4"/>
-    <mergeCell ref="L5:L6"/>
-    <mergeCell ref="L7:L8"/>
-    <mergeCell ref="L9:L10"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="C3:C6"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="J3:J6"/>
+    <mergeCell ref="C7:C9"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="K4:K5"/>
+    <mergeCell ref="K6:K7"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="F1:G2"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="F7:G10"/>
     <mergeCell ref="A9:A10"/>
     <mergeCell ref="B8:B9"/>
     <mergeCell ref="K8:K9"/>
@@ -7282,17 +6683,17 @@
     <mergeCell ref="H1:H5"/>
     <mergeCell ref="H6:H10"/>
     <mergeCell ref="E6:E10"/>
-    <mergeCell ref="J1:J2"/>
-    <mergeCell ref="J3:J6"/>
-    <mergeCell ref="C7:C9"/>
-    <mergeCell ref="K2:K3"/>
-    <mergeCell ref="K4:K5"/>
-    <mergeCell ref="K6:K7"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="F1:G2"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="F7:G10"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="C3:C6"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="L3:L4"/>
+    <mergeCell ref="L5:L6"/>
+    <mergeCell ref="L7:L8"/>
+    <mergeCell ref="L9:L10"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7306,193 +6707,193 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="38" customHeight="1"/>
   <sheetData>
     <row r="1" spans="1:12" ht="38" customHeight="1" thickBot="1">
-      <c r="A1" s="25"/>
+      <c r="A1" s="33"/>
       <c r="B1" s="10"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="29" t="s">
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
-      <c r="H1" s="29"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
       <c r="I1" s="32"/>
       <c r="J1" s="32"/>
       <c r="K1" s="32"/>
     </row>
     <row r="2" spans="1:12" ht="38" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A2" s="25"/>
-      <c r="B2" s="34" t="s">
+      <c r="A2" s="33"/>
+      <c r="B2" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="39"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="29"/>
-      <c r="H2" s="29"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="25"/>
       <c r="I2" s="32"/>
       <c r="J2" s="32"/>
-      <c r="K2" s="33"/>
-      <c r="L2" s="25"/>
+      <c r="K2" s="40"/>
+      <c r="L2" s="33"/>
     </row>
     <row r="3" spans="1:12" ht="38" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A3" s="25"/>
-      <c r="B3" s="36"/>
-      <c r="C3" s="34" t="s">
+      <c r="A3" s="33"/>
+      <c r="B3" s="37"/>
+      <c r="C3" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="38"/>
-      <c r="E3" s="29"/>
-      <c r="F3" s="29"/>
-      <c r="G3" s="29"/>
-      <c r="H3" s="29"/>
-      <c r="I3" s="33"/>
-      <c r="J3" s="33"/>
-      <c r="K3" s="41" t="s">
+      <c r="D3" s="30"/>
+      <c r="E3" s="25"/>
+      <c r="F3" s="25"/>
+      <c r="G3" s="25"/>
+      <c r="H3" s="25"/>
+      <c r="I3" s="40"/>
+      <c r="J3" s="40"/>
+      <c r="K3" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="L3" s="25"/>
+      <c r="L3" s="33"/>
     </row>
     <row r="4" spans="1:12" ht="38" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A4" s="25"/>
-      <c r="B4" s="40"/>
-      <c r="C4" s="35"/>
-      <c r="D4" s="39"/>
+      <c r="A4" s="33"/>
+      <c r="B4" s="43"/>
+      <c r="C4" s="42"/>
+      <c r="D4" s="31"/>
       <c r="E4" s="32"/>
-      <c r="F4" s="22" t="s">
+      <c r="F4" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="G4" s="22"/>
-      <c r="H4" s="35"/>
-      <c r="I4" s="41" t="s">
+      <c r="G4" s="29"/>
+      <c r="H4" s="42"/>
+      <c r="I4" s="38" t="s">
         <v>8</v>
       </c>
-      <c r="J4" s="31"/>
-      <c r="K4" s="42"/>
-      <c r="L4" s="25"/>
+      <c r="J4" s="35"/>
+      <c r="K4" s="39"/>
+      <c r="L4" s="33"/>
     </row>
     <row r="5" spans="1:12" ht="38" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A5" s="25"/>
-      <c r="B5" s="39"/>
-      <c r="C5" s="35"/>
-      <c r="D5" s="34" t="s">
+      <c r="A5" s="33"/>
+      <c r="B5" s="31"/>
+      <c r="C5" s="42"/>
+      <c r="D5" s="36" t="s">
         <v>11</v>
       </c>
       <c r="E5" s="32"/>
-      <c r="F5" s="22"/>
-      <c r="G5" s="22"/>
-      <c r="H5" s="35"/>
-      <c r="I5" s="43"/>
+      <c r="F5" s="29"/>
+      <c r="G5" s="29"/>
+      <c r="H5" s="42"/>
+      <c r="I5" s="41"/>
       <c r="J5" s="32"/>
-      <c r="K5" s="31"/>
-      <c r="L5" s="25"/>
+      <c r="K5" s="35"/>
+      <c r="L5" s="33"/>
     </row>
     <row r="6" spans="1:12" ht="38" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A6" s="25"/>
-      <c r="B6" s="34" t="s">
+      <c r="A6" s="33"/>
+      <c r="B6" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="36"/>
-      <c r="D6" s="35"/>
+      <c r="C6" s="37"/>
+      <c r="D6" s="42"/>
       <c r="E6" s="32"/>
-      <c r="F6" s="35"/>
-      <c r="G6" s="43"/>
-      <c r="H6" s="35"/>
-      <c r="I6" s="43"/>
+      <c r="F6" s="42"/>
+      <c r="G6" s="41"/>
+      <c r="H6" s="42"/>
+      <c r="I6" s="41"/>
       <c r="J6" s="32"/>
-      <c r="K6" s="33"/>
-      <c r="L6" s="25"/>
+      <c r="K6" s="40"/>
+      <c r="L6" s="33"/>
     </row>
     <row r="7" spans="1:12" ht="38" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A7" s="25"/>
-      <c r="B7" s="36"/>
-      <c r="C7" s="31"/>
-      <c r="D7" s="35"/>
-      <c r="E7" s="33"/>
-      <c r="F7" s="35"/>
-      <c r="G7" s="43"/>
-      <c r="H7" s="36"/>
-      <c r="I7" s="43"/>
-      <c r="J7" s="33"/>
-      <c r="K7" s="41" t="s">
+      <c r="A7" s="33"/>
+      <c r="B7" s="37"/>
+      <c r="C7" s="35"/>
+      <c r="D7" s="42"/>
+      <c r="E7" s="40"/>
+      <c r="F7" s="42"/>
+      <c r="G7" s="41"/>
+      <c r="H7" s="37"/>
+      <c r="I7" s="41"/>
+      <c r="J7" s="40"/>
+      <c r="K7" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="L7" s="25"/>
+      <c r="L7" s="33"/>
     </row>
     <row r="8" spans="1:12" ht="38" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A8" s="25"/>
-      <c r="B8" s="40"/>
+      <c r="A8" s="33"/>
+      <c r="B8" s="43"/>
       <c r="C8" s="32"/>
-      <c r="D8" s="35"/>
-      <c r="E8" s="31"/>
-      <c r="F8" s="31" t="s">
+      <c r="D8" s="42"/>
+      <c r="E8" s="35"/>
+      <c r="F8" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="G8" s="31"/>
-      <c r="H8" s="31"/>
-      <c r="I8" s="42"/>
-      <c r="J8" s="41" t="s">
+      <c r="G8" s="35"/>
+      <c r="H8" s="35"/>
+      <c r="I8" s="39"/>
+      <c r="J8" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="K8" s="42"/>
-      <c r="L8" s="25"/>
+      <c r="K8" s="39"/>
+      <c r="L8" s="33"/>
     </row>
     <row r="9" spans="1:12" ht="38" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A9" s="25"/>
-      <c r="B9" s="39"/>
+      <c r="A9" s="33"/>
+      <c r="B9" s="31"/>
       <c r="C9" s="32"/>
-      <c r="D9" s="35"/>
+      <c r="D9" s="42"/>
       <c r="E9" s="32"/>
       <c r="F9" s="32"/>
       <c r="G9" s="32"/>
       <c r="H9" s="32"/>
-      <c r="I9" s="31"/>
-      <c r="J9" s="43"/>
-      <c r="K9" s="31"/>
-      <c r="L9" s="25"/>
+      <c r="I9" s="35"/>
+      <c r="J9" s="41"/>
+      <c r="K9" s="35"/>
+      <c r="L9" s="33"/>
     </row>
     <row r="10" spans="1:12" ht="38" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A10" s="25"/>
-      <c r="B10" s="34" t="s">
+      <c r="A10" s="33"/>
+      <c r="B10" s="36" t="s">
         <v>6</v>
       </c>
       <c r="C10" s="32"/>
-      <c r="D10" s="35"/>
+      <c r="D10" s="42"/>
       <c r="E10" s="32"/>
-      <c r="F10" s="38"/>
-      <c r="G10" s="38"/>
+      <c r="F10" s="30"/>
+      <c r="G10" s="30"/>
       <c r="H10" s="32"/>
       <c r="I10" s="32"/>
-      <c r="J10" s="42"/>
-      <c r="K10" s="33"/>
-      <c r="L10" s="25"/>
+      <c r="J10" s="39"/>
+      <c r="K10" s="40"/>
+      <c r="L10" s="33"/>
     </row>
     <row r="11" spans="1:12" ht="38" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A11" s="25"/>
-      <c r="B11" s="36"/>
-      <c r="C11" s="31"/>
-      <c r="D11" s="31"/>
+      <c r="A11" s="33"/>
+      <c r="B11" s="37"/>
+      <c r="C11" s="35"/>
+      <c r="D11" s="35"/>
       <c r="E11" s="32"/>
-      <c r="F11" s="38"/>
-      <c r="G11" s="38"/>
+      <c r="F11" s="30"/>
+      <c r="G11" s="30"/>
       <c r="H11" s="32"/>
       <c r="I11" s="32"/>
-      <c r="J11" s="40"/>
-      <c r="K11" s="40"/>
-      <c r="L11" s="25"/>
+      <c r="J11" s="43"/>
+      <c r="K11" s="43"/>
+      <c r="L11" s="33"/>
     </row>
     <row r="12" spans="1:12" ht="38" customHeight="1" thickTop="1">
-      <c r="A12" s="25"/>
+      <c r="A12" s="33"/>
       <c r="C12" s="32"/>
       <c r="D12" s="32"/>
       <c r="E12" s="32"/>
-      <c r="F12" s="38"/>
-      <c r="G12" s="38"/>
+      <c r="F12" s="30"/>
+      <c r="G12" s="30"/>
       <c r="H12" s="32"/>
       <c r="I12" s="32"/>
-      <c r="J12" s="38"/>
-      <c r="K12" s="38"/>
+      <c r="J12" s="30"/>
+      <c r="K12" s="30"/>
     </row>
     <row r="13" spans="1:12" ht="38" customHeight="1">
       <c r="A13" s="4"/>
@@ -7604,36 +7005,6 @@
     </row>
   </sheetData>
   <mergeCells count="46">
-    <mergeCell ref="E1:H3"/>
-    <mergeCell ref="E4:E7"/>
-    <mergeCell ref="H4:H7"/>
-    <mergeCell ref="L6:L7"/>
-    <mergeCell ref="L8:L9"/>
-    <mergeCell ref="L10:L11"/>
-    <mergeCell ref="I1:I3"/>
-    <mergeCell ref="J1:J3"/>
-    <mergeCell ref="K1:K2"/>
-    <mergeCell ref="K3:K4"/>
-    <mergeCell ref="K5:K6"/>
-    <mergeCell ref="K7:K8"/>
-    <mergeCell ref="K9:K10"/>
-    <mergeCell ref="L2:L3"/>
-    <mergeCell ref="L4:L5"/>
-    <mergeCell ref="J8:J10"/>
-    <mergeCell ref="J4:J7"/>
-    <mergeCell ref="I4:I8"/>
-    <mergeCell ref="I9:I12"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="J11:J12"/>
-    <mergeCell ref="K11:K12"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="E8:E12"/>
-    <mergeCell ref="F8:G9"/>
-    <mergeCell ref="H8:H12"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="F10:G12"/>
     <mergeCell ref="D1:D4"/>
     <mergeCell ref="F4:G5"/>
     <mergeCell ref="C7:C10"/>
@@ -7650,6 +7021,36 @@
     <mergeCell ref="F6:F7"/>
     <mergeCell ref="G6:G7"/>
     <mergeCell ref="A7:A8"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="E8:E12"/>
+    <mergeCell ref="F8:G9"/>
+    <mergeCell ref="H8:H12"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="F10:G12"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="J11:J12"/>
+    <mergeCell ref="K11:K12"/>
+    <mergeCell ref="L10:L11"/>
+    <mergeCell ref="I1:I3"/>
+    <mergeCell ref="J1:J3"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="K3:K4"/>
+    <mergeCell ref="K5:K6"/>
+    <mergeCell ref="K7:K8"/>
+    <mergeCell ref="K9:K10"/>
+    <mergeCell ref="L2:L3"/>
+    <mergeCell ref="L4:L5"/>
+    <mergeCell ref="J8:J10"/>
+    <mergeCell ref="J4:J7"/>
+    <mergeCell ref="I4:I8"/>
+    <mergeCell ref="I9:I12"/>
+    <mergeCell ref="E1:H3"/>
+    <mergeCell ref="E4:E7"/>
+    <mergeCell ref="H4:H7"/>
+    <mergeCell ref="L6:L7"/>
+    <mergeCell ref="L8:L9"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7663,197 +7064,197 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="38" customHeight="1"/>
   <sheetData>
     <row r="1" spans="1:12" ht="38" customHeight="1" thickBot="1">
-      <c r="A1" s="25"/>
+      <c r="A1" s="33"/>
       <c r="B1" s="10"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="29" t="s">
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
-      <c r="H1" s="29"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
       <c r="I1" s="32"/>
       <c r="J1" s="32"/>
       <c r="K1" s="7"/>
-      <c r="L1" s="25"/>
+      <c r="L1" s="33"/>
     </row>
     <row r="2" spans="1:12" ht="38" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A2" s="25"/>
-      <c r="B2" s="34" t="s">
+      <c r="A2" s="33"/>
+      <c r="B2" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="39"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="29"/>
-      <c r="H2" s="29"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="25"/>
       <c r="I2" s="32"/>
-      <c r="J2" s="33"/>
-      <c r="K2" s="41" t="s">
+      <c r="J2" s="40"/>
+      <c r="K2" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="L2" s="25"/>
+      <c r="L2" s="33"/>
     </row>
     <row r="3" spans="1:12" ht="38" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A3" s="25"/>
-      <c r="B3" s="36"/>
-      <c r="C3" s="34" t="s">
+      <c r="A3" s="33"/>
+      <c r="B3" s="37"/>
+      <c r="C3" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="38"/>
-      <c r="E3" s="29"/>
-      <c r="F3" s="29"/>
-      <c r="G3" s="29"/>
-      <c r="H3" s="29"/>
+      <c r="D3" s="30"/>
+      <c r="E3" s="25"/>
+      <c r="F3" s="25"/>
+      <c r="G3" s="25"/>
+      <c r="H3" s="25"/>
       <c r="I3" s="32"/>
-      <c r="J3" s="41" t="s">
+      <c r="J3" s="38" t="s">
         <v>8</v>
       </c>
-      <c r="K3" s="42"/>
-      <c r="L3" s="25"/>
+      <c r="K3" s="39"/>
+      <c r="L3" s="33"/>
     </row>
     <row r="4" spans="1:12" ht="38" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A4" s="25"/>
-      <c r="B4" s="40"/>
-      <c r="C4" s="35"/>
-      <c r="D4" s="39"/>
+      <c r="A4" s="33"/>
+      <c r="B4" s="43"/>
+      <c r="C4" s="42"/>
+      <c r="D4" s="31"/>
       <c r="E4" s="32"/>
-      <c r="F4" s="22" t="s">
+      <c r="F4" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="G4" s="22"/>
+      <c r="G4" s="29"/>
       <c r="H4" s="32"/>
-      <c r="I4" s="33"/>
-      <c r="J4" s="43"/>
-      <c r="K4" s="31"/>
-      <c r="L4" s="25"/>
+      <c r="I4" s="40"/>
+      <c r="J4" s="41"/>
+      <c r="K4" s="35"/>
+      <c r="L4" s="33"/>
     </row>
     <row r="5" spans="1:12" ht="38" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A5" s="25"/>
-      <c r="B5" s="39"/>
-      <c r="C5" s="35"/>
-      <c r="D5" s="34" t="s">
+      <c r="A5" s="33"/>
+      <c r="B5" s="31"/>
+      <c r="C5" s="42"/>
+      <c r="D5" s="36" t="s">
         <v>11</v>
       </c>
       <c r="E5" s="32"/>
-      <c r="F5" s="22"/>
-      <c r="G5" s="22"/>
+      <c r="F5" s="29"/>
+      <c r="G5" s="29"/>
       <c r="H5" s="32"/>
-      <c r="I5" s="41" t="s">
+      <c r="I5" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="J5" s="43"/>
-      <c r="K5" s="33"/>
-      <c r="L5" s="25"/>
+      <c r="J5" s="41"/>
+      <c r="K5" s="40"/>
+      <c r="L5" s="33"/>
     </row>
     <row r="6" spans="1:12" ht="38" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A6" s="25"/>
-      <c r="B6" s="34" t="s">
+      <c r="A6" s="33"/>
+      <c r="B6" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="36"/>
-      <c r="D6" s="35"/>
+      <c r="C6" s="37"/>
+      <c r="D6" s="42"/>
       <c r="E6" s="32"/>
-      <c r="F6" s="35"/>
-      <c r="G6" s="43"/>
+      <c r="F6" s="42"/>
+      <c r="G6" s="41"/>
       <c r="H6" s="32"/>
-      <c r="I6" s="43"/>
-      <c r="J6" s="42"/>
-      <c r="K6" s="41" t="s">
+      <c r="I6" s="41"/>
+      <c r="J6" s="39"/>
+      <c r="K6" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="L6" s="25"/>
+      <c r="L6" s="33"/>
     </row>
     <row r="7" spans="1:12" ht="38" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A7" s="25"/>
-      <c r="B7" s="36"/>
-      <c r="C7" s="31"/>
-      <c r="D7" s="35"/>
-      <c r="E7" s="33"/>
-      <c r="F7" s="35"/>
-      <c r="G7" s="43"/>
-      <c r="H7" s="33"/>
-      <c r="I7" s="43"/>
-      <c r="J7" s="31"/>
-      <c r="K7" s="42"/>
-      <c r="L7" s="25"/>
+      <c r="A7" s="33"/>
+      <c r="B7" s="37"/>
+      <c r="C7" s="35"/>
+      <c r="D7" s="42"/>
+      <c r="E7" s="40"/>
+      <c r="F7" s="42"/>
+      <c r="G7" s="41"/>
+      <c r="H7" s="40"/>
+      <c r="I7" s="41"/>
+      <c r="J7" s="35"/>
+      <c r="K7" s="39"/>
+      <c r="L7" s="33"/>
     </row>
     <row r="8" spans="1:12" ht="38" customHeight="1" thickTop="1">
-      <c r="A8" s="25"/>
-      <c r="B8" s="40"/>
+      <c r="A8" s="33"/>
+      <c r="B8" s="43"/>
       <c r="C8" s="32"/>
-      <c r="D8" s="35"/>
-      <c r="E8" s="31"/>
-      <c r="F8" s="31" t="s">
+      <c r="D8" s="42"/>
+      <c r="E8" s="35"/>
+      <c r="F8" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="G8" s="31"/>
-      <c r="H8" s="31"/>
-      <c r="I8" s="43"/>
+      <c r="G8" s="35"/>
+      <c r="H8" s="35"/>
+      <c r="I8" s="41"/>
       <c r="J8" s="32"/>
-      <c r="K8" s="31"/>
-      <c r="L8" s="25"/>
+      <c r="K8" s="35"/>
+      <c r="L8" s="33"/>
     </row>
     <row r="9" spans="1:12" ht="38" customHeight="1" thickBot="1">
-      <c r="A9" s="25"/>
-      <c r="B9" s="39"/>
+      <c r="A9" s="33"/>
+      <c r="B9" s="31"/>
       <c r="C9" s="32"/>
-      <c r="D9" s="35"/>
+      <c r="D9" s="42"/>
       <c r="E9" s="32"/>
       <c r="F9" s="32"/>
       <c r="G9" s="32"/>
       <c r="H9" s="32"/>
-      <c r="I9" s="43"/>
+      <c r="I9" s="41"/>
       <c r="J9" s="32"/>
-      <c r="K9" s="33"/>
-      <c r="L9" s="25"/>
+      <c r="K9" s="40"/>
+      <c r="L9" s="33"/>
     </row>
     <row r="10" spans="1:12" ht="38" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A10" s="25"/>
-      <c r="B10" s="34" t="s">
+      <c r="A10" s="33"/>
+      <c r="B10" s="36" t="s">
         <v>6</v>
       </c>
       <c r="C10" s="32"/>
-      <c r="D10" s="35"/>
+      <c r="D10" s="42"/>
       <c r="E10" s="32"/>
-      <c r="F10" s="38"/>
-      <c r="G10" s="38"/>
+      <c r="F10" s="30"/>
+      <c r="G10" s="30"/>
       <c r="H10" s="32"/>
-      <c r="I10" s="43"/>
+      <c r="I10" s="41"/>
       <c r="J10" s="32"/>
-      <c r="K10" s="41" t="s">
+      <c r="K10" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="L10" s="25"/>
+      <c r="L10" s="33"/>
     </row>
     <row r="11" spans="1:12" ht="38" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A11" s="25"/>
-      <c r="B11" s="36"/>
-      <c r="C11" s="31"/>
-      <c r="D11" s="31"/>
+      <c r="A11" s="33"/>
+      <c r="B11" s="37"/>
+      <c r="C11" s="35"/>
+      <c r="D11" s="35"/>
       <c r="E11" s="32"/>
-      <c r="F11" s="38"/>
-      <c r="G11" s="38"/>
+      <c r="F11" s="30"/>
+      <c r="G11" s="30"/>
       <c r="H11" s="32"/>
-      <c r="I11" s="31"/>
-      <c r="J11" s="31"/>
-      <c r="K11" s="42"/>
-      <c r="L11" s="25"/>
+      <c r="I11" s="35"/>
+      <c r="J11" s="35"/>
+      <c r="K11" s="39"/>
+      <c r="L11" s="33"/>
     </row>
     <row r="12" spans="1:12" ht="38" customHeight="1" thickTop="1">
-      <c r="A12" s="25"/>
+      <c r="A12" s="33"/>
       <c r="C12" s="32"/>
       <c r="D12" s="32"/>
       <c r="E12" s="32"/>
-      <c r="F12" s="38"/>
-      <c r="G12" s="38"/>
+      <c r="F12" s="30"/>
+      <c r="G12" s="30"/>
       <c r="H12" s="32"/>
       <c r="I12" s="32"/>
       <c r="J12" s="32"/>
       <c r="K12" s="1"/>
-      <c r="L12" s="25"/>
+      <c r="L12" s="33"/>
     </row>
     <row r="13" spans="1:12" ht="38" customHeight="1">
       <c r="A13" s="4"/>
@@ -7965,6 +7366,36 @@
     </row>
   </sheetData>
   <mergeCells count="46">
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="L5:L6"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="K6:K7"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="C7:C10"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="C3:C6"/>
+    <mergeCell ref="J3:J6"/>
+    <mergeCell ref="E1:H3"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D4"/>
+    <mergeCell ref="K4:K5"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="I5:I10"/>
+    <mergeCell ref="I1:I4"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="D5:D10"/>
+    <mergeCell ref="F4:G5"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="F8:G9"/>
     <mergeCell ref="L11:L12"/>
     <mergeCell ref="C11:C12"/>
     <mergeCell ref="D11:D12"/>
@@ -7981,36 +7412,6 @@
     <mergeCell ref="E4:E7"/>
     <mergeCell ref="H4:H7"/>
     <mergeCell ref="L3:L4"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="D5:D10"/>
-    <mergeCell ref="F4:G5"/>
-    <mergeCell ref="F6:F7"/>
-    <mergeCell ref="G6:G7"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="F8:G9"/>
-    <mergeCell ref="K4:K5"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="I5:I10"/>
-    <mergeCell ref="I1:I4"/>
-    <mergeCell ref="J1:J2"/>
-    <mergeCell ref="L1:L2"/>
-    <mergeCell ref="L5:L6"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="K6:K7"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="C7:C10"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="K2:K3"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="C3:C6"/>
-    <mergeCell ref="J3:J6"/>
-    <mergeCell ref="E1:H3"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D4"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8024,10 +7425,10 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="34" customHeight="1"/>
   <sheetData>
     <row r="1" spans="1:12" ht="34" customHeight="1" thickBot="1">
-      <c r="A1" s="25"/>
+      <c r="A1" s="33"/>
       <c r="B1" s="10"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
       <c r="E1" s="32"/>
       <c r="F1" s="44" t="s">
         <v>14</v>
@@ -8037,215 +7438,215 @@
       <c r="I1" s="32"/>
       <c r="J1" s="32"/>
       <c r="K1" s="7"/>
-      <c r="L1" s="25"/>
+      <c r="L1" s="33"/>
     </row>
     <row r="2" spans="1:12" ht="34" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A2" s="25"/>
-      <c r="B2" s="34" t="s">
+      <c r="A2" s="33"/>
+      <c r="B2" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="39"/>
-      <c r="D2" s="38"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="30"/>
       <c r="E2" s="32"/>
       <c r="F2" s="44"/>
       <c r="G2" s="44"/>
       <c r="H2" s="32"/>
       <c r="I2" s="32"/>
-      <c r="J2" s="33"/>
-      <c r="K2" s="41" t="s">
+      <c r="J2" s="40"/>
+      <c r="K2" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="L2" s="25"/>
+      <c r="L2" s="33"/>
     </row>
     <row r="3" spans="1:12" ht="34" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A3" s="25"/>
-      <c r="B3" s="36"/>
-      <c r="C3" s="34" t="s">
+      <c r="A3" s="33"/>
+      <c r="B3" s="37"/>
+      <c r="C3" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="38"/>
+      <c r="D3" s="30"/>
       <c r="E3" s="32"/>
       <c r="F3" s="44"/>
       <c r="G3" s="44"/>
       <c r="H3" s="32"/>
       <c r="I3" s="32"/>
-      <c r="J3" s="41" t="s">
+      <c r="J3" s="38" t="s">
         <v>8</v>
       </c>
-      <c r="K3" s="42"/>
-      <c r="L3" s="25"/>
+      <c r="K3" s="39"/>
+      <c r="L3" s="33"/>
     </row>
     <row r="4" spans="1:12" ht="34" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A4" s="25"/>
-      <c r="B4" s="40"/>
-      <c r="C4" s="35"/>
-      <c r="D4" s="39"/>
+      <c r="A4" s="33"/>
+      <c r="B4" s="43"/>
+      <c r="C4" s="42"/>
+      <c r="D4" s="31"/>
       <c r="E4" s="32"/>
       <c r="F4" s="44"/>
       <c r="G4" s="44"/>
       <c r="H4" s="32"/>
-      <c r="I4" s="33"/>
-      <c r="J4" s="43"/>
-      <c r="K4" s="31"/>
-      <c r="L4" s="25"/>
+      <c r="I4" s="40"/>
+      <c r="J4" s="41"/>
+      <c r="K4" s="35"/>
+      <c r="L4" s="33"/>
     </row>
     <row r="5" spans="1:12" ht="34" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A5" s="25"/>
-      <c r="B5" s="39"/>
-      <c r="C5" s="35"/>
-      <c r="D5" s="34" t="s">
+      <c r="A5" s="33"/>
+      <c r="B5" s="31"/>
+      <c r="C5" s="42"/>
+      <c r="D5" s="36" t="s">
         <v>13</v>
       </c>
       <c r="E5" s="32"/>
-      <c r="F5" s="22" t="s">
+      <c r="F5" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="G5" s="22"/>
+      <c r="G5" s="29"/>
       <c r="H5" s="32"/>
-      <c r="I5" s="41" t="s">
+      <c r="I5" s="38" t="s">
         <v>13</v>
       </c>
-      <c r="J5" s="43"/>
-      <c r="K5" s="33"/>
-      <c r="L5" s="25"/>
+      <c r="J5" s="41"/>
+      <c r="K5" s="40"/>
+      <c r="L5" s="33"/>
     </row>
     <row r="6" spans="1:12" ht="34" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A6" s="25"/>
-      <c r="B6" s="34" t="s">
+      <c r="A6" s="33"/>
+      <c r="B6" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="36"/>
-      <c r="D6" s="35"/>
+      <c r="C6" s="37"/>
+      <c r="D6" s="42"/>
       <c r="E6" s="32"/>
-      <c r="F6" s="22"/>
-      <c r="G6" s="22"/>
+      <c r="F6" s="29"/>
+      <c r="G6" s="29"/>
       <c r="H6" s="32"/>
-      <c r="I6" s="43"/>
-      <c r="J6" s="42"/>
-      <c r="K6" s="41" t="s">
+      <c r="I6" s="41"/>
+      <c r="J6" s="39"/>
+      <c r="K6" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="L6" s="25"/>
+      <c r="L6" s="33"/>
     </row>
     <row r="7" spans="1:12" ht="34" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A7" s="25"/>
-      <c r="B7" s="36"/>
-      <c r="C7" s="31"/>
-      <c r="D7" s="35"/>
+      <c r="A7" s="33"/>
+      <c r="B7" s="37"/>
+      <c r="C7" s="35"/>
+      <c r="D7" s="42"/>
       <c r="E7" s="32"/>
-      <c r="F7" s="35"/>
-      <c r="G7" s="43"/>
+      <c r="F7" s="42"/>
+      <c r="G7" s="41"/>
       <c r="H7" s="32"/>
-      <c r="I7" s="43"/>
-      <c r="J7" s="31"/>
-      <c r="K7" s="42"/>
-      <c r="L7" s="25"/>
+      <c r="I7" s="41"/>
+      <c r="J7" s="35"/>
+      <c r="K7" s="39"/>
+      <c r="L7" s="33"/>
     </row>
     <row r="8" spans="1:12" ht="34" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A8" s="25"/>
-      <c r="B8" s="40"/>
+      <c r="A8" s="33"/>
+      <c r="B8" s="43"/>
       <c r="C8" s="32"/>
-      <c r="D8" s="35"/>
+      <c r="D8" s="42"/>
       <c r="E8" s="32"/>
-      <c r="F8" s="36"/>
-      <c r="G8" s="42"/>
+      <c r="F8" s="37"/>
+      <c r="G8" s="39"/>
       <c r="H8" s="32"/>
-      <c r="I8" s="43"/>
+      <c r="I8" s="41"/>
       <c r="J8" s="32"/>
-      <c r="K8" s="31"/>
-      <c r="L8" s="25"/>
+      <c r="K8" s="35"/>
+      <c r="L8" s="33"/>
     </row>
     <row r="9" spans="1:12" ht="34" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A9" s="25"/>
-      <c r="B9" s="39"/>
+      <c r="A9" s="33"/>
+      <c r="B9" s="31"/>
       <c r="C9" s="32"/>
-      <c r="D9" s="35"/>
-      <c r="E9" s="31"/>
-      <c r="F9" s="31" t="s">
+      <c r="D9" s="42"/>
+      <c r="E9" s="35"/>
+      <c r="F9" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="G9" s="31"/>
-      <c r="H9" s="31"/>
-      <c r="I9" s="43"/>
+      <c r="G9" s="35"/>
+      <c r="H9" s="35"/>
+      <c r="I9" s="41"/>
       <c r="J9" s="32"/>
-      <c r="K9" s="33"/>
-      <c r="L9" s="25"/>
+      <c r="K9" s="40"/>
+      <c r="L9" s="33"/>
     </row>
     <row r="10" spans="1:12" ht="34" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A10" s="25"/>
-      <c r="B10" s="34" t="s">
+      <c r="A10" s="33"/>
+      <c r="B10" s="36" t="s">
         <v>6</v>
       </c>
       <c r="C10" s="32"/>
-      <c r="D10" s="35"/>
+      <c r="D10" s="42"/>
       <c r="E10" s="32"/>
       <c r="F10" s="32"/>
       <c r="G10" s="32"/>
       <c r="H10" s="32"/>
-      <c r="I10" s="43"/>
+      <c r="I10" s="41"/>
       <c r="J10" s="32"/>
-      <c r="K10" s="41" t="s">
+      <c r="K10" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="L10" s="25"/>
+      <c r="L10" s="33"/>
     </row>
     <row r="11" spans="1:12" ht="34" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A11" s="25"/>
-      <c r="B11" s="36"/>
-      <c r="C11" s="34" t="s">
+      <c r="A11" s="33"/>
+      <c r="B11" s="37"/>
+      <c r="C11" s="36" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="35"/>
+      <c r="D11" s="42"/>
       <c r="E11" s="32"/>
-      <c r="F11" s="38"/>
-      <c r="G11" s="38"/>
+      <c r="F11" s="30"/>
+      <c r="G11" s="30"/>
       <c r="H11" s="32"/>
-      <c r="I11" s="31"/>
-      <c r="J11" s="31"/>
-      <c r="K11" s="42"/>
-      <c r="L11" s="25"/>
+      <c r="I11" s="35"/>
+      <c r="J11" s="35"/>
+      <c r="K11" s="39"/>
+      <c r="L11" s="33"/>
     </row>
     <row r="12" spans="1:12" ht="34" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A12" s="25"/>
-      <c r="B12" s="40"/>
-      <c r="C12" s="35"/>
-      <c r="D12" s="36"/>
+      <c r="A12" s="33"/>
+      <c r="B12" s="43"/>
+      <c r="C12" s="42"/>
+      <c r="D12" s="37"/>
       <c r="E12" s="32"/>
-      <c r="F12" s="38"/>
-      <c r="G12" s="38"/>
+      <c r="F12" s="30"/>
+      <c r="G12" s="30"/>
       <c r="H12" s="32"/>
       <c r="I12" s="32"/>
       <c r="J12" s="32"/>
       <c r="K12" s="32"/>
-      <c r="L12" s="25"/>
+      <c r="L12" s="33"/>
     </row>
     <row r="13" spans="1:12" ht="34" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A13" s="25"/>
-      <c r="B13" s="39"/>
-      <c r="C13" s="36"/>
-      <c r="D13" s="31"/>
+      <c r="A13" s="33"/>
+      <c r="B13" s="31"/>
+      <c r="C13" s="37"/>
+      <c r="D13" s="35"/>
       <c r="E13" s="32"/>
-      <c r="F13" s="38"/>
-      <c r="G13" s="38"/>
+      <c r="F13" s="30"/>
+      <c r="G13" s="30"/>
       <c r="H13" s="32"/>
       <c r="I13" s="32"/>
       <c r="J13" s="32"/>
       <c r="K13" s="32"/>
-      <c r="L13" s="25"/>
+      <c r="L13" s="33"/>
     </row>
     <row r="14" spans="1:12" ht="34" customHeight="1" thickTop="1">
-      <c r="A14" s="25"/>
+      <c r="A14" s="33"/>
       <c r="B14" s="2"/>
       <c r="C14" s="1"/>
       <c r="D14" s="32"/>
       <c r="E14" s="32"/>
-      <c r="F14" s="38"/>
-      <c r="G14" s="38"/>
+      <c r="F14" s="30"/>
+      <c r="G14" s="30"/>
       <c r="H14" s="32"/>
       <c r="I14" s="32"/>
       <c r="J14" s="32"/>
       <c r="K14" s="32"/>
-      <c r="L14" s="25"/>
+      <c r="L14" s="33"/>
     </row>
     <row r="15" spans="1:12" ht="34" customHeight="1">
       <c r="A15" s="4"/>
@@ -8335,24 +7736,22 @@
     </row>
   </sheetData>
   <mergeCells count="50">
-    <mergeCell ref="I5:I10"/>
-    <mergeCell ref="K10:K11"/>
-    <mergeCell ref="J7:J10"/>
-    <mergeCell ref="L7:L8"/>
-    <mergeCell ref="L9:L10"/>
-    <mergeCell ref="K4:K5"/>
-    <mergeCell ref="I1:I4"/>
-    <mergeCell ref="J1:J2"/>
-    <mergeCell ref="L1:L2"/>
-    <mergeCell ref="L3:L4"/>
-    <mergeCell ref="L11:L12"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="D13:D14"/>
-    <mergeCell ref="L13:L14"/>
-    <mergeCell ref="K12:K14"/>
-    <mergeCell ref="J11:J14"/>
-    <mergeCell ref="I11:I14"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="C3:C6"/>
+    <mergeCell ref="J3:J6"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D4"/>
+    <mergeCell ref="E1:E8"/>
+    <mergeCell ref="F1:G4"/>
+    <mergeCell ref="H1:H8"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="G7:G8"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="D5:D12"/>
     <mergeCell ref="F5:G6"/>
     <mergeCell ref="L5:L6"/>
     <mergeCell ref="B6:B7"/>
@@ -8369,22 +7768,24 @@
     <mergeCell ref="A11:A12"/>
     <mergeCell ref="C11:C13"/>
     <mergeCell ref="F11:G14"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="K2:K3"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="C3:C6"/>
-    <mergeCell ref="J3:J6"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D4"/>
-    <mergeCell ref="E1:E8"/>
-    <mergeCell ref="F1:G4"/>
-    <mergeCell ref="H1:H8"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="G7:G8"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="D5:D12"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="L13:L14"/>
+    <mergeCell ref="K12:K14"/>
+    <mergeCell ref="J11:J14"/>
+    <mergeCell ref="I11:I14"/>
+    <mergeCell ref="I5:I10"/>
+    <mergeCell ref="K10:K11"/>
+    <mergeCell ref="J7:J10"/>
+    <mergeCell ref="L7:L8"/>
+    <mergeCell ref="L9:L10"/>
+    <mergeCell ref="K4:K5"/>
+    <mergeCell ref="I1:I4"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="L3:L4"/>
+    <mergeCell ref="L11:L12"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8398,10 +7799,10 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="34" customHeight="1"/>
   <sheetData>
     <row r="1" spans="1:12" ht="34" customHeight="1" thickBot="1">
-      <c r="A1" s="25"/>
+      <c r="A1" s="33"/>
       <c r="B1" s="10"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
       <c r="E1" s="32"/>
       <c r="F1" s="44" t="s">
         <v>14</v>
@@ -8411,217 +7812,217 @@
       <c r="I1" s="32"/>
       <c r="J1" s="32"/>
       <c r="K1" s="7"/>
-      <c r="L1" s="25"/>
+      <c r="L1" s="33"/>
     </row>
     <row r="2" spans="1:12" ht="34" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A2" s="25"/>
-      <c r="B2" s="34" t="s">
+      <c r="A2" s="33"/>
+      <c r="B2" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="39"/>
-      <c r="D2" s="38"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="30"/>
       <c r="E2" s="32"/>
       <c r="F2" s="44"/>
       <c r="G2" s="44"/>
       <c r="H2" s="32"/>
       <c r="I2" s="32"/>
-      <c r="J2" s="33"/>
-      <c r="K2" s="41" t="s">
+      <c r="J2" s="40"/>
+      <c r="K2" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="L2" s="25"/>
+      <c r="L2" s="33"/>
     </row>
     <row r="3" spans="1:12" ht="34" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A3" s="25"/>
-      <c r="B3" s="36"/>
-      <c r="C3" s="34" t="s">
+      <c r="A3" s="33"/>
+      <c r="B3" s="37"/>
+      <c r="C3" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="38"/>
+      <c r="D3" s="30"/>
       <c r="E3" s="32"/>
       <c r="F3" s="44"/>
       <c r="G3" s="44"/>
       <c r="H3" s="32"/>
       <c r="I3" s="32"/>
-      <c r="J3" s="41" t="s">
+      <c r="J3" s="38" t="s">
         <v>8</v>
       </c>
-      <c r="K3" s="42"/>
-      <c r="L3" s="25"/>
+      <c r="K3" s="39"/>
+      <c r="L3" s="33"/>
     </row>
     <row r="4" spans="1:12" ht="34" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A4" s="25"/>
-      <c r="B4" s="40"/>
-      <c r="C4" s="35"/>
-      <c r="D4" s="39"/>
+      <c r="A4" s="33"/>
+      <c r="B4" s="43"/>
+      <c r="C4" s="42"/>
+      <c r="D4" s="31"/>
       <c r="E4" s="32"/>
       <c r="F4" s="44"/>
       <c r="G4" s="44"/>
       <c r="H4" s="32"/>
-      <c r="I4" s="33"/>
-      <c r="J4" s="43"/>
-      <c r="K4" s="31"/>
-      <c r="L4" s="25"/>
+      <c r="I4" s="40"/>
+      <c r="J4" s="41"/>
+      <c r="K4" s="35"/>
+      <c r="L4" s="33"/>
     </row>
     <row r="5" spans="1:12" ht="34" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A5" s="25"/>
-      <c r="B5" s="39"/>
-      <c r="C5" s="35"/>
-      <c r="D5" s="34">
+      <c r="A5" s="33"/>
+      <c r="B5" s="31"/>
+      <c r="C5" s="42"/>
+      <c r="D5" s="36">
         <v>14</v>
       </c>
       <c r="E5" s="32"/>
-      <c r="F5" s="22" t="s">
+      <c r="F5" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="G5" s="22"/>
+      <c r="G5" s="29"/>
       <c r="H5" s="32"/>
-      <c r="I5" s="41" t="s">
+      <c r="I5" s="38" t="s">
         <v>13</v>
       </c>
-      <c r="J5" s="43"/>
-      <c r="K5" s="33"/>
-      <c r="L5" s="25"/>
+      <c r="J5" s="41"/>
+      <c r="K5" s="40"/>
+      <c r="L5" s="33"/>
     </row>
     <row r="6" spans="1:12" ht="34" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A6" s="25"/>
-      <c r="B6" s="34" t="s">
+      <c r="A6" s="33"/>
+      <c r="B6" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="36"/>
-      <c r="D6" s="35"/>
+      <c r="C6" s="37"/>
+      <c r="D6" s="42"/>
       <c r="E6" s="32"/>
-      <c r="F6" s="22"/>
-      <c r="G6" s="22"/>
+      <c r="F6" s="29"/>
+      <c r="G6" s="29"/>
       <c r="H6" s="32"/>
-      <c r="I6" s="43"/>
-      <c r="J6" s="42"/>
-      <c r="K6" s="41" t="s">
+      <c r="I6" s="41"/>
+      <c r="J6" s="39"/>
+      <c r="K6" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="L6" s="25"/>
+      <c r="L6" s="33"/>
     </row>
     <row r="7" spans="1:12" ht="34" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A7" s="25"/>
-      <c r="B7" s="36"/>
-      <c r="C7" s="31"/>
-      <c r="D7" s="35"/>
+      <c r="A7" s="33"/>
+      <c r="B7" s="37"/>
+      <c r="C7" s="35"/>
+      <c r="D7" s="42"/>
       <c r="E7" s="32"/>
-      <c r="F7" s="35"/>
-      <c r="G7" s="43"/>
+      <c r="F7" s="42"/>
+      <c r="G7" s="41"/>
       <c r="H7" s="32"/>
-      <c r="I7" s="43"/>
-      <c r="J7" s="31"/>
-      <c r="K7" s="42"/>
-      <c r="L7" s="25"/>
+      <c r="I7" s="41"/>
+      <c r="J7" s="35"/>
+      <c r="K7" s="39"/>
+      <c r="L7" s="33"/>
     </row>
     <row r="8" spans="1:12" ht="34" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A8" s="25"/>
-      <c r="B8" s="40"/>
+      <c r="A8" s="33"/>
+      <c r="B8" s="43"/>
       <c r="C8" s="32"/>
-      <c r="D8" s="35"/>
+      <c r="D8" s="42"/>
       <c r="E8" s="32"/>
-      <c r="F8" s="36"/>
-      <c r="G8" s="42"/>
+      <c r="F8" s="37"/>
+      <c r="G8" s="39"/>
       <c r="H8" s="32"/>
-      <c r="I8" s="43"/>
+      <c r="I8" s="41"/>
       <c r="J8" s="32"/>
-      <c r="K8" s="31"/>
-      <c r="L8" s="25"/>
+      <c r="K8" s="35"/>
+      <c r="L8" s="33"/>
     </row>
     <row r="9" spans="1:12" ht="34" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A9" s="25"/>
-      <c r="B9" s="39"/>
+      <c r="A9" s="33"/>
+      <c r="B9" s="31"/>
       <c r="C9" s="32"/>
-      <c r="D9" s="35"/>
-      <c r="E9" s="31"/>
-      <c r="F9" s="31" t="s">
+      <c r="D9" s="42"/>
+      <c r="E9" s="35"/>
+      <c r="F9" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="G9" s="31"/>
-      <c r="H9" s="31"/>
-      <c r="I9" s="43"/>
+      <c r="G9" s="35"/>
+      <c r="H9" s="35"/>
+      <c r="I9" s="41"/>
       <c r="J9" s="32"/>
-      <c r="K9" s="33"/>
-      <c r="L9" s="25"/>
+      <c r="K9" s="40"/>
+      <c r="L9" s="33"/>
     </row>
     <row r="10" spans="1:12" ht="34" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A10" s="25"/>
-      <c r="B10" s="34" t="s">
+      <c r="A10" s="33"/>
+      <c r="B10" s="36" t="s">
         <v>6</v>
       </c>
       <c r="C10" s="32"/>
-      <c r="D10" s="35"/>
+      <c r="D10" s="42"/>
       <c r="E10" s="32"/>
       <c r="F10" s="32"/>
       <c r="G10" s="32"/>
       <c r="H10" s="32"/>
-      <c r="I10" s="43"/>
-      <c r="J10" s="33"/>
-      <c r="K10" s="41" t="s">
+      <c r="I10" s="41"/>
+      <c r="J10" s="40"/>
+      <c r="K10" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="L10" s="25"/>
+      <c r="L10" s="33"/>
     </row>
     <row r="11" spans="1:12" ht="34" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A11" s="25"/>
-      <c r="B11" s="36"/>
-      <c r="C11" s="34" t="s">
+      <c r="A11" s="33"/>
+      <c r="B11" s="37"/>
+      <c r="C11" s="36" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="35"/>
+      <c r="D11" s="42"/>
       <c r="E11" s="32"/>
-      <c r="F11" s="38"/>
-      <c r="G11" s="38"/>
+      <c r="F11" s="30"/>
+      <c r="G11" s="30"/>
       <c r="H11" s="32"/>
-      <c r="I11" s="43"/>
-      <c r="J11" s="41" t="s">
+      <c r="I11" s="41"/>
+      <c r="J11" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="K11" s="42"/>
-      <c r="L11" s="25"/>
+      <c r="K11" s="39"/>
+      <c r="L11" s="33"/>
     </row>
     <row r="12" spans="1:12" ht="34" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A12" s="25"/>
-      <c r="B12" s="40"/>
-      <c r="C12" s="35"/>
-      <c r="D12" s="36"/>
+      <c r="A12" s="33"/>
+      <c r="B12" s="43"/>
+      <c r="C12" s="42"/>
+      <c r="D12" s="37"/>
       <c r="E12" s="32"/>
-      <c r="F12" s="38"/>
-      <c r="G12" s="38"/>
+      <c r="F12" s="30"/>
+      <c r="G12" s="30"/>
       <c r="H12" s="32"/>
-      <c r="I12" s="42"/>
-      <c r="J12" s="43"/>
-      <c r="K12" s="31"/>
-      <c r="L12" s="25"/>
+      <c r="I12" s="39"/>
+      <c r="J12" s="41"/>
+      <c r="K12" s="35"/>
+      <c r="L12" s="33"/>
     </row>
     <row r="13" spans="1:12" ht="34" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A13" s="25"/>
-      <c r="B13" s="39"/>
-      <c r="C13" s="36"/>
-      <c r="D13" s="31"/>
+      <c r="A13" s="33"/>
+      <c r="B13" s="31"/>
+      <c r="C13" s="37"/>
+      <c r="D13" s="35"/>
       <c r="E13" s="32"/>
-      <c r="F13" s="38"/>
-      <c r="G13" s="38"/>
+      <c r="F13" s="30"/>
+      <c r="G13" s="30"/>
       <c r="H13" s="32"/>
-      <c r="I13" s="31"/>
-      <c r="J13" s="42"/>
-      <c r="K13" s="33"/>
-      <c r="L13" s="25"/>
+      <c r="I13" s="35"/>
+      <c r="J13" s="39"/>
+      <c r="K13" s="40"/>
+      <c r="L13" s="33"/>
     </row>
     <row r="14" spans="1:12" ht="34" customHeight="1" thickTop="1">
-      <c r="A14" s="25"/>
+      <c r="A14" s="33"/>
       <c r="B14" s="2"/>
       <c r="C14" s="1"/>
       <c r="D14" s="32"/>
       <c r="E14" s="32"/>
-      <c r="F14" s="38"/>
-      <c r="G14" s="38"/>
+      <c r="F14" s="30"/>
+      <c r="G14" s="30"/>
       <c r="H14" s="32"/>
       <c r="I14" s="32"/>
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
-      <c r="L14" s="25"/>
+      <c r="L14" s="33"/>
     </row>
     <row r="15" spans="1:12" ht="34" customHeight="1">
       <c r="A15" s="4"/>
@@ -8711,18 +8112,28 @@
     </row>
   </sheetData>
   <mergeCells count="50">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D4"/>
-    <mergeCell ref="E1:E8"/>
-    <mergeCell ref="F1:G4"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="G7:G8"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="C3:C6"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="L9:L10"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="H9:H14"/>
+    <mergeCell ref="F11:G14"/>
+    <mergeCell ref="E9:E14"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="L13:L14"/>
+    <mergeCell ref="C11:C13"/>
+    <mergeCell ref="K10:K11"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="J11:J13"/>
+    <mergeCell ref="L11:L12"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="K12:K13"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="J7:J10"/>
+    <mergeCell ref="L7:L8"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="K8:K9"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="F9:G10"/>
     <mergeCell ref="J3:J6"/>
     <mergeCell ref="L3:L4"/>
     <mergeCell ref="B4:B5"/>
@@ -8739,28 +8150,18 @@
     <mergeCell ref="I1:I4"/>
     <mergeCell ref="J1:J2"/>
     <mergeCell ref="L1:L2"/>
-    <mergeCell ref="K2:K3"/>
-    <mergeCell ref="L13:L14"/>
-    <mergeCell ref="C11:C13"/>
-    <mergeCell ref="K10:K11"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="J11:J13"/>
-    <mergeCell ref="L11:L12"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="K12:K13"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="J7:J10"/>
-    <mergeCell ref="L7:L8"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="K8:K9"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="F9:G10"/>
-    <mergeCell ref="D13:D14"/>
-    <mergeCell ref="L9:L10"/>
-    <mergeCell ref="I13:I14"/>
-    <mergeCell ref="H9:H14"/>
-    <mergeCell ref="F11:G14"/>
-    <mergeCell ref="E9:E14"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D4"/>
+    <mergeCell ref="E1:E8"/>
+    <mergeCell ref="F1:G4"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="G7:G8"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="C3:C6"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B2:B3"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8774,10 +8175,10 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="30" customHeight="1"/>
   <sheetData>
     <row r="1" spans="1:12" ht="30" customHeight="1" thickBot="1">
-      <c r="A1" s="25"/>
+      <c r="A1" s="33"/>
       <c r="B1" s="10"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
       <c r="E1" s="32"/>
       <c r="F1" s="46" t="s">
         <v>14</v>
@@ -8790,225 +8191,225 @@
       <c r="L1" s="45"/>
     </row>
     <row r="2" spans="1:12" ht="30" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A2" s="25"/>
-      <c r="B2" s="34" t="s">
+      <c r="A2" s="33"/>
+      <c r="B2" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="39"/>
-      <c r="D2" s="38"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="30"/>
       <c r="E2" s="32"/>
       <c r="F2" s="47"/>
       <c r="G2" s="47"/>
       <c r="H2" s="32"/>
       <c r="I2" s="32"/>
-      <c r="J2" s="33"/>
-      <c r="K2" s="41" t="s">
+      <c r="J2" s="40"/>
+      <c r="K2" s="38" t="s">
         <v>0</v>
       </c>
       <c r="L2" s="45"/>
     </row>
     <row r="3" spans="1:12" ht="30" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A3" s="25"/>
-      <c r="B3" s="36"/>
-      <c r="C3" s="34" t="s">
+      <c r="A3" s="33"/>
+      <c r="B3" s="37"/>
+      <c r="C3" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="38"/>
+      <c r="D3" s="30"/>
       <c r="E3" s="32"/>
       <c r="F3" s="47"/>
       <c r="G3" s="47"/>
       <c r="H3" s="32"/>
       <c r="I3" s="32"/>
-      <c r="J3" s="41" t="s">
+      <c r="J3" s="38" t="s">
         <v>8</v>
       </c>
-      <c r="K3" s="42"/>
+      <c r="K3" s="39"/>
       <c r="L3" s="45"/>
     </row>
     <row r="4" spans="1:12" ht="30" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A4" s="25"/>
-      <c r="B4" s="40"/>
-      <c r="C4" s="35"/>
-      <c r="D4" s="39"/>
+      <c r="A4" s="33"/>
+      <c r="B4" s="43"/>
+      <c r="C4" s="42"/>
+      <c r="D4" s="31"/>
       <c r="E4" s="32"/>
       <c r="F4" s="47"/>
       <c r="G4" s="47"/>
       <c r="H4" s="32"/>
-      <c r="I4" s="33"/>
-      <c r="J4" s="43"/>
-      <c r="K4" s="31"/>
+      <c r="I4" s="40"/>
+      <c r="J4" s="41"/>
+      <c r="K4" s="35"/>
       <c r="L4" s="45"/>
     </row>
     <row r="5" spans="1:12" ht="30" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A5" s="25"/>
-      <c r="B5" s="39"/>
-      <c r="C5" s="35"/>
-      <c r="D5" s="34" t="s">
+      <c r="A5" s="33"/>
+      <c r="B5" s="31"/>
+      <c r="C5" s="42"/>
+      <c r="D5" s="36" t="s">
         <v>1</v>
       </c>
       <c r="E5" s="32"/>
-      <c r="F5" s="22" t="s">
+      <c r="F5" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="G5" s="22"/>
+      <c r="G5" s="29"/>
       <c r="H5" s="32"/>
-      <c r="I5" s="41" t="s">
+      <c r="I5" s="38" t="s">
         <v>13</v>
       </c>
-      <c r="J5" s="43"/>
-      <c r="K5" s="33"/>
+      <c r="J5" s="41"/>
+      <c r="K5" s="40"/>
       <c r="L5" s="45"/>
     </row>
     <row r="6" spans="1:12" ht="30" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A6" s="25"/>
-      <c r="B6" s="34" t="s">
+      <c r="A6" s="33"/>
+      <c r="B6" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="36"/>
-      <c r="D6" s="35"/>
+      <c r="C6" s="37"/>
+      <c r="D6" s="42"/>
       <c r="E6" s="32"/>
-      <c r="F6" s="22"/>
-      <c r="G6" s="22"/>
+      <c r="F6" s="29"/>
+      <c r="G6" s="29"/>
       <c r="H6" s="32"/>
-      <c r="I6" s="43"/>
-      <c r="J6" s="42"/>
-      <c r="K6" s="41" t="s">
+      <c r="I6" s="41"/>
+      <c r="J6" s="39"/>
+      <c r="K6" s="38" t="s">
         <v>3</v>
       </c>
       <c r="L6" s="45"/>
     </row>
     <row r="7" spans="1:12" ht="30" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A7" s="25"/>
-      <c r="B7" s="36"/>
-      <c r="C7" s="31"/>
-      <c r="D7" s="35"/>
+      <c r="A7" s="33"/>
+      <c r="B7" s="37"/>
+      <c r="C7" s="35"/>
+      <c r="D7" s="42"/>
       <c r="E7" s="32"/>
-      <c r="F7" s="35"/>
-      <c r="G7" s="43"/>
+      <c r="F7" s="42"/>
+      <c r="G7" s="41"/>
       <c r="H7" s="32"/>
-      <c r="I7" s="43"/>
-      <c r="J7" s="31"/>
-      <c r="K7" s="42"/>
+      <c r="I7" s="41"/>
+      <c r="J7" s="35"/>
+      <c r="K7" s="39"/>
       <c r="L7" s="45"/>
     </row>
     <row r="8" spans="1:12" ht="30" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A8" s="25"/>
-      <c r="B8" s="40"/>
+      <c r="A8" s="33"/>
+      <c r="B8" s="43"/>
       <c r="C8" s="32"/>
-      <c r="D8" s="35"/>
+      <c r="D8" s="42"/>
       <c r="E8" s="32"/>
-      <c r="F8" s="36"/>
-      <c r="G8" s="42"/>
+      <c r="F8" s="37"/>
+      <c r="G8" s="39"/>
       <c r="H8" s="32"/>
-      <c r="I8" s="43"/>
+      <c r="I8" s="41"/>
       <c r="J8" s="32"/>
-      <c r="K8" s="31"/>
+      <c r="K8" s="35"/>
       <c r="L8" s="45"/>
     </row>
     <row r="9" spans="1:12" ht="30" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A9" s="25"/>
-      <c r="B9" s="39"/>
+      <c r="A9" s="33"/>
+      <c r="B9" s="31"/>
       <c r="C9" s="32"/>
-      <c r="D9" s="35"/>
-      <c r="E9" s="31"/>
-      <c r="F9" s="31" t="s">
+      <c r="D9" s="42"/>
+      <c r="E9" s="35"/>
+      <c r="F9" s="35" t="s">
         <v>2</v>
       </c>
-      <c r="G9" s="31"/>
-      <c r="H9" s="31"/>
-      <c r="I9" s="43"/>
+      <c r="G9" s="35"/>
+      <c r="H9" s="35"/>
+      <c r="I9" s="41"/>
       <c r="J9" s="32"/>
-      <c r="K9" s="33"/>
+      <c r="K9" s="40"/>
       <c r="L9" s="45"/>
     </row>
     <row r="10" spans="1:12" ht="30" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A10" s="25"/>
-      <c r="B10" s="34" t="s">
+      <c r="A10" s="33"/>
+      <c r="B10" s="36" t="s">
         <v>6</v>
       </c>
       <c r="C10" s="32"/>
-      <c r="D10" s="35"/>
+      <c r="D10" s="42"/>
       <c r="E10" s="32"/>
       <c r="F10" s="32"/>
       <c r="G10" s="32"/>
       <c r="H10" s="32"/>
-      <c r="I10" s="43"/>
-      <c r="J10" s="33"/>
-      <c r="K10" s="41" t="s">
+      <c r="I10" s="41"/>
+      <c r="J10" s="40"/>
+      <c r="K10" s="38" t="s">
         <v>6</v>
       </c>
       <c r="L10" s="45"/>
     </row>
     <row r="11" spans="1:12" ht="30" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A11" s="25"/>
-      <c r="B11" s="36"/>
-      <c r="C11" s="34" t="s">
+      <c r="A11" s="33"/>
+      <c r="B11" s="37"/>
+      <c r="C11" s="36" t="s">
         <v>13</v>
       </c>
-      <c r="D11" s="35"/>
+      <c r="D11" s="42"/>
       <c r="E11" s="32"/>
-      <c r="F11" s="38"/>
-      <c r="G11" s="38"/>
+      <c r="F11" s="30"/>
+      <c r="G11" s="30"/>
       <c r="H11" s="32"/>
-      <c r="I11" s="43"/>
-      <c r="J11" s="41" t="s">
+      <c r="I11" s="41"/>
+      <c r="J11" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="K11" s="42"/>
+      <c r="K11" s="39"/>
       <c r="L11" s="45"/>
     </row>
     <row r="12" spans="1:12" ht="30" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A12" s="25"/>
-      <c r="B12" s="40"/>
-      <c r="C12" s="35"/>
-      <c r="D12" s="36"/>
+      <c r="A12" s="33"/>
+      <c r="B12" s="43"/>
+      <c r="C12" s="42"/>
+      <c r="D12" s="37"/>
       <c r="E12" s="32"/>
-      <c r="F12" s="38"/>
-      <c r="G12" s="38"/>
+      <c r="F12" s="30"/>
+      <c r="G12" s="30"/>
       <c r="H12" s="32"/>
-      <c r="I12" s="42"/>
-      <c r="J12" s="43"/>
-      <c r="K12" s="31"/>
+      <c r="I12" s="39"/>
+      <c r="J12" s="41"/>
+      <c r="K12" s="35"/>
       <c r="L12" s="45"/>
     </row>
     <row r="13" spans="1:12" ht="30" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A13" s="25"/>
-      <c r="B13" s="39"/>
-      <c r="C13" s="35"/>
+      <c r="A13" s="33"/>
+      <c r="B13" s="31"/>
+      <c r="C13" s="42"/>
       <c r="D13" s="32"/>
       <c r="E13" s="32"/>
-      <c r="F13" s="38"/>
-      <c r="G13" s="38"/>
+      <c r="F13" s="30"/>
+      <c r="G13" s="30"/>
       <c r="H13" s="32"/>
-      <c r="I13" s="31"/>
-      <c r="J13" s="42"/>
-      <c r="K13" s="33"/>
+      <c r="I13" s="35"/>
+      <c r="J13" s="39"/>
+      <c r="K13" s="40"/>
       <c r="L13" s="45"/>
     </row>
     <row r="14" spans="1:12" ht="30" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A14" s="25"/>
-      <c r="B14" s="34" t="s">
+      <c r="A14" s="33"/>
+      <c r="B14" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="36"/>
+      <c r="C14" s="37"/>
       <c r="D14" s="32"/>
       <c r="E14" s="32"/>
-      <c r="F14" s="38"/>
-      <c r="G14" s="38"/>
+      <c r="F14" s="30"/>
+      <c r="G14" s="30"/>
       <c r="H14" s="32"/>
       <c r="I14" s="32"/>
-      <c r="J14" s="31"/>
-      <c r="K14" s="31"/>
+      <c r="J14" s="35"/>
+      <c r="K14" s="35"/>
       <c r="L14" s="45"/>
     </row>
     <row r="15" spans="1:12" ht="30" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A15" s="25"/>
-      <c r="B15" s="36"/>
+      <c r="A15" s="33"/>
+      <c r="B15" s="37"/>
       <c r="C15" s="32"/>
       <c r="D15" s="32"/>
       <c r="E15" s="32"/>
-      <c r="F15" s="38"/>
-      <c r="G15" s="38"/>
+      <c r="F15" s="30"/>
+      <c r="G15" s="30"/>
       <c r="H15" s="32"/>
       <c r="I15" s="32"/>
       <c r="J15" s="32"/>
@@ -9016,12 +8417,12 @@
       <c r="L15" s="45"/>
     </row>
     <row r="16" spans="1:12" ht="30" customHeight="1" thickTop="1">
-      <c r="A16" s="25"/>
+      <c r="A16" s="33"/>
       <c r="C16" s="32"/>
       <c r="D16" s="32"/>
       <c r="E16" s="32"/>
-      <c r="F16" s="38"/>
-      <c r="G16" s="38"/>
+      <c r="F16" s="30"/>
+      <c r="G16" s="30"/>
       <c r="H16" s="32"/>
       <c r="I16" s="32"/>
       <c r="J16" s="32"/>
@@ -9094,21 +8495,31 @@
     </row>
   </sheetData>
   <mergeCells count="56">
-    <mergeCell ref="F1:G4"/>
-    <mergeCell ref="H1:H8"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="G7:G8"/>
-    <mergeCell ref="L5:L6"/>
-    <mergeCell ref="K6:K7"/>
-    <mergeCell ref="L1:L2"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D4"/>
-    <mergeCell ref="E1:E8"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="L15:L16"/>
+    <mergeCell ref="J11:J13"/>
+    <mergeCell ref="J14:J16"/>
+    <mergeCell ref="K10:K11"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="C11:C14"/>
+    <mergeCell ref="F11:G16"/>
+    <mergeCell ref="L11:L12"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="K12:K13"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="D13:D16"/>
+    <mergeCell ref="J7:J10"/>
+    <mergeCell ref="L7:L8"/>
+    <mergeCell ref="K14:K16"/>
+    <mergeCell ref="I13:I16"/>
+    <mergeCell ref="L13:L14"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="K8:K9"/>
+    <mergeCell ref="E9:E16"/>
+    <mergeCell ref="F9:G10"/>
+    <mergeCell ref="H9:H16"/>
     <mergeCell ref="K2:K3"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="L9:L10"/>
@@ -9125,31 +8536,21 @@
     <mergeCell ref="C3:C6"/>
     <mergeCell ref="J3:J6"/>
     <mergeCell ref="L3:L4"/>
-    <mergeCell ref="K14:K16"/>
-    <mergeCell ref="I13:I16"/>
-    <mergeCell ref="L13:L14"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="K8:K9"/>
-    <mergeCell ref="E9:E16"/>
-    <mergeCell ref="F9:G10"/>
-    <mergeCell ref="H9:H16"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="C15:C16"/>
-    <mergeCell ref="L15:L16"/>
-    <mergeCell ref="J11:J13"/>
-    <mergeCell ref="J14:J16"/>
-    <mergeCell ref="K10:K11"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="C11:C14"/>
-    <mergeCell ref="F11:G16"/>
-    <mergeCell ref="L11:L12"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="K12:K13"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="D13:D16"/>
-    <mergeCell ref="J7:J10"/>
-    <mergeCell ref="L7:L8"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D4"/>
+    <mergeCell ref="E1:E8"/>
+    <mergeCell ref="F1:G4"/>
+    <mergeCell ref="H1:H8"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="G7:G8"/>
+    <mergeCell ref="L5:L6"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="K6:K7"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="B2:B3"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
